--- a/Översikt LILLA EDET.xlsx
+++ b/Översikt LILLA EDET.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE183"/>
+  <dimension ref="A1:AE182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>46169</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 434-2024</t>
+          <t>A 315-2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45296</v>
+        <v>45295</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -736,172 +736,49 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>6.3</v>
+        <v>16</v>
       </c>
       <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
         <v>9</v>
       </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>6</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>7</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
       <c r="T3" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="U3" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Grönfink
-Entita
-Grönsångare
-Gulsparv
-Järnsparv
-Mindre hackspett
-Talltita
-Västlig hakmossa
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 434-2024 artfynd.xlsx", "A 434-2024")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 434-2024 karta.png", "A 434-2024")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 434-2024 georefererad karta.tif", "A 434-2024")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 434-2024 FSC-klagomål.docx", "A 434-2024")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 434-2024 FSC-klagomål mail.docx", "A 434-2024")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 434-2024 tillsynsbegäran.docx", "A 434-2024")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 434-2024 tillsynsbegäran mail.docx", "A 434-2024")</f>
-        <v/>
-      </c>
-      <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 434-2024 prioriterade fågelarter.docx", "A 434-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 315-2024</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>45295</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>16</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>9</v>
-      </c>
-      <c r="T4" t="n">
-        <v>28</v>
-      </c>
-      <c r="U4" t="n">
-        <v>28</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Fällmossa
 Havstulpanlav
@@ -914,116 +791,116 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 315-2024 artfynd.xlsx", "A 315-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 315-2024 karta.png", "A 315-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 315-2024 georefererad karta.tif", "A 315-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 315-2024 FSC-klagomål.docx", "A 315-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 315-2024 FSC-klagomål mail.docx", "A 315-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 315-2024 tillsynsbegäran.docx", "A 315-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 315-2024 tillsynsbegäran mail.docx", "A 315-2024")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE3">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 315-2024 prioriterade fågelarter.docx", "A 315-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>A 318-2024</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
         <v>45295</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="E4" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>Kyrkan</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="I4" t="n">
         <v>8.1</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J4" t="n">
         <v>2</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K4" t="n">
         <v>5</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L4" t="n">
         <v>1</v>
       </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>1</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
         <v>8</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T4" t="n">
         <v>17</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U4" t="n">
         <v>17</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Kattfotslav
 Blåmossa
@@ -1035,111 +912,111 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 318-2024 artfynd.xlsx", "A 318-2024")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 318-2024 karta.png", "A 318-2024")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 318-2024 georefererad karta.tif", "A 318-2024")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 318-2024 FSC-klagomål.docx", "A 318-2024")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 318-2024 FSC-klagomål mail.docx", "A 318-2024")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 318-2024 tillsynsbegäran.docx", "A 318-2024")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 318-2024 tillsynsbegäran mail.docx", "A 318-2024")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 318-2024 prioriterade fågelarter.docx", "A 318-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>A 30285-2025</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
         <v>45827</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
+      <c r="E5" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>29.6</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J5" t="n">
         <v>3</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K5" t="n">
         <v>4</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L5" t="n">
         <v>1</v>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>1</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
         <v>8</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T5" t="n">
         <v>38</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U5" t="n">
         <v>1</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Dofttaggsvamp
 Blåmossa
@@ -1151,36 +1028,147 @@
 Revlummer</t>
         </is>
       </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 30285-2025 artfynd.xlsx", "A 30285-2025")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 30285-2025 karta.png", "A 30285-2025")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 30285-2025 georefererad karta.tif", "A 30285-2025")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 30285-2025 FSC-klagomål.docx", "A 30285-2025")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 30285-2025 FSC-klagomål mail.docx", "A 30285-2025")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 30285-2025 tillsynsbegäran.docx", "A 30285-2025")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 30285-2025 tillsynsbegäran mail.docx", "A 30285-2025")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 30285-2025 prioriterade fågelarter.docx", "A 30285-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 62846-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45272</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>7</v>
+      </c>
+      <c r="T6" t="n">
+        <v>17</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Kattfotslav
+Blåmossa
+Bronshjon
+Stor revmossa
+Vågbandad barkbock
+Större vattensalamander
+Revlummer</t>
+        </is>
+      </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 30285-2025 artfynd.xlsx", "A 30285-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 62846-2023 artfynd.xlsx", "A 62846-2023")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 30285-2025 karta.png", "A 30285-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 62846-2023 karta.png", "A 62846-2023")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 30285-2025 georefererad karta.tif", "A 30285-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 62846-2023 georefererad karta.tif", "A 62846-2023")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 30285-2025 FSC-klagomål.docx", "A 30285-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 62846-2023 FSC-klagomål.docx", "A 62846-2023")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 30285-2025 FSC-klagomål mail.docx", "A 30285-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 62846-2023 FSC-klagomål mail.docx", "A 62846-2023")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 30285-2025 tillsynsbegäran.docx", "A 30285-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 62846-2023 tillsynsbegäran.docx", "A 62846-2023")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 30285-2025 tillsynsbegäran mail.docx", "A 30285-2025")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 30285-2025 prioriterade fågelarter.docx", "A 30285-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 62846-2023 tillsynsbegäran mail.docx", "A 62846-2023")</f>
         <v/>
       </c>
     </row>
@@ -1204,7 +1192,7 @@
         <v>45139</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1290,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 62846-2023</t>
+          <t>A 4017-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1316,10 +1304,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45272</v>
+        <v>46044</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1332,16 +1320,16 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1356,132 +1344,21 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T8" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Kattfotslav
-Blåmossa
-Bronshjon
-Stor revmossa
-Vågbandad barkbock
-Större vattensalamander
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 62846-2023 artfynd.xlsx", "A 62846-2023")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 62846-2023 karta.png", "A 62846-2023")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 62846-2023 georefererad karta.tif", "A 62846-2023")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 62846-2023 FSC-klagomål.docx", "A 62846-2023")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 62846-2023 FSC-klagomål mail.docx", "A 62846-2023")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 62846-2023 tillsynsbegäran.docx", "A 62846-2023")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 62846-2023 tillsynsbegäran mail.docx", "A 62846-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 4017-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46044</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>5</v>
-      </c>
-      <c r="T9" t="n">
-        <v>14</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Klippfrullania
 Stor revmossa
@@ -1490,116 +1367,116 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 4017-2026 artfynd.xlsx", "A 4017-2026")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 4017-2026 karta.png", "A 4017-2026")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 4017-2026 georefererad karta.tif", "A 4017-2026")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 4017-2026 FSC-klagomål.docx", "A 4017-2026")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 4017-2026 FSC-klagomål mail.docx", "A 4017-2026")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 4017-2026 tillsynsbegäran.docx", "A 4017-2026")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 4017-2026 tillsynsbegäran mail.docx", "A 4017-2026")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 4017-2026 prioriterade fågelarter.docx", "A 4017-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>A 25298-2024</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
         <v>45462</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="E9" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="I9" t="n">
         <v>5.9</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J9" t="n">
         <v>2</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K9" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>4</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T9" t="n">
         <v>5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U9" t="n">
         <v>5</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Västlig hakmossa
@@ -1607,36 +1484,144 @@
 Revlummer</t>
         </is>
       </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 25298-2024 artfynd.xlsx", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 25298-2024 karta.png", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 25298-2024 georefererad karta.tif", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 25298-2024 FSC-klagomål.docx", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 25298-2024 FSC-klagomål mail.docx", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 25298-2024 tillsynsbegäran.docx", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 25298-2024 tillsynsbegäran mail.docx", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 25298-2024 prioriterade fågelarter.docx", "A 25298-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 43771-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45187</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Slåtterfibbla
+Vätteros
+Blåsippa</t>
+        </is>
+      </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 25298-2024 artfynd.xlsx", "A 25298-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 43771-2023 artfynd.xlsx", "A 43771-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 25298-2024 karta.png", "A 25298-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 43771-2023 karta.png", "A 43771-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 25298-2024 georefererad karta.tif", "A 25298-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 43771-2023 georefererad karta.tif", "A 43771-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 25298-2024 FSC-klagomål.docx", "A 25298-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 43771-2023 FSC-klagomål.docx", "A 43771-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 25298-2024 FSC-klagomål mail.docx", "A 25298-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 43771-2023 FSC-klagomål mail.docx", "A 43771-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 25298-2024 tillsynsbegäran.docx", "A 25298-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 43771-2023 tillsynsbegäran.docx", "A 43771-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 25298-2024 tillsynsbegäran mail.docx", "A 25298-2024")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 25298-2024 prioriterade fågelarter.docx", "A 25298-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 43771-2023 tillsynsbegäran mail.docx", "A 43771-2023")</f>
         <v/>
       </c>
     </row>
@@ -1660,7 +1645,7 @@
         <v>45819</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1740,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 24290-2026</t>
+          <t>A 23563-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1769,10 +1754,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46169</v>
+        <v>45072</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1784,18 +1769,23 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
@@ -1809,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1818,12 +1808,120 @@
         <v>4</v>
       </c>
       <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>7</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Nordfladdermus
+Dvärgpipistrell
+Vattenfladdermus
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23563-2023 artfynd.xlsx", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23563-2023 karta.png", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23563-2023 georefererad karta.tif", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23563-2023 FSC-klagomål.docx", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23563-2023 FSC-klagomål mail.docx", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23563-2023 tillsynsbegäran.docx", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23563-2023 tillsynsbegäran mail.docx", "A 23563-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 24290-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46169</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" t="n">
         <v>5</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U13" t="n">
         <v>5</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Blanksvart trämyra
 Grönpyrola
@@ -1831,156 +1929,43 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 24290-2026 artfynd.xlsx", "A 24290-2026")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 24290-2026 karta.png", "A 24290-2026")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 24290-2026 georefererad karta.tif", "A 24290-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 24290-2026 FSC-klagomål.docx", "A 24290-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 24290-2026 FSC-klagomål mail.docx", "A 24290-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 24290-2026 tillsynsbegäran.docx", "A 24290-2026")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 24290-2026 tillsynsbegäran mail.docx", "A 24290-2026")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 24290-2026 prioriterade fågelarter.docx", "A 24290-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 23563-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45072</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>4</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>7</v>
-      </c>
-      <c r="U13" t="n">
-        <v>7</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Nordfladdermus
-Dvärgpipistrell
-Vattenfladdermus
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23563-2023 artfynd.xlsx", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23563-2023 karta.png", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23563-2023 georefererad karta.tif", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23563-2023 FSC-klagomål.docx", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23563-2023 FSC-klagomål mail.docx", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23563-2023 tillsynsbegäran.docx", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23563-2023 tillsynsbegäran mail.docx", "A 23563-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 43771-2023</t>
+          <t>A 25655-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1994,10 +1979,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45187</v>
+        <v>45089</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2010,22 +1995,22 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.7</v>
+        <v>5.1</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2037,51 +2022,50 @@
         <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Ask
-Slåtterfibbla
-Vätteros
-Blåsippa</t>
+          <t>Bergjohannesört
+Svinrot
+Fläcknycklar</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 43771-2023 artfynd.xlsx", "A 43771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 25655-2023 artfynd.xlsx", "A 25655-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 43771-2023 karta.png", "A 43771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 25655-2023 karta.png", "A 25655-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 43771-2023 georefererad karta.tif", "A 43771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 25655-2023 georefererad karta.tif", "A 25655-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 43771-2023 FSC-klagomål.docx", "A 43771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 25655-2023 FSC-klagomål.docx", "A 25655-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 43771-2023 FSC-klagomål mail.docx", "A 43771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 25655-2023 FSC-klagomål mail.docx", "A 25655-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 43771-2023 tillsynsbegäran.docx", "A 43771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 25655-2023 tillsynsbegäran.docx", "A 25655-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 43771-2023 tillsynsbegäran mail.docx", "A 43771-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 25655-2023 tillsynsbegäran mail.docx", "A 25655-2023")</f>
         <v/>
       </c>
     </row>
@@ -2105,7 +2089,7 @@
         <v>46119</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2195,7 +2179,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 25655-2023</t>
+          <t>A 28021-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2209,10 +2193,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45089</v>
+        <v>45098</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2225,16 +2209,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.1</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2249,7 +2233,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2258,278 +2242,286 @@
         <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Bergjohannesört
-Svinrot
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 25655-2023 artfynd.xlsx", "A 25655-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 25655-2023 karta.png", "A 25655-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 25655-2023 georefererad karta.tif", "A 25655-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 25655-2023 FSC-klagomål.docx", "A 25655-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 25655-2023 FSC-klagomål mail.docx", "A 25655-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 25655-2023 tillsynsbegäran.docx", "A 25655-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 25655-2023 tillsynsbegäran mail.docx", "A 25655-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 28021-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45098</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Stor revmossa
 Nattskärra
 Törnskata</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 28021-2023 artfynd.xlsx", "A 28021-2023")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 28021-2023 karta.png", "A 28021-2023")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 28021-2023 georefererad karta.tif", "A 28021-2023")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 28021-2023 FSC-klagomål.docx", "A 28021-2023")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 28021-2023 FSC-klagomål mail.docx", "A 28021-2023")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 28021-2023 tillsynsbegäran.docx", "A 28021-2023")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 28021-2023 tillsynsbegäran mail.docx", "A 28021-2023")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 28021-2023 prioriterade fågelarter.docx", "A 28021-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 23559-2023</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>45072</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
+      <c r="E17" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>Kyrkan</t>
         </is>
       </c>
-      <c r="I18" t="n">
+      <c r="I17" t="n">
         <v>1.7</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>1</v>
       </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>1</v>
       </c>
-      <c r="R18" t="n">
+      <c r="R17" t="n">
         <v>1</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S17" t="n">
         <v>3</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T17" t="n">
         <v>8</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U17" t="n">
         <v>8</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Flodpärlmussla
 Spillkråka
 Revlummer</t>
         </is>
       </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23559-2023 artfynd.xlsx", "A 23559-2023")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23559-2023 karta.png", "A 23559-2023")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23559-2023 georefererad karta.tif", "A 23559-2023")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23559-2023 FSC-klagomål.docx", "A 23559-2023")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23559-2023 FSC-klagomål mail.docx", "A 23559-2023")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23559-2023 tillsynsbegäran.docx", "A 23559-2023")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23559-2023 tillsynsbegäran mail.docx", "A 23559-2023")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 23559-2023 prioriterade fågelarter.docx", "A 23559-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 5866-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>9</v>
+      </c>
+      <c r="U18" t="n">
+        <v>9</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Revlummer</t>
+        </is>
+      </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23559-2023 artfynd.xlsx", "A 23559-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 5866-2026 artfynd.xlsx", "A 5866-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23559-2023 karta.png", "A 23559-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 5866-2026 karta.png", "A 5866-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23559-2023 georefererad karta.tif", "A 23559-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 5866-2026 georefererad karta.tif", "A 5866-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23559-2023 FSC-klagomål.docx", "A 23559-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 5866-2026 FSC-klagomål.docx", "A 5866-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23559-2023 FSC-klagomål mail.docx", "A 23559-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 5866-2026 FSC-klagomål mail.docx", "A 5866-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23559-2023 tillsynsbegäran.docx", "A 23559-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 5866-2026 tillsynsbegäran.docx", "A 5866-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23559-2023 tillsynsbegäran mail.docx", "A 23559-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 5866-2026 tillsynsbegäran mail.docx", "A 5866-2026")</f>
         <v/>
       </c>
       <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 23559-2023 prioriterade fågelarter.docx", "A 23559-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 5866-2026 prioriterade fågelarter.docx", "A 5866-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 5866-2026</t>
+          <t>A 23497-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2543,10 +2535,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46052</v>
+        <v>45072</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2560,17 +2552,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2597,169 +2589,169 @@
         <v>2</v>
       </c>
       <c r="T19" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Stor revmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23497-2023 artfynd.xlsx", "A 23497-2023")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23497-2023 karta.png", "A 23497-2023")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23497-2023 georefererad karta.tif", "A 23497-2023")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23497-2023 FSC-klagomål.docx", "A 23497-2023")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23497-2023 FSC-klagomål mail.docx", "A 23497-2023")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23497-2023 tillsynsbegäran.docx", "A 23497-2023")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23497-2023 tillsynsbegäran mail.docx", "A 23497-2023")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 23497-2023 prioriterade fågelarter.docx", "A 23497-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 23494-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45072</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 5866-2026 artfynd.xlsx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 5866-2026 karta.png", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 5866-2026 georefererad karta.tif", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 5866-2026 FSC-klagomål.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 5866-2026 FSC-klagomål mail.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 5866-2026 tillsynsbegäran.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 5866-2026 tillsynsbegäran mail.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 5866-2026 prioriterade fågelarter.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 23497-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45072</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3</v>
-      </c>
-      <c r="U20" t="n">
-        <v>3</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Stor revmossa
-Spillkråka</t>
-        </is>
-      </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23497-2023 artfynd.xlsx", "A 23497-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23494-2023 artfynd.xlsx", "A 23494-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23497-2023 karta.png", "A 23497-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23494-2023 karta.png", "A 23494-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23497-2023 georefererad karta.tif", "A 23497-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23494-2023 georefererad karta.tif", "A 23494-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23497-2023 FSC-klagomål.docx", "A 23497-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23494-2023 FSC-klagomål.docx", "A 23494-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23497-2023 FSC-klagomål mail.docx", "A 23497-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23494-2023 FSC-klagomål mail.docx", "A 23494-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23497-2023 tillsynsbegäran.docx", "A 23497-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23494-2023 tillsynsbegäran.docx", "A 23494-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23497-2023 tillsynsbegäran mail.docx", "A 23497-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23494-2023 tillsynsbegäran mail.docx", "A 23494-2023")</f>
         <v/>
       </c>
       <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 23497-2023 prioriterade fågelarter.docx", "A 23497-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 23494-2023 prioriterade fågelarter.docx", "A 23494-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 23494-2023</t>
+          <t>A 13699-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2773,10 +2765,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45072</v>
+        <v>45390</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2788,19 +2780,14 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>1.3</v>
+        <v>6.6</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2827,54 +2814,54 @@
         <v>2</v>
       </c>
       <c r="T21" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka
-Revlummer</t>
+          <t>Västlig hakmossa
+Spillkråka</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23494-2023 artfynd.xlsx", "A 23494-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 13699-2024 artfynd.xlsx", "A 13699-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23494-2023 karta.png", "A 23494-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 13699-2024 karta.png", "A 13699-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23494-2023 georefererad karta.tif", "A 23494-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 13699-2024 georefererad karta.tif", "A 13699-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23494-2023 FSC-klagomål.docx", "A 23494-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 13699-2024 FSC-klagomål.docx", "A 13699-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23494-2023 FSC-klagomål mail.docx", "A 23494-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 13699-2024 FSC-klagomål mail.docx", "A 13699-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23494-2023 tillsynsbegäran.docx", "A 23494-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 13699-2024 tillsynsbegäran.docx", "A 13699-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23494-2023 tillsynsbegäran mail.docx", "A 23494-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 13699-2024 tillsynsbegäran mail.docx", "A 13699-2024")</f>
         <v/>
       </c>
       <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 23494-2023 prioriterade fågelarter.docx", "A 23494-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 13699-2024 prioriterade fågelarter.docx", "A 13699-2024")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 13699-2024</t>
+          <t>A 32690-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2888,10 +2875,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45390</v>
+        <v>46240</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2903,20 +2890,25 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
       </c>
       <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2928,63 +2920,59 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>2</v>
       </c>
       <c r="T22" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa
-Spillkråka</t>
+          <t>Skirmossa
+Dunmossa</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 13699-2024 artfynd.xlsx", "A 13699-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 32690-2026 artfynd.xlsx", "A 32690-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 13699-2024 karta.png", "A 13699-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 32690-2026 karta.png", "A 32690-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 13699-2024 georefererad karta.tif", "A 13699-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 32690-2026 georefererad karta.tif", "A 32690-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 13699-2024 FSC-klagomål.docx", "A 13699-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 32690-2026 FSC-klagomål.docx", "A 32690-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 13699-2024 FSC-klagomål mail.docx", "A 13699-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 32690-2026 FSC-klagomål mail.docx", "A 32690-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 13699-2024 tillsynsbegäran.docx", "A 13699-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 32690-2026 tillsynsbegäran.docx", "A 32690-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 13699-2024 tillsynsbegäran mail.docx", "A 13699-2024")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 13699-2024 prioriterade fågelarter.docx", "A 13699-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 32690-2026 tillsynsbegäran mail.docx", "A 32690-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32690-2026</t>
+          <t>A 41756-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2998,10 +2986,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46240</v>
+        <v>45902</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3013,13 +3001,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3028,74 +3011,73 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
         <v>1</v>
       </c>
-      <c r="M23" t="n">
+      <c r="T23" t="n">
         <v>1</v>
       </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Skirmossa
-Dunmossa</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 32690-2026 artfynd.xlsx", "A 32690-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 41756-2025 artfynd.xlsx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 32690-2026 karta.png", "A 32690-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 41756-2025 karta.png", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 32690-2026 georefererad karta.tif", "A 32690-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 41756-2025 georefererad karta.tif", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 32690-2026 FSC-klagomål.docx", "A 32690-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 41756-2025 FSC-klagomål.docx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 32690-2026 FSC-klagomål mail.docx", "A 32690-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 41756-2025 FSC-klagomål mail.docx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 32690-2026 tillsynsbegäran.docx", "A 32690-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 41756-2025 tillsynsbegäran.docx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 32690-2026 tillsynsbegäran mail.docx", "A 32690-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 41756-2025 tillsynsbegäran mail.docx", "A 41756-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 30273-2022</t>
+          <t>A 49384-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3105,14 +3087,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44759</v>
+        <v>45205</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3124,18 +3106,23 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>12.5</v>
+        <v>1.2</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
@@ -3149,7 +3136,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3158,49 +3145,49 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 30273-2022 artfynd.xlsx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 49384-2023 artfynd.xlsx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 30273-2022 karta.png", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 49384-2023 karta.png", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 30273-2022 georefererad karta.tif", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 49384-2023 georefererad karta.tif", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 30273-2022 FSC-klagomål.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 49384-2023 FSC-klagomål.docx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 30273-2022 FSC-klagomål mail.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 49384-2023 FSC-klagomål mail.docx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 30273-2022 tillsynsbegäran.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 49384-2023 tillsynsbegäran.docx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 30273-2022 tillsynsbegäran mail.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 49384-2023 tillsynsbegäran mail.docx", "A 49384-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 49384-2023</t>
+          <t>A 45941-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3210,14 +3197,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45205</v>
+        <v>45924</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3227,11 +3214,6 @@
       <c r="G25" t="inlineStr">
         <is>
           <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -3268,49 +3250,49 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 49384-2023 artfynd.xlsx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 45941-2025 artfynd.xlsx", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 49384-2023 karta.png", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 45941-2025 karta.png", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 49384-2023 georefererad karta.tif", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 45941-2025 georefererad karta.tif", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 49384-2023 FSC-klagomål.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 45941-2025 FSC-klagomål.docx", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 49384-2023 FSC-klagomål mail.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 45941-2025 FSC-klagomål mail.docx", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 49384-2023 tillsynsbegäran.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 45941-2025 tillsynsbegäran.docx", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 49384-2023 tillsynsbegäran mail.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 45941-2025 tillsynsbegäran mail.docx", "A 45941-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41756-2025</t>
+          <t>A 30273-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3324,10 +3306,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45902</v>
+        <v>44759</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3340,7 +3322,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>12.5</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3373,49 +3355,49 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 41756-2025 artfynd.xlsx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 30273-2022 artfynd.xlsx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 41756-2025 karta.png", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 30273-2022 karta.png", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 41756-2025 georefererad karta.tif", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 30273-2022 georefererad karta.tif", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 41756-2025 FSC-klagomål.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 30273-2022 FSC-klagomål.docx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 41756-2025 FSC-klagomål mail.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 30273-2022 FSC-klagomål mail.docx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 41756-2025 tillsynsbegäran.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 30273-2022 tillsynsbegäran.docx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 41756-2025 tillsynsbegäran mail.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 30273-2022 tillsynsbegäran mail.docx", "A 30273-2022")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 45941-2025</t>
+          <t>A 38522-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3429,10 +3411,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45924</v>
+        <v>45546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3444,17 +3426,22 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>5.3</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3469,7 +3456,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3478,49 +3465,53 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 45941-2025 artfynd.xlsx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 38522-2024 artfynd.xlsx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 45941-2025 karta.png", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 38522-2024 karta.png", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 45941-2025 georefererad karta.tif", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 38522-2024 georefererad karta.tif", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 45941-2025 FSC-klagomål.docx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 38522-2024 FSC-klagomål.docx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 45941-2025 FSC-klagomål mail.docx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 38522-2024 FSC-klagomål mail.docx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 45941-2025 tillsynsbegäran.docx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 38522-2024 tillsynsbegäran.docx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 45941-2025 tillsynsbegäran mail.docx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 38522-2024 tillsynsbegäran mail.docx", "A 38522-2024")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 38522-2024 prioriterade fågelarter.docx", "A 38522-2024")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 7062-2024</t>
+          <t>A 11102-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3530,14 +3521,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45343</v>
+        <v>45371</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3550,20 +3541,20 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>9.1</v>
+        <v>2.8</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
@@ -3574,10 +3565,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3590,42 +3581,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 7062-2024 artfynd.xlsx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 11102-2024 artfynd.xlsx", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 7062-2024 karta.png", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 11102-2024 karta.png", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 7062-2024 georefererad karta.tif", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 11102-2024 georefererad karta.tif", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 7062-2024 FSC-klagomål.docx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 11102-2024 FSC-klagomål.docx", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 7062-2024 FSC-klagomål mail.docx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 11102-2024 FSC-klagomål mail.docx", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 7062-2024 tillsynsbegäran.docx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 11102-2024 tillsynsbegäran.docx", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 7062-2024 tillsynsbegäran mail.docx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 11102-2024 tillsynsbegäran mail.docx", "A 11102-2024")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 38522-2024</t>
+          <t>A 7062-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3635,14 +3626,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45546</v>
+        <v>45343</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3654,13 +3645,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>5.3</v>
+        <v>9.1</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3696,50 +3682,46 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 38522-2024 artfynd.xlsx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 7062-2024 artfynd.xlsx", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 38522-2024 karta.png", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 7062-2024 karta.png", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 38522-2024 georefererad karta.tif", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 7062-2024 georefererad karta.tif", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 38522-2024 FSC-klagomål.docx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 7062-2024 FSC-klagomål.docx", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 38522-2024 FSC-klagomål mail.docx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 7062-2024 FSC-klagomål mail.docx", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 38522-2024 tillsynsbegäran.docx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 7062-2024 tillsynsbegäran.docx", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 38522-2024 tillsynsbegäran mail.docx", "A 38522-2024")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 38522-2024 prioriterade fågelarter.docx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 7062-2024 tillsynsbegäran mail.docx", "A 7062-2024")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 11102-2024</t>
+          <t>A 32692-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3753,10 +3735,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45371</v>
+        <v>46240</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3768,8 +3750,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3781,7 +3768,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -3793,10 +3780,10 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3809,42 +3796,42 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 11102-2024 artfynd.xlsx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 32692-2026 artfynd.xlsx", "A 32692-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 11102-2024 karta.png", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 32692-2026 karta.png", "A 32692-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 11102-2024 georefererad karta.tif", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 32692-2026 georefererad karta.tif", "A 32692-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 11102-2024 FSC-klagomål.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 32692-2026 FSC-klagomål.docx", "A 32692-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 11102-2024 FSC-klagomål mail.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 32692-2026 FSC-klagomål mail.docx", "A 32692-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 11102-2024 tillsynsbegäran.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 32692-2026 tillsynsbegäran.docx", "A 32692-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 11102-2024 tillsynsbegäran mail.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 32692-2026 tillsynsbegäran mail.docx", "A 32692-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32692-2026</t>
+          <t>A 38384-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3858,10 +3845,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46240</v>
+        <v>44812</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3873,13 +3860,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3909,52 +3891,20 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
       </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Ormbär</t>
-        </is>
-      </c>
-      <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 32692-2026 artfynd.xlsx", "A 32692-2026")</f>
-        <v/>
-      </c>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 32692-2026 karta.png", "A 32692-2026")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 32692-2026 georefererad karta.tif", "A 32692-2026")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 32692-2026 FSC-klagomål.docx", "A 32692-2026")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 32692-2026 FSC-klagomål mail.docx", "A 32692-2026")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 32692-2026 tillsynsbegäran.docx", "A 32692-2026")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 32692-2026 tillsynsbegäran mail.docx", "A 32692-2026")</f>
-        <v/>
-      </c>
+      <c r="V31" s="2" t="inlineStr"/>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 38384-2022</t>
+          <t>A 2991-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3964,14 +3914,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44812</v>
+        <v>44581</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3984,7 +3934,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4027,7 +3977,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 2991-2022</t>
+          <t>A 52891-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4037,14 +3987,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44581</v>
+        <v>44875</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4057,7 +4007,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.1</v>
+        <v>4.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4100,7 +4050,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 52891-2022</t>
+          <t>A 12363-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4114,10 +4064,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44875</v>
+        <v>44637</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4130,7 +4080,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4173,7 +4123,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 18346-2022</t>
+          <t>A 30285-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4187,10 +4137,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44685</v>
+        <v>44760</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4203,7 +4153,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4246,7 +4196,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30285-2022</t>
+          <t>A 18346-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4260,10 +4210,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44760</v>
+        <v>44685</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4276,7 +4226,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4319,7 +4269,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 12363-2022</t>
+          <t>A 23297-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4333,10 +4283,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44637</v>
+        <v>44720</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4349,7 +4299,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4392,7 +4342,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 23297-2022</t>
+          <t>A 10729-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4402,14 +4352,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44720</v>
+        <v>44627</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4422,7 +4372,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4465,7 +4415,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 10729-2022</t>
+          <t>A 55768-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4475,14 +4425,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44627</v>
+        <v>44476</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4495,7 +4445,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4538,7 +4488,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 55768-2021</t>
+          <t>A 52953-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4552,10 +4502,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44476</v>
+        <v>44467</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4568,7 +4518,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.3</v>
+        <v>4.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4611,7 +4561,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 52953-2021</t>
+          <t>A 36359-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4625,10 +4575,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44467</v>
+        <v>44803</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4641,7 +4591,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4684,7 +4634,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 36359-2022</t>
+          <t>A 38386-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4698,10 +4648,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44803</v>
+        <v>44812</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4714,7 +4664,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4757,7 +4707,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 38386-2022</t>
+          <t>A 41420-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4771,10 +4721,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44812</v>
+        <v>44826</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4787,7 +4737,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4830,7 +4780,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 41420-2022</t>
+          <t>A 51569-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4844,10 +4794,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44826</v>
+        <v>44462</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4860,7 +4810,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>4.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4903,7 +4853,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 51569-2021</t>
+          <t>A 38059-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4917,10 +4867,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44462</v>
+        <v>44811</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4933,7 +4883,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.1</v>
+        <v>0.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4976,7 +4926,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 38059-2022</t>
+          <t>A 296-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4990,10 +4940,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44811</v>
+        <v>44565</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5006,7 +4956,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5049,7 +4999,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 296-2022</t>
+          <t>A 30284-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5063,10 +5013,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44565</v>
+        <v>44760</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5079,7 +5029,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5122,7 +5072,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 30284-2022</t>
+          <t>A 30287-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5139,7 +5089,7 @@
         <v>44760</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5195,7 +5145,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 30287-2022</t>
+          <t>A 10726-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5209,10 +5159,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44760</v>
+        <v>44627</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5225,7 +5175,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5268,7 +5218,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 10726-2022</t>
+          <t>A 58750-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5282,10 +5232,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44627</v>
+        <v>44489</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5298,7 +5248,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5358,7 +5308,7 @@
         <v>45378</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5414,7 +5364,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 13887-2024</t>
+          <t>A 4881-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5428,10 +5378,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45391</v>
+        <v>45329</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5444,7 +5394,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>11.3</v>
+        <v>3.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5487,7 +5437,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 61284-2022</t>
+          <t>A 26443-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5501,10 +5451,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44915</v>
+        <v>45092</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5517,7 +5467,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5560,7 +5510,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 52431-2023</t>
+          <t>A 54681-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5574,10 +5524,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45225</v>
+        <v>44473</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5590,7 +5540,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5633,7 +5583,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 11104-2024</t>
+          <t>A 43770-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5647,10 +5597,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45371</v>
+        <v>45187</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5663,7 +5613,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5706,7 +5656,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 65619-2021</t>
+          <t>A 30724-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5716,14 +5666,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44516</v>
+        <v>45496</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5736,7 +5686,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5779,7 +5729,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 51488-2022</t>
+          <t>A 23374-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5793,10 +5743,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44869</v>
+        <v>45791</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5809,7 +5759,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5852,7 +5802,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 28910-2024</t>
+          <t>A 23509-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5866,10 +5816,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45480</v>
+        <v>45792</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5882,7 +5832,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5925,7 +5875,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 1382-2024</t>
+          <t>A 5743-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5939,10 +5889,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45303</v>
+        <v>45694</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5955,7 +5905,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5998,7 +5948,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 11604-2024</t>
+          <t>A 406-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6012,10 +5962,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45373</v>
+        <v>45296</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6028,7 +5978,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6071,7 +6021,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 15567-2022</t>
+          <t>A 24053-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6081,14 +6031,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44662</v>
+        <v>45796</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6101,7 +6051,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.6</v>
+        <v>11.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6144,7 +6094,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 587-2025</t>
+          <t>A 7819-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6158,10 +6108,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45664</v>
+        <v>45706</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6174,7 +6124,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.3</v>
+        <v>5.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6217,7 +6167,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 7912-2024</t>
+          <t>A 5740-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6231,10 +6181,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45350</v>
+        <v>45694</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6247,7 +6197,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6290,7 +6240,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 6323-2023</t>
+          <t>A 6384-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6304,10 +6254,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44960</v>
+        <v>45699</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6319,13 +6269,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6368,7 +6313,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 33993-2023</t>
+          <t>A 36984-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6382,10 +6327,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45134</v>
+        <v>45539</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6398,7 +6343,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6441,7 +6386,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 28515-2025</t>
+          <t>A 27222-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6455,10 +6400,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45819</v>
+        <v>45812</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6471,7 +6416,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6514,7 +6459,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 33996-2023</t>
+          <t>A 2867-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6528,10 +6473,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45134</v>
+        <v>45677</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6544,7 +6489,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>10.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6587,7 +6532,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 12784-2025</t>
+          <t>A 28515-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6601,10 +6546,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45733</v>
+        <v>45819</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6617,7 +6562,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6660,7 +6605,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 54804-2022</t>
+          <t>A 41759-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6674,10 +6619,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44883</v>
+        <v>45902</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6690,7 +6635,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>22.6</v>
+        <v>1.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6733,7 +6678,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 56584-2025</t>
+          <t>A 41758-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6747,10 +6692,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45974</v>
+        <v>45902</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6763,7 +6708,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6806,7 +6751,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 2867-2025</t>
+          <t>A 41760-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6820,10 +6765,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45677</v>
+        <v>45902</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6836,7 +6781,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>10.7</v>
+        <v>1.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6879,7 +6824,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 35423-2025</t>
+          <t>A 41761-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6893,10 +6838,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45855</v>
+        <v>45902</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6909,7 +6854,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6952,7 +6897,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 8117-2023</t>
+          <t>A 35422-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6966,10 +6911,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44974</v>
+        <v>45855</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6982,7 +6927,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>11</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7025,7 +6970,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 12628-2023</t>
+          <t>A 42857-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7039,10 +6984,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45000</v>
+        <v>45908</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7055,7 +7000,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7098,7 +7043,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 41758-2025</t>
+          <t>A 47511-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7112,10 +7057,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45902</v>
+        <v>45587</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7128,7 +7073,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7171,7 +7116,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 41760-2025</t>
+          <t>A 44104-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7185,10 +7130,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45902</v>
+        <v>45915</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7201,7 +7146,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7244,7 +7189,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 41761-2025</t>
+          <t>A 43684-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7258,10 +7203,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45902</v>
+        <v>45912</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7274,7 +7219,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>6.6</v>
+        <v>1.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7317,7 +7262,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 41759-2025</t>
+          <t>A 61435-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7331,10 +7276,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45902</v>
+        <v>45646</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7347,7 +7292,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7390,7 +7335,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 35420-2025</t>
+          <t>A 44916-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7404,10 +7349,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45855</v>
+        <v>45918</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7463,7 +7408,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 35422-2025</t>
+          <t>A 44918-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7477,10 +7422,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45855</v>
+        <v>45918</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7493,7 +7438,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.5</v>
+        <v>5.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7536,7 +7481,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 50349-2024</t>
+          <t>A 44914-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7550,10 +7495,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45600</v>
+        <v>45918</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7566,7 +7511,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7609,7 +7554,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 42857-2025</t>
+          <t>A 44915-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7623,10 +7568,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45908</v>
+        <v>45918</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7639,7 +7584,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7682,7 +7627,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 35717-2025</t>
+          <t>A 5612-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7696,10 +7641,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45860</v>
+        <v>45693</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7712,7 +7657,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7755,7 +7700,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 43684-2025</t>
+          <t>A 35420-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7769,10 +7714,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45912</v>
+        <v>45855</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7828,7 +7773,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 44104-2025</t>
+          <t>A 37063-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7842,10 +7787,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45915</v>
+        <v>45539</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7858,7 +7803,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7901,7 +7846,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 44914-2025</t>
+          <t>A 587-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7915,10 +7860,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45918</v>
+        <v>45664</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7931,7 +7876,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7974,7 +7919,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 44915-2025</t>
+          <t>A 35717-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7988,10 +7933,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45918</v>
+        <v>45860</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8004,7 +7949,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8047,7 +7992,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 44918-2025</t>
+          <t>A 57381-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8061,10 +8006,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45918</v>
+        <v>44896</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8077,7 +8022,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5.7</v>
+        <v>2.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8120,7 +8065,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 44916-2025</t>
+          <t>A 56584-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8134,10 +8079,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45918</v>
+        <v>45974</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8150,7 +8095,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8193,7 +8138,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 28903-2024</t>
+          <t>A 48730-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8207,10 +8152,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45480</v>
+        <v>45936</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8223,7 +8168,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8266,7 +8211,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 12647-2023</t>
+          <t>A 48727-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8280,10 +8225,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45000</v>
+        <v>45936</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8296,7 +8241,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>6.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8339,7 +8284,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 57381-2022</t>
+          <t>A 12628-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8353,10 +8298,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44896</v>
+        <v>45000</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8369,7 +8314,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8412,7 +8357,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 48727-2025</t>
+          <t>A 49188-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8426,10 +8371,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45936</v>
+        <v>45938</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8442,7 +8387,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>6.1</v>
+        <v>1.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8485,7 +8430,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 48730-2025</t>
+          <t>A 13801-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8499,10 +8444,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45936</v>
+        <v>45737</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8515,7 +8460,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8558,7 +8503,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 13801-2025</t>
+          <t>A 65619-2021</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8572,10 +8517,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45737</v>
+        <v>44516</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8588,7 +8533,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8631,7 +8576,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 49188-2025</t>
+          <t>A 12784-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8645,10 +8590,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45938</v>
+        <v>45733</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8661,7 +8606,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8704,7 +8649,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 5328-2025</t>
+          <t>A 15351-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8718,10 +8663,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45692</v>
+        <v>45400</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8733,8 +8678,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8777,7 +8727,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 15351-2024</t>
+          <t>A 35423-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8791,10 +8741,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45400</v>
+        <v>45855</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8806,13 +8756,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8855,7 +8800,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 14427-2026</t>
+          <t>A 41411-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8869,10 +8814,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46100</v>
+        <v>44826</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8885,7 +8830,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8928,7 +8873,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 55324-2025</t>
+          <t>A 12647-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8942,10 +8887,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45971</v>
+        <v>45000</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8957,13 +8902,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9006,7 +8946,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 17377-2026</t>
+          <t>A 8117-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9020,10 +8960,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46119</v>
+        <v>44974</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9036,7 +8976,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.4</v>
+        <v>11</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9079,7 +9019,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 18841-2026</t>
+          <t>A 14427-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9093,10 +9033,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46129</v>
+        <v>46100</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9109,7 +9049,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9152,7 +9092,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 26886-2023</t>
+          <t>A 17377-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9166,10 +9106,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45093</v>
+        <v>46119</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9182,7 +9122,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9225,7 +9165,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 19079-2025</t>
+          <t>A 18841-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9239,10 +9179,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45766</v>
+        <v>46129</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9255,7 +9195,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9298,7 +9238,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 26443-2023</t>
+          <t>A 55324-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9312,10 +9252,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45092</v>
+        <v>45971</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9327,8 +9267,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9371,7 +9316,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 17114-2023</t>
+          <t>A 19079-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9385,10 +9330,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45034</v>
+        <v>45766</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9401,7 +9346,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9444,7 +9389,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 58750-2021</t>
+          <t>A 61952-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9458,10 +9403,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44489</v>
+        <v>45653</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9474,7 +9419,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9517,7 +9462,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 7947-2024</t>
+          <t>A 28022-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9531,10 +9476,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45350</v>
+        <v>45098</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9547,7 +9492,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.8</v>
+        <v>5.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9590,7 +9535,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 28022-2023</t>
+          <t>A 55972-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9604,10 +9549,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45098</v>
+        <v>44889</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9620,7 +9565,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9663,7 +9608,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 48904-2024</t>
+          <t>A 50349-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9677,10 +9622,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45594</v>
+        <v>45600</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9693,7 +9638,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9736,7 +9681,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 13581-2023</t>
+          <t>A 61475-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9750,10 +9695,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45006</v>
+        <v>46001</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9765,13 +9710,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9814,7 +9754,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 61952-2024</t>
+          <t>A 7912-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9828,10 +9768,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45653</v>
+        <v>45350</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9844,7 +9784,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9887,7 +9827,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 61475-2025</t>
+          <t>A 13581-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9901,10 +9841,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46001</v>
+        <v>45006</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9916,8 +9856,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9960,7 +9905,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 54681-2021</t>
+          <t>A 8071-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9974,10 +9919,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44473</v>
+        <v>45351</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9990,7 +9935,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10033,7 +9978,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 55972-2022</t>
+          <t>A 48904-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10047,10 +9992,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44889</v>
+        <v>45594</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10063,7 +10008,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10106,7 +10051,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 47511-2024</t>
+          <t>A 13975-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10120,10 +10065,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45587</v>
+        <v>45008</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10136,7 +10081,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10179,7 +10124,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 43770-2023</t>
+          <t>A 16473-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10193,10 +10138,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45187</v>
+        <v>44671</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10209,7 +10154,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10252,7 +10197,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 4881-2024</t>
+          <t>A 6323-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10266,10 +10211,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45329</v>
+        <v>44960</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10281,8 +10226,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10325,7 +10275,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 61695-2025</t>
+          <t>A 40092-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10339,10 +10289,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46002</v>
+        <v>45554</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10355,7 +10305,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10398,7 +10348,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 22257-2026</t>
+          <t>A 57754-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10412,10 +10362,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46154</v>
+        <v>45246</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10428,7 +10378,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10471,7 +10421,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 9046-2022</t>
+          <t>A 61695-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10485,10 +10435,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44615</v>
+        <v>46002</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10501,7 +10451,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10544,7 +10494,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 61435-2024</t>
+          <t>A 26886-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10558,10 +10508,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45646</v>
+        <v>45093</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10574,7 +10524,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10617,7 +10567,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 23541-2026</t>
+          <t>A 22257-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10627,14 +10577,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46163</v>
+        <v>46154</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10647,7 +10597,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10690,7 +10640,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 14929-2024</t>
+          <t>A 302-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10704,10 +10654,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45398</v>
+        <v>45295</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10719,8 +10669,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>5.1</v>
+        <v>2.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10763,7 +10718,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 21630-2024</t>
+          <t>A 23541-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10773,14 +10728,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45442</v>
+        <v>46163</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10793,7 +10748,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>4.6</v>
+        <v>0.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10853,7 +10808,7 @@
         <v>45743</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10926,7 +10881,7 @@
         <v>46171</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10987,7 +10942,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 43767-2023</t>
+          <t>A 29068-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11001,10 +10956,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45187</v>
+        <v>45481</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11017,7 +10972,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11060,7 +11015,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 33991-2023</t>
+          <t>A 25729-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11074,10 +11029,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45134</v>
+        <v>46178</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11090,7 +11045,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11133,7 +11088,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 41411-2022</t>
+          <t>A 27643-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11147,10 +11102,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44826</v>
+        <v>46190</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11163,7 +11118,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11206,7 +11161,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 25729-2026</t>
+          <t>A 4225-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11220,10 +11175,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46178</v>
+        <v>45324</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11236,7 +11191,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11279,7 +11234,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 4225-2024</t>
+          <t>A 4227-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11296,7 +11251,7 @@
         <v>45324</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11309,7 +11264,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11352,7 +11307,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 4227-2024</t>
+          <t>A 38093-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11366,10 +11321,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45324</v>
+        <v>44811</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11382,7 +11337,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11425,7 +11380,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 27643-2026</t>
+          <t>A 32822-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11439,10 +11394,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46190</v>
+        <v>46242</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11498,7 +11453,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 37508-2023</t>
+          <t>A 33842-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11512,10 +11467,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45158</v>
+        <v>46251</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11528,7 +11483,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11571,7 +11526,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 37509-2023</t>
+          <t>A 5420-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11585,10 +11540,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45158</v>
+        <v>45692</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11601,7 +11556,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11644,7 +11599,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 32822-2026</t>
+          <t>A 51488-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11658,10 +11613,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46242</v>
+        <v>44869</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11674,7 +11629,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11717,7 +11672,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 13382-2023</t>
+          <t>A 2438-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11731,10 +11686,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45005</v>
+        <v>46036</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11747,7 +11702,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11790,7 +11745,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 38093-2022</t>
+          <t>A 30605-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11804,10 +11759,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44811</v>
+        <v>46210</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11820,7 +11775,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.4</v>
+        <v>10.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11863,7 +11818,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 16473-2022</t>
+          <t>A 6489-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11877,10 +11832,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44671</v>
+        <v>45699</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11893,7 +11848,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11936,7 +11891,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 40092-2024</t>
+          <t>A 9046-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11950,10 +11905,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45554</v>
+        <v>44615</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11966,7 +11921,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12009,7 +11964,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 57754-2023</t>
+          <t>A 35883-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12023,10 +11978,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45246</v>
+        <v>46266</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12039,7 +11994,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.7</v>
+        <v>6.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12082,7 +12037,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 33842-2026</t>
+          <t>A 28903-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12096,10 +12051,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46251</v>
+        <v>45480</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12112,7 +12067,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>7.2</v>
+        <v>3.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12155,7 +12110,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 30605-2026</t>
+          <t>A 61284-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12169,10 +12124,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46210</v>
+        <v>44915</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12185,7 +12140,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>10.5</v>
+        <v>1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12228,7 +12183,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 2438-2026</t>
+          <t>A 12760-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12242,10 +12197,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46036</v>
+        <v>45001</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12258,7 +12213,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12301,7 +12256,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 44445-2023</t>
+          <t>A 62730-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12315,10 +12270,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45189</v>
+        <v>45268</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12331,7 +12286,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12374,7 +12329,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 17116-2023</t>
+          <t>A 36722-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12388,10 +12343,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45034</v>
+        <v>46272</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12403,8 +12358,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12447,7 +12407,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 12760-2023</t>
+          <t>A 37037-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12461,10 +12421,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45001</v>
+        <v>46273</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12477,7 +12437,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12520,7 +12480,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 5612-2025</t>
+          <t>A 36773-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12534,10 +12494,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45693</v>
+        <v>46272</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12549,8 +12509,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12593,7 +12558,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 302-2024</t>
+          <t>A 11604-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12607,10 +12572,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45295</v>
+        <v>45373</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12622,13 +12587,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12671,7 +12631,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 29068-2024</t>
+          <t>A 5324-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12685,10 +12645,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45481</v>
+        <v>45692</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12701,7 +12661,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.8</v>
+        <v>5.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12744,7 +12704,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 5324-2025</t>
+          <t>A 54804-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12758,10 +12718,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45692</v>
+        <v>44883</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12774,7 +12734,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>5.1</v>
+        <v>22.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12817,7 +12777,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 13631-2024</t>
+          <t>A 52431-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12831,10 +12791,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45390</v>
+        <v>45225</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12847,7 +12807,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>16.4</v>
+        <v>0.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12890,7 +12850,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 35883-2026</t>
+          <t>A 33993-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12904,10 +12864,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46266</v>
+        <v>45134</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12920,7 +12880,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>6.6</v>
+        <v>0.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12963,7 +12923,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 37063-2024</t>
+          <t>A 33996-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12977,10 +12937,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45539</v>
+        <v>45134</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12993,7 +12953,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>8.800000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13036,7 +12996,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 15159-2023</t>
+          <t>A 7947-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13050,10 +13010,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45016</v>
+        <v>45350</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13065,13 +13025,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13114,7 +13069,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 550-2024</t>
+          <t>A 17116-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13128,10 +13083,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45299</v>
+        <v>45034</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13144,7 +13099,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13187,7 +13142,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 13975-2023</t>
+          <t>A 15567-2022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13201,10 +13156,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45008</v>
+        <v>44662</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13217,7 +13172,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13260,7 +13215,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 36773-2026</t>
+          <t>A 21630-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13274,10 +13229,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46272</v>
+        <v>45442</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13289,13 +13244,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13338,7 +13288,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 36722-2026</t>
+          <t>A 13382-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13352,10 +13302,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46272</v>
+        <v>45005</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13367,13 +13317,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13416,7 +13361,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 8071-2024</t>
+          <t>A 550-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13430,10 +13375,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45351</v>
+        <v>45299</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13446,7 +13391,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13489,7 +13434,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 6489-2025</t>
+          <t>A 13887-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13503,10 +13448,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45699</v>
+        <v>45391</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13519,7 +13464,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.6</v>
+        <v>11.3</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13562,7 +13507,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 37037-2026</t>
+          <t>A 14929-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13576,10 +13521,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46273</v>
+        <v>45398</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13592,7 +13537,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13635,7 +13580,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 406-2024</t>
+          <t>A 11104-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13649,10 +13594,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45296</v>
+        <v>45371</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13665,7 +13610,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13708,7 +13653,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 62730-2023</t>
+          <t>A 28910-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13722,10 +13667,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45268</v>
+        <v>45480</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13738,7 +13683,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13781,7 +13726,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 49879-2023</t>
+          <t>A 1382-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13795,10 +13740,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45213</v>
+        <v>45303</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13811,7 +13756,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>5</v>
+        <v>1.4</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13854,7 +13799,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 5420-2025</t>
+          <t>A 17114-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13868,10 +13813,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45692</v>
+        <v>45034</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13884,7 +13829,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13927,7 +13872,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 3867-2025</t>
+          <t>A 43767-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13941,10 +13886,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45684</v>
+        <v>45187</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13957,7 +13902,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14000,7 +13945,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 21617-2024</t>
+          <t>A 13631-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14014,10 +13959,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45441</v>
+        <v>45390</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14030,7 +13975,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>9.699999999999999</v>
+        <v>16.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14073,7 +14018,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 30724-2024</t>
+          <t>A 37508-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14083,14 +14028,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45496</v>
+        <v>45158</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14103,7 +14048,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2.5</v>
+        <v>6.9</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14146,7 +14091,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 22561-2025</t>
+          <t>A 37509-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14160,10 +14105,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45789</v>
+        <v>45158</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14176,7 +14121,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14219,7 +14164,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 23509-2025</t>
+          <t>A 15159-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14233,10 +14178,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45792</v>
+        <v>45016</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14248,8 +14193,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14292,7 +14242,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 23374-2025</t>
+          <t>A 49879-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14306,10 +14256,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45791</v>
+        <v>45213</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14322,7 +14272,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14365,7 +14315,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 12790-2025</t>
+          <t>A 44445-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14379,10 +14329,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45733</v>
+        <v>45189</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14395,7 +14345,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14438,7 +14388,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 12243-2025</t>
+          <t>A 33991-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14452,10 +14402,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45729</v>
+        <v>45134</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14468,7 +14418,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>10.2</v>
+        <v>0.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14511,7 +14461,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 24053-2025</t>
+          <t>A 5328-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14521,14 +14471,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45796</v>
+        <v>45692</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14541,7 +14491,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14584,7 +14534,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 5743-2025</t>
+          <t>A 3867-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14598,10 +14548,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45694</v>
+        <v>45684</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14614,7 +14564,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14657,7 +14607,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 7819-2025</t>
+          <t>A 21617-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14671,10 +14621,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45706</v>
+        <v>45441</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14687,7 +14637,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>5.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14730,7 +14680,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 5740-2025</t>
+          <t>A 22561-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14744,10 +14694,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45694</v>
+        <v>45789</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14760,7 +14710,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14803,7 +14753,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 6384-2025</t>
+          <t>A 12790-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14817,10 +14767,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45699</v>
+        <v>45733</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14833,7 +14783,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14876,7 +14826,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 36984-2024</t>
+          <t>A 12243-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14890,10 +14840,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45539</v>
+        <v>45729</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14906,7 +14856,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.7</v>
+        <v>10.2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14946,27 +14896,27 @@
       </c>
       <c r="V181" s="2" t="inlineStr"/>
     </row>
-    <row r="182" ht="15" customHeight="1">
+    <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 27222-2025</t>
+          <t>S 460-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45812</v>
+        <v>44964</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14979,7 +14929,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15018,79 +14968,6 @@
         <v>0</v>
       </c>
       <c r="V182" s="2" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>S 460-2023</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D183" s="1" t="n">
-        <v>44964</v>
-      </c>
-      <c r="E183" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I183" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J183" t="n">
-        <v>0</v>
-      </c>
-      <c r="K183" t="n">
-        <v>0</v>
-      </c>
-      <c r="L183" t="n">
-        <v>0</v>
-      </c>
-      <c r="M183" t="n">
-        <v>0</v>
-      </c>
-      <c r="N183" t="n">
-        <v>0</v>
-      </c>
-      <c r="O183" t="n">
-        <v>0</v>
-      </c>
-      <c r="P183" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
-      <c r="R183" t="n">
-        <v>0</v>
-      </c>
-      <c r="S183" t="n">
-        <v>0</v>
-      </c>
-      <c r="T183" t="n">
-        <v>0</v>
-      </c>
-      <c r="U183" t="n">
-        <v>0</v>
-      </c>
-      <c r="V183" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LILLA EDET.xlsx
+++ b/Översikt LILLA EDET.xlsx
@@ -601,7 +601,7 @@
         <v>46169</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45295</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45295</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45827</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 62846-2023</t>
+          <t>A 34396-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45272</v>
+        <v>45139</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.4</v>
+        <v>7</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1127,12 +1127,127 @@
         <v>7</v>
       </c>
       <c r="T6" t="n">
+        <v>24</v>
+      </c>
+      <c r="U6" t="n">
+        <v>24</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Blåmossa
+Kambräken
+Stor revmossa
+Västlig hakmossa
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 34396-2023 artfynd.xlsx", "A 34396-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 34396-2023 karta.png", "A 34396-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 34396-2023 georefererad karta.tif", "A 34396-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 34396-2023 FSC-klagomål.docx", "A 34396-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 34396-2023 FSC-klagomål mail.docx", "A 34396-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 34396-2023 tillsynsbegäran.docx", "A 34396-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 34396-2023 tillsynsbegäran mail.docx", "A 34396-2023")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 34396-2023 prioriterade fågelarter.docx", "A 34396-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 62846-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45272</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>7</v>
+      </c>
+      <c r="T7" t="n">
         <v>17</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Kattfotslav
 Blåmossa
@@ -1143,147 +1258,32 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 62846-2023 artfynd.xlsx", "A 62846-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 62846-2023 karta.png", "A 62846-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 62846-2023 georefererad karta.tif", "A 62846-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 62846-2023 FSC-klagomål.docx", "A 62846-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 62846-2023 FSC-klagomål mail.docx", "A 62846-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 62846-2023 tillsynsbegäran.docx", "A 62846-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 62846-2023 tillsynsbegäran mail.docx", "A 62846-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 34396-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45139</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>5</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>7</v>
-      </c>
-      <c r="T7" t="n">
-        <v>24</v>
-      </c>
-      <c r="U7" t="n">
-        <v>24</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Blåmossa
-Kambräken
-Stor revmossa
-Västlig hakmossa
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 34396-2023 artfynd.xlsx", "A 34396-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 34396-2023 karta.png", "A 34396-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 34396-2023 georefererad karta.tif", "A 34396-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 34396-2023 FSC-klagomål.docx", "A 34396-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 34396-2023 FSC-klagomål mail.docx", "A 34396-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 34396-2023 tillsynsbegäran.docx", "A 34396-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 34396-2023 tillsynsbegäran mail.docx", "A 34396-2023")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 34396-2023 prioriterade fågelarter.docx", "A 34396-2023")</f>
         <v/>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
         <v>46044</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25298-2024</t>
+          <t>A 28512-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45462</v>
+        <v>45819</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1432,13 +1432,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>5.9</v>
+        <v>10.9</v>
       </c>
       <c r="J9" t="n">
         <v>2</v>
@@ -1471,12 +1466,354 @@
         <v>4</v>
       </c>
       <c r="T9" t="n">
+        <v>19</v>
+      </c>
+      <c r="U9" t="n">
+        <v>19</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Västlig hakmossa
+Spillkråka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 28512-2025 artfynd.xlsx", "A 28512-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 28512-2025 karta.png", "A 28512-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 28512-2025 georefererad karta.tif", "A 28512-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 28512-2025 FSC-klagomål.docx", "A 28512-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 28512-2025 FSC-klagomål mail.docx", "A 28512-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 28512-2025 tillsynsbegäran.docx", "A 28512-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 28512-2025 tillsynsbegäran mail.docx", "A 28512-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 28512-2025 prioriterade fågelarter.docx", "A 28512-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 24290-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46169</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="n">
         <v>5</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>5</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Blanksvart trämyra
+Grönpyrola
+Västlig hakmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 24290-2026 artfynd.xlsx", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 24290-2026 karta.png", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 24290-2026 georefererad karta.tif", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 24290-2026 FSC-klagomål.docx", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 24290-2026 FSC-klagomål mail.docx", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 24290-2026 tillsynsbegäran.docx", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 24290-2026 tillsynsbegäran mail.docx", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 24290-2026 prioriterade fågelarter.docx", "A 24290-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 23563-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45072</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7</v>
+      </c>
+      <c r="U11" t="n">
+        <v>7</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Nordfladdermus
+Dvärgpipistrell
+Vattenfladdermus
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23563-2023 artfynd.xlsx", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23563-2023 karta.png", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23563-2023 georefererad karta.tif", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23563-2023 FSC-klagomål.docx", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23563-2023 FSC-klagomål mail.docx", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23563-2023 tillsynsbegäran.docx", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23563-2023 tillsynsbegäran mail.docx", "A 23563-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 25298-2024</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45462</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Västlig hakmossa
@@ -1484,111 +1821,111 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 25298-2024 artfynd.xlsx", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 25298-2024 karta.png", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 25298-2024 georefererad karta.tif", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 25298-2024 FSC-klagomål.docx", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 25298-2024 FSC-klagomål mail.docx", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 25298-2024 tillsynsbegäran.docx", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 25298-2024 tillsynsbegäran mail.docx", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 25298-2024 prioriterade fågelarter.docx", "A 25298-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 43771-2023</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>45187</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E13" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>1.7</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K13" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>1</v>
       </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>2</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R13" t="n">
         <v>1</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S13" t="n">
         <v>4</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T13" t="n">
         <v>4</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Ask
 Slåtterfibbla
@@ -1596,376 +1933,39 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 43771-2023 artfynd.xlsx", "A 43771-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 43771-2023 karta.png", "A 43771-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 43771-2023 georefererad karta.tif", "A 43771-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 43771-2023 FSC-klagomål.docx", "A 43771-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 43771-2023 FSC-klagomål mail.docx", "A 43771-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 43771-2023 tillsynsbegäran.docx", "A 43771-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 43771-2023 tillsynsbegäran mail.docx", "A 43771-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 28512-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45819</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>19</v>
-      </c>
-      <c r="U11" t="n">
-        <v>19</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa
-Västlig hakmossa
-Spillkråka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 28512-2025 artfynd.xlsx", "A 28512-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 28512-2025 karta.png", "A 28512-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 28512-2025 georefererad karta.tif", "A 28512-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 28512-2025 FSC-klagomål.docx", "A 28512-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 28512-2025 FSC-klagomål mail.docx", "A 28512-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 28512-2025 tillsynsbegäran.docx", "A 28512-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 28512-2025 tillsynsbegäran mail.docx", "A 28512-2025")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 28512-2025 prioriterade fågelarter.docx", "A 28512-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 23563-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45072</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>7</v>
-      </c>
-      <c r="U12" t="n">
-        <v>7</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Nordfladdermus
-Dvärgpipistrell
-Vattenfladdermus
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23563-2023 artfynd.xlsx", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23563-2023 karta.png", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23563-2023 georefererad karta.tif", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23563-2023 FSC-klagomål.docx", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23563-2023 FSC-klagomål mail.docx", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23563-2023 tillsynsbegäran.docx", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23563-2023 tillsynsbegäran mail.docx", "A 23563-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 24290-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46169</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>5</v>
-      </c>
-      <c r="U13" t="n">
-        <v>5</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Blanksvart trämyra
-Grönpyrola
-Västlig hakmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 24290-2026 artfynd.xlsx", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 24290-2026 karta.png", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 24290-2026 georefererad karta.tif", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 24290-2026 FSC-klagomål.docx", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 24290-2026 FSC-klagomål mail.docx", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 24290-2026 tillsynsbegäran.docx", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 24290-2026 tillsynsbegäran mail.docx", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 24290-2026 prioriterade fågelarter.docx", "A 24290-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 25655-2023</t>
+          <t>A 17376-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45089</v>
+        <v>46119</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.1</v>
+        <v>2.5</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
         <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2019,271 +2019,271 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
       </c>
       <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Slåttergubbe
+Almsnabbvinge
+Granspira</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 17376-2026 artfynd.xlsx", "A 17376-2026")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 17376-2026 karta.png", "A 17376-2026")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 17376-2026 georefererad karta.tif", "A 17376-2026")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 17376-2026 FSC-klagomål.docx", "A 17376-2026")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 17376-2026 FSC-klagomål mail.docx", "A 17376-2026")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 17376-2026 tillsynsbegäran.docx", "A 17376-2026")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 17376-2026 tillsynsbegäran mail.docx", "A 17376-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 28021-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45098</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Stor revmossa
+Nattskärra
+Törnskata</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 28021-2023 artfynd.xlsx", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 28021-2023 karta.png", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 28021-2023 georefererad karta.tif", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 28021-2023 FSC-klagomål.docx", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 28021-2023 FSC-klagomål mail.docx", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 28021-2023 tillsynsbegäran.docx", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 28021-2023 tillsynsbegäran mail.docx", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 28021-2023 prioriterade fågelarter.docx", "A 28021-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 25655-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45089</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
         <v>9</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U16" t="n">
         <v>7</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Bergjohannesört
 Svinrot
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 25655-2023 artfynd.xlsx", "A 25655-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 25655-2023 karta.png", "A 25655-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 25655-2023 georefererad karta.tif", "A 25655-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 25655-2023 FSC-klagomål.docx", "A 25655-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 25655-2023 FSC-klagomål mail.docx", "A 25655-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 25655-2023 tillsynsbegäran.docx", "A 25655-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 25655-2023 tillsynsbegäran mail.docx", "A 25655-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 17376-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46119</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Slåttergubbe
-Almsnabbvinge
-Granspira</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 17376-2026 artfynd.xlsx", "A 17376-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 17376-2026 karta.png", "A 17376-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 17376-2026 georefererad karta.tif", "A 17376-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 17376-2026 FSC-klagomål.docx", "A 17376-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 17376-2026 FSC-klagomål mail.docx", "A 17376-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 17376-2026 tillsynsbegäran.docx", "A 17376-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 17376-2026 tillsynsbegäran mail.docx", "A 17376-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 28021-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45098</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Stor revmossa
-Nattskärra
-Törnskata</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 28021-2023 artfynd.xlsx", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 28021-2023 karta.png", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 28021-2023 georefererad karta.tif", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 28021-2023 FSC-klagomål.docx", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 28021-2023 FSC-klagomål mail.docx", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 28021-2023 tillsynsbegäran.docx", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 28021-2023 tillsynsbegäran mail.docx", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 28021-2023 prioriterade fågelarter.docx", "A 28021-2023")</f>
         <v/>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
         <v>45072</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 5866-2026</t>
+          <t>A 23497-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46052</v>
+        <v>45072</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,17 +2437,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2474,169 +2474,169 @@
         <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Stor revmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23497-2023 artfynd.xlsx", "A 23497-2023")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23497-2023 karta.png", "A 23497-2023")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23497-2023 georefererad karta.tif", "A 23497-2023")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23497-2023 FSC-klagomål.docx", "A 23497-2023")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23497-2023 FSC-klagomål mail.docx", "A 23497-2023")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23497-2023 tillsynsbegäran.docx", "A 23497-2023")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23497-2023 tillsynsbegäran mail.docx", "A 23497-2023")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 23497-2023 prioriterade fågelarter.docx", "A 23497-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 23494-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45072</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 5866-2026 artfynd.xlsx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 5866-2026 karta.png", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 5866-2026 georefererad karta.tif", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 5866-2026 FSC-klagomål.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 5866-2026 FSC-klagomål mail.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 5866-2026 tillsynsbegäran.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 5866-2026 tillsynsbegäran mail.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 5866-2026 prioriterade fågelarter.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 23497-2023</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45072</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>3</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Stor revmossa
-Spillkråka</t>
-        </is>
-      </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23497-2023 artfynd.xlsx", "A 23497-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23494-2023 artfynd.xlsx", "A 23494-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23497-2023 karta.png", "A 23497-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23494-2023 karta.png", "A 23494-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23497-2023 georefererad karta.tif", "A 23497-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23494-2023 georefererad karta.tif", "A 23494-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23497-2023 FSC-klagomål.docx", "A 23497-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23494-2023 FSC-klagomål.docx", "A 23494-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23497-2023 FSC-klagomål mail.docx", "A 23497-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23494-2023 FSC-klagomål mail.docx", "A 23494-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23497-2023 tillsynsbegäran.docx", "A 23497-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23494-2023 tillsynsbegäran.docx", "A 23494-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23497-2023 tillsynsbegäran mail.docx", "A 23497-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23494-2023 tillsynsbegäran mail.docx", "A 23494-2023")</f>
         <v/>
       </c>
       <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 23497-2023 prioriterade fågelarter.docx", "A 23497-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 23494-2023 prioriterade fågelarter.docx", "A 23494-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 23494-2023</t>
+          <t>A 5866-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45072</v>
+        <v>46052</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2667,11 +2667,11 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J20" t="n">
         <v>2</v>
@@ -2704,10 +2704,10 @@
         <v>2</v>
       </c>
       <c r="T20" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U20" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
@@ -2716,35 +2716,35 @@
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23494-2023 artfynd.xlsx", "A 23494-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 5866-2026 artfynd.xlsx", "A 5866-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23494-2023 karta.png", "A 23494-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 5866-2026 karta.png", "A 5866-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23494-2023 georefererad karta.tif", "A 23494-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 5866-2026 georefererad karta.tif", "A 5866-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23494-2023 FSC-klagomål.docx", "A 23494-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 5866-2026 FSC-klagomål.docx", "A 5866-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23494-2023 FSC-klagomål mail.docx", "A 23494-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 5866-2026 FSC-klagomål mail.docx", "A 5866-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23494-2023 tillsynsbegäran.docx", "A 23494-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 5866-2026 tillsynsbegäran.docx", "A 5866-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23494-2023 tillsynsbegäran mail.docx", "A 23494-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 5866-2026 tillsynsbegäran mail.docx", "A 5866-2026")</f>
         <v/>
       </c>
       <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 23494-2023 prioriterade fågelarter.docx", "A 23494-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 5866-2026 prioriterade fågelarter.docx", "A 5866-2026")</f>
         <v/>
       </c>
     </row>
@@ -2768,7 +2768,7 @@
         <v>45390</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>46240</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 41756-2025</t>
+          <t>A 30273-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2986,10 +2986,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45902</v>
+        <v>44759</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>12.5</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3035,42 +3035,42 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 41756-2025 artfynd.xlsx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 30273-2022 artfynd.xlsx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 41756-2025 karta.png", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 30273-2022 karta.png", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 41756-2025 georefererad karta.tif", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 30273-2022 georefererad karta.tif", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 41756-2025 FSC-klagomål.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 30273-2022 FSC-klagomål.docx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 41756-2025 FSC-klagomål mail.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 30273-2022 FSC-klagomål mail.docx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 41756-2025 tillsynsbegäran.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 30273-2022 tillsynsbegäran.docx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 41756-2025 tillsynsbegäran mail.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 30273-2022 tillsynsbegäran mail.docx", "A 30273-2022")</f>
         <v/>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
         <v>45205</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 45941-2025</t>
+          <t>A 41756-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3201,10 +3201,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45924</v>
+        <v>45902</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3217,16 +3217,16 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3250,49 +3250,49 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 45941-2025 artfynd.xlsx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 41756-2025 artfynd.xlsx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 45941-2025 karta.png", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 41756-2025 karta.png", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 45941-2025 georefererad karta.tif", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 41756-2025 georefererad karta.tif", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 45941-2025 FSC-klagomål.docx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 41756-2025 FSC-klagomål.docx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 45941-2025 FSC-klagomål mail.docx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 41756-2025 FSC-klagomål mail.docx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 45941-2025 tillsynsbegäran.docx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 41756-2025 tillsynsbegäran.docx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 45941-2025 tillsynsbegäran mail.docx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 41756-2025 tillsynsbegäran mail.docx", "A 41756-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 30273-2022</t>
+          <t>A 45941-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44759</v>
+        <v>45924</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3322,17 +3322,17 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>12.5</v>
+        <v>1.2</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
@@ -3346,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3362,35 +3362,35 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 30273-2022 artfynd.xlsx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 45941-2025 artfynd.xlsx", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 30273-2022 karta.png", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 45941-2025 karta.png", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 30273-2022 georefererad karta.tif", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 45941-2025 georefererad karta.tif", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 30273-2022 FSC-klagomål.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 45941-2025 FSC-klagomål.docx", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 30273-2022 FSC-klagomål mail.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 45941-2025 FSC-klagomål mail.docx", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 30273-2022 tillsynsbegäran.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 45941-2025 tillsynsbegäran.docx", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 30273-2022 tillsynsbegäran mail.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 45941-2025 tillsynsbegäran mail.docx", "A 45941-2025")</f>
         <v/>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
         <v>45546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 11102-2024</t>
+          <t>A 7062-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3521,14 +3521,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45371</v>
+        <v>45343</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.8</v>
+        <v>9.1</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -3553,7 +3553,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3565,10 +3565,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3581,42 +3581,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 11102-2024 artfynd.xlsx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 7062-2024 artfynd.xlsx", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 11102-2024 karta.png", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 7062-2024 karta.png", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 11102-2024 georefererad karta.tif", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 7062-2024 georefererad karta.tif", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 11102-2024 FSC-klagomål.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 7062-2024 FSC-klagomål.docx", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 11102-2024 FSC-klagomål mail.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 7062-2024 FSC-klagomål mail.docx", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 11102-2024 tillsynsbegäran.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 7062-2024 tillsynsbegäran.docx", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 11102-2024 tillsynsbegäran mail.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 7062-2024 tillsynsbegäran mail.docx", "A 7062-2024")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 7062-2024</t>
+          <t>A 11102-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3626,14 +3626,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45343</v>
+        <v>45371</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3646,20 +3646,20 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>9.1</v>
+        <v>2.8</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
@@ -3670,10 +3670,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3686,35 +3686,35 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 7062-2024 artfynd.xlsx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 11102-2024 artfynd.xlsx", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 7062-2024 karta.png", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 11102-2024 karta.png", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 7062-2024 georefererad karta.tif", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 11102-2024 georefererad karta.tif", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 7062-2024 FSC-klagomål.docx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 11102-2024 FSC-klagomål.docx", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 7062-2024 FSC-klagomål mail.docx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 11102-2024 FSC-klagomål mail.docx", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 7062-2024 tillsynsbegäran.docx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 11102-2024 tillsynsbegäran.docx", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 7062-2024 tillsynsbegäran mail.docx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 11102-2024 tillsynsbegäran mail.docx", "A 11102-2024")</f>
         <v/>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
         <v>46240</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44812</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44581</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>44875</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>44637</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 30285-2022</t>
+          <t>A 18346-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44760</v>
+        <v>44685</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4196,7 +4196,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 18346-2022</t>
+          <t>A 30285-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44685</v>
+        <v>44760</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4286,7 +4286,7 @@
         <v>44720</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>44627</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>44476</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>44467</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>44803</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>44812</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 41420-2022</t>
+          <t>A 12234-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4721,10 +4721,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44826</v>
+        <v>45378</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4780,7 +4780,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 51569-2021</t>
+          <t>A 43767-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4794,10 +4794,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44462</v>
+        <v>45187</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4853,7 +4853,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 38059-2022</t>
+          <t>A 51569-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4867,10 +4867,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44811</v>
+        <v>44462</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.4</v>
+        <v>4.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4926,7 +4926,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 296-2022</t>
+          <t>A 38059-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44565</v>
+        <v>44811</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4999,7 +4999,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 30284-2022</t>
+          <t>A 296-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44760</v>
+        <v>44565</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5072,7 +5072,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 30287-2022</t>
+          <t>A 30284-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5089,7 +5089,7 @@
         <v>44760</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 10726-2022</t>
+          <t>A 30287-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5159,10 +5159,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44627</v>
+        <v>44760</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5218,7 +5218,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 58750-2021</t>
+          <t>A 41420-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5232,10 +5232,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44489</v>
+        <v>44826</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5291,7 +5291,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 12234-2024</t>
+          <t>A 33991-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5305,10 +5305,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45378</v>
+        <v>45134</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5364,7 +5364,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 4881-2024</t>
+          <t>A 13887-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5378,10 +5378,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45329</v>
+        <v>45391</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.5</v>
+        <v>11.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5437,7 +5437,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 26443-2023</t>
+          <t>A 10726-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45092</v>
+        <v>44627</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5510,7 +5510,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 54681-2021</t>
+          <t>A 61284-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5524,10 +5524,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44473</v>
+        <v>44915</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5583,7 +5583,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 43770-2023</t>
+          <t>A 52431-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45187</v>
+        <v>45225</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5656,7 +5656,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 30724-2024</t>
+          <t>A 12784-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5666,14 +5666,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45496</v>
+        <v>45733</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5729,7 +5729,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 23374-2025</t>
+          <t>A 41411-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5743,10 +5743,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45791</v>
+        <v>44826</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5802,7 +5802,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 23509-2025</t>
+          <t>A 11104-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45792</v>
+        <v>45371</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.3</v>
+        <v>3.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 5743-2025</t>
+          <t>A 4225-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5889,10 +5889,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45694</v>
+        <v>45324</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5948,7 +5948,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 406-2024</t>
+          <t>A 4227-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5962,10 +5962,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45296</v>
+        <v>45324</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6021,7 +6021,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 24053-2025</t>
+          <t>A 33993-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6031,14 +6031,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45796</v>
+        <v>45134</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>11.1</v>
+        <v>0.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6094,7 +6094,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 7819-2025</t>
+          <t>A 33996-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6108,10 +6108,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45706</v>
+        <v>45134</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.6</v>
+        <v>0.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6167,7 +6167,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 5740-2025</t>
+          <t>A 2867-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6181,10 +6181,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45694</v>
+        <v>45677</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.4</v>
+        <v>10.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6240,7 +6240,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 6384-2025</t>
+          <t>A 35423-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6254,10 +6254,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45699</v>
+        <v>45855</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6313,7 +6313,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 36984-2024</t>
+          <t>A 65619-2021</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6327,10 +6327,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45539</v>
+        <v>44516</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6386,7 +6386,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 27222-2025</t>
+          <t>A 15351-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6400,10 +6400,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45812</v>
+        <v>45400</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6415,8 +6415,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6459,7 +6464,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 2867-2025</t>
+          <t>A 51488-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6473,10 +6478,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45677</v>
+        <v>44869</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6489,7 +6494,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>10.7</v>
+        <v>2.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6532,7 +6537,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 28515-2025</t>
+          <t>A 37508-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6546,10 +6551,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45819</v>
+        <v>45158</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6562,7 +6567,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.7</v>
+        <v>6.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6605,7 +6610,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 41759-2025</t>
+          <t>A 37509-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6619,10 +6624,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45902</v>
+        <v>45158</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6635,7 +6640,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6678,7 +6683,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 41758-2025</t>
+          <t>A 28910-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6692,10 +6697,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45902</v>
+        <v>45480</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6708,7 +6713,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6751,7 +6756,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 41760-2025</t>
+          <t>A 11604-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6765,10 +6770,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45902</v>
+        <v>45373</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6781,7 +6786,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6824,7 +6829,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 41761-2025</t>
+          <t>A 15567-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6838,10 +6843,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45902</v>
+        <v>44662</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6854,7 +6859,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>6.6</v>
+        <v>1.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6897,7 +6902,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 35422-2025</t>
+          <t>A 41758-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6911,10 +6916,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45855</v>
+        <v>45902</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6927,7 +6932,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6970,7 +6975,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 42857-2025</t>
+          <t>A 41760-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6984,10 +6989,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45908</v>
+        <v>45902</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7000,7 +7005,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7043,7 +7048,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 47511-2024</t>
+          <t>A 41761-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7057,10 +7062,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45587</v>
+        <v>45902</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7073,7 +7078,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>6.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7116,7 +7121,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 44104-2025</t>
+          <t>A 41759-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7130,10 +7135,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45915</v>
+        <v>45902</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7146,7 +7151,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7189,7 +7194,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 43684-2025</t>
+          <t>A 1382-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7203,10 +7208,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45912</v>
+        <v>45303</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7219,7 +7224,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7262,7 +7267,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 61435-2024</t>
+          <t>A 14427-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7276,10 +7281,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45646</v>
+        <v>46100</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7292,7 +7297,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7335,7 +7340,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 44916-2025</t>
+          <t>A 35422-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7349,10 +7354,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45918</v>
+        <v>45855</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7365,7 +7370,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7408,7 +7413,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 44918-2025</t>
+          <t>A 42857-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7422,10 +7427,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45918</v>
+        <v>45908</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7438,7 +7443,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>5.7</v>
+        <v>1.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7481,7 +7486,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 44914-2025</t>
+          <t>A 587-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7495,10 +7500,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45918</v>
+        <v>45664</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7511,7 +7516,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7554,7 +7559,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 44915-2025</t>
+          <t>A 43684-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7568,10 +7573,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45918</v>
+        <v>45912</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7584,7 +7589,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7627,7 +7632,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 5612-2025</t>
+          <t>A 44104-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7641,10 +7646,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45693</v>
+        <v>45915</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7657,7 +7662,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7700,7 +7705,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 35420-2025</t>
+          <t>A 44914-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7714,10 +7719,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45855</v>
+        <v>45918</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7730,7 +7735,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7773,7 +7778,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 37063-2024</t>
+          <t>A 44915-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7787,10 +7792,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45539</v>
+        <v>45918</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7803,7 +7808,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>8.800000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7846,7 +7851,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 587-2025</t>
+          <t>A 44918-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7860,10 +7865,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45664</v>
+        <v>45918</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7876,7 +7881,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.3</v>
+        <v>5.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7919,7 +7924,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 35717-2025</t>
+          <t>A 44916-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7933,10 +7938,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45860</v>
+        <v>45918</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7949,7 +7954,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7992,7 +7997,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 57381-2022</t>
+          <t>A 7912-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8006,10 +8011,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44896</v>
+        <v>45350</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8022,7 +8027,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8065,7 +8070,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 56584-2025</t>
+          <t>A 17377-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8079,10 +8084,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45974</v>
+        <v>46119</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8095,7 +8100,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8138,7 +8143,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 48730-2025</t>
+          <t>A 6323-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8152,10 +8157,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45936</v>
+        <v>44960</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8167,8 +8172,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8211,7 +8221,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 48727-2025</t>
+          <t>A 54804-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8225,10 +8235,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45936</v>
+        <v>44883</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8241,7 +8251,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>6.1</v>
+        <v>22.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8284,7 +8294,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 12628-2023</t>
+          <t>A 57381-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8298,10 +8308,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45000</v>
+        <v>44896</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8314,7 +8324,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8357,7 +8367,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 49188-2025</t>
+          <t>A 48727-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8371,10 +8381,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45938</v>
+        <v>45936</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8387,7 +8397,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.7</v>
+        <v>6.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8430,7 +8440,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 13801-2025</t>
+          <t>A 18841-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8444,10 +8454,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45737</v>
+        <v>46129</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8460,7 +8470,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8503,7 +8513,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 65619-2021</t>
+          <t>A 48730-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8517,10 +8527,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44516</v>
+        <v>45936</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8533,7 +8543,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8576,7 +8586,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 12784-2025</t>
+          <t>A 13801-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8590,10 +8600,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45733</v>
+        <v>45737</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8606,7 +8616,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8649,7 +8659,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 15351-2024</t>
+          <t>A 49188-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8663,10 +8673,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45400</v>
+        <v>45938</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8678,13 +8688,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8727,7 +8732,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 35423-2025</t>
+          <t>A 8117-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8741,10 +8746,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45855</v>
+        <v>44974</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8757,7 +8762,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8800,7 +8805,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 41411-2022</t>
+          <t>A 12628-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8814,10 +8819,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44826</v>
+        <v>45000</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8830,7 +8835,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8873,7 +8878,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 12647-2023</t>
+          <t>A 19079-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8887,10 +8892,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45000</v>
+        <v>45766</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8903,7 +8908,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8946,7 +8951,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 8117-2023</t>
+          <t>A 50349-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8960,10 +8965,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44974</v>
+        <v>45600</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8976,7 +8981,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>11</v>
+        <v>1.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9019,7 +9024,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 14427-2026</t>
+          <t>A 28022-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9033,10 +9038,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46100</v>
+        <v>45098</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9049,7 +9054,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.2</v>
+        <v>5.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9092,7 +9097,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 17377-2026</t>
+          <t>A 48904-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9106,10 +9111,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46119</v>
+        <v>45594</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9122,7 +9127,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9165,7 +9170,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 18841-2026</t>
+          <t>A 55324-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9179,10 +9184,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46129</v>
+        <v>45971</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9194,8 +9199,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9238,7 +9248,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 55324-2025</t>
+          <t>A 28903-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9252,10 +9262,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45971</v>
+        <v>45480</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9267,13 +9277,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9316,7 +9321,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 19079-2025</t>
+          <t>A 61952-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9330,10 +9335,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45766</v>
+        <v>45653</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9346,7 +9351,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9389,7 +9394,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 61952-2024</t>
+          <t>A 61475-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9403,10 +9408,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45653</v>
+        <v>46001</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9419,7 +9424,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9462,7 +9467,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 28022-2023</t>
+          <t>A 12647-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9476,10 +9481,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45098</v>
+        <v>45000</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9492,7 +9497,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>5.7</v>
+        <v>1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9552,7 +9557,7 @@
         <v>44889</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9608,7 +9613,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 50349-2024</t>
+          <t>A 13382-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9622,10 +9627,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45600</v>
+        <v>45005</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9638,7 +9643,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9681,7 +9686,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 61475-2025</t>
+          <t>A 38093-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9695,10 +9700,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46001</v>
+        <v>44811</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9711,7 +9716,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9754,7 +9759,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 7912-2024</t>
+          <t>A 5328-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9768,10 +9773,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45350</v>
+        <v>45692</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9827,7 +9832,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 13581-2023</t>
+          <t>A 61695-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9841,10 +9846,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45006</v>
+        <v>46002</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9856,13 +9861,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 8071-2024</t>
+          <t>A 16473-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9919,10 +9919,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45351</v>
+        <v>44671</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9978,7 +9978,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 48904-2024</t>
+          <t>A 22257-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9992,10 +9992,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45594</v>
+        <v>46154</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10008,7 +10008,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.9</v>
+        <v>1.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10051,7 +10051,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 13975-2023</t>
+          <t>A 23541-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10061,14 +10061,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45008</v>
+        <v>46163</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10124,7 +10124,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 16473-2022</t>
+          <t>A 40092-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10138,10 +10138,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44671</v>
+        <v>45554</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 6323-2023</t>
+          <t>A 57754-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10211,10 +10211,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44960</v>
+        <v>45246</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10226,13 +10226,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10275,7 +10270,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 40092-2024</t>
+          <t>A 14891-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10289,10 +10284,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45554</v>
+        <v>45743</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10305,7 +10300,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10348,7 +10343,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 57754-2023</t>
+          <t>A 24700-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10362,10 +10357,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45246</v>
+        <v>46171</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10377,8 +10372,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10421,7 +10421,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 61695-2025</t>
+          <t>A 26886-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10435,10 +10435,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46002</v>
+        <v>45093</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10494,7 +10494,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 26886-2023</t>
+          <t>A 26443-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10508,10 +10508,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45093</v>
+        <v>45092</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10524,7 +10524,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10567,7 +10567,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 22257-2026</t>
+          <t>A 17114-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10581,10 +10581,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46154</v>
+        <v>45034</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10597,7 +10597,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10640,7 +10640,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 302-2024</t>
+          <t>A 58750-2021</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10654,10 +10654,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45295</v>
+        <v>44489</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10669,13 +10669,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10718,7 +10713,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 23541-2026</t>
+          <t>A 7947-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10728,14 +10723,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46163</v>
+        <v>45350</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10748,7 +10743,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10791,7 +10786,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 14891-2025</t>
+          <t>A 25729-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10805,10 +10800,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45743</v>
+        <v>46178</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10821,7 +10816,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10864,7 +10859,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 24700-2026</t>
+          <t>A 56584-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10878,10 +10873,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46171</v>
+        <v>45974</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10893,13 +10888,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10942,7 +10932,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 29068-2024</t>
+          <t>A 27643-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10956,10 +10946,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45481</v>
+        <v>46190</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10972,7 +10962,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11015,7 +11005,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 25729-2026</t>
+          <t>A 13581-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11029,10 +11019,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46178</v>
+        <v>45006</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11044,8 +11034,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11088,7 +11083,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 27643-2026</t>
+          <t>A 54681-2021</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11102,10 +11097,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46190</v>
+        <v>44473</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11118,7 +11113,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11161,7 +11156,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 4225-2024</t>
+          <t>A 44445-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11175,10 +11170,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45324</v>
+        <v>45189</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11191,7 +11186,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11234,7 +11229,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 4227-2024</t>
+          <t>A 17116-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11248,10 +11243,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45324</v>
+        <v>45034</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11264,7 +11259,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11307,7 +11302,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 38093-2022</t>
+          <t>A 12760-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11321,10 +11316,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44811</v>
+        <v>45001</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11337,7 +11332,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11397,7 +11392,7 @@
         <v>46242</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11453,7 +11448,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 33842-2026</t>
+          <t>A 5612-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11467,10 +11462,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46251</v>
+        <v>45693</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11483,7 +11478,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>7.2</v>
+        <v>1.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11526,7 +11521,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 5420-2025</t>
+          <t>A 47511-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11540,10 +11535,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45692</v>
+        <v>45587</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11556,7 +11551,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11599,7 +11594,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 51488-2022</t>
+          <t>A 43770-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11613,10 +11608,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44869</v>
+        <v>45187</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11629,7 +11624,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11672,7 +11667,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 2438-2026</t>
+          <t>A 4881-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11686,10 +11681,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46036</v>
+        <v>45329</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11702,7 +11697,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11745,7 +11740,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 30605-2026</t>
+          <t>A 302-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11759,10 +11754,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46210</v>
+        <v>45295</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11774,8 +11769,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>10.5</v>
+        <v>2.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11818,7 +11818,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 6489-2025</t>
+          <t>A 29068-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11832,10 +11832,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45699</v>
+        <v>45481</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11848,7 +11848,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11891,7 +11891,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 9046-2022</t>
+          <t>A 33842-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11905,10 +11905,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44615</v>
+        <v>46251</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
+        <v>7.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11964,7 +11964,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 35883-2026</t>
+          <t>A 5324-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11978,10 +11978,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46266</v>
+        <v>45692</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12037,7 +12037,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 28903-2024</t>
+          <t>A 30605-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12051,10 +12051,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45480</v>
+        <v>46210</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3.4</v>
+        <v>10.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12110,7 +12110,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 61284-2022</t>
+          <t>A 9046-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12124,10 +12124,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44915</v>
+        <v>44615</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12183,7 +12183,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 12760-2023</t>
+          <t>A 2438-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12197,10 +12197,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45001</v>
+        <v>46036</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12256,7 +12256,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 62730-2023</t>
+          <t>A 13631-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12270,10 +12270,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45268</v>
+        <v>45390</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>3.1</v>
+        <v>16.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12329,7 +12329,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 36722-2026</t>
+          <t>A 61435-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12343,10 +12343,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46272</v>
+        <v>45646</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12358,13 +12358,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12407,7 +12402,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 37037-2026</t>
+          <t>A 37063-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12421,10 +12416,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46273</v>
+        <v>45539</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12437,7 +12432,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12480,7 +12475,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 36773-2026</t>
+          <t>A 15159-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12494,10 +12489,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46272</v>
+        <v>45016</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12515,7 +12510,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12558,7 +12553,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 11604-2024</t>
+          <t>A 550-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12572,10 +12567,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45373</v>
+        <v>45299</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12588,7 +12583,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12631,7 +12626,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 5324-2025</t>
+          <t>A 14929-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12645,10 +12640,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45692</v>
+        <v>45398</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12704,7 +12699,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 54804-2022</t>
+          <t>A 21630-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12718,10 +12713,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44883</v>
+        <v>45442</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12734,7 +12729,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>22.6</v>
+        <v>4.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12777,7 +12772,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 52431-2023</t>
+          <t>A 13975-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12791,10 +12786,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45225</v>
+        <v>45008</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12807,7 +12802,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12850,7 +12845,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 33993-2023</t>
+          <t>A 35883-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12864,10 +12859,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45134</v>
+        <v>46266</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12880,7 +12875,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.8</v>
+        <v>6.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12923,7 +12918,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 33996-2023</t>
+          <t>A 8071-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12937,10 +12932,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45134</v>
+        <v>45351</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12953,7 +12948,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12996,7 +12991,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 7947-2024</t>
+          <t>A 6489-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13010,10 +13005,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45350</v>
+        <v>45699</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13026,7 +13021,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13069,7 +13064,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 17116-2023</t>
+          <t>A 36773-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13083,10 +13078,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45034</v>
+        <v>46272</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13098,8 +13093,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13142,7 +13142,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 15567-2022</t>
+          <t>A 406-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13156,10 +13156,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44662</v>
+        <v>45296</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13172,7 +13172,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13215,7 +13215,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 21630-2024</t>
+          <t>A 36722-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45442</v>
+        <v>46272</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13244,8 +13244,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13288,7 +13293,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 13382-2023</t>
+          <t>A 62730-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13302,10 +13307,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45005</v>
+        <v>45268</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13318,7 +13323,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13361,7 +13366,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 550-2024</t>
+          <t>A 37037-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13375,10 +13380,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45299</v>
+        <v>46273</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13391,7 +13396,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13434,7 +13439,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 13887-2024</t>
+          <t>A 49879-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13448,10 +13453,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45391</v>
+        <v>45213</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13464,7 +13469,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>11.3</v>
+        <v>5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13507,7 +13512,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 14929-2024</t>
+          <t>A 5420-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13521,10 +13526,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45398</v>
+        <v>45692</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13537,7 +13542,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>5.1</v>
+        <v>0.6</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13580,7 +13585,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 11104-2024</t>
+          <t>A 3867-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13594,10 +13599,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45371</v>
+        <v>45684</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13610,7 +13615,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13653,7 +13658,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 28910-2024</t>
+          <t>A 21617-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13667,10 +13672,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45480</v>
+        <v>45441</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13683,7 +13688,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13726,7 +13731,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 1382-2024</t>
+          <t>A 30724-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13736,14 +13741,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45303</v>
+        <v>45496</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13756,7 +13761,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13799,7 +13804,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 17114-2023</t>
+          <t>A 22561-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13813,10 +13818,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45034</v>
+        <v>45789</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13829,7 +13834,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13872,7 +13877,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 43767-2023</t>
+          <t>A 23509-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13886,10 +13891,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45187</v>
+        <v>45792</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13902,7 +13907,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13945,7 +13950,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 13631-2024</t>
+          <t>A 23374-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13959,10 +13964,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45390</v>
+        <v>45791</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13975,7 +13980,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>16.4</v>
+        <v>0.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14018,7 +14023,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 37508-2023</t>
+          <t>A 12790-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14032,10 +14037,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45158</v>
+        <v>45733</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14048,7 +14053,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>6.9</v>
+        <v>2.9</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14091,7 +14096,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 37509-2023</t>
+          <t>A 12243-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14105,10 +14110,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45158</v>
+        <v>45729</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14121,7 +14126,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.9</v>
+        <v>10.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14164,7 +14169,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 15159-2023</t>
+          <t>A 24053-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14174,14 +14179,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45016</v>
+        <v>45796</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14193,13 +14198,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>0.9</v>
+        <v>11.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14242,7 +14242,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 49879-2023</t>
+          <t>A 5743-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14256,10 +14256,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45213</v>
+        <v>45694</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14315,7 +14315,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 44445-2023</t>
+          <t>A 7819-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14329,10 +14329,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45189</v>
+        <v>45706</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>3.8</v>
+        <v>5.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14388,7 +14388,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 33991-2023</t>
+          <t>A 5740-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14402,10 +14402,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45134</v>
+        <v>45694</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14461,7 +14461,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 5328-2025</t>
+          <t>A 6384-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14475,10 +14475,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45692</v>
+        <v>45699</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14534,7 +14534,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 3867-2025</t>
+          <t>A 36984-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14548,10 +14548,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45684</v>
+        <v>45539</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14607,7 +14607,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 21617-2024</t>
+          <t>A 27222-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14621,10 +14621,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45441</v>
+        <v>45812</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>9.699999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14680,7 +14680,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 22561-2025</t>
+          <t>A 28515-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14694,10 +14694,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45789</v>
+        <v>45819</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14753,7 +14753,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 12790-2025</t>
+          <t>A 35420-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14767,10 +14767,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45733</v>
+        <v>45855</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14826,7 +14826,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 12243-2025</t>
+          <t>A 35717-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14840,10 +14840,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45729</v>
+        <v>45860</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14856,7 +14856,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>10.2</v>
+        <v>0.6</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14916,7 +14916,7 @@
         <v>44964</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>

--- a/Översikt LILLA EDET.xlsx
+++ b/Översikt LILLA EDET.xlsx
@@ -601,7 +601,7 @@
         <v>46169</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45295</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45295</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45827</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 34396-2023</t>
+          <t>A 62846-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45139</v>
+        <v>45272</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1127,12 +1127,123 @@
         <v>7</v>
       </c>
       <c r="T6" t="n">
+        <v>17</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Kattfotslav
+Blåmossa
+Bronshjon
+Stor revmossa
+Vågbandad barkbock
+Större vattensalamander
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 62846-2023 artfynd.xlsx", "A 62846-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 62846-2023 karta.png", "A 62846-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 62846-2023 georefererad karta.tif", "A 62846-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 62846-2023 FSC-klagomål.docx", "A 62846-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 62846-2023 FSC-klagomål mail.docx", "A 62846-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 62846-2023 tillsynsbegäran.docx", "A 62846-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 62846-2023 tillsynsbegäran mail.docx", "A 62846-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 34396-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45139</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>7</v>
+      </c>
+      <c r="T7" t="n">
         <v>24</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>24</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Blåmossa
@@ -1143,147 +1254,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 34396-2023 artfynd.xlsx", "A 34396-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 34396-2023 karta.png", "A 34396-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 34396-2023 georefererad karta.tif", "A 34396-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 34396-2023 FSC-klagomål.docx", "A 34396-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 34396-2023 FSC-klagomål mail.docx", "A 34396-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 34396-2023 tillsynsbegäran.docx", "A 34396-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 34396-2023 tillsynsbegäran mail.docx", "A 34396-2023")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 34396-2023 prioriterade fågelarter.docx", "A 34396-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 62846-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45272</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>7</v>
-      </c>
-      <c r="T7" t="n">
-        <v>17</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Kattfotslav
-Blåmossa
-Bronshjon
-Stor revmossa
-Vågbandad barkbock
-Större vattensalamander
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 62846-2023 artfynd.xlsx", "A 62846-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 62846-2023 karta.png", "A 62846-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 62846-2023 georefererad karta.tif", "A 62846-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 62846-2023 FSC-klagomål.docx", "A 62846-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 62846-2023 FSC-klagomål mail.docx", "A 62846-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 62846-2023 tillsynsbegäran.docx", "A 62846-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 62846-2023 tillsynsbegäran mail.docx", "A 62846-2023")</f>
         <v/>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
         <v>46044</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 28512-2025</t>
+          <t>A 25298-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45819</v>
+        <v>45462</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1432,8 +1432,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>10.9</v>
+        <v>5.9</v>
       </c>
       <c r="J9" t="n">
         <v>2</v>
@@ -1466,12 +1471,232 @@
         <v>4</v>
       </c>
       <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>5</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Västlig hakmossa
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 25298-2024 artfynd.xlsx", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 25298-2024 karta.png", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 25298-2024 georefererad karta.tif", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 25298-2024 FSC-klagomål.docx", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 25298-2024 FSC-klagomål mail.docx", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 25298-2024 tillsynsbegäran.docx", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 25298-2024 tillsynsbegäran mail.docx", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 25298-2024 prioriterade fågelarter.docx", "A 25298-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 43771-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45187</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Slåtterfibbla
+Vätteros
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 43771-2023 artfynd.xlsx", "A 43771-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 43771-2023 karta.png", "A 43771-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 43771-2023 georefererad karta.tif", "A 43771-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 43771-2023 FSC-klagomål.docx", "A 43771-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 43771-2023 FSC-klagomål mail.docx", "A 43771-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 43771-2023 tillsynsbegäran.docx", "A 43771-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 43771-2023 tillsynsbegäran mail.docx", "A 43771-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 28512-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45819</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
         <v>19</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U11" t="n">
         <v>19</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Västlig hakmossa
@@ -1479,111 +1704,224 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 28512-2025 artfynd.xlsx", "A 28512-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 28512-2025 karta.png", "A 28512-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 28512-2025 georefererad karta.tif", "A 28512-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 28512-2025 FSC-klagomål.docx", "A 28512-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 28512-2025 FSC-klagomål mail.docx", "A 28512-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 28512-2025 tillsynsbegäran.docx", "A 28512-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 28512-2025 tillsynsbegäran mail.docx", "A 28512-2025")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 28512-2025 prioriterade fågelarter.docx", "A 28512-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 23563-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45072</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>7</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Nordfladdermus
+Dvärgpipistrell
+Vattenfladdermus
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23563-2023 artfynd.xlsx", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23563-2023 karta.png", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23563-2023 georefererad karta.tif", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23563-2023 FSC-klagomål.docx", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23563-2023 FSC-klagomål mail.docx", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23563-2023 tillsynsbegäran.docx", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23563-2023 tillsynsbegäran mail.docx", "A 23563-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 24290-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>46169</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E13" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>3.6</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K13" t="n">
         <v>3</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>4</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T13" t="n">
         <v>5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U13" t="n">
         <v>5</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Blanksvart trämyra
 Grönpyrola
@@ -1591,381 +1929,43 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 24290-2026 artfynd.xlsx", "A 24290-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 24290-2026 karta.png", "A 24290-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 24290-2026 georefererad karta.tif", "A 24290-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 24290-2026 FSC-klagomål.docx", "A 24290-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 24290-2026 FSC-klagomål mail.docx", "A 24290-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 24290-2026 tillsynsbegäran.docx", "A 24290-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 24290-2026 tillsynsbegäran mail.docx", "A 24290-2026")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 24290-2026 prioriterade fågelarter.docx", "A 24290-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 23563-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45072</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>7</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Nordfladdermus
-Dvärgpipistrell
-Vattenfladdermus
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23563-2023 artfynd.xlsx", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23563-2023 karta.png", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23563-2023 georefererad karta.tif", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23563-2023 FSC-klagomål.docx", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23563-2023 FSC-klagomål mail.docx", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23563-2023 tillsynsbegäran.docx", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23563-2023 tillsynsbegäran mail.docx", "A 23563-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 25298-2024</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45462</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>5</v>
-      </c>
-      <c r="U12" t="n">
-        <v>5</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Västlig hakmossa
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 25298-2024 artfynd.xlsx", "A 25298-2024")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 25298-2024 karta.png", "A 25298-2024")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 25298-2024 georefererad karta.tif", "A 25298-2024")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 25298-2024 FSC-klagomål.docx", "A 25298-2024")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 25298-2024 FSC-klagomål mail.docx", "A 25298-2024")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 25298-2024 tillsynsbegäran.docx", "A 25298-2024")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 25298-2024 tillsynsbegäran mail.docx", "A 25298-2024")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 25298-2024 prioriterade fågelarter.docx", "A 25298-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 43771-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45187</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>4</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Slåtterfibbla
-Vätteros
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 43771-2023 artfynd.xlsx", "A 43771-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 43771-2023 karta.png", "A 43771-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 43771-2023 georefererad karta.tif", "A 43771-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 43771-2023 FSC-klagomål.docx", "A 43771-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 43771-2023 FSC-klagomål mail.docx", "A 43771-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 43771-2023 tillsynsbegäran.docx", "A 43771-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 43771-2023 tillsynsbegäran mail.docx", "A 43771-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 17376-2026</t>
+          <t>A 25655-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46119</v>
+        <v>45089</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
         <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2019,271 +2019,271 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
       </c>
       <c r="T14" t="n">
+        <v>9</v>
+      </c>
+      <c r="U14" t="n">
+        <v>7</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Bergjohannesört
+Svinrot
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 25655-2023 artfynd.xlsx", "A 25655-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 25655-2023 karta.png", "A 25655-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 25655-2023 georefererad karta.tif", "A 25655-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 25655-2023 FSC-klagomål.docx", "A 25655-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 25655-2023 FSC-klagomål mail.docx", "A 25655-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 25655-2023 tillsynsbegäran.docx", "A 25655-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 25655-2023 tillsynsbegäran mail.docx", "A 25655-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 17376-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46119</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>3</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Slåttergubbe
 Almsnabbvinge
 Granspira</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 17376-2026 artfynd.xlsx", "A 17376-2026")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 17376-2026 karta.png", "A 17376-2026")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 17376-2026 georefererad karta.tif", "A 17376-2026")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 17376-2026 FSC-klagomål.docx", "A 17376-2026")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 17376-2026 FSC-klagomål mail.docx", "A 17376-2026")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 17376-2026 tillsynsbegäran.docx", "A 17376-2026")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 17376-2026 tillsynsbegäran mail.docx", "A 17376-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>A 28021-2023</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
         <v>45098</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E16" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>1.5</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J16" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K16" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>3</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T16" t="n">
         <v>3</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U16" t="n">
         <v>3</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Stor revmossa
 Nattskärra
 Törnskata</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 28021-2023 artfynd.xlsx", "A 28021-2023")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 28021-2023 karta.png", "A 28021-2023")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 28021-2023 georefererad karta.tif", "A 28021-2023")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 28021-2023 FSC-klagomål.docx", "A 28021-2023")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 28021-2023 FSC-klagomål mail.docx", "A 28021-2023")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 28021-2023 tillsynsbegäran.docx", "A 28021-2023")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 28021-2023 tillsynsbegäran mail.docx", "A 28021-2023")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 28021-2023 prioriterade fågelarter.docx", "A 28021-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 25655-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45089</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>9</v>
-      </c>
-      <c r="U16" t="n">
-        <v>7</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Bergjohannesört
-Svinrot
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 25655-2023 artfynd.xlsx", "A 25655-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 25655-2023 karta.png", "A 25655-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 25655-2023 georefererad karta.tif", "A 25655-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 25655-2023 FSC-klagomål.docx", "A 25655-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 25655-2023 FSC-klagomål mail.docx", "A 25655-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 25655-2023 tillsynsbegäran.docx", "A 25655-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 25655-2023 tillsynsbegäran mail.docx", "A 25655-2023")</f>
         <v/>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
         <v>45072</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 23497-2023</t>
+          <t>A 5866-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45072</v>
+        <v>46052</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,17 +2437,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2474,277 +2474,277 @@
         <v>2</v>
       </c>
       <c r="T18" t="n">
+        <v>9</v>
+      </c>
+      <c r="U18" t="n">
+        <v>9</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 5866-2026 artfynd.xlsx", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 5866-2026 karta.png", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 5866-2026 georefererad karta.tif", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 5866-2026 FSC-klagomål.docx", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 5866-2026 FSC-klagomål mail.docx", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 5866-2026 tillsynsbegäran.docx", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 5866-2026 tillsynsbegäran mail.docx", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 5866-2026 prioriterade fågelarter.docx", "A 5866-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 23497-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45072</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
         <v>3</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>3</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Stor revmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23497-2023 artfynd.xlsx", "A 23497-2023")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23497-2023 karta.png", "A 23497-2023")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23497-2023 georefererad karta.tif", "A 23497-2023")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23497-2023 FSC-klagomål.docx", "A 23497-2023")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23497-2023 FSC-klagomål mail.docx", "A 23497-2023")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23497-2023 tillsynsbegäran.docx", "A 23497-2023")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23497-2023 tillsynsbegäran mail.docx", "A 23497-2023")</f>
         <v/>
       </c>
-      <c r="AE18">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 23497-2023 prioriterade fågelarter.docx", "A 23497-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 23494-2023</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
         <v>45072</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
+      <c r="E20" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t>Kyrkan</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="I20" t="n">
         <v>1.3</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J20" t="n">
         <v>2</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T20" t="n">
         <v>4</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U20" t="n">
         <v>4</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23494-2023 artfynd.xlsx", "A 23494-2023")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23494-2023 karta.png", "A 23494-2023")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23494-2023 georefererad karta.tif", "A 23494-2023")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23494-2023 FSC-klagomål.docx", "A 23494-2023")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23494-2023 FSC-klagomål mail.docx", "A 23494-2023")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23494-2023 tillsynsbegäran.docx", "A 23494-2023")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23494-2023 tillsynsbegäran mail.docx", "A 23494-2023")</f>
         <v/>
       </c>
-      <c r="AE19">
+      <c r="AE20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 23494-2023 prioriterade fågelarter.docx", "A 23494-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 5866-2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>46052</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>9</v>
-      </c>
-      <c r="U20" t="n">
-        <v>9</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 5866-2026 artfynd.xlsx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 5866-2026 karta.png", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 5866-2026 georefererad karta.tif", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 5866-2026 FSC-klagomål.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 5866-2026 FSC-klagomål mail.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 5866-2026 tillsynsbegäran.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 5866-2026 tillsynsbegäran mail.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 5866-2026 prioriterade fågelarter.docx", "A 5866-2026")</f>
         <v/>
       </c>
     </row>
@@ -2768,7 +2768,7 @@
         <v>45390</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>46240</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 30273-2022</t>
+          <t>A 49384-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2982,14 +2982,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44759</v>
+        <v>45205</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3001,18 +3001,23 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>12.5</v>
+        <v>1.2</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
@@ -3026,7 +3031,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3035,49 +3040,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 30273-2022 artfynd.xlsx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 49384-2023 artfynd.xlsx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 30273-2022 karta.png", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 49384-2023 karta.png", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 30273-2022 georefererad karta.tif", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 49384-2023 georefererad karta.tif", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 30273-2022 FSC-klagomål.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 49384-2023 FSC-klagomål.docx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 30273-2022 FSC-klagomål mail.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 49384-2023 FSC-klagomål mail.docx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 30273-2022 tillsynsbegäran.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 49384-2023 tillsynsbegäran.docx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 30273-2022 tillsynsbegäran mail.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 49384-2023 tillsynsbegäran mail.docx", "A 49384-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 49384-2023</t>
+          <t>A 41756-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3087,14 +3092,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45205</v>
+        <v>45902</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3106,22 +3111,17 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3136,7 +3136,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3148,46 +3148,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 49384-2023 artfynd.xlsx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 41756-2025 artfynd.xlsx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 49384-2023 karta.png", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 41756-2025 karta.png", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 49384-2023 georefererad karta.tif", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 41756-2025 georefererad karta.tif", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 49384-2023 FSC-klagomål.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 41756-2025 FSC-klagomål.docx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 49384-2023 FSC-klagomål mail.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 41756-2025 FSC-klagomål mail.docx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 49384-2023 tillsynsbegäran.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 41756-2025 tillsynsbegäran.docx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 49384-2023 tillsynsbegäran mail.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 41756-2025 tillsynsbegäran mail.docx", "A 41756-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 41756-2025</t>
+          <t>A 45941-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3201,10 +3201,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45902</v>
+        <v>45924</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3217,17 +3217,17 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
@@ -3241,7 +3241,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3250,49 +3250,49 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 41756-2025 artfynd.xlsx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 45941-2025 artfynd.xlsx", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 41756-2025 karta.png", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 45941-2025 karta.png", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 41756-2025 georefererad karta.tif", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 45941-2025 georefererad karta.tif", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 41756-2025 FSC-klagomål.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 45941-2025 FSC-klagomål.docx", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 41756-2025 FSC-klagomål mail.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 45941-2025 FSC-klagomål mail.docx", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 41756-2025 tillsynsbegäran.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 45941-2025 tillsynsbegäran.docx", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 41756-2025 tillsynsbegäran mail.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 45941-2025 tillsynsbegäran mail.docx", "A 45941-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 45941-2025</t>
+          <t>A 30273-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45924</v>
+        <v>44759</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3322,16 +3322,16 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.2</v>
+        <v>12.5</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3346,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3362,42 +3362,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 45941-2025 artfynd.xlsx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 30273-2022 artfynd.xlsx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 45941-2025 karta.png", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 30273-2022 karta.png", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 45941-2025 georefererad karta.tif", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 30273-2022 georefererad karta.tif", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 45941-2025 FSC-klagomål.docx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 30273-2022 FSC-klagomål.docx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 45941-2025 FSC-klagomål mail.docx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 30273-2022 FSC-klagomål mail.docx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 45941-2025 tillsynsbegäran.docx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 30273-2022 tillsynsbegäran.docx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 45941-2025 tillsynsbegäran mail.docx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 30273-2022 tillsynsbegäran mail.docx", "A 30273-2022")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 38522-2024</t>
+          <t>A 11102-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3411,10 +3411,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45546</v>
+        <v>45371</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3426,26 +3426,21 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>5.3</v>
+        <v>2.8</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
@@ -3456,10 +3451,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3468,43 +3463,39 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 38522-2024 artfynd.xlsx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 11102-2024 artfynd.xlsx", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 38522-2024 karta.png", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 11102-2024 karta.png", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 38522-2024 georefererad karta.tif", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 11102-2024 georefererad karta.tif", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 38522-2024 FSC-klagomål.docx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 11102-2024 FSC-klagomål.docx", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 38522-2024 FSC-klagomål mail.docx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 11102-2024 FSC-klagomål mail.docx", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 38522-2024 tillsynsbegäran.docx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 11102-2024 tillsynsbegäran.docx", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 38522-2024 tillsynsbegäran mail.docx", "A 38522-2024")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 38522-2024 prioriterade fågelarter.docx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 11102-2024 tillsynsbegäran mail.docx", "A 11102-2024")</f>
         <v/>
       </c>
     </row>
@@ -3528,7 +3519,7 @@
         <v>45343</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3616,7 +3607,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 11102-2024</t>
+          <t>A 38522-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3630,10 +3621,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45371</v>
+        <v>45546</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3645,11 +3636,16 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -3658,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3670,10 +3666,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3682,39 +3678,43 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 11102-2024 artfynd.xlsx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 38522-2024 artfynd.xlsx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 11102-2024 karta.png", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 38522-2024 karta.png", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 11102-2024 georefererad karta.tif", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 38522-2024 georefererad karta.tif", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 11102-2024 FSC-klagomål.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 38522-2024 FSC-klagomål.docx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 11102-2024 FSC-klagomål mail.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 38522-2024 FSC-klagomål mail.docx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 11102-2024 tillsynsbegäran.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 38522-2024 tillsynsbegäran.docx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 11102-2024 tillsynsbegäran mail.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 38522-2024 tillsynsbegäran mail.docx", "A 38522-2024")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 38522-2024 prioriterade fågelarter.docx", "A 38522-2024")</f>
         <v/>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
         <v>46240</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44812</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44581</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>44875</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>44637</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>44685</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>44760</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>44720</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>44627</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>44476</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>44467</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>44803</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>44812</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 12234-2024</t>
+          <t>A 41420-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4721,10 +4721,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45378</v>
+        <v>44826</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4780,7 +4780,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 43767-2023</t>
+          <t>A 51569-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4794,10 +4794,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45187</v>
+        <v>44462</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4853,7 +4853,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 51569-2021</t>
+          <t>A 38059-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4867,10 +4867,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44462</v>
+        <v>44811</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.1</v>
+        <v>0.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4926,7 +4926,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 38059-2022</t>
+          <t>A 30284-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44811</v>
+        <v>44760</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>44565</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 30284-2022</t>
+          <t>A 30287-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5089,7 +5089,7 @@
         <v>44760</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 30287-2022</t>
+          <t>A 10726-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5159,10 +5159,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44760</v>
+        <v>44627</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5218,7 +5218,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 41420-2022</t>
+          <t>A 12234-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5232,10 +5232,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44826</v>
+        <v>45378</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5291,7 +5291,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 33991-2023</t>
+          <t>A 4881-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5305,10 +5305,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45134</v>
+        <v>45329</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5364,7 +5364,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 13887-2024</t>
+          <t>A 26443-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5378,10 +5378,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45391</v>
+        <v>45092</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>11.3</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5437,7 +5437,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 10726-2022</t>
+          <t>A 43770-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44627</v>
+        <v>45187</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5510,7 +5510,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 61284-2022</t>
+          <t>A 58750-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5524,10 +5524,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44915</v>
+        <v>44489</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5583,7 +5583,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 52431-2023</t>
+          <t>A 54681-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45225</v>
+        <v>44473</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5656,7 +5656,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 12784-2025</t>
+          <t>A 406-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45733</v>
+        <v>45296</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5729,7 +5729,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 41411-2022</t>
+          <t>A 7819-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5743,10 +5743,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44826</v>
+        <v>45706</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5802,7 +5802,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11104-2024</t>
+          <t>A 5740-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45371</v>
+        <v>45694</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 4225-2024</t>
+          <t>A 6384-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5889,10 +5889,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45324</v>
+        <v>45699</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5948,7 +5948,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 4227-2024</t>
+          <t>A 36984-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5962,10 +5962,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45324</v>
+        <v>45539</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6021,7 +6021,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 33993-2023</t>
+          <t>A 27222-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6035,10 +6035,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45134</v>
+        <v>45812</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6094,7 +6094,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 33996-2023</t>
+          <t>A 47511-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6108,10 +6108,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45134</v>
+        <v>45587</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6184,7 +6184,7 @@
         <v>45677</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 35423-2025</t>
+          <t>A 28515-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6254,10 +6254,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45855</v>
+        <v>45819</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6313,7 +6313,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 65619-2021</t>
+          <t>A 61435-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6327,10 +6327,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44516</v>
+        <v>45646</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6386,7 +6386,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 15351-2024</t>
+          <t>A 41759-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6400,10 +6400,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45400</v>
+        <v>45902</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6415,13 +6415,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6464,7 +6459,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 51488-2022</t>
+          <t>A 41758-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6478,10 +6473,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44869</v>
+        <v>45902</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6494,7 +6489,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6537,7 +6532,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 37508-2023</t>
+          <t>A 41760-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6551,10 +6546,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45158</v>
+        <v>45902</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6567,7 +6562,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>6.9</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6610,7 +6605,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 37509-2023</t>
+          <t>A 41761-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6624,10 +6619,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45158</v>
+        <v>45902</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6640,7 +6635,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>6.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6683,7 +6678,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 28910-2024</t>
+          <t>A 5612-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6697,10 +6692,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45480</v>
+        <v>45693</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6713,7 +6708,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6756,7 +6751,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 11604-2024</t>
+          <t>A 35422-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6770,10 +6765,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45373</v>
+        <v>45855</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6786,7 +6781,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6829,7 +6824,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 15567-2022</t>
+          <t>A 42857-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6843,10 +6838,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44662</v>
+        <v>45908</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6902,7 +6897,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 41758-2025</t>
+          <t>A 37063-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6916,10 +6911,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45902</v>
+        <v>45539</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6932,7 +6927,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6975,7 +6970,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 41760-2025</t>
+          <t>A 587-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6989,10 +6984,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45902</v>
+        <v>45664</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7005,7 +7000,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7048,7 +7043,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 41761-2025</t>
+          <t>A 44104-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7062,10 +7057,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45902</v>
+        <v>45915</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7078,7 +7073,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>6.6</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7121,7 +7116,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 41759-2025</t>
+          <t>A 43684-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7135,10 +7130,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45902</v>
+        <v>45912</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7151,7 +7146,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7194,7 +7189,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 1382-2024</t>
+          <t>A 12628-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7208,10 +7203,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45303</v>
+        <v>45000</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7224,7 +7219,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7267,7 +7262,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 14427-2026</t>
+          <t>A 44916-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7281,10 +7276,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46100</v>
+        <v>45918</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7297,7 +7292,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7340,7 +7335,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 35422-2025</t>
+          <t>A 44918-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7354,10 +7349,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45855</v>
+        <v>45918</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7370,7 +7365,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>5.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7413,7 +7408,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 42857-2025</t>
+          <t>A 44914-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7427,10 +7422,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45908</v>
+        <v>45918</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7443,7 +7438,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7486,7 +7481,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 587-2025</t>
+          <t>A 44915-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7500,10 +7495,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45664</v>
+        <v>45918</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7516,7 +7511,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7559,7 +7554,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 43684-2025</t>
+          <t>A 65619-2021</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7573,10 +7568,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45912</v>
+        <v>44516</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7589,7 +7584,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7632,7 +7627,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 44104-2025</t>
+          <t>A 35420-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7646,10 +7641,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45915</v>
+        <v>45855</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7662,7 +7657,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7705,7 +7700,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 44914-2025</t>
+          <t>A 35717-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7719,10 +7714,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45918</v>
+        <v>45860</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7735,7 +7730,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7778,7 +7773,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 44915-2025</t>
+          <t>A 57381-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7792,10 +7787,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45918</v>
+        <v>44896</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7808,7 +7803,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7851,7 +7846,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 44918-2025</t>
+          <t>A 48730-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7865,10 +7860,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45918</v>
+        <v>45936</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7881,7 +7876,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7924,7 +7919,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 44916-2025</t>
+          <t>A 41411-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7938,10 +7933,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45918</v>
+        <v>44826</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7954,7 +7949,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7997,7 +7992,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 7912-2024</t>
+          <t>A 48727-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8011,10 +8006,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45350</v>
+        <v>45936</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8027,7 +8022,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.1</v>
+        <v>6.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8070,7 +8065,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 17377-2026</t>
+          <t>A 12647-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8084,10 +8079,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46119</v>
+        <v>45000</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8100,7 +8095,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8143,7 +8138,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 6323-2023</t>
+          <t>A 49188-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8157,10 +8152,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44960</v>
+        <v>45938</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8172,13 +8167,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8221,7 +8211,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 54804-2022</t>
+          <t>A 13801-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8235,10 +8225,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44883</v>
+        <v>45737</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8251,7 +8241,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>22.6</v>
+        <v>2.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8294,7 +8284,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 57381-2022</t>
+          <t>A 8117-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8308,10 +8298,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44896</v>
+        <v>44974</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8324,7 +8314,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.7</v>
+        <v>11</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8367,7 +8357,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 48727-2025</t>
+          <t>A 12784-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8381,10 +8371,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45936</v>
+        <v>45733</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8397,7 +8387,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>6.1</v>
+        <v>1.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8440,7 +8430,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 18841-2026</t>
+          <t>A 35423-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8454,10 +8444,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46129</v>
+        <v>45855</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8470,7 +8460,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8513,7 +8503,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 48730-2025</t>
+          <t>A 55324-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8527,10 +8517,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45936</v>
+        <v>45971</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8542,8 +8532,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8586,7 +8581,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 13801-2025</t>
+          <t>A 56584-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8600,10 +8595,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45737</v>
+        <v>45974</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8616,7 +8611,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8659,7 +8654,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 49188-2025</t>
+          <t>A 50349-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8673,10 +8668,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45938</v>
+        <v>45600</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8732,7 +8727,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 8117-2023</t>
+          <t>A 7912-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8746,10 +8741,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44974</v>
+        <v>45350</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8762,7 +8757,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>11</v>
+        <v>1.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8805,7 +8800,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 12628-2023</t>
+          <t>A 15351-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8819,10 +8814,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45000</v>
+        <v>45400</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8834,8 +8829,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8878,7 +8878,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 19079-2025</t>
+          <t>A 13581-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8892,10 +8892,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45766</v>
+        <v>45006</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8907,8 +8907,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8951,7 +8956,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 50349-2024</t>
+          <t>A 8071-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8965,10 +8970,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45600</v>
+        <v>45351</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8981,7 +8986,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9024,7 +9029,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 28022-2023</t>
+          <t>A 13975-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9038,10 +9043,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45098</v>
+        <v>45008</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9054,7 +9059,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>5.7</v>
+        <v>2.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9097,7 +9102,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 48904-2024</t>
+          <t>A 16473-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9111,10 +9116,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45594</v>
+        <v>44671</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9127,7 +9132,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9170,7 +9175,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 55324-2025</t>
+          <t>A 6323-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9184,10 +9189,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45971</v>
+        <v>44960</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9201,11 +9206,11 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9248,7 +9253,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 28903-2024</t>
+          <t>A 40092-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9262,10 +9267,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45480</v>
+        <v>45554</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9278,7 +9283,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9321,7 +9326,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 61952-2024</t>
+          <t>A 14427-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9335,10 +9340,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45653</v>
+        <v>46100</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9351,7 +9356,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>4.2</v>
+        <v>1.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9394,7 +9399,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 61475-2025</t>
+          <t>A 57754-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9408,10 +9413,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46001</v>
+        <v>45246</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9424,7 +9429,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4.6</v>
+        <v>0.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9467,7 +9472,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 12647-2023</t>
+          <t>A 26886-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9481,10 +9486,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45000</v>
+        <v>45093</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9497,7 +9502,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9540,7 +9545,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 55972-2022</t>
+          <t>A 302-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9554,10 +9559,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44889</v>
+        <v>45295</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9569,8 +9574,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9613,7 +9623,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 13382-2023</t>
+          <t>A 17377-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9627,10 +9637,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45005</v>
+        <v>46119</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9643,7 +9653,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9686,7 +9696,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 38093-2022</t>
+          <t>A 18841-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9700,10 +9710,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44811</v>
+        <v>46129</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9716,7 +9726,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9759,7 +9769,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 5328-2025</t>
+          <t>A 29068-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9773,10 +9783,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45692</v>
+        <v>45481</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9789,7 +9799,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9832,7 +9842,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 61695-2025</t>
+          <t>A 4225-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9846,10 +9856,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46002</v>
+        <v>45324</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9862,7 +9872,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9905,7 +9915,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 16473-2022</t>
+          <t>A 4227-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9919,10 +9929,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44671</v>
+        <v>45324</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9935,7 +9945,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9978,7 +9988,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 22257-2026</t>
+          <t>A 38093-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9992,10 +10002,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46154</v>
+        <v>44811</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10051,7 +10061,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 23541-2026</t>
+          <t>A 5420-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10061,14 +10071,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46163</v>
+        <v>45692</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10081,7 +10091,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10124,7 +10134,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 40092-2024</t>
+          <t>A 51488-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10138,10 +10148,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45554</v>
+        <v>44869</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10154,7 +10164,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10197,7 +10207,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 57754-2023</t>
+          <t>A 6489-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10211,10 +10221,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45246</v>
+        <v>45699</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10227,7 +10237,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10270,7 +10280,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 14891-2025</t>
+          <t>A 9046-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10284,10 +10294,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45743</v>
+        <v>44615</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10300,7 +10310,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10343,7 +10353,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 24700-2026</t>
+          <t>A 19079-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10357,10 +10367,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46171</v>
+        <v>45766</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10372,13 +10382,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10421,7 +10426,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 26886-2023</t>
+          <t>A 61952-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10435,10 +10440,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45093</v>
+        <v>45653</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10451,7 +10456,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10494,7 +10499,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 26443-2023</t>
+          <t>A 28022-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10508,10 +10513,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45092</v>
+        <v>45098</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10524,7 +10529,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10567,7 +10572,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 17114-2023</t>
+          <t>A 55972-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10581,10 +10586,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45034</v>
+        <v>44889</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10597,7 +10602,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10640,7 +10645,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 58750-2021</t>
+          <t>A 28903-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10654,10 +10659,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44489</v>
+        <v>45480</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10670,7 +10675,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10713,7 +10718,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 7947-2024</t>
+          <t>A 61475-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10727,10 +10732,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45350</v>
+        <v>46001</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10743,7 +10748,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10786,7 +10791,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 25729-2026</t>
+          <t>A 61284-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10800,10 +10805,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46178</v>
+        <v>44915</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10816,7 +10821,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10859,7 +10864,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 56584-2025</t>
+          <t>A 12760-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10873,10 +10878,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45974</v>
+        <v>45001</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10889,7 +10894,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10932,7 +10937,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 27643-2026</t>
+          <t>A 62730-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10946,10 +10951,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46190</v>
+        <v>45268</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10962,7 +10967,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11005,7 +11010,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 13581-2023</t>
+          <t>A 11604-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11019,10 +11024,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45006</v>
+        <v>45373</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11034,13 +11039,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11083,7 +11083,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 54681-2021</t>
+          <t>A 48904-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11097,10 +11097,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44473</v>
+        <v>45594</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11156,7 +11156,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 44445-2023</t>
+          <t>A 5324-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11170,10 +11170,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45189</v>
+        <v>45692</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11229,7 +11229,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 17116-2023</t>
+          <t>A 61695-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11243,10 +11243,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45034</v>
+        <v>46002</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11302,7 +11302,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 12760-2023</t>
+          <t>A 54804-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11316,10 +11316,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45001</v>
+        <v>44883</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.1</v>
+        <v>22.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11375,7 +11375,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 32822-2026</t>
+          <t>A 52431-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11389,10 +11389,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46242</v>
+        <v>45225</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11448,7 +11448,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 5612-2025</t>
+          <t>A 22257-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11462,10 +11462,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45693</v>
+        <v>46154</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11521,7 +11521,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 47511-2024</t>
+          <t>A 33993-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11535,10 +11535,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45587</v>
+        <v>45134</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11594,7 +11594,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 43770-2023</t>
+          <t>A 33996-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11608,10 +11608,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45187</v>
+        <v>45134</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11624,7 +11624,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11667,7 +11667,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 4881-2024</t>
+          <t>A 23541-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11677,14 +11677,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45329</v>
+        <v>46163</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11740,7 +11740,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 302-2024</t>
+          <t>A 7947-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11754,10 +11754,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45295</v>
+        <v>45350</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11769,13 +11769,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11818,7 +11813,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 29068-2024</t>
+          <t>A 17116-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11832,10 +11827,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45481</v>
+        <v>45034</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11848,7 +11843,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11891,7 +11886,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 33842-2026</t>
+          <t>A 15567-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11905,10 +11900,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46251</v>
+        <v>44662</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11921,7 +11916,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>7.2</v>
+        <v>1.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11964,7 +11959,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 5324-2025</t>
+          <t>A 21630-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11978,10 +11973,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45692</v>
+        <v>45442</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11994,7 +11989,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12037,7 +12032,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 30605-2026</t>
+          <t>A 14891-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12051,10 +12046,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46210</v>
+        <v>45743</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12067,7 +12062,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>10.5</v>
+        <v>0.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12110,7 +12105,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 9046-2022</t>
+          <t>A 24700-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12124,10 +12119,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44615</v>
+        <v>46171</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12139,8 +12134,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12183,7 +12183,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 2438-2026</t>
+          <t>A 13382-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12197,10 +12197,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46036</v>
+        <v>45005</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12256,7 +12256,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 13631-2024</t>
+          <t>A 550-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12270,10 +12270,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45390</v>
+        <v>45299</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>16.4</v>
+        <v>2.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12329,7 +12329,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 61435-2024</t>
+          <t>A 25729-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12343,10 +12343,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45646</v>
+        <v>46178</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12402,7 +12402,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 37063-2024</t>
+          <t>A 27643-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12416,10 +12416,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45539</v>
+        <v>46190</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>8.800000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12475,7 +12475,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 15159-2023</t>
+          <t>A 13887-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12489,10 +12489,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45016</v>
+        <v>45391</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12504,13 +12504,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>0.9</v>
+        <v>11.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12553,7 +12548,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 550-2024</t>
+          <t>A 32822-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12567,10 +12562,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45299</v>
+        <v>46242</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12583,7 +12578,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12643,7 +12638,7 @@
         <v>45398</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12699,7 +12694,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 21630-2024</t>
+          <t>A 33842-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12713,10 +12708,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45442</v>
+        <v>46251</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12729,7 +12724,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12772,7 +12767,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 13975-2023</t>
+          <t>A 11104-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12786,10 +12781,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45008</v>
+        <v>45371</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12802,7 +12797,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12845,7 +12840,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 35883-2026</t>
+          <t>A 2438-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12859,10 +12854,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46266</v>
+        <v>46036</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12875,7 +12870,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>6.6</v>
+        <v>2.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12918,7 +12913,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 8071-2024</t>
+          <t>A 30605-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12932,10 +12927,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45351</v>
+        <v>46210</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12948,7 +12943,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.6</v>
+        <v>10.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12991,7 +12986,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 6489-2025</t>
+          <t>A 28910-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13005,10 +13000,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45699</v>
+        <v>45480</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13021,7 +13016,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13064,7 +13059,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 36773-2026</t>
+          <t>A 1382-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13078,10 +13073,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46272</v>
+        <v>45303</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13093,13 +13088,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13142,7 +13132,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 406-2024</t>
+          <t>A 17114-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13156,10 +13146,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45296</v>
+        <v>45034</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13172,7 +13162,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>4.8</v>
+        <v>1.2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13215,7 +13205,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 36722-2026</t>
+          <t>A 43767-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13229,10 +13219,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46272</v>
+        <v>45187</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13244,13 +13234,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13293,7 +13278,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 62730-2023</t>
+          <t>A 35883-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13307,10 +13292,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45268</v>
+        <v>46266</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13323,7 +13308,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>3.1</v>
+        <v>6.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13366,7 +13351,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 37037-2026</t>
+          <t>A 13631-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13380,10 +13365,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46273</v>
+        <v>45390</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13396,7 +13381,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>3.9</v>
+        <v>16.4</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13439,7 +13424,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 49879-2023</t>
+          <t>A 37508-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13453,10 +13438,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45213</v>
+        <v>45158</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13469,7 +13454,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>5</v>
+        <v>6.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13512,7 +13497,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 5420-2025</t>
+          <t>A 37509-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13526,10 +13511,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45692</v>
+        <v>45158</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13542,7 +13527,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13585,7 +13570,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 3867-2025</t>
+          <t>A 15159-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13599,10 +13584,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45684</v>
+        <v>45016</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13614,8 +13599,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13658,7 +13648,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 21617-2024</t>
+          <t>A 36722-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13672,10 +13662,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45441</v>
+        <v>46272</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13687,8 +13677,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>9.699999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13731,7 +13726,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 30724-2024</t>
+          <t>A 37037-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13741,14 +13736,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45496</v>
+        <v>46273</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13761,7 +13756,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13804,7 +13799,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 22561-2025</t>
+          <t>A 36773-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13818,10 +13813,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45789</v>
+        <v>46272</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13833,8 +13828,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13877,7 +13877,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 23509-2025</t>
+          <t>A 49879-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13891,10 +13891,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45792</v>
+        <v>45213</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.3</v>
+        <v>5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13950,7 +13950,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 23374-2025</t>
+          <t>A 44445-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13964,10 +13964,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45791</v>
+        <v>45189</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14023,7 +14023,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 12790-2025</t>
+          <t>A 33991-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14037,10 +14037,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45733</v>
+        <v>45134</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14096,7 +14096,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 12243-2025</t>
+          <t>A 5328-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14110,10 +14110,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45729</v>
+        <v>45692</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>10.2</v>
+        <v>1.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14169,7 +14169,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 24053-2025</t>
+          <t>A 3867-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14179,14 +14179,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45796</v>
+        <v>45684</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>11.1</v>
+        <v>1.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14242,7 +14242,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 5743-2025</t>
+          <t>A 21617-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14256,10 +14256,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45694</v>
+        <v>45441</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14315,7 +14315,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 7819-2025</t>
+          <t>A 22561-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14329,10 +14329,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45706</v>
+        <v>45789</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>5.6</v>
+        <v>2.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14388,7 +14388,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 5740-2025</t>
+          <t>A 12790-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14402,10 +14402,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45694</v>
+        <v>45733</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14461,7 +14461,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 6384-2025</t>
+          <t>A 12243-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14475,10 +14475,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45699</v>
+        <v>45729</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2</v>
+        <v>10.2</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14534,7 +14534,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 36984-2024</t>
+          <t>A 30724-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14544,14 +14544,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45539</v>
+        <v>45496</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14607,7 +14607,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 27222-2025</t>
+          <t>A 23374-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14621,10 +14621,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45812</v>
+        <v>45791</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14680,7 +14680,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 28515-2025</t>
+          <t>A 23509-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14694,10 +14694,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45819</v>
+        <v>45792</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14753,7 +14753,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 35420-2025</t>
+          <t>A 5743-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14767,10 +14767,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45855</v>
+        <v>45694</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14826,7 +14826,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 35717-2025</t>
+          <t>A 24053-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14836,14 +14836,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45860</v>
+        <v>45796</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14856,7 +14856,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.6</v>
+        <v>11.1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14916,7 +14916,7 @@
         <v>44964</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>

--- a/Översikt LILLA EDET.xlsx
+++ b/Översikt LILLA EDET.xlsx
@@ -601,7 +601,7 @@
         <v>46169</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45295</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 318-2024</t>
+          <t>A 30285-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45295</v>
+        <v>45827</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,19 +856,14 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I4" t="n">
-        <v>8.1</v>
+        <v>29.6</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -895,12 +890,133 @@
         <v>8</v>
       </c>
       <c r="T4" t="n">
+        <v>38</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp
+Blåmossa
+Klippfrullania
+Stor revmossa
+Västlig hakmossa
+Mattlummer
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 30285-2025 artfynd.xlsx", "A 30285-2025")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 30285-2025 karta.png", "A 30285-2025")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 30285-2025 georefererad karta.tif", "A 30285-2025")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 30285-2025 FSC-klagomål.docx", "A 30285-2025")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 30285-2025 FSC-klagomål mail.docx", "A 30285-2025")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 30285-2025 tillsynsbegäran.docx", "A 30285-2025")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 30285-2025 tillsynsbegäran mail.docx", "A 30285-2025")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 30285-2025 prioriterade fågelarter.docx", "A 30285-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 318-2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45295</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>8</v>
+      </c>
+      <c r="T5" t="n">
         <v>17</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>17</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Kattfotslav
 Blåmossa
@@ -912,227 +1028,226 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 318-2024 artfynd.xlsx", "A 318-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 318-2024 karta.png", "A 318-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 318-2024 georefererad karta.tif", "A 318-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 318-2024 FSC-klagomål.docx", "A 318-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 318-2024 FSC-klagomål mail.docx", "A 318-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 318-2024 tillsynsbegäran.docx", "A 318-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 318-2024 tillsynsbegäran mail.docx", "A 318-2024")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 318-2024 prioriterade fågelarter.docx", "A 318-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 30285-2025</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45827</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>8</v>
-      </c>
-      <c r="T5" t="n">
-        <v>38</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Dofttaggsvamp
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 34396-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45139</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>7</v>
+      </c>
+      <c r="T6" t="n">
+        <v>24</v>
+      </c>
+      <c r="U6" t="n">
+        <v>24</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
 Blåmossa
-Klippfrullania
+Kambräken
 Stor revmossa
 Västlig hakmossa
-Mattlummer
 Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 30285-2025 artfynd.xlsx", "A 30285-2025")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 30285-2025 karta.png", "A 30285-2025")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 30285-2025 georefererad karta.tif", "A 30285-2025")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 30285-2025 FSC-klagomål.docx", "A 30285-2025")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 30285-2025 FSC-klagomål mail.docx", "A 30285-2025")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 30285-2025 tillsynsbegäran.docx", "A 30285-2025")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 30285-2025 tillsynsbegäran mail.docx", "A 30285-2025")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 30285-2025 prioriterade fågelarter.docx", "A 30285-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 34396-2023 artfynd.xlsx", "A 34396-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 34396-2023 karta.png", "A 34396-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 34396-2023 georefererad karta.tif", "A 34396-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 34396-2023 FSC-klagomål.docx", "A 34396-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 34396-2023 FSC-klagomål mail.docx", "A 34396-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 34396-2023 tillsynsbegäran.docx", "A 34396-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 34396-2023 tillsynsbegäran mail.docx", "A 34396-2023")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 34396-2023 prioriterade fågelarter.docx", "A 34396-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>A 62846-2023</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
         <v>45272</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
+      <c r="E7" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>3.4</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J7" t="n">
         <v>2</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K7" t="n">
         <v>4</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T7" t="n">
         <v>17</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Kattfotslav
 Blåmossa
@@ -1143,147 +1258,32 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 62846-2023 artfynd.xlsx", "A 62846-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 62846-2023 karta.png", "A 62846-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 62846-2023 georefererad karta.tif", "A 62846-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 62846-2023 FSC-klagomål.docx", "A 62846-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 62846-2023 FSC-klagomål mail.docx", "A 62846-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 62846-2023 tillsynsbegäran.docx", "A 62846-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 62846-2023 tillsynsbegäran mail.docx", "A 62846-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 34396-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45139</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>5</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>7</v>
-      </c>
-      <c r="T7" t="n">
-        <v>24</v>
-      </c>
-      <c r="U7" t="n">
-        <v>24</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Blåmossa
-Kambräken
-Stor revmossa
-Västlig hakmossa
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 34396-2023 artfynd.xlsx", "A 34396-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 34396-2023 karta.png", "A 34396-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 34396-2023 georefererad karta.tif", "A 34396-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 34396-2023 FSC-klagomål.docx", "A 34396-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 34396-2023 FSC-klagomål mail.docx", "A 34396-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 34396-2023 tillsynsbegäran.docx", "A 34396-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 34396-2023 tillsynsbegäran mail.docx", "A 34396-2023")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 34396-2023 prioriterade fågelarter.docx", "A 34396-2023")</f>
         <v/>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
         <v>46044</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25298-2024</t>
+          <t>A 28512-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45462</v>
+        <v>45819</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1432,13 +1432,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>5.9</v>
+        <v>10.9</v>
       </c>
       <c r="J9" t="n">
         <v>2</v>
@@ -1471,12 +1466,354 @@
         <v>4</v>
       </c>
       <c r="T9" t="n">
+        <v>19</v>
+      </c>
+      <c r="U9" t="n">
+        <v>19</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Västlig hakmossa
+Spillkråka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 28512-2025 artfynd.xlsx", "A 28512-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 28512-2025 karta.png", "A 28512-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 28512-2025 georefererad karta.tif", "A 28512-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 28512-2025 FSC-klagomål.docx", "A 28512-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 28512-2025 FSC-klagomål mail.docx", "A 28512-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 28512-2025 tillsynsbegäran.docx", "A 28512-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 28512-2025 tillsynsbegäran mail.docx", "A 28512-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 28512-2025 prioriterade fågelarter.docx", "A 28512-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 24290-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46169</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="n">
         <v>5</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>5</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Blanksvart trämyra
+Grönpyrola
+Västlig hakmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 24290-2026 artfynd.xlsx", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 24290-2026 karta.png", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 24290-2026 georefererad karta.tif", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 24290-2026 FSC-klagomål.docx", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 24290-2026 FSC-klagomål mail.docx", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 24290-2026 tillsynsbegäran.docx", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 24290-2026 tillsynsbegäran mail.docx", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 24290-2026 prioriterade fågelarter.docx", "A 24290-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 23563-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45072</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7</v>
+      </c>
+      <c r="U11" t="n">
+        <v>7</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Nordfladdermus
+Dvärgpipistrell
+Vattenfladdermus
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23563-2023 artfynd.xlsx", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23563-2023 karta.png", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23563-2023 georefererad karta.tif", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23563-2023 FSC-klagomål.docx", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23563-2023 FSC-klagomål mail.docx", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23563-2023 tillsynsbegäran.docx", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23563-2023 tillsynsbegäran mail.docx", "A 23563-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 25298-2024</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45462</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Västlig hakmossa
@@ -1484,111 +1821,111 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 25298-2024 artfynd.xlsx", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 25298-2024 karta.png", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 25298-2024 georefererad karta.tif", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 25298-2024 FSC-klagomål.docx", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 25298-2024 FSC-klagomål mail.docx", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 25298-2024 tillsynsbegäran.docx", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 25298-2024 tillsynsbegäran mail.docx", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 25298-2024 prioriterade fågelarter.docx", "A 25298-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 43771-2023</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>45187</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E13" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>1.7</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K13" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>1</v>
       </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>2</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R13" t="n">
         <v>1</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S13" t="n">
         <v>4</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T13" t="n">
         <v>4</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Ask
 Slåtterfibbla
@@ -1596,376 +1933,39 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 43771-2023 artfynd.xlsx", "A 43771-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 43771-2023 karta.png", "A 43771-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 43771-2023 georefererad karta.tif", "A 43771-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 43771-2023 FSC-klagomål.docx", "A 43771-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 43771-2023 FSC-klagomål mail.docx", "A 43771-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 43771-2023 tillsynsbegäran.docx", "A 43771-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 43771-2023 tillsynsbegäran mail.docx", "A 43771-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 28512-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45819</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>19</v>
-      </c>
-      <c r="U11" t="n">
-        <v>19</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa
-Västlig hakmossa
-Spillkråka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 28512-2025 artfynd.xlsx", "A 28512-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 28512-2025 karta.png", "A 28512-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 28512-2025 georefererad karta.tif", "A 28512-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 28512-2025 FSC-klagomål.docx", "A 28512-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 28512-2025 FSC-klagomål mail.docx", "A 28512-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 28512-2025 tillsynsbegäran.docx", "A 28512-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 28512-2025 tillsynsbegäran mail.docx", "A 28512-2025")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 28512-2025 prioriterade fågelarter.docx", "A 28512-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 23563-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45072</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>7</v>
-      </c>
-      <c r="U12" t="n">
-        <v>7</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Nordfladdermus
-Dvärgpipistrell
-Vattenfladdermus
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23563-2023 artfynd.xlsx", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23563-2023 karta.png", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23563-2023 georefererad karta.tif", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23563-2023 FSC-klagomål.docx", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23563-2023 FSC-klagomål mail.docx", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23563-2023 tillsynsbegäran.docx", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23563-2023 tillsynsbegäran mail.docx", "A 23563-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 24290-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46169</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>5</v>
-      </c>
-      <c r="U13" t="n">
-        <v>5</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Blanksvart trämyra
-Grönpyrola
-Västlig hakmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 24290-2026 artfynd.xlsx", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 24290-2026 karta.png", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 24290-2026 georefererad karta.tif", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 24290-2026 FSC-klagomål.docx", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 24290-2026 FSC-klagomål mail.docx", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 24290-2026 tillsynsbegäran.docx", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 24290-2026 tillsynsbegäran mail.docx", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 24290-2026 prioriterade fågelarter.docx", "A 24290-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 25655-2023</t>
+          <t>A 17376-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45089</v>
+        <v>46119</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.1</v>
+        <v>2.5</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
         <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2019,271 +2019,271 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
       </c>
       <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Slåttergubbe
+Almsnabbvinge
+Granspira</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 17376-2026 artfynd.xlsx", "A 17376-2026")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 17376-2026 karta.png", "A 17376-2026")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 17376-2026 georefererad karta.tif", "A 17376-2026")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 17376-2026 FSC-klagomål.docx", "A 17376-2026")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 17376-2026 FSC-klagomål mail.docx", "A 17376-2026")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 17376-2026 tillsynsbegäran.docx", "A 17376-2026")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 17376-2026 tillsynsbegäran mail.docx", "A 17376-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 28021-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45098</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Stor revmossa
+Nattskärra
+Törnskata</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 28021-2023 artfynd.xlsx", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 28021-2023 karta.png", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 28021-2023 georefererad karta.tif", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 28021-2023 FSC-klagomål.docx", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 28021-2023 FSC-klagomål mail.docx", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 28021-2023 tillsynsbegäran.docx", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 28021-2023 tillsynsbegäran mail.docx", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 28021-2023 prioriterade fågelarter.docx", "A 28021-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 25655-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45089</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
         <v>9</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U16" t="n">
         <v>7</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Bergjohannesört
 Svinrot
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 25655-2023 artfynd.xlsx", "A 25655-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 25655-2023 karta.png", "A 25655-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 25655-2023 georefererad karta.tif", "A 25655-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 25655-2023 FSC-klagomål.docx", "A 25655-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 25655-2023 FSC-klagomål mail.docx", "A 25655-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 25655-2023 tillsynsbegäran.docx", "A 25655-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 25655-2023 tillsynsbegäran mail.docx", "A 25655-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 17376-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46119</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Slåttergubbe
-Almsnabbvinge
-Granspira</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 17376-2026 artfynd.xlsx", "A 17376-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 17376-2026 karta.png", "A 17376-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 17376-2026 georefererad karta.tif", "A 17376-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 17376-2026 FSC-klagomål.docx", "A 17376-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 17376-2026 FSC-klagomål mail.docx", "A 17376-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 17376-2026 tillsynsbegäran.docx", "A 17376-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 17376-2026 tillsynsbegäran mail.docx", "A 17376-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 28021-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45098</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Stor revmossa
-Nattskärra
-Törnskata</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 28021-2023 artfynd.xlsx", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 28021-2023 karta.png", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 28021-2023 georefererad karta.tif", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 28021-2023 FSC-klagomål.docx", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 28021-2023 FSC-klagomål mail.docx", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 28021-2023 tillsynsbegäran.docx", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 28021-2023 tillsynsbegäran mail.docx", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 28021-2023 prioriterade fågelarter.docx", "A 28021-2023")</f>
         <v/>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
         <v>45072</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 5866-2026</t>
+          <t>A 23497-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46052</v>
+        <v>45072</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,17 +2437,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2474,169 +2474,169 @@
         <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Stor revmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23497-2023 artfynd.xlsx", "A 23497-2023")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23497-2023 karta.png", "A 23497-2023")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23497-2023 georefererad karta.tif", "A 23497-2023")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23497-2023 FSC-klagomål.docx", "A 23497-2023")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23497-2023 FSC-klagomål mail.docx", "A 23497-2023")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23497-2023 tillsynsbegäran.docx", "A 23497-2023")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23497-2023 tillsynsbegäran mail.docx", "A 23497-2023")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 23497-2023 prioriterade fågelarter.docx", "A 23497-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 23494-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45072</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 5866-2026 artfynd.xlsx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 5866-2026 karta.png", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 5866-2026 georefererad karta.tif", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 5866-2026 FSC-klagomål.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 5866-2026 FSC-klagomål mail.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 5866-2026 tillsynsbegäran.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 5866-2026 tillsynsbegäran mail.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 5866-2026 prioriterade fågelarter.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 23497-2023</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45072</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>3</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Stor revmossa
-Spillkråka</t>
-        </is>
-      </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23497-2023 artfynd.xlsx", "A 23497-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23494-2023 artfynd.xlsx", "A 23494-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23497-2023 karta.png", "A 23497-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23494-2023 karta.png", "A 23494-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23497-2023 georefererad karta.tif", "A 23497-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23494-2023 georefererad karta.tif", "A 23494-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23497-2023 FSC-klagomål.docx", "A 23497-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23494-2023 FSC-klagomål.docx", "A 23494-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23497-2023 FSC-klagomål mail.docx", "A 23497-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23494-2023 FSC-klagomål mail.docx", "A 23494-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23497-2023 tillsynsbegäran.docx", "A 23497-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23494-2023 tillsynsbegäran.docx", "A 23494-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23497-2023 tillsynsbegäran mail.docx", "A 23497-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23494-2023 tillsynsbegäran mail.docx", "A 23494-2023")</f>
         <v/>
       </c>
       <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 23497-2023 prioriterade fågelarter.docx", "A 23497-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 23494-2023 prioriterade fågelarter.docx", "A 23494-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 23494-2023</t>
+          <t>A 13699-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45072</v>
+        <v>45390</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2665,19 +2665,14 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>6.6</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2704,275 +2699,280 @@
         <v>2</v>
       </c>
       <c r="T20" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 13699-2024 artfynd.xlsx", "A 13699-2024")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 13699-2024 karta.png", "A 13699-2024")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 13699-2024 georefererad karta.tif", "A 13699-2024")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 13699-2024 FSC-klagomål.docx", "A 13699-2024")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 13699-2024 FSC-klagomål mail.docx", "A 13699-2024")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 13699-2024 tillsynsbegäran.docx", "A 13699-2024")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 13699-2024 tillsynsbegäran mail.docx", "A 13699-2024")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 13699-2024 prioriterade fågelarter.docx", "A 13699-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 32690-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Skirmossa
+Dunmossa</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 32690-2026 artfynd.xlsx", "A 32690-2026")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 32690-2026 karta.png", "A 32690-2026")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 32690-2026 georefererad karta.tif", "A 32690-2026")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 32690-2026 FSC-klagomål.docx", "A 32690-2026")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 32690-2026 FSC-klagomål mail.docx", "A 32690-2026")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 32690-2026 tillsynsbegäran.docx", "A 32690-2026")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 32690-2026 tillsynsbegäran mail.docx", "A 32690-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 5866-2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>9</v>
+      </c>
+      <c r="U22" t="n">
+        <v>9</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23494-2023 artfynd.xlsx", "A 23494-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23494-2023 karta.png", "A 23494-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23494-2023 georefererad karta.tif", "A 23494-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23494-2023 FSC-klagomål.docx", "A 23494-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23494-2023 FSC-klagomål mail.docx", "A 23494-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23494-2023 tillsynsbegäran.docx", "A 23494-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23494-2023 tillsynsbegäran mail.docx", "A 23494-2023")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 23494-2023 prioriterade fågelarter.docx", "A 23494-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 13699-2024</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45390</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>7</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Västlig hakmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 13699-2024 artfynd.xlsx", "A 13699-2024")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 13699-2024 karta.png", "A 13699-2024")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 13699-2024 georefererad karta.tif", "A 13699-2024")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 13699-2024 FSC-klagomål.docx", "A 13699-2024")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 13699-2024 FSC-klagomål mail.docx", "A 13699-2024")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 13699-2024 tillsynsbegäran.docx", "A 13699-2024")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 13699-2024 tillsynsbegäran mail.docx", "A 13699-2024")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 13699-2024 prioriterade fågelarter.docx", "A 13699-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 32690-2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>46240</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Skirmossa
-Dunmossa</t>
-        </is>
-      </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 32690-2026 artfynd.xlsx", "A 32690-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 5866-2026 artfynd.xlsx", "A 5866-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 32690-2026 karta.png", "A 32690-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 5866-2026 karta.png", "A 5866-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 32690-2026 georefererad karta.tif", "A 32690-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 5866-2026 georefererad karta.tif", "A 5866-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 32690-2026 FSC-klagomål.docx", "A 32690-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 5866-2026 FSC-klagomål.docx", "A 5866-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 32690-2026 FSC-klagomål mail.docx", "A 32690-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 5866-2026 FSC-klagomål mail.docx", "A 5866-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 32690-2026 tillsynsbegäran.docx", "A 32690-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 5866-2026 tillsynsbegäran.docx", "A 5866-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 32690-2026 tillsynsbegäran mail.docx", "A 32690-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 5866-2026 tillsynsbegäran mail.docx", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 5866-2026 prioriterade fågelarter.docx", "A 5866-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 49384-2023</t>
+          <t>A 30273-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2982,14 +2982,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45205</v>
+        <v>44759</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3001,22 +3001,17 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>1.2</v>
+        <v>12.5</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -3031,7 +3026,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3040,49 +3035,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 49384-2023 artfynd.xlsx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 30273-2022 artfynd.xlsx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 49384-2023 karta.png", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 30273-2022 karta.png", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 49384-2023 georefererad karta.tif", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 30273-2022 georefererad karta.tif", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 49384-2023 FSC-klagomål.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 30273-2022 FSC-klagomål.docx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 49384-2023 FSC-klagomål mail.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 30273-2022 FSC-klagomål mail.docx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 49384-2023 tillsynsbegäran.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 30273-2022 tillsynsbegäran.docx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 49384-2023 tillsynsbegäran mail.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 30273-2022 tillsynsbegäran mail.docx", "A 30273-2022")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 41756-2025</t>
+          <t>A 49384-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3092,14 +3087,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45902</v>
+        <v>45205</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3111,18 +3106,23 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
@@ -3136,7 +3136,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3148,46 +3148,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 41756-2025 artfynd.xlsx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 49384-2023 artfynd.xlsx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 41756-2025 karta.png", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 49384-2023 karta.png", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 41756-2025 georefererad karta.tif", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 49384-2023 georefererad karta.tif", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 41756-2025 FSC-klagomål.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 49384-2023 FSC-klagomål.docx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 41756-2025 FSC-klagomål mail.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 49384-2023 FSC-klagomål mail.docx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 41756-2025 tillsynsbegäran.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 49384-2023 tillsynsbegäran.docx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 41756-2025 tillsynsbegäran mail.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 49384-2023 tillsynsbegäran mail.docx", "A 49384-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 45941-2025</t>
+          <t>A 41756-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3201,10 +3201,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45924</v>
+        <v>45902</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3217,16 +3217,16 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3250,49 +3250,49 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 45941-2025 artfynd.xlsx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 41756-2025 artfynd.xlsx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 45941-2025 karta.png", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 41756-2025 karta.png", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 45941-2025 georefererad karta.tif", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 41756-2025 georefererad karta.tif", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 45941-2025 FSC-klagomål.docx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 41756-2025 FSC-klagomål.docx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 45941-2025 FSC-klagomål mail.docx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 41756-2025 FSC-klagomål mail.docx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 45941-2025 tillsynsbegäran.docx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 41756-2025 tillsynsbegäran.docx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 45941-2025 tillsynsbegäran mail.docx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 41756-2025 tillsynsbegäran mail.docx", "A 41756-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 30273-2022</t>
+          <t>A 38522-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44759</v>
+        <v>45546</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3321,8 +3321,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>12.5</v>
+        <v>5.3</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3355,49 +3360,53 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 30273-2022 artfynd.xlsx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 38522-2024 artfynd.xlsx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 30273-2022 karta.png", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 38522-2024 karta.png", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 30273-2022 georefererad karta.tif", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 38522-2024 georefererad karta.tif", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 30273-2022 FSC-klagomål.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 38522-2024 FSC-klagomål.docx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 30273-2022 FSC-klagomål mail.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 38522-2024 FSC-klagomål mail.docx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 30273-2022 tillsynsbegäran.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 38522-2024 tillsynsbegäran.docx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 30273-2022 tillsynsbegäran mail.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 38522-2024 tillsynsbegäran mail.docx", "A 38522-2024")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 38522-2024 prioriterade fågelarter.docx", "A 38522-2024")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 11102-2024</t>
+          <t>A 45941-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3411,10 +3420,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45371</v>
+        <v>45924</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3427,7 +3436,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3436,10 +3445,10 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3454,48 +3463,48 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 11102-2024 artfynd.xlsx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 45941-2025 artfynd.xlsx", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 11102-2024 karta.png", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 45941-2025 karta.png", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 11102-2024 georefererad karta.tif", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 45941-2025 georefererad karta.tif", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 11102-2024 FSC-klagomål.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 45941-2025 FSC-klagomål.docx", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 11102-2024 FSC-klagomål mail.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 45941-2025 FSC-klagomål mail.docx", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 11102-2024 tillsynsbegäran.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 45941-2025 tillsynsbegäran.docx", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 11102-2024 tillsynsbegäran mail.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 45941-2025 tillsynsbegäran mail.docx", "A 45941-2025")</f>
         <v/>
       </c>
     </row>
@@ -3519,7 +3528,7 @@
         <v>45343</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3607,7 +3616,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 38522-2024</t>
+          <t>A 11102-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3621,10 +3630,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45546</v>
+        <v>45371</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3636,26 +3645,21 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>5.3</v>
+        <v>2.8</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
@@ -3666,10 +3670,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3678,43 +3682,39 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 38522-2024 artfynd.xlsx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 11102-2024 artfynd.xlsx", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 38522-2024 karta.png", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 11102-2024 karta.png", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 38522-2024 georefererad karta.tif", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 11102-2024 georefererad karta.tif", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 38522-2024 FSC-klagomål.docx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 11102-2024 FSC-klagomål.docx", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 38522-2024 FSC-klagomål mail.docx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 11102-2024 FSC-klagomål mail.docx", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 38522-2024 tillsynsbegäran.docx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 11102-2024 tillsynsbegäran.docx", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 38522-2024 tillsynsbegäran mail.docx", "A 38522-2024")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 38522-2024 prioriterade fågelarter.docx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 11102-2024 tillsynsbegäran mail.docx", "A 11102-2024")</f>
         <v/>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
         <v>46240</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44812</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44581</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>44875</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>44637</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>44685</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>44760</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>44720</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>44627</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>44476</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>44467</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>44803</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>44812</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>44826</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>44462</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>44811</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 30284-2022</t>
+          <t>A 296-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44760</v>
+        <v>44565</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4999,7 +4999,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 296-2022</t>
+          <t>A 30284-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44565</v>
+        <v>44760</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5089,7 +5089,7 @@
         <v>44760</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>44627</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>45378</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 4881-2024</t>
+          <t>A 13887-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5305,10 +5305,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45329</v>
+        <v>45391</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.5</v>
+        <v>11.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5364,7 +5364,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 26443-2023</t>
+          <t>A 61284-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5378,10 +5378,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45092</v>
+        <v>44915</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5437,7 +5437,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 43770-2023</t>
+          <t>A 52431-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45187</v>
+        <v>45225</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5510,7 +5510,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 58750-2021</t>
+          <t>A 11104-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5524,10 +5524,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44489</v>
+        <v>45371</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5583,7 +5583,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 54681-2021</t>
+          <t>A 65619-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44473</v>
+        <v>44516</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5656,7 +5656,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 406-2024</t>
+          <t>A 51488-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45296</v>
+        <v>44869</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.8</v>
+        <v>2.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5729,7 +5729,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 7819-2025</t>
+          <t>A 28910-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5743,10 +5743,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45706</v>
+        <v>45480</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>5.6</v>
+        <v>1.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5802,7 +5802,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 5740-2025</t>
+          <t>A 11604-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45694</v>
+        <v>45373</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 6384-2025</t>
+          <t>A 1382-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5889,10 +5889,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45699</v>
+        <v>45303</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5948,7 +5948,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 36984-2024</t>
+          <t>A 33993-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5962,10 +5962,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45539</v>
+        <v>45134</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6021,7 +6021,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 27222-2025</t>
+          <t>A 33996-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6035,10 +6035,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45812</v>
+        <v>45134</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6094,7 +6094,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 47511-2024</t>
+          <t>A 587-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6108,10 +6108,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45587</v>
+        <v>45664</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6167,7 +6167,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 2867-2025</t>
+          <t>A 15567-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6181,10 +6181,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45677</v>
+        <v>44662</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>10.7</v>
+        <v>1.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6240,7 +6240,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 28515-2025</t>
+          <t>A 7912-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6254,10 +6254,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45819</v>
+        <v>45350</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6313,7 +6313,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 61435-2024</t>
+          <t>A 6323-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6327,10 +6327,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45646</v>
+        <v>44960</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6342,8 +6342,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6386,7 +6391,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 41759-2025</t>
+          <t>A 54804-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6400,10 +6405,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45902</v>
+        <v>44883</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6416,7 +6421,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>22.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6459,7 +6464,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 41758-2025</t>
+          <t>A 12784-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6473,10 +6478,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45902</v>
+        <v>45733</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6489,7 +6494,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6532,7 +6537,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 41760-2025</t>
+          <t>A 28515-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6546,10 +6551,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45902</v>
+        <v>45819</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6562,7 +6567,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6605,7 +6610,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 41761-2025</t>
+          <t>A 2867-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6619,10 +6624,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45902</v>
+        <v>45677</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6635,7 +6640,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>6.6</v>
+        <v>10.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6678,7 +6683,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 5612-2025</t>
+          <t>A 56584-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6692,10 +6697,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45693</v>
+        <v>45974</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6708,7 +6713,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6751,7 +6756,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 35422-2025</t>
+          <t>A 35423-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6768,7 +6773,7 @@
         <v>45855</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6781,7 +6786,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6824,7 +6829,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 42857-2025</t>
+          <t>A 8117-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6838,10 +6843,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45908</v>
+        <v>44974</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6854,7 +6859,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.6</v>
+        <v>11</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6897,7 +6902,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 37063-2024</t>
+          <t>A 15351-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6911,10 +6916,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45539</v>
+        <v>45400</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6926,8 +6931,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>8.800000000000001</v>
+        <v>3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6970,7 +6980,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 587-2025</t>
+          <t>A 12628-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6984,10 +6994,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45664</v>
+        <v>45000</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7000,7 +7010,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7043,7 +7053,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 44104-2025</t>
+          <t>A 50349-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7057,10 +7067,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45915</v>
+        <v>45600</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7073,7 +7083,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7116,7 +7126,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 43684-2025</t>
+          <t>A 14427-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7130,10 +7140,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45912</v>
+        <v>46100</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7146,7 +7156,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7189,7 +7199,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 12628-2023</t>
+          <t>A 35420-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7203,10 +7213,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45000</v>
+        <v>45855</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7219,7 +7229,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7262,7 +7272,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 44916-2025</t>
+          <t>A 35717-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7276,10 +7286,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45918</v>
+        <v>45860</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7292,7 +7302,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7335,7 +7345,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 44918-2025</t>
+          <t>A 28903-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7349,10 +7359,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45918</v>
+        <v>45480</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7365,7 +7375,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7408,7 +7418,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 44914-2025</t>
+          <t>A 12647-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7422,10 +7432,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45918</v>
+        <v>45000</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7438,7 +7448,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7481,7 +7491,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 44915-2025</t>
+          <t>A 17377-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7495,10 +7505,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45918</v>
+        <v>46119</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7511,7 +7521,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7554,7 +7564,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 65619-2021</t>
+          <t>A 18841-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7568,10 +7578,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44516</v>
+        <v>46129</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7584,7 +7594,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7627,7 +7637,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 35420-2025</t>
+          <t>A 41758-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7641,10 +7651,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45855</v>
+        <v>45902</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7657,7 +7667,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7700,7 +7710,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 35717-2025</t>
+          <t>A 41760-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7714,10 +7724,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45860</v>
+        <v>45902</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7730,7 +7740,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7773,7 +7783,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 57381-2022</t>
+          <t>A 41761-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7787,10 +7797,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44896</v>
+        <v>45902</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7803,7 +7813,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.7</v>
+        <v>6.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7846,7 +7856,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 48730-2025</t>
+          <t>A 41759-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7860,10 +7870,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45936</v>
+        <v>45902</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7876,7 +7886,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7919,7 +7929,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 41411-2022</t>
+          <t>A 5328-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7933,10 +7943,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44826</v>
+        <v>45692</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7949,7 +7959,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7992,7 +8002,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 48727-2025</t>
+          <t>A 35422-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8006,10 +8016,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45936</v>
+        <v>45855</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8022,7 +8032,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>6.1</v>
+        <v>1.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8065,7 +8075,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 12647-2023</t>
+          <t>A 42857-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8079,10 +8089,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45000</v>
+        <v>45908</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8095,7 +8105,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8138,7 +8148,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 49188-2025</t>
+          <t>A 43684-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8152,10 +8162,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45938</v>
+        <v>45912</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8168,7 +8178,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8211,7 +8221,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 13801-2025</t>
+          <t>A 44104-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8225,10 +8235,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45737</v>
+        <v>45915</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8241,7 +8251,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8284,7 +8294,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 8117-2023</t>
+          <t>A 44914-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8298,10 +8308,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44974</v>
+        <v>45918</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8314,7 +8324,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8357,7 +8367,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 12784-2025</t>
+          <t>A 44915-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8371,10 +8381,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45733</v>
+        <v>45918</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8430,7 +8440,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 35423-2025</t>
+          <t>A 44918-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8444,10 +8454,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45855</v>
+        <v>45918</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8460,7 +8470,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8503,7 +8513,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 55324-2025</t>
+          <t>A 19079-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8517,10 +8527,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45971</v>
+        <v>45766</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8532,13 +8542,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8581,7 +8586,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 56584-2025</t>
+          <t>A 44916-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8595,10 +8600,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45974</v>
+        <v>45918</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8611,7 +8616,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8654,7 +8659,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 50349-2024</t>
+          <t>A 28022-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8668,10 +8673,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45600</v>
+        <v>45098</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8684,7 +8689,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.7</v>
+        <v>5.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8727,7 +8732,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 7912-2024</t>
+          <t>A 48904-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8741,10 +8746,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45350</v>
+        <v>45594</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8757,7 +8762,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8800,7 +8805,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 15351-2024</t>
+          <t>A 61952-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8814,10 +8819,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45400</v>
+        <v>45653</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8829,13 +8834,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8878,7 +8878,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 13581-2023</t>
+          <t>A 61475-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8892,10 +8892,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45006</v>
+        <v>46001</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8907,13 +8907,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8956,7 +8951,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 8071-2024</t>
+          <t>A 55972-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8970,10 +8965,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45351</v>
+        <v>44889</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8986,7 +8981,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9029,7 +9024,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 13975-2023</t>
+          <t>A 61695-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9043,10 +9038,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45008</v>
+        <v>46002</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9059,7 +9054,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9102,7 +9097,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 16473-2022</t>
+          <t>A 57381-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9116,10 +9111,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44671</v>
+        <v>44896</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9132,7 +9127,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9175,7 +9170,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 6323-2023</t>
+          <t>A 48727-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9189,10 +9184,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44960</v>
+        <v>45936</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9204,13 +9199,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>0.5</v>
+        <v>6.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9253,7 +9243,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 40092-2024</t>
+          <t>A 26886-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9267,10 +9257,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45554</v>
+        <v>45093</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9283,7 +9273,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9326,7 +9316,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 14427-2026</t>
+          <t>A 22257-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9340,10 +9330,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46100</v>
+        <v>46154</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9356,7 +9346,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9399,7 +9389,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 57754-2023</t>
+          <t>A 48730-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9413,10 +9403,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45246</v>
+        <v>45936</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9429,7 +9419,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9472,7 +9462,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 26886-2023</t>
+          <t>A 26443-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9486,10 +9476,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45093</v>
+        <v>45092</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9502,7 +9492,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9545,7 +9535,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 302-2024</t>
+          <t>A 17114-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9559,10 +9549,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45295</v>
+        <v>45034</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9574,13 +9564,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9623,7 +9608,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 17377-2026</t>
+          <t>A 58750-2021</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9637,10 +9622,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46119</v>
+        <v>44489</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9653,7 +9638,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9696,7 +9681,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 18841-2026</t>
+          <t>A 7947-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9710,10 +9695,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46129</v>
+        <v>45350</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9726,7 +9711,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9769,7 +9754,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 29068-2024</t>
+          <t>A 13801-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9783,10 +9768,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45481</v>
+        <v>45737</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9799,7 +9784,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9842,7 +9827,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 4225-2024</t>
+          <t>A 49188-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9856,10 +9841,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45324</v>
+        <v>45938</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9872,7 +9857,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9915,7 +9900,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 4227-2024</t>
+          <t>A 23541-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9925,14 +9910,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45324</v>
+        <v>46163</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9945,7 +9930,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9988,7 +9973,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 38093-2022</t>
+          <t>A 13581-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10002,10 +9987,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44811</v>
+        <v>45006</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10017,8 +10002,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10061,7 +10051,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 5420-2025</t>
+          <t>A 54681-2021</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10075,10 +10065,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45692</v>
+        <v>44473</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10091,7 +10081,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10134,7 +10124,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 51488-2022</t>
+          <t>A 14891-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10148,10 +10138,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44869</v>
+        <v>45743</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10164,7 +10154,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10207,7 +10197,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 6489-2025</t>
+          <t>A 24700-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10221,10 +10211,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45699</v>
+        <v>46171</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10236,8 +10226,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10280,7 +10275,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 9046-2022</t>
+          <t>A 47511-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10294,10 +10289,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44615</v>
+        <v>45587</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10310,7 +10305,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10353,7 +10348,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 19079-2025</t>
+          <t>A 43770-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10367,10 +10362,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45766</v>
+        <v>45187</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10383,7 +10378,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10426,7 +10421,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 61952-2024</t>
+          <t>A 4881-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10440,10 +10435,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45653</v>
+        <v>45329</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10456,7 +10451,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10499,7 +10494,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 28022-2023</t>
+          <t>A 25729-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10513,10 +10508,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45098</v>
+        <v>46178</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10529,7 +10524,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>5.7</v>
+        <v>1.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10572,7 +10567,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 55972-2022</t>
+          <t>A 27643-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10586,10 +10581,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44889</v>
+        <v>46190</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10602,7 +10597,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10645,7 +10640,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 28903-2024</t>
+          <t>A 9046-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10659,10 +10654,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45480</v>
+        <v>44615</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10675,7 +10670,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10718,7 +10713,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 61475-2025</t>
+          <t>A 55324-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10732,10 +10727,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46001</v>
+        <v>45971</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10747,8 +10742,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10791,7 +10791,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 61284-2022</t>
+          <t>A 61435-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10805,10 +10805,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44915</v>
+        <v>45646</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10864,7 +10864,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 12760-2023</t>
+          <t>A 32822-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10878,10 +10878,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45001</v>
+        <v>46242</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10937,7 +10937,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 62730-2023</t>
+          <t>A 14929-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10951,10 +10951,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45268</v>
+        <v>45398</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11010,7 +11010,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 11604-2024</t>
+          <t>A 21630-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11024,10 +11024,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45373</v>
+        <v>45442</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11083,7 +11083,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 48904-2024</t>
+          <t>A 33842-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11097,10 +11097,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45594</v>
+        <v>46251</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3.9</v>
+        <v>7.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11156,7 +11156,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 5324-2025</t>
+          <t>A 43767-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11170,10 +11170,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45692</v>
+        <v>45187</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>5.1</v>
+        <v>2.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11229,7 +11229,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 61695-2025</t>
+          <t>A 30605-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11243,10 +11243,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46002</v>
+        <v>46210</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.7</v>
+        <v>10.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11302,7 +11302,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 54804-2022</t>
+          <t>A 2438-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11316,10 +11316,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44883</v>
+        <v>46036</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>22.6</v>
+        <v>2.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11375,7 +11375,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 52431-2023</t>
+          <t>A 33991-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11389,10 +11389,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45225</v>
+        <v>45134</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11448,7 +11448,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 22257-2026</t>
+          <t>A 41411-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11462,10 +11462,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46154</v>
+        <v>44826</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11521,7 +11521,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 33993-2023</t>
+          <t>A 4225-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11535,10 +11535,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45134</v>
+        <v>45324</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11594,7 +11594,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 33996-2023</t>
+          <t>A 4227-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11608,10 +11608,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45134</v>
+        <v>45324</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11624,7 +11624,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11667,7 +11667,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 23541-2026</t>
+          <t>A 35883-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11677,14 +11677,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46163</v>
+        <v>46266</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.4</v>
+        <v>6.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11740,7 +11740,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 7947-2024</t>
+          <t>A 37508-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11754,10 +11754,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45350</v>
+        <v>45158</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.8</v>
+        <v>6.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11813,7 +11813,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 17116-2023</t>
+          <t>A 37509-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11827,10 +11827,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45034</v>
+        <v>45158</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11886,7 +11886,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 15567-2022</t>
+          <t>A 36773-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11900,10 +11900,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44662</v>
+        <v>46272</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11915,8 +11915,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11959,7 +11964,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 21630-2024</t>
+          <t>A 36722-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11973,10 +11978,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45442</v>
+        <v>46272</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11988,8 +11993,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12032,7 +12042,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 14891-2025</t>
+          <t>A 37037-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12046,10 +12056,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45743</v>
+        <v>46273</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12062,7 +12072,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12105,7 +12115,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 24700-2026</t>
+          <t>A 13382-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12119,10 +12129,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46171</v>
+        <v>45005</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12134,13 +12144,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12183,7 +12188,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 13382-2023</t>
+          <t>A 38093-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12197,10 +12202,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45005</v>
+        <v>44811</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12213,7 +12218,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12256,7 +12261,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 550-2024</t>
+          <t>A 16473-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12270,10 +12275,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45299</v>
+        <v>44671</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12286,7 +12291,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12329,7 +12334,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 25729-2026</t>
+          <t>A 40092-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12343,10 +12348,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46178</v>
+        <v>45554</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12359,7 +12364,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12402,7 +12407,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 27643-2026</t>
+          <t>A 57754-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12416,10 +12421,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46190</v>
+        <v>45246</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12432,7 +12437,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12475,7 +12480,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 13887-2024</t>
+          <t>A 44445-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12489,10 +12494,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45391</v>
+        <v>45189</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12505,7 +12510,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>11.3</v>
+        <v>3.8</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12548,7 +12553,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 32822-2026</t>
+          <t>A 17116-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12562,10 +12567,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46242</v>
+        <v>45034</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12578,7 +12583,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12621,7 +12626,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 14929-2024</t>
+          <t>A 12760-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12635,10 +12640,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45398</v>
+        <v>45001</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12651,7 +12656,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12694,7 +12699,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 33842-2026</t>
+          <t>A 5612-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12708,10 +12713,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46251</v>
+        <v>45693</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12724,7 +12729,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>7.2</v>
+        <v>1.2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12767,7 +12772,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 11104-2024</t>
+          <t>A 302-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12781,10 +12786,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45371</v>
+        <v>45295</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12796,8 +12801,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12840,7 +12850,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 2438-2026</t>
+          <t>A 29068-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12854,10 +12864,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46036</v>
+        <v>45481</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12870,7 +12880,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12913,7 +12923,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 30605-2026</t>
+          <t>A 5324-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12927,10 +12937,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46210</v>
+        <v>45692</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12943,7 +12953,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>10.5</v>
+        <v>5.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12986,7 +12996,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 28910-2024</t>
+          <t>A 13631-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13000,10 +13010,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45480</v>
+        <v>45390</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13016,7 +13026,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.7</v>
+        <v>16.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13059,7 +13069,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 1382-2024</t>
+          <t>A 37063-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13073,10 +13083,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45303</v>
+        <v>45539</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13089,7 +13099,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13132,7 +13142,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 17114-2023</t>
+          <t>A 15159-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13146,10 +13156,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45034</v>
+        <v>45016</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13161,8 +13171,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13205,7 +13220,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 43767-2023</t>
+          <t>A 550-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13219,10 +13234,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45187</v>
+        <v>45299</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13278,7 +13293,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 35883-2026</t>
+          <t>A 13975-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13292,10 +13307,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46266</v>
+        <v>45008</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13308,7 +13323,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>6.6</v>
+        <v>2.2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13351,7 +13366,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 13631-2024</t>
+          <t>A 8071-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13365,10 +13380,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45390</v>
+        <v>45351</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13381,7 +13396,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>16.4</v>
+        <v>1.6</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13424,7 +13439,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 37508-2023</t>
+          <t>A 6489-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13438,10 +13453,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45158</v>
+        <v>45699</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13454,7 +13469,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>6.9</v>
+        <v>0.6</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13497,7 +13512,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 37509-2023</t>
+          <t>A 406-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13511,10 +13526,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45158</v>
+        <v>45296</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13527,7 +13542,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.9</v>
+        <v>4.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13570,7 +13585,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 15159-2023</t>
+          <t>A 62730-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13584,10 +13599,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45016</v>
+        <v>45268</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13599,13 +13614,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13648,7 +13658,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 36722-2026</t>
+          <t>A 49879-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13662,10 +13672,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46272</v>
+        <v>45213</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13677,13 +13687,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13726,7 +13731,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 37037-2026</t>
+          <t>A 5420-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13740,10 +13745,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46273</v>
+        <v>45692</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13756,7 +13761,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13799,7 +13804,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 36773-2026</t>
+          <t>A 3867-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13813,10 +13818,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46272</v>
+        <v>45684</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13828,13 +13833,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13877,7 +13877,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 49879-2023</t>
+          <t>A 21617-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13891,10 +13891,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45213</v>
+        <v>45441</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13950,7 +13950,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 44445-2023</t>
+          <t>A 30724-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13960,14 +13960,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45189</v>
+        <v>45496</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14023,7 +14023,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 33991-2023</t>
+          <t>A 22561-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14037,10 +14037,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45134</v>
+        <v>45789</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14096,7 +14096,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 5328-2025</t>
+          <t>A 23509-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14110,10 +14110,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45692</v>
+        <v>45792</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14169,7 +14169,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 3867-2025</t>
+          <t>A 23374-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14183,10 +14183,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45684</v>
+        <v>45791</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14242,7 +14242,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 21617-2024</t>
+          <t>A 12790-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14256,10 +14256,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45441</v>
+        <v>45733</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>9.699999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14315,7 +14315,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 22561-2025</t>
+          <t>A 12243-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14329,10 +14329,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45789</v>
+        <v>45729</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.2</v>
+        <v>10.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14388,7 +14388,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 12790-2025</t>
+          <t>A 24053-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14398,14 +14398,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45733</v>
+        <v>45796</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2.9</v>
+        <v>11.1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14461,7 +14461,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 12243-2025</t>
+          <t>A 5743-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14475,10 +14475,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45729</v>
+        <v>45694</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>10.2</v>
+        <v>0.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14534,7 +14534,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 30724-2024</t>
+          <t>A 7819-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14544,14 +14544,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45496</v>
+        <v>45706</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>2.5</v>
+        <v>5.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14607,7 +14607,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 23374-2025</t>
+          <t>A 5740-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14621,10 +14621,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45791</v>
+        <v>45694</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14680,7 +14680,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 23509-2025</t>
+          <t>A 6384-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14694,10 +14694,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45792</v>
+        <v>45699</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14753,7 +14753,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 5743-2025</t>
+          <t>A 36984-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14767,10 +14767,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45694</v>
+        <v>45539</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14826,7 +14826,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 24053-2025</t>
+          <t>A 27222-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14836,14 +14836,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45796</v>
+        <v>45812</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14856,7 +14856,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>11.1</v>
+        <v>1.3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14916,7 +14916,7 @@
         <v>44964</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>

--- a/Översikt LILLA EDET.xlsx
+++ b/Översikt LILLA EDET.xlsx
@@ -601,7 +601,7 @@
         <v>46169</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45295</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 30285-2025</t>
+          <t>A 318-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45827</v>
+        <v>45295</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,14 +856,19 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I4" t="n">
-        <v>29.6</v>
+        <v>8.1</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -890,12 +895,128 @@
         <v>8</v>
       </c>
       <c r="T4" t="n">
+        <v>17</v>
+      </c>
+      <c r="U4" t="n">
+        <v>17</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Kattfotslav
+Blåmossa
+Fällmossa
+Klippfrullania
+Stor revmossa
+Västlig hakmossa
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 318-2024 artfynd.xlsx", "A 318-2024")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 318-2024 karta.png", "A 318-2024")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 318-2024 georefererad karta.tif", "A 318-2024")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 318-2024 FSC-klagomål.docx", "A 318-2024")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 318-2024 FSC-klagomål mail.docx", "A 318-2024")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 318-2024 tillsynsbegäran.docx", "A 318-2024")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 318-2024 tillsynsbegäran mail.docx", "A 318-2024")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 318-2024 prioriterade fågelarter.docx", "A 318-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 30285-2025</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45827</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>8</v>
+      </c>
+      <c r="T5" t="n">
         <v>38</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Dofttaggsvamp
 Blåmossa
@@ -907,232 +1028,222 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 30285-2025 artfynd.xlsx", "A 30285-2025")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 30285-2025 karta.png", "A 30285-2025")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 30285-2025 georefererad karta.tif", "A 30285-2025")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 30285-2025 FSC-klagomål.docx", "A 30285-2025")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 30285-2025 FSC-klagomål mail.docx", "A 30285-2025")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 30285-2025 tillsynsbegäran.docx", "A 30285-2025")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 30285-2025 tillsynsbegäran mail.docx", "A 30285-2025")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 30285-2025 prioriterade fågelarter.docx", "A 30285-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 318-2024</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45295</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J5" t="n">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 62846-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45272</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J6" t="n">
         <v>2</v>
       </c>
-      <c r="K5" t="n">
-        <v>5</v>
-      </c>
-      <c r="L5" t="n">
+      <c r="K6" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>1</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>8</v>
-      </c>
-      <c r="T5" t="n">
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>7</v>
+      </c>
+      <c r="T6" t="n">
         <v>17</v>
       </c>
-      <c r="U5" t="n">
-        <v>17</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Kattfotslav
 Blåmossa
-Fällmossa
-Klippfrullania
+Bronshjon
 Stor revmossa
-Västlig hakmossa
-Spillkråka
+Vågbandad barkbock
+Större vattensalamander
 Revlummer</t>
         </is>
       </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 318-2024 artfynd.xlsx", "A 318-2024")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 318-2024 karta.png", "A 318-2024")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 318-2024 georefererad karta.tif", "A 318-2024")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 318-2024 FSC-klagomål.docx", "A 318-2024")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 318-2024 FSC-klagomål mail.docx", "A 318-2024")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 318-2024 tillsynsbegäran.docx", "A 318-2024")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 318-2024 tillsynsbegäran mail.docx", "A 318-2024")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 318-2024 prioriterade fågelarter.docx", "A 318-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 62846-2023 artfynd.xlsx", "A 62846-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 62846-2023 karta.png", "A 62846-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 62846-2023 georefererad karta.tif", "A 62846-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 62846-2023 FSC-klagomål.docx", "A 62846-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 62846-2023 FSC-klagomål mail.docx", "A 62846-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 62846-2023 tillsynsbegäran.docx", "A 62846-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 62846-2023 tillsynsbegäran mail.docx", "A 62846-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>A 34396-2023</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
         <v>45139</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
+      <c r="E7" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>7</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J7" t="n">
         <v>2</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K7" t="n">
         <v>5</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T7" t="n">
         <v>24</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>24</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Blåmossa
@@ -1143,147 +1254,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 34396-2023 artfynd.xlsx", "A 34396-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 34396-2023 karta.png", "A 34396-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 34396-2023 georefererad karta.tif", "A 34396-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 34396-2023 FSC-klagomål.docx", "A 34396-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 34396-2023 FSC-klagomål mail.docx", "A 34396-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 34396-2023 tillsynsbegäran.docx", "A 34396-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 34396-2023 tillsynsbegäran mail.docx", "A 34396-2023")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 34396-2023 prioriterade fågelarter.docx", "A 34396-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 62846-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45272</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>7</v>
-      </c>
-      <c r="T7" t="n">
-        <v>17</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Kattfotslav
-Blåmossa
-Bronshjon
-Stor revmossa
-Vågbandad barkbock
-Större vattensalamander
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 62846-2023 artfynd.xlsx", "A 62846-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 62846-2023 karta.png", "A 62846-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 62846-2023 georefererad karta.tif", "A 62846-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 62846-2023 FSC-klagomål.docx", "A 62846-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 62846-2023 FSC-klagomål mail.docx", "A 62846-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 62846-2023 tillsynsbegäran.docx", "A 62846-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 62846-2023 tillsynsbegäran mail.docx", "A 62846-2023")</f>
         <v/>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
         <v>46044</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 28512-2025</t>
+          <t>A 25298-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45819</v>
+        <v>45462</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1432,8 +1432,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>10.9</v>
+        <v>5.9</v>
       </c>
       <c r="J9" t="n">
         <v>2</v>
@@ -1466,12 +1471,124 @@
         <v>4</v>
       </c>
       <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>5</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Västlig hakmossa
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 25298-2024 artfynd.xlsx", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 25298-2024 karta.png", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 25298-2024 georefererad karta.tif", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 25298-2024 FSC-klagomål.docx", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 25298-2024 FSC-klagomål mail.docx", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 25298-2024 tillsynsbegäran.docx", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 25298-2024 tillsynsbegäran mail.docx", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 25298-2024 prioriterade fågelarter.docx", "A 25298-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 28512-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45819</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="n">
         <v>19</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>19</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Västlig hakmossa
@@ -1479,111 +1596,224 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 28512-2025 artfynd.xlsx", "A 28512-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 28512-2025 karta.png", "A 28512-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 28512-2025 georefererad karta.tif", "A 28512-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 28512-2025 FSC-klagomål.docx", "A 28512-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 28512-2025 FSC-klagomål mail.docx", "A 28512-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 28512-2025 tillsynsbegäran.docx", "A 28512-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 28512-2025 tillsynsbegäran mail.docx", "A 28512-2025")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 28512-2025 prioriterade fågelarter.docx", "A 28512-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 23563-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45072</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7</v>
+      </c>
+      <c r="U11" t="n">
+        <v>7</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Nordfladdermus
+Dvärgpipistrell
+Vattenfladdermus
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23563-2023 artfynd.xlsx", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23563-2023 karta.png", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23563-2023 georefererad karta.tif", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23563-2023 FSC-klagomål.docx", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23563-2023 FSC-klagomål mail.docx", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23563-2023 tillsynsbegäran.docx", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23563-2023 tillsynsbegäran mail.docx", "A 23563-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 24290-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
         <v>46169</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>3.6</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K12" t="n">
         <v>3</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>4</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T12" t="n">
         <v>5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U12" t="n">
         <v>5</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Blanksvart trämyra
 Grönpyrola
@@ -1591,266 +1821,36 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 24290-2026 artfynd.xlsx", "A 24290-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 24290-2026 karta.png", "A 24290-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 24290-2026 georefererad karta.tif", "A 24290-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 24290-2026 FSC-klagomål.docx", "A 24290-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 24290-2026 FSC-klagomål mail.docx", "A 24290-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 24290-2026 tillsynsbegäran.docx", "A 24290-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 24290-2026 tillsynsbegäran mail.docx", "A 24290-2026")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 24290-2026 prioriterade fågelarter.docx", "A 24290-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 23563-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45072</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>7</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Nordfladdermus
-Dvärgpipistrell
-Vattenfladdermus
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23563-2023 artfynd.xlsx", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23563-2023 karta.png", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23563-2023 georefererad karta.tif", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23563-2023 FSC-klagomål.docx", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23563-2023 FSC-klagomål mail.docx", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23563-2023 tillsynsbegäran.docx", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23563-2023 tillsynsbegäran mail.docx", "A 23563-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 25298-2024</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45462</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>5</v>
-      </c>
-      <c r="U12" t="n">
-        <v>5</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Västlig hakmossa
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 25298-2024 artfynd.xlsx", "A 25298-2024")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 25298-2024 karta.png", "A 25298-2024")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 25298-2024 georefererad karta.tif", "A 25298-2024")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 25298-2024 FSC-klagomål.docx", "A 25298-2024")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 25298-2024 FSC-klagomål mail.docx", "A 25298-2024")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 25298-2024 tillsynsbegäran.docx", "A 25298-2024")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 25298-2024 tillsynsbegäran mail.docx", "A 25298-2024")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 25298-2024 prioriterade fågelarter.docx", "A 25298-2024")</f>
         <v/>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
         <v>45187</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 17376-2026</t>
+          <t>A 25655-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46119</v>
+        <v>45089</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
         <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2019,387 +2019,387 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
       </c>
       <c r="T14" t="n">
+        <v>9</v>
+      </c>
+      <c r="U14" t="n">
+        <v>7</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Bergjohannesört
+Svinrot
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 25655-2023 artfynd.xlsx", "A 25655-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 25655-2023 karta.png", "A 25655-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 25655-2023 georefererad karta.tif", "A 25655-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 25655-2023 FSC-klagomål.docx", "A 25655-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 25655-2023 FSC-klagomål mail.docx", "A 25655-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 25655-2023 tillsynsbegäran.docx", "A 25655-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 25655-2023 tillsynsbegäran mail.docx", "A 25655-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 28021-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45098</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>3</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Stor revmossa
+Nattskärra
+Törnskata</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 28021-2023 artfynd.xlsx", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 28021-2023 karta.png", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 28021-2023 georefererad karta.tif", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 28021-2023 FSC-klagomål.docx", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 28021-2023 FSC-klagomål mail.docx", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 28021-2023 tillsynsbegäran.docx", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 28021-2023 tillsynsbegäran mail.docx", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 28021-2023 prioriterade fågelarter.docx", "A 28021-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 23559-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45072</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>8</v>
+      </c>
+      <c r="U16" t="n">
+        <v>8</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Flodpärlmussla
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23559-2023 artfynd.xlsx", "A 23559-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23559-2023 karta.png", "A 23559-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23559-2023 georefererad karta.tif", "A 23559-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23559-2023 FSC-klagomål.docx", "A 23559-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23559-2023 FSC-klagomål mail.docx", "A 23559-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23559-2023 tillsynsbegäran.docx", "A 23559-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23559-2023 tillsynsbegäran mail.docx", "A 23559-2023")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 23559-2023 prioriterade fågelarter.docx", "A 23559-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 17376-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46119</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Slåttergubbe
 Almsnabbvinge
 Granspira</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 17376-2026 artfynd.xlsx", "A 17376-2026")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 17376-2026 karta.png", "A 17376-2026")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 17376-2026 georefererad karta.tif", "A 17376-2026")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 17376-2026 FSC-klagomål.docx", "A 17376-2026")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 17376-2026 FSC-klagomål mail.docx", "A 17376-2026")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 17376-2026 tillsynsbegäran.docx", "A 17376-2026")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 17376-2026 tillsynsbegäran mail.docx", "A 17376-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 28021-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45098</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Stor revmossa
-Nattskärra
-Törnskata</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 28021-2023 artfynd.xlsx", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 28021-2023 karta.png", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 28021-2023 georefererad karta.tif", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 28021-2023 FSC-klagomål.docx", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 28021-2023 FSC-klagomål mail.docx", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 28021-2023 tillsynsbegäran.docx", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 28021-2023 tillsynsbegäran mail.docx", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 28021-2023 prioriterade fågelarter.docx", "A 28021-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 25655-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45089</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>9</v>
-      </c>
-      <c r="U16" t="n">
-        <v>7</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Bergjohannesört
-Svinrot
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 25655-2023 artfynd.xlsx", "A 25655-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 25655-2023 karta.png", "A 25655-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 25655-2023 georefererad karta.tif", "A 25655-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 25655-2023 FSC-klagomål.docx", "A 25655-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 25655-2023 FSC-klagomål mail.docx", "A 25655-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 25655-2023 tillsynsbegäran.docx", "A 25655-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 25655-2023 tillsynsbegäran mail.docx", "A 25655-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 23559-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45072</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>8</v>
-      </c>
-      <c r="U17" t="n">
-        <v>8</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Flodpärlmussla
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23559-2023 artfynd.xlsx", "A 23559-2023")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23559-2023 karta.png", "A 23559-2023")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23559-2023 georefererad karta.tif", "A 23559-2023")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23559-2023 FSC-klagomål.docx", "A 23559-2023")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23559-2023 FSC-klagomål mail.docx", "A 23559-2023")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23559-2023 tillsynsbegäran.docx", "A 23559-2023")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23559-2023 tillsynsbegäran mail.docx", "A 23559-2023")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 23559-2023 prioriterade fågelarter.docx", "A 23559-2023")</f>
         <v/>
       </c>
     </row>
@@ -2423,7 +2423,7 @@
         <v>45072</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45072</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 13699-2024</t>
+          <t>A 5866-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45390</v>
+        <v>46052</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2665,14 +2665,19 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>6.6</v>
+        <v>3.1</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2699,280 +2704,275 @@
         <v>2</v>
       </c>
       <c r="T20" t="n">
+        <v>9</v>
+      </c>
+      <c r="U20" t="n">
+        <v>9</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 5866-2026 artfynd.xlsx", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 5866-2026 karta.png", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 5866-2026 georefererad karta.tif", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 5866-2026 FSC-klagomål.docx", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 5866-2026 FSC-klagomål mail.docx", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 5866-2026 tillsynsbegäran.docx", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 5866-2026 tillsynsbegäran mail.docx", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 5866-2026 prioriterade fågelarter.docx", "A 5866-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 13699-2024</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45390</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
         <v>7</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Västlig hakmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 13699-2024 artfynd.xlsx", "A 13699-2024")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 13699-2024 karta.png", "A 13699-2024")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 13699-2024 georefererad karta.tif", "A 13699-2024")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 13699-2024 FSC-klagomål.docx", "A 13699-2024")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 13699-2024 FSC-klagomål mail.docx", "A 13699-2024")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 13699-2024 tillsynsbegäran.docx", "A 13699-2024")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 13699-2024 tillsynsbegäran mail.docx", "A 13699-2024")</f>
         <v/>
       </c>
-      <c r="AE20">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 13699-2024 prioriterade fågelarter.docx", "A 13699-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>A 32690-2026</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="E22" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>Kyrkan</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>4.6</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M22" t="n">
         <v>1</v>
       </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>2</v>
       </c>
-      <c r="R21" t="n">
+      <c r="R22" t="n">
         <v>1</v>
       </c>
-      <c r="S21" t="n">
+      <c r="S22" t="n">
         <v>2</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>2</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>1</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Skirmossa
 Dunmossa</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 32690-2026 artfynd.xlsx", "A 32690-2026")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 32690-2026 karta.png", "A 32690-2026")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 32690-2026 georefererad karta.tif", "A 32690-2026")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 32690-2026 FSC-klagomål.docx", "A 32690-2026")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 32690-2026 FSC-klagomål mail.docx", "A 32690-2026")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 32690-2026 tillsynsbegäran.docx", "A 32690-2026")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 32690-2026 tillsynsbegäran mail.docx", "A 32690-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 5866-2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>46052</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>9</v>
-      </c>
-      <c r="U22" t="n">
-        <v>9</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 5866-2026 artfynd.xlsx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 5866-2026 karta.png", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 5866-2026 georefererad karta.tif", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 5866-2026 FSC-klagomål.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 5866-2026 FSC-klagomål mail.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 5866-2026 tillsynsbegäran.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 5866-2026 tillsynsbegäran mail.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 5866-2026 prioriterade fågelarter.docx", "A 5866-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 30273-2022</t>
+          <t>A 49384-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2982,14 +2982,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44759</v>
+        <v>45205</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3001,18 +3001,23 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>12.5</v>
+        <v>1.2</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
@@ -3026,7 +3031,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3035,49 +3040,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 30273-2022 artfynd.xlsx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 49384-2023 artfynd.xlsx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 30273-2022 karta.png", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 49384-2023 karta.png", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 30273-2022 georefererad karta.tif", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 49384-2023 georefererad karta.tif", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 30273-2022 FSC-klagomål.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 49384-2023 FSC-klagomål.docx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 30273-2022 FSC-klagomål mail.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 49384-2023 FSC-klagomål mail.docx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 30273-2022 tillsynsbegäran.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 49384-2023 tillsynsbegäran.docx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 30273-2022 tillsynsbegäran mail.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 49384-2023 tillsynsbegäran mail.docx", "A 49384-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 49384-2023</t>
+          <t>A 30273-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3087,14 +3092,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45205</v>
+        <v>44759</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3106,22 +3111,17 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>1.2</v>
+        <v>12.5</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3136,7 +3136,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3145,49 +3145,49 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 49384-2023 artfynd.xlsx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 30273-2022 artfynd.xlsx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 49384-2023 karta.png", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 30273-2022 karta.png", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 49384-2023 georefererad karta.tif", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 30273-2022 georefererad karta.tif", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 49384-2023 FSC-klagomål.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 30273-2022 FSC-klagomål.docx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 49384-2023 FSC-klagomål mail.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 30273-2022 FSC-klagomål mail.docx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 49384-2023 tillsynsbegäran.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 30273-2022 tillsynsbegäran.docx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 49384-2023 tillsynsbegäran mail.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 30273-2022 tillsynsbegäran mail.docx", "A 30273-2022")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 41756-2025</t>
+          <t>A 38522-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3201,10 +3201,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45902</v>
+        <v>45546</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3216,8 +3216,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>5.3</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3253,46 +3258,50 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 41756-2025 artfynd.xlsx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 38522-2024 artfynd.xlsx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 41756-2025 karta.png", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 38522-2024 karta.png", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 41756-2025 georefererad karta.tif", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 38522-2024 georefererad karta.tif", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 41756-2025 FSC-klagomål.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 38522-2024 FSC-klagomål.docx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 41756-2025 FSC-klagomål mail.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 38522-2024 FSC-klagomål mail.docx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 41756-2025 tillsynsbegäran.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 38522-2024 tillsynsbegäran.docx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 41756-2025 tillsynsbegäran mail.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 38522-2024 tillsynsbegäran mail.docx", "A 38522-2024")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 38522-2024 prioriterade fågelarter.docx", "A 38522-2024")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 38522-2024</t>
+          <t>A 11102-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3306,10 +3315,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45546</v>
+        <v>45371</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3321,26 +3330,21 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>5.3</v>
+        <v>2.8</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
@@ -3351,10 +3355,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3363,50 +3367,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 38522-2024 artfynd.xlsx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 11102-2024 artfynd.xlsx", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 38522-2024 karta.png", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 11102-2024 karta.png", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 38522-2024 georefererad karta.tif", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 11102-2024 georefererad karta.tif", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 38522-2024 FSC-klagomål.docx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 11102-2024 FSC-klagomål.docx", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 38522-2024 FSC-klagomål mail.docx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 11102-2024 FSC-klagomål mail.docx", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 38522-2024 tillsynsbegäran.docx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 11102-2024 tillsynsbegäran.docx", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 38522-2024 tillsynsbegäran mail.docx", "A 38522-2024")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 38522-2024 prioriterade fågelarter.docx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 11102-2024 tillsynsbegäran mail.docx", "A 11102-2024")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 45941-2025</t>
+          <t>A 41756-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3420,10 +3420,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45924</v>
+        <v>45902</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3436,16 +3436,16 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3460,7 +3460,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3469,49 +3469,49 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 45941-2025 artfynd.xlsx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 41756-2025 artfynd.xlsx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 45941-2025 karta.png", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 41756-2025 karta.png", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 45941-2025 georefererad karta.tif", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 41756-2025 georefererad karta.tif", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 45941-2025 FSC-klagomål.docx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 41756-2025 FSC-klagomål.docx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 45941-2025 FSC-klagomål mail.docx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 41756-2025 FSC-klagomål mail.docx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 45941-2025 tillsynsbegäran.docx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 41756-2025 tillsynsbegäran.docx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 45941-2025 tillsynsbegäran mail.docx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 41756-2025 tillsynsbegäran mail.docx", "A 41756-2025")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 7062-2024</t>
+          <t>A 45941-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3521,14 +3521,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45343</v>
+        <v>45924</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3541,17 +3541,17 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>9.1</v>
+        <v>1.2</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3574,49 +3574,49 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 7062-2024 artfynd.xlsx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 45941-2025 artfynd.xlsx", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 7062-2024 karta.png", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 45941-2025 karta.png", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 7062-2024 georefererad karta.tif", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 45941-2025 georefererad karta.tif", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 7062-2024 FSC-klagomål.docx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 45941-2025 FSC-klagomål.docx", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 7062-2024 FSC-klagomål mail.docx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 45941-2025 FSC-klagomål mail.docx", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 7062-2024 tillsynsbegäran.docx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 45941-2025 tillsynsbegäran.docx", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 7062-2024 tillsynsbegäran mail.docx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 45941-2025 tillsynsbegäran mail.docx", "A 45941-2025")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 11102-2024</t>
+          <t>A 7062-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3626,14 +3626,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45371</v>
+        <v>45343</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.8</v>
+        <v>9.1</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -3658,7 +3658,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3670,10 +3670,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3686,35 +3686,35 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 11102-2024 artfynd.xlsx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 7062-2024 artfynd.xlsx", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 11102-2024 karta.png", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 7062-2024 karta.png", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 11102-2024 georefererad karta.tif", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 7062-2024 georefererad karta.tif", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 11102-2024 FSC-klagomål.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 7062-2024 FSC-klagomål.docx", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 11102-2024 FSC-klagomål mail.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 7062-2024 FSC-klagomål mail.docx", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 11102-2024 tillsynsbegäran.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 7062-2024 tillsynsbegäran.docx", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 11102-2024 tillsynsbegäran mail.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 7062-2024 tillsynsbegäran mail.docx", "A 7062-2024")</f>
         <v/>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
         <v>46240</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44812</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44581</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>44875</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>44637</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>44685</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>44760</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>44720</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>44627</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>44476</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>44467</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>44803</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>44812</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>44826</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>44462</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>44811</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 296-2022</t>
+          <t>A 30284-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44565</v>
+        <v>44760</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4999,7 +4999,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 30284-2022</t>
+          <t>A 30287-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5016,7 +5016,7 @@
         <v>44760</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 30287-2022</t>
+          <t>A 296-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5086,10 +5086,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44760</v>
+        <v>44565</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5162,7 +5162,7 @@
         <v>44627</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 12234-2024</t>
+          <t>A 58750-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5232,10 +5232,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45378</v>
+        <v>44489</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5291,7 +5291,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 13887-2024</t>
+          <t>A 12234-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5305,10 +5305,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45391</v>
+        <v>45378</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>11.3</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5364,7 +5364,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 61284-2022</t>
+          <t>A 4881-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5378,10 +5378,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44915</v>
+        <v>45329</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5437,7 +5437,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 52431-2023</t>
+          <t>A 26443-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45225</v>
+        <v>45092</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5510,7 +5510,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 11104-2024</t>
+          <t>A 43770-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5524,10 +5524,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45371</v>
+        <v>45187</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5583,7 +5583,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 65619-2021</t>
+          <t>A 54681-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44516</v>
+        <v>44473</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5656,7 +5656,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 51488-2022</t>
+          <t>A 406-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44869</v>
+        <v>45296</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5729,7 +5729,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 28910-2024</t>
+          <t>A 61435-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5743,10 +5743,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45480</v>
+        <v>45646</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5802,7 +5802,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11604-2024</t>
+          <t>A 5612-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45373</v>
+        <v>45693</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 1382-2024</t>
+          <t>A 37063-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5889,10 +5889,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45303</v>
+        <v>45539</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5948,7 +5948,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 33993-2023</t>
+          <t>A 587-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5962,10 +5962,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45134</v>
+        <v>45664</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6021,7 +6021,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 33996-2023</t>
+          <t>A 12628-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6035,10 +6035,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45134</v>
+        <v>45000</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6094,7 +6094,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 587-2025</t>
+          <t>A 65619-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6108,10 +6108,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45664</v>
+        <v>44516</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.3</v>
+        <v>2.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6167,7 +6167,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 15567-2022</t>
+          <t>A 47511-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6181,10 +6181,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44662</v>
+        <v>45587</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6240,7 +6240,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 7912-2024</t>
+          <t>A 41411-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6254,10 +6254,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45350</v>
+        <v>44826</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6313,7 +6313,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 6323-2023</t>
+          <t>A 12647-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6327,10 +6327,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44960</v>
+        <v>45000</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6342,13 +6342,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6391,7 +6386,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 54804-2022</t>
+          <t>A 8117-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6405,10 +6400,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44883</v>
+        <v>44974</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6421,7 +6416,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>22.6</v>
+        <v>11</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6464,7 +6459,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 12784-2025</t>
+          <t>A 19079-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6478,10 +6473,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45733</v>
+        <v>45766</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6494,7 +6489,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6537,7 +6532,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 28515-2025</t>
+          <t>A 61952-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6551,10 +6546,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45819</v>
+        <v>45653</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6567,7 +6562,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6610,7 +6605,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 2867-2025</t>
+          <t>A 28022-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6624,10 +6619,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45677</v>
+        <v>45098</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6640,7 +6635,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>10.7</v>
+        <v>5.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6683,7 +6678,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 56584-2025</t>
+          <t>A 55972-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6697,10 +6692,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45974</v>
+        <v>44889</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6713,7 +6708,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6756,7 +6751,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 35423-2025</t>
+          <t>A 50349-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6770,10 +6765,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45855</v>
+        <v>45600</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6786,7 +6781,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6829,7 +6824,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 8117-2023</t>
+          <t>A 2867-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6843,10 +6838,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44974</v>
+        <v>45677</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6859,7 +6854,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6902,7 +6897,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 15351-2024</t>
+          <t>A 35423-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6916,10 +6911,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45400</v>
+        <v>45855</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6931,13 +6926,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6980,7 +6970,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 12628-2023</t>
+          <t>A 7912-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6994,10 +6984,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45000</v>
+        <v>45350</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7010,7 +7000,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7053,7 +7043,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 50349-2024</t>
+          <t>A 61475-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7067,10 +7057,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45600</v>
+        <v>46001</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7083,7 +7073,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.7</v>
+        <v>4.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7126,7 +7116,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 14427-2026</t>
+          <t>A 41759-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7140,10 +7130,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46100</v>
+        <v>45902</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7199,7 +7189,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 35420-2025</t>
+          <t>A 13581-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7213,10 +7203,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45855</v>
+        <v>45006</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7228,8 +7218,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7272,7 +7267,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35717-2025</t>
+          <t>A 41758-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7286,10 +7281,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45860</v>
+        <v>45902</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7302,7 +7297,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7345,7 +7340,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 28903-2024</t>
+          <t>A 41760-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7359,10 +7354,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45480</v>
+        <v>45902</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7375,7 +7370,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7418,7 +7413,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 12647-2023</t>
+          <t>A 41761-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7432,10 +7427,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45000</v>
+        <v>45902</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7448,7 +7443,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>6.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7491,7 +7486,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 17377-2026</t>
+          <t>A 8071-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7505,10 +7500,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46119</v>
+        <v>45351</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7521,7 +7516,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7564,7 +7559,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 18841-2026</t>
+          <t>A 35422-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7578,10 +7573,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46129</v>
+        <v>45855</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7594,7 +7589,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7637,7 +7632,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 41758-2025</t>
+          <t>A 42857-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7651,10 +7646,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45902</v>
+        <v>45908</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7667,7 +7662,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7710,7 +7705,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 41760-2025</t>
+          <t>A 13975-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7724,10 +7719,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45902</v>
+        <v>45008</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7740,7 +7735,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7783,7 +7778,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 41761-2025</t>
+          <t>A 44104-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7797,10 +7792,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45902</v>
+        <v>45915</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7813,7 +7808,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>6.6</v>
+        <v>1.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7856,7 +7851,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 41759-2025</t>
+          <t>A 48904-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7870,10 +7865,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45902</v>
+        <v>45594</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7886,7 +7881,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7929,7 +7924,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 5328-2025</t>
+          <t>A 43684-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7943,10 +7938,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45692</v>
+        <v>45912</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7959,7 +7954,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8002,7 +7997,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 35422-2025</t>
+          <t>A 16473-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8016,10 +8011,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45855</v>
+        <v>44671</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8032,7 +8027,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8075,7 +8070,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 42857-2025</t>
+          <t>A 44916-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8089,10 +8084,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45908</v>
+        <v>45918</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8148,7 +8143,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 43684-2025</t>
+          <t>A 6323-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8162,10 +8157,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45912</v>
+        <v>44960</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8177,8 +8172,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8221,7 +8221,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 44104-2025</t>
+          <t>A 44918-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8235,10 +8235,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45915</v>
+        <v>45918</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.5</v>
+        <v>5.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8311,7 +8311,7 @@
         <v>45918</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>45918</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 44918-2025</t>
+          <t>A 40092-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8454,10 +8454,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45918</v>
+        <v>45554</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>5.7</v>
+        <v>1.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8513,7 +8513,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 19079-2025</t>
+          <t>A 57754-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8527,10 +8527,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45766</v>
+        <v>45246</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8586,7 +8586,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 44916-2025</t>
+          <t>A 26886-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45918</v>
+        <v>45093</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8659,7 +8659,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 28022-2023</t>
+          <t>A 57381-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8673,10 +8673,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45098</v>
+        <v>44896</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8689,7 +8689,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>5.7</v>
+        <v>2.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8732,7 +8732,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 48904-2024</t>
+          <t>A 48730-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8746,10 +8746,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45594</v>
+        <v>45936</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8805,7 +8805,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 61952-2024</t>
+          <t>A 48727-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8819,10 +8819,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45653</v>
+        <v>45936</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4.2</v>
+        <v>6.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8878,7 +8878,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 61475-2025</t>
+          <t>A 61695-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8892,10 +8892,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 55972-2022</t>
+          <t>A 49188-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8965,10 +8965,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44889</v>
+        <v>45938</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9024,7 +9024,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 61695-2025</t>
+          <t>A 13801-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9038,10 +9038,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46002</v>
+        <v>45737</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9054,7 +9054,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9097,7 +9097,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 57381-2022</t>
+          <t>A 302-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44896</v>
+        <v>45295</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9126,8 +9126,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9170,7 +9175,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 48727-2025</t>
+          <t>A 29068-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9184,10 +9189,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45936</v>
+        <v>45481</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9200,7 +9205,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>6.1</v>
+        <v>1.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9243,7 +9248,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 26886-2023</t>
+          <t>A 4225-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9257,10 +9262,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45093</v>
+        <v>45324</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9273,7 +9278,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9316,7 +9321,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 22257-2026</t>
+          <t>A 4227-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9330,10 +9335,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46154</v>
+        <v>45324</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9346,7 +9351,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9389,7 +9394,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 48730-2025</t>
+          <t>A 38093-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9403,10 +9408,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45936</v>
+        <v>44811</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9419,7 +9424,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9462,7 +9467,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 26443-2023</t>
+          <t>A 5420-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9476,10 +9481,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45092</v>
+        <v>45692</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9492,7 +9497,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9535,7 +9540,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 17114-2023</t>
+          <t>A 51488-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9549,10 +9554,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45034</v>
+        <v>44869</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9565,7 +9570,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9608,7 +9613,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 58750-2021</t>
+          <t>A 6489-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9622,10 +9627,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44489</v>
+        <v>45699</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9638,7 +9643,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9681,7 +9686,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 7947-2024</t>
+          <t>A 9046-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9695,10 +9700,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45350</v>
+        <v>44615</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9711,7 +9716,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9754,7 +9759,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 13801-2025</t>
+          <t>A 22257-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9768,10 +9773,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45737</v>
+        <v>46154</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9784,7 +9789,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9827,7 +9832,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 49188-2025</t>
+          <t>A 55324-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9841,10 +9846,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45938</v>
+        <v>45971</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9856,8 +9861,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9900,7 +9910,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 23541-2026</t>
+          <t>A 28903-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9910,14 +9920,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46163</v>
+        <v>45480</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9930,7 +9940,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.4</v>
+        <v>3.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9973,7 +9983,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 13581-2023</t>
+          <t>A 61284-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9987,10 +9997,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45006</v>
+        <v>44915</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10002,13 +10012,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10051,7 +10056,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 54681-2021</t>
+          <t>A 12760-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10065,10 +10070,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44473</v>
+        <v>45001</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10081,7 +10086,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10124,7 +10129,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 14891-2025</t>
+          <t>A 62730-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10138,10 +10143,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45743</v>
+        <v>45268</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10154,7 +10159,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10197,7 +10202,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 24700-2026</t>
+          <t>A 11604-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10211,10 +10216,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46171</v>
+        <v>45373</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10226,13 +10231,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10275,7 +10275,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 47511-2024</t>
+          <t>A 23541-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10285,14 +10285,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45587</v>
+        <v>46163</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10348,7 +10348,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 43770-2023</t>
+          <t>A 5324-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10362,10 +10362,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45187</v>
+        <v>45692</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.9</v>
+        <v>5.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10421,7 +10421,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 4881-2024</t>
+          <t>A 54804-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10435,10 +10435,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45329</v>
+        <v>44883</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.5</v>
+        <v>22.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10494,7 +10494,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 25729-2026</t>
+          <t>A 52431-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10508,10 +10508,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46178</v>
+        <v>45225</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10524,7 +10524,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10567,7 +10567,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 27643-2026</t>
+          <t>A 33993-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10581,10 +10581,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46190</v>
+        <v>45134</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10597,7 +10597,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10640,7 +10640,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 9046-2022</t>
+          <t>A 33996-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10654,10 +10654,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44615</v>
+        <v>45134</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10713,7 +10713,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 55324-2025</t>
+          <t>A 14891-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10727,10 +10727,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45971</v>
+        <v>45743</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10742,13 +10742,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10791,7 +10786,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 61435-2024</t>
+          <t>A 7947-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10805,10 +10800,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45646</v>
+        <v>45350</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10821,7 +10816,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10864,7 +10859,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 32822-2026</t>
+          <t>A 17116-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10878,10 +10873,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46242</v>
+        <v>45034</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10894,7 +10889,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10937,7 +10932,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 14929-2024</t>
+          <t>A 24700-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10951,10 +10946,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45398</v>
+        <v>46171</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10966,8 +10961,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>5.1</v>
+        <v>1.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11010,7 +11010,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 21630-2024</t>
+          <t>A 15567-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11024,10 +11024,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45442</v>
+        <v>44662</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>4.6</v>
+        <v>1.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11083,7 +11083,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 33842-2026</t>
+          <t>A 21630-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11097,10 +11097,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46251</v>
+        <v>45442</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11156,7 +11156,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 43767-2023</t>
+          <t>A 13382-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11170,10 +11170,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45187</v>
+        <v>45005</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11229,7 +11229,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 30605-2026</t>
+          <t>A 56584-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11243,10 +11243,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46210</v>
+        <v>45974</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>10.5</v>
+        <v>1.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11302,7 +11302,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 2438-2026</t>
+          <t>A 550-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11316,10 +11316,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46036</v>
+        <v>45299</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 33991-2023</t>
+          <t>A 25729-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11389,10 +11389,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45134</v>
+        <v>46178</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11448,7 +11448,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 41411-2022</t>
+          <t>A 15351-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11462,10 +11462,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44826</v>
+        <v>45400</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11477,8 +11477,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11521,7 +11526,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 4225-2024</t>
+          <t>A 27643-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11535,10 +11540,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45324</v>
+        <v>46190</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11551,7 +11556,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11594,7 +11599,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 4227-2024</t>
+          <t>A 14427-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11608,10 +11613,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45324</v>
+        <v>46100</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11624,7 +11629,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11667,7 +11672,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 35883-2026</t>
+          <t>A 13887-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11681,10 +11686,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46266</v>
+        <v>45391</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11697,7 +11702,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>6.6</v>
+        <v>11.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11740,7 +11745,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 37508-2023</t>
+          <t>A 32822-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11754,10 +11759,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45158</v>
+        <v>46242</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11770,7 +11775,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>6.9</v>
+        <v>2.2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11813,7 +11818,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 37509-2023</t>
+          <t>A 14929-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11827,10 +11832,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45158</v>
+        <v>45398</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11843,7 +11848,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.9</v>
+        <v>5.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11886,7 +11891,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 36773-2026</t>
+          <t>A 17377-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11900,10 +11905,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46272</v>
+        <v>46119</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11915,13 +11920,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11964,7 +11964,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 36722-2026</t>
+          <t>A 18841-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11978,10 +11978,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46272</v>
+        <v>46129</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11993,13 +11993,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12042,7 +12037,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 37037-2026</t>
+          <t>A 11104-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12056,10 +12051,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46273</v>
+        <v>45371</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12072,7 +12067,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12115,7 +12110,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 13382-2023</t>
+          <t>A 28910-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12129,10 +12124,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45005</v>
+        <v>45480</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12145,7 +12140,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12188,7 +12183,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 38093-2022</t>
+          <t>A 1382-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12202,10 +12197,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44811</v>
+        <v>45303</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12261,7 +12256,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 16473-2022</t>
+          <t>A 17114-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12275,10 +12270,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44671</v>
+        <v>45034</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12291,7 +12286,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12334,7 +12329,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 40092-2024</t>
+          <t>A 33842-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12348,10 +12343,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45554</v>
+        <v>46251</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12364,7 +12359,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.7</v>
+        <v>7.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12407,7 +12402,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 57754-2023</t>
+          <t>A 43767-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12421,10 +12416,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45246</v>
+        <v>45187</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12437,7 +12432,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12480,7 +12475,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 44445-2023</t>
+          <t>A 2438-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12494,10 +12489,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45189</v>
+        <v>46036</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12510,7 +12505,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12553,7 +12548,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 17116-2023</t>
+          <t>A 30605-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12567,10 +12562,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45034</v>
+        <v>46210</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12583,7 +12578,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1</v>
+        <v>10.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12626,7 +12621,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 12760-2023</t>
+          <t>A 13631-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12640,10 +12635,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45001</v>
+        <v>45390</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12656,7 +12651,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.1</v>
+        <v>16.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12699,7 +12694,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 5612-2025</t>
+          <t>A 37508-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12713,10 +12708,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45693</v>
+        <v>45158</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12729,7 +12724,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.2</v>
+        <v>6.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12772,7 +12767,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 302-2024</t>
+          <t>A 37509-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12786,10 +12781,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45295</v>
+        <v>45158</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12801,13 +12796,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12850,7 +12840,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 29068-2024</t>
+          <t>A 15159-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12864,10 +12854,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45481</v>
+        <v>45016</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12879,8 +12869,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12923,7 +12918,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 5324-2025</t>
+          <t>A 49879-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12937,10 +12932,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45692</v>
+        <v>45213</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12953,7 +12948,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12996,7 +12991,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 13631-2024</t>
+          <t>A 35883-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13010,10 +13005,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45390</v>
+        <v>46266</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13026,7 +13021,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>16.4</v>
+        <v>6.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13069,7 +13064,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 37063-2024</t>
+          <t>A 44445-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13083,10 +13078,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45539</v>
+        <v>45189</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13099,7 +13094,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>8.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13142,7 +13137,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 15159-2023</t>
+          <t>A 33991-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13156,10 +13151,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45016</v>
+        <v>45134</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13171,13 +13166,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13220,7 +13210,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 550-2024</t>
+          <t>A 5328-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13234,10 +13224,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45299</v>
+        <v>45692</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13250,7 +13240,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13293,7 +13283,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 13975-2023</t>
+          <t>A 36722-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13307,10 +13297,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45008</v>
+        <v>46272</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13320,6 +13310,11 @@
       <c r="G160" t="inlineStr">
         <is>
           <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I160" t="n">
@@ -13366,7 +13361,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 8071-2024</t>
+          <t>A 37037-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13380,10 +13375,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45351</v>
+        <v>46273</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13396,7 +13391,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13439,7 +13434,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 6489-2025</t>
+          <t>A 36773-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13453,10 +13448,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45699</v>
+        <v>46272</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13468,8 +13463,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13512,7 +13512,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 406-2024</t>
+          <t>A 3867-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13526,10 +13526,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45296</v>
+        <v>45684</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13585,7 +13585,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 62730-2023</t>
+          <t>A 21617-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13599,10 +13599,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45268</v>
+        <v>45441</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>3.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13658,7 +13658,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 49879-2023</t>
+          <t>A 22561-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13672,10 +13672,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45213</v>
+        <v>45789</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13688,7 +13688,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13731,7 +13731,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 5420-2025</t>
+          <t>A 12790-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45692</v>
+        <v>45733</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13804,7 +13804,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 3867-2025</t>
+          <t>A 12243-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13818,10 +13818,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45684</v>
+        <v>45729</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.5</v>
+        <v>10.2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13877,7 +13877,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 21617-2024</t>
+          <t>A 30724-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13887,14 +13887,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45441</v>
+        <v>45496</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>9.699999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13950,7 +13950,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 30724-2024</t>
+          <t>A 23374-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13960,14 +13960,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45496</v>
+        <v>45791</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14023,7 +14023,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 22561-2025</t>
+          <t>A 23509-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14037,10 +14037,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45789</v>
+        <v>45792</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14096,7 +14096,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 23509-2025</t>
+          <t>A 5743-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14110,10 +14110,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45792</v>
+        <v>45694</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14169,7 +14169,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 23374-2025</t>
+          <t>A 24053-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14179,14 +14179,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45791</v>
+        <v>45796</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.6</v>
+        <v>11.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14242,7 +14242,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 12790-2025</t>
+          <t>A 7819-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14256,10 +14256,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45733</v>
+        <v>45706</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.9</v>
+        <v>5.6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14315,7 +14315,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 12243-2025</t>
+          <t>A 5740-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14329,10 +14329,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45729</v>
+        <v>45694</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>10.2</v>
+        <v>1.4</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14388,7 +14388,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 24053-2025</t>
+          <t>A 6384-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14398,14 +14398,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45796</v>
+        <v>45699</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>11.1</v>
+        <v>2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14461,7 +14461,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 5743-2025</t>
+          <t>A 36984-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14475,10 +14475,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45694</v>
+        <v>45539</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14534,7 +14534,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 7819-2025</t>
+          <t>A 27222-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14548,10 +14548,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45706</v>
+        <v>45812</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>5.6</v>
+        <v>1.3</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14607,7 +14607,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 5740-2025</t>
+          <t>A 28515-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14621,10 +14621,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45694</v>
+        <v>45819</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14680,7 +14680,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 6384-2025</t>
+          <t>A 35420-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14694,10 +14694,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45699</v>
+        <v>45855</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14753,7 +14753,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 36984-2024</t>
+          <t>A 35717-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14767,10 +14767,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45539</v>
+        <v>45860</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14826,7 +14826,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 27222-2025</t>
+          <t>A 12784-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14840,10 +14840,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45812</v>
+        <v>45733</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14856,7 +14856,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14916,7 +14916,7 @@
         <v>44964</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>

--- a/Översikt LILLA EDET.xlsx
+++ b/Översikt LILLA EDET.xlsx
@@ -601,7 +601,7 @@
         <v>46169</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45295</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45295</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45827</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45272</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>45139</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46044</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>45462</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>45819</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>45072</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>46169</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>45187</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>45089</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>45098</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>45072</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>46119</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>45072</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45072</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>46052</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>45390</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>46240</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45205</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>44759</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>45546</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>45371</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45902</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>45924</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45343</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>46240</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44812</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44581</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>44875</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>44637</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>44685</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>44760</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>44720</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>44627</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>44476</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>44467</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>44803</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>44812</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>44826</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>44462</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>44811</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         <v>44760</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>44760</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>44565</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>44627</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>44489</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>45378</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         <v>45329</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>45092</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>45187</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>44473</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>45296</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>45646</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>45693</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>45539</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>45664</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>45000</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>44516</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>45587</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>44826</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>45000</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>44974</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         <v>45766</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>45653</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>45098</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>44889</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>45600</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>45677</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>45855</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>45350</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>46001</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>45902</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>45006</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>45902</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>45902</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>45902</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>45351</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>45855</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>45908</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>45008</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>45915</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>45594</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>45912</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         <v>44671</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
         <v>45918</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         <v>44960</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>45918</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>45918</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>45918</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>45554</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         <v>45246</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>45093</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>44896</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>45936</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>45936</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8895,7 +8895,7 @@
         <v>46002</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>45938</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>45737</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>45295</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         <v>45481</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>45324</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>45324</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>44811</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9484,7 +9484,7 @@
         <v>45692</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>44869</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>45699</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>44615</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>46154</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>45971</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>45480</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>44915</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
         <v>45001</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>45268</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
         <v>45373</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>46163</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         <v>45692</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>44883</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>45225</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>45134</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         <v>45134</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>45743</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>45350</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>45034</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>46171</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>44662</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>45442</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         <v>45005</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>45974</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>45299</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
         <v>46178</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11465,7 +11465,7 @@
         <v>45400</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
         <v>46190</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11616,7 +11616,7 @@
         <v>46100</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
         <v>45391</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
         <v>46242</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>45398</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11908,7 +11908,7 @@
         <v>46119</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11981,7 +11981,7 @@
         <v>46129</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>45371</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>45480</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12200,7 +12200,7 @@
         <v>45303</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         <v>45034</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>46251</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12419,7 +12419,7 @@
         <v>45187</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>46036</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>46210</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12638,7 +12638,7 @@
         <v>45390</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         <v>45158</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>45158</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>45016</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>45213</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13008,7 +13008,7 @@
         <v>46266</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
         <v>45189</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>45134</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>45692</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>46272</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13378,7 +13378,7 @@
         <v>46273</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13451,7 +13451,7 @@
         <v>46272</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>45684</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>45441</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>45789</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>45733</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>45729</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         <v>45496</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13967,7 +13967,7 @@
         <v>45791</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>45792</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>45694</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>45796</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>45706</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>45694</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>45699</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>45539</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>45812</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>45819</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         <v>45855</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>45860</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>45733</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>44964</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>

--- a/Översikt LILLA EDET.xlsx
+++ b/Översikt LILLA EDET.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE182"/>
+  <dimension ref="A1:AE179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>46169</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45295</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45295</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45827</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45272</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>45139</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46044</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>45462</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>45819</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>45072</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>46169</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>45187</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>45089</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>45098</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>45072</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>46119</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>45072</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 23494-2023</t>
+          <t>A 13699-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2535,10 +2535,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45072</v>
+        <v>45390</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2550,19 +2550,14 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>6.6</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2589,383 +2584,388 @@
         <v>2</v>
       </c>
       <c r="T19" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 13699-2024 artfynd.xlsx", "A 13699-2024")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 13699-2024 karta.png", "A 13699-2024")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 13699-2024 georefererad karta.tif", "A 13699-2024")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 13699-2024 FSC-klagomål.docx", "A 13699-2024")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 13699-2024 FSC-klagomål mail.docx", "A 13699-2024")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 13699-2024 tillsynsbegäran.docx", "A 13699-2024")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 13699-2024 tillsynsbegäran mail.docx", "A 13699-2024")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 13699-2024 prioriterade fågelarter.docx", "A 13699-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 5866-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>9</v>
+      </c>
+      <c r="U20" t="n">
+        <v>9</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23494-2023 artfynd.xlsx", "A 23494-2023")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23494-2023 karta.png", "A 23494-2023")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23494-2023 georefererad karta.tif", "A 23494-2023")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23494-2023 FSC-klagomål.docx", "A 23494-2023")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23494-2023 FSC-klagomål mail.docx", "A 23494-2023")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23494-2023 tillsynsbegäran.docx", "A 23494-2023")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23494-2023 tillsynsbegäran mail.docx", "A 23494-2023")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 23494-2023 prioriterade fågelarter.docx", "A 23494-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 5866-2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>46052</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J20" t="n">
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 5866-2026 artfynd.xlsx", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 5866-2026 karta.png", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 5866-2026 georefererad karta.tif", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 5866-2026 FSC-klagomål.docx", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 5866-2026 FSC-klagomål mail.docx", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 5866-2026 tillsynsbegäran.docx", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 5866-2026 tillsynsbegäran mail.docx", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 5866-2026 prioriterade fågelarter.docx", "A 5866-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 32690-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>2</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
         <v>2</v>
       </c>
-      <c r="T20" t="n">
-        <v>9</v>
-      </c>
-      <c r="U20" t="n">
-        <v>9</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Skirmossa
+Dunmossa</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 32690-2026 artfynd.xlsx", "A 32690-2026")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 32690-2026 karta.png", "A 32690-2026")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 32690-2026 georefererad karta.tif", "A 32690-2026")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 32690-2026 FSC-klagomål.docx", "A 32690-2026")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 32690-2026 FSC-klagomål mail.docx", "A 32690-2026")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 32690-2026 tillsynsbegäran.docx", "A 32690-2026")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 32690-2026 tillsynsbegäran mail.docx", "A 32690-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 23494-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45072</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 5866-2026 artfynd.xlsx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 5866-2026 karta.png", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 5866-2026 georefererad karta.tif", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 5866-2026 FSC-klagomål.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 5866-2026 FSC-klagomål mail.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 5866-2026 tillsynsbegäran.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 5866-2026 tillsynsbegäran mail.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 5866-2026 prioriterade fågelarter.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 13699-2024</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45390</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>7</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Västlig hakmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 13699-2024 artfynd.xlsx", "A 13699-2024")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 13699-2024 karta.png", "A 13699-2024")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 13699-2024 georefererad karta.tif", "A 13699-2024")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 13699-2024 FSC-klagomål.docx", "A 13699-2024")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 13699-2024 FSC-klagomål mail.docx", "A 13699-2024")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 13699-2024 tillsynsbegäran.docx", "A 13699-2024")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 13699-2024 tillsynsbegäran mail.docx", "A 13699-2024")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 13699-2024 prioriterade fågelarter.docx", "A 13699-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 32690-2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>46240</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Skirmossa
-Dunmossa</t>
-        </is>
-      </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 32690-2026 artfynd.xlsx", "A 32690-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23494-2023 artfynd.xlsx", "A 23494-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 32690-2026 karta.png", "A 32690-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23494-2023 karta.png", "A 23494-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 32690-2026 georefererad karta.tif", "A 32690-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23494-2023 georefererad karta.tif", "A 23494-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 32690-2026 FSC-klagomål.docx", "A 32690-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23494-2023 FSC-klagomål.docx", "A 23494-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 32690-2026 FSC-klagomål mail.docx", "A 32690-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23494-2023 FSC-klagomål mail.docx", "A 23494-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 32690-2026 tillsynsbegäran.docx", "A 32690-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23494-2023 tillsynsbegäran.docx", "A 23494-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 32690-2026 tillsynsbegäran mail.docx", "A 32690-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23494-2023 tillsynsbegäran mail.docx", "A 23494-2023")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 23494-2023 prioriterade fågelarter.docx", "A 23494-2023")</f>
         <v/>
       </c>
     </row>
@@ -2989,7 +2989,7 @@
         <v>45205</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>44759</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>45546</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 11102-2024</t>
+          <t>A 41756-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45371</v>
+        <v>45902</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3331,10 +3331,10 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -3343,7 +3343,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3355,10 +3355,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3371,42 +3371,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 11102-2024 artfynd.xlsx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 41756-2025 artfynd.xlsx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 11102-2024 karta.png", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 41756-2025 karta.png", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 11102-2024 georefererad karta.tif", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 41756-2025 georefererad karta.tif", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 11102-2024 FSC-klagomål.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 41756-2025 FSC-klagomål.docx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 11102-2024 FSC-klagomål mail.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 41756-2025 FSC-klagomål mail.docx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 11102-2024 tillsynsbegäran.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 41756-2025 tillsynsbegäran.docx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 11102-2024 tillsynsbegäran mail.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 41756-2025 tillsynsbegäran mail.docx", "A 41756-2025")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 41756-2025</t>
+          <t>A 11102-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3420,10 +3420,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45902</v>
+        <v>45371</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3436,20 +3436,20 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
@@ -3460,10 +3460,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3476,35 +3476,35 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 41756-2025 artfynd.xlsx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 11102-2024 artfynd.xlsx", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 41756-2025 karta.png", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 11102-2024 karta.png", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 41756-2025 georefererad karta.tif", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 11102-2024 georefererad karta.tif", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 41756-2025 FSC-klagomål.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 11102-2024 FSC-klagomål.docx", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 41756-2025 FSC-klagomål mail.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 11102-2024 FSC-klagomål mail.docx", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 41756-2025 tillsynsbegäran.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 11102-2024 tillsynsbegäran.docx", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 41756-2025 tillsynsbegäran mail.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 11102-2024 tillsynsbegäran mail.docx", "A 11102-2024")</f>
         <v/>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
         <v>45924</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45343</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>46240</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44812</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44581</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>44875</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 12363-2022</t>
+          <t>A 18346-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4064,10 +4064,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44637</v>
+        <v>44685</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4123,7 +4123,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 18346-2022</t>
+          <t>A 30285-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44685</v>
+        <v>44760</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4196,7 +4196,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30285-2022</t>
+          <t>A 12363-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44760</v>
+        <v>44637</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4286,7 +4286,7 @@
         <v>44720</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>44627</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>44476</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>44467</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>44803</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>44812</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>44826</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>44462</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>44811</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 30284-2022</t>
+          <t>A 296-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44760</v>
+        <v>44565</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4999,7 +4999,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 30287-2022</t>
+          <t>A 30284-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5016,7 +5016,7 @@
         <v>44760</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 296-2022</t>
+          <t>A 30287-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5086,10 +5086,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44565</v>
+        <v>44760</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5162,7 +5162,7 @@
         <v>44627</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 58750-2021</t>
+          <t>A 12234-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5232,10 +5232,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44489</v>
+        <v>45378</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5291,7 +5291,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 12234-2024</t>
+          <t>A 4881-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5305,10 +5305,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45378</v>
+        <v>45329</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5364,7 +5364,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 4881-2024</t>
+          <t>A 26443-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5378,10 +5378,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45329</v>
+        <v>45092</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5437,7 +5437,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 26443-2023</t>
+          <t>A 43770-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45092</v>
+        <v>45187</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5510,7 +5510,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 43770-2023</t>
+          <t>A 58750-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5524,10 +5524,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45187</v>
+        <v>44489</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5600,7 +5600,7 @@
         <v>44473</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>45296</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 61435-2024</t>
+          <t>A 47511-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5743,10 +5743,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45646</v>
+        <v>45587</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5802,7 +5802,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 5612-2025</t>
+          <t>A 61435-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45693</v>
+        <v>45646</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 37063-2024</t>
+          <t>A 5612-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5889,10 +5889,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45539</v>
+        <v>45693</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>8.800000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5948,7 +5948,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 587-2025</t>
+          <t>A 37063-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5962,10 +5962,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45664</v>
+        <v>45539</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6021,7 +6021,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 12628-2023</t>
+          <t>A 587-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6035,10 +6035,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45000</v>
+        <v>45664</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6094,7 +6094,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 65619-2021</t>
+          <t>A 12628-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6108,10 +6108,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44516</v>
+        <v>45000</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6167,7 +6167,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 47511-2024</t>
+          <t>A 65619-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6181,10 +6181,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45587</v>
+        <v>44516</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6257,7 +6257,7 @@
         <v>44826</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>45000</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>44974</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 19079-2025</t>
+          <t>A 12784-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6473,10 +6473,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45766</v>
+        <v>45733</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6532,7 +6532,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 61952-2024</t>
+          <t>A 2867-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45653</v>
+        <v>45677</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.2</v>
+        <v>10.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6605,7 +6605,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 28022-2023</t>
+          <t>A 19079-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45098</v>
+        <v>45766</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5.7</v>
+        <v>2.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6678,7 +6678,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 55972-2022</t>
+          <t>A 61952-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6692,10 +6692,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44889</v>
+        <v>45653</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6751,7 +6751,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 50349-2024</t>
+          <t>A 28022-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6765,10 +6765,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45600</v>
+        <v>45098</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.7</v>
+        <v>5.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6824,7 +6824,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 2867-2025</t>
+          <t>A 55972-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6838,10 +6838,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45677</v>
+        <v>44889</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>10.7</v>
+        <v>4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6914,7 +6914,7 @@
         <v>45855</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 7912-2024</t>
+          <t>A 41759-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6984,10 +6984,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45350</v>
+        <v>45902</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 61475-2025</t>
+          <t>A 41758-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46001</v>
+        <v>45902</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7116,7 +7116,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 41759-2025</t>
+          <t>A 41760-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7133,7 +7133,7 @@
         <v>45902</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7189,7 +7189,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 13581-2023</t>
+          <t>A 35422-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7203,10 +7203,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45006</v>
+        <v>45855</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7218,13 +7218,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7267,7 +7262,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 41758-2025</t>
+          <t>A 42857-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7281,10 +7276,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45902</v>
+        <v>45908</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7297,7 +7292,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7340,7 +7335,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 41760-2025</t>
+          <t>A 61475-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7354,10 +7349,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45902</v>
+        <v>46001</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7370,7 +7365,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7413,7 +7408,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 41761-2025</t>
+          <t>A 43684-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7427,10 +7422,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45902</v>
+        <v>45912</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7443,7 +7438,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>6.6</v>
+        <v>1.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7486,7 +7481,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 8071-2024</t>
+          <t>A 44916-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7500,10 +7495,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45351</v>
+        <v>45918</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7559,7 +7554,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 35422-2025</t>
+          <t>A 44918-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7573,10 +7568,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45855</v>
+        <v>45918</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7589,7 +7584,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.5</v>
+        <v>5.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7632,7 +7627,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 42857-2025</t>
+          <t>A 44914-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7646,10 +7641,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45908</v>
+        <v>45918</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7662,7 +7657,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7705,7 +7700,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 13975-2023</t>
+          <t>A 44915-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7719,10 +7714,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45008</v>
+        <v>45918</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7735,7 +7730,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7778,7 +7773,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 44104-2025</t>
+          <t>A 50349-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7792,10 +7787,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45915</v>
+        <v>45600</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7808,7 +7803,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7851,7 +7846,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 48904-2024</t>
+          <t>A 7912-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7865,10 +7860,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45594</v>
+        <v>45350</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7881,7 +7876,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7924,7 +7919,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 43684-2025</t>
+          <t>A 57381-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7938,10 +7933,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45912</v>
+        <v>44896</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7954,7 +7949,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7997,7 +7992,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 16473-2022</t>
+          <t>A 48730-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8011,10 +8006,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44671</v>
+        <v>45936</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8027,7 +8022,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8070,7 +8065,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 44916-2025</t>
+          <t>A 48727-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8084,10 +8079,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45918</v>
+        <v>45936</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8100,7 +8095,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.6</v>
+        <v>6.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8143,7 +8138,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 6323-2023</t>
+          <t>A 48904-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8157,10 +8152,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44960</v>
+        <v>45594</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8172,13 +8167,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8221,7 +8211,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 44918-2025</t>
+          <t>A 13581-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8235,10 +8225,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45918</v>
+        <v>45006</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8250,8 +8240,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>5.7</v>
+        <v>3.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8294,7 +8289,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 44914-2025</t>
+          <t>A 61695-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8308,10 +8303,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45918</v>
+        <v>46002</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8324,7 +8319,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8367,7 +8362,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 44915-2025</t>
+          <t>A 8071-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8381,10 +8376,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45918</v>
+        <v>45351</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8397,7 +8392,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8440,7 +8435,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 40092-2024</t>
+          <t>A 49188-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8454,10 +8449,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45554</v>
+        <v>45938</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8513,7 +8508,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 57754-2023</t>
+          <t>A 13801-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8527,10 +8522,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45246</v>
+        <v>45737</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8543,7 +8538,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8586,7 +8581,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 26886-2023</t>
+          <t>A 13975-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8600,10 +8595,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45093</v>
+        <v>45008</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8616,7 +8611,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8659,7 +8654,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 57381-2022</t>
+          <t>A 16473-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8673,10 +8668,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44896</v>
+        <v>44671</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8689,7 +8684,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8732,7 +8727,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 48730-2025</t>
+          <t>A 6323-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8746,10 +8741,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45936</v>
+        <v>44960</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8761,8 +8756,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8805,7 +8805,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 48727-2025</t>
+          <t>A 40092-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8819,10 +8819,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45936</v>
+        <v>45554</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>6.1</v>
+        <v>1.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8878,7 +8878,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 61695-2025</t>
+          <t>A 57754-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8892,10 +8892,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46002</v>
+        <v>45246</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 49188-2025</t>
+          <t>A 26886-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8965,10 +8965,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45938</v>
+        <v>45093</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9024,7 +9024,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 13801-2025</t>
+          <t>A 23541-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9034,14 +9034,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45737</v>
+        <v>46163</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9054,7 +9054,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9097,7 +9097,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 302-2024</t>
+          <t>A 55324-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45295</v>
+        <v>45971</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9128,11 +9128,11 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9175,7 +9175,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 29068-2024</t>
+          <t>A 302-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9189,10 +9189,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45481</v>
+        <v>45295</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9204,8 +9204,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9248,7 +9253,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 4225-2024</t>
+          <t>A 29068-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9262,10 +9267,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45324</v>
+        <v>45481</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9278,7 +9283,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9321,7 +9326,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 4227-2024</t>
+          <t>A 4225-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9338,7 +9343,7 @@
         <v>45324</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9351,7 +9356,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9394,7 +9399,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 38093-2022</t>
+          <t>A 4227-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9408,10 +9413,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44811</v>
+        <v>45324</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9424,7 +9429,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9467,7 +9472,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 5420-2025</t>
+          <t>A 14891-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9481,10 +9486,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45692</v>
+        <v>45743</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9497,7 +9502,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9540,7 +9545,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 51488-2022</t>
+          <t>A 38093-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9554,10 +9559,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44869</v>
+        <v>44811</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9570,7 +9575,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9613,7 +9618,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 6489-2025</t>
+          <t>A 24700-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9627,10 +9632,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45699</v>
+        <v>46171</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9642,8 +9647,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9686,7 +9696,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 9046-2022</t>
+          <t>A 5420-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9700,10 +9710,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44615</v>
+        <v>45692</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9716,7 +9726,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9759,7 +9769,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 22257-2026</t>
+          <t>A 51488-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9773,10 +9783,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46154</v>
+        <v>44869</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9789,7 +9799,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9832,7 +9842,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 55324-2025</t>
+          <t>A 6489-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9846,10 +9856,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45971</v>
+        <v>45699</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9861,13 +9871,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9910,7 +9915,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 28903-2024</t>
+          <t>A 9046-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9924,10 +9929,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45480</v>
+        <v>44615</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9940,7 +9945,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9983,7 +9988,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 61284-2022</t>
+          <t>A 28903-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9997,10 +10002,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44915</v>
+        <v>45480</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10013,7 +10018,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10056,7 +10061,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 12760-2023</t>
+          <t>A 61284-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10070,10 +10075,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45001</v>
+        <v>44915</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10086,7 +10091,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10129,7 +10134,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 62730-2023</t>
+          <t>A 12760-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10143,10 +10148,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45268</v>
+        <v>45001</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10159,7 +10164,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10202,7 +10207,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 11604-2024</t>
+          <t>A 62730-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10216,10 +10221,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45373</v>
+        <v>45268</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10232,7 +10237,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10275,7 +10280,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 23541-2026</t>
+          <t>A 25729-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10285,14 +10290,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46163</v>
+        <v>46178</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10305,7 +10310,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10348,7 +10353,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 5324-2025</t>
+          <t>A 11604-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10362,10 +10367,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45692</v>
+        <v>45373</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10378,7 +10383,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>5.1</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10421,7 +10426,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 54804-2022</t>
+          <t>A 27643-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10435,10 +10440,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44883</v>
+        <v>46190</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10451,7 +10456,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>22.6</v>
+        <v>2.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10494,7 +10499,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 52431-2023</t>
+          <t>A 5324-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10508,10 +10513,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45225</v>
+        <v>45692</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10524,7 +10529,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.6</v>
+        <v>5.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10567,7 +10572,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 33993-2023</t>
+          <t>A 56584-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10581,10 +10586,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45134</v>
+        <v>45974</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10597,7 +10602,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10640,7 +10645,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 33996-2023</t>
+          <t>A 54804-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10654,10 +10659,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45134</v>
+        <v>44883</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10670,7 +10675,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.6</v>
+        <v>22.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10713,7 +10718,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 14891-2025</t>
+          <t>A 52431-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10727,10 +10732,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45743</v>
+        <v>45225</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10743,7 +10748,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10786,7 +10791,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 7947-2024</t>
+          <t>A 33993-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10800,10 +10805,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45350</v>
+        <v>45134</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10816,7 +10821,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10859,7 +10864,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 17116-2023</t>
+          <t>A 33996-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10873,10 +10878,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45034</v>
+        <v>45134</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10889,7 +10894,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10932,7 +10937,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 24700-2026</t>
+          <t>A 15351-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10946,10 +10951,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46171</v>
+        <v>45400</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10967,7 +10972,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11010,7 +11015,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 15567-2022</t>
+          <t>A 14427-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11024,10 +11029,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44662</v>
+        <v>46100</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11040,7 +11045,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11083,7 +11088,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 21630-2024</t>
+          <t>A 7947-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11097,10 +11102,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45442</v>
+        <v>45350</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11113,7 +11118,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11156,7 +11161,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 13382-2023</t>
+          <t>A 17116-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11170,10 +11175,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45005</v>
+        <v>45034</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11186,7 +11191,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11229,7 +11234,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 56584-2025</t>
+          <t>A 15567-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11243,10 +11248,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45974</v>
+        <v>44662</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11259,7 +11264,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11302,7 +11307,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 550-2024</t>
+          <t>A 21630-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11316,10 +11321,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45299</v>
+        <v>45442</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11332,7 +11337,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.3</v>
+        <v>4.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11375,7 +11380,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 25729-2026</t>
+          <t>A 17377-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11389,10 +11394,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46178</v>
+        <v>46119</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11448,7 +11453,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 15351-2024</t>
+          <t>A 18841-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11462,10 +11467,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45400</v>
+        <v>46129</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11477,13 +11482,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11526,7 +11526,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 27643-2026</t>
+          <t>A 13382-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11540,10 +11540,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46190</v>
+        <v>45005</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11599,7 +11599,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 14427-2026</t>
+          <t>A 550-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11613,10 +11613,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46100</v>
+        <v>45299</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11672,7 +11672,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 13887-2024</t>
+          <t>A 33842-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11686,10 +11686,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45391</v>
+        <v>46251</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>11.3</v>
+        <v>7.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11745,7 +11745,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 32822-2026</t>
+          <t>A 2438-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11759,10 +11759,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46242</v>
+        <v>46036</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11818,7 +11818,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 14929-2024</t>
+          <t>A 30605-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11832,10 +11832,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45398</v>
+        <v>46210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11848,7 +11848,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11891,7 +11891,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 17377-2026</t>
+          <t>A 13887-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11905,10 +11905,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46119</v>
+        <v>45391</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.4</v>
+        <v>11.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11964,7 +11964,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 18841-2026</t>
+          <t>A 14929-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11978,10 +11978,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46129</v>
+        <v>45398</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.3</v>
+        <v>5.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12037,7 +12037,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 11104-2024</t>
+          <t>A 35883-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12051,10 +12051,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45371</v>
+        <v>46266</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12110,7 +12110,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 28910-2024</t>
+          <t>A 11104-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12124,10 +12124,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45480</v>
+        <v>45371</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12183,7 +12183,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 1382-2024</t>
+          <t>A 28910-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12197,10 +12197,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45303</v>
+        <v>45480</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12256,7 +12256,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 17114-2023</t>
+          <t>A 36722-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12270,10 +12270,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45034</v>
+        <v>46272</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12285,8 +12285,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12329,7 +12334,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 33842-2026</t>
+          <t>A 1382-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12343,10 +12348,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46251</v>
+        <v>45303</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12359,7 +12364,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>7.2</v>
+        <v>1.4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12402,7 +12407,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 43767-2023</t>
+          <t>A 37037-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12416,10 +12421,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45187</v>
+        <v>46273</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12432,7 +12437,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12475,7 +12480,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 2438-2026</t>
+          <t>A 36773-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12489,10 +12494,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46036</v>
+        <v>46272</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12504,8 +12509,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12548,7 +12558,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 30605-2026</t>
+          <t>A 17114-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12562,10 +12572,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46210</v>
+        <v>45034</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12578,7 +12588,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>10.5</v>
+        <v>1.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12621,7 +12631,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 13631-2024</t>
+          <t>A 43767-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12635,10 +12645,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45390</v>
+        <v>45187</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12651,7 +12661,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>16.4</v>
+        <v>2.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12694,7 +12704,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 37508-2023</t>
+          <t>A 13631-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12708,10 +12718,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45158</v>
+        <v>45390</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12724,7 +12734,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>6.9</v>
+        <v>16.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12767,7 +12777,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 37509-2023</t>
+          <t>A 37508-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12784,7 +12794,7 @@
         <v>45158</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12797,7 +12807,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.9</v>
+        <v>6.9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12840,7 +12850,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 15159-2023</t>
+          <t>A 37509-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12854,10 +12864,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45016</v>
+        <v>45158</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12867,11 +12877,6 @@
       <c r="G154" t="inlineStr">
         <is>
           <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I154" t="n">
@@ -12918,7 +12923,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 49879-2023</t>
+          <t>A 15159-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12932,10 +12937,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45213</v>
+        <v>45016</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12947,8 +12952,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12991,7 +13001,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 35883-2026</t>
+          <t>A 32822-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13005,10 +13015,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46266</v>
+        <v>46242</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13021,7 +13031,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>6.6</v>
+        <v>2.2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13064,7 +13074,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 44445-2023</t>
+          <t>A 49879-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13078,10 +13088,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45189</v>
+        <v>45213</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13094,7 +13104,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13137,7 +13147,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 33991-2023</t>
+          <t>A 44445-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13151,10 +13161,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45134</v>
+        <v>45189</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13167,7 +13177,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13210,7 +13220,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 5328-2025</t>
+          <t>A 33991-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13224,10 +13234,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45692</v>
+        <v>45134</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13240,7 +13250,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13283,7 +13293,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 36722-2026</t>
+          <t>A 5328-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13297,10 +13307,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46272</v>
+        <v>45692</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13312,13 +13322,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13361,7 +13366,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 37037-2026</t>
+          <t>A 3867-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13375,10 +13380,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46273</v>
+        <v>45684</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13391,7 +13396,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13434,7 +13439,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 36773-2026</t>
+          <t>A 21617-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13448,10 +13453,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46272</v>
+        <v>45441</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13463,13 +13468,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>2.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13512,7 +13512,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 3867-2025</t>
+          <t>A 22561-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13526,10 +13526,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45684</v>
+        <v>45789</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13585,7 +13585,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 21617-2024</t>
+          <t>A 12790-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13599,10 +13599,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45441</v>
+        <v>45733</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>9.699999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13658,7 +13658,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 22561-2025</t>
+          <t>A 12243-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13672,10 +13672,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45789</v>
+        <v>45729</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13688,7 +13688,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.2</v>
+        <v>10.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13731,7 +13731,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 12790-2025</t>
+          <t>A 30724-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13741,14 +13741,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45733</v>
+        <v>45496</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13804,7 +13804,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 12243-2025</t>
+          <t>A 23374-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13818,10 +13818,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45729</v>
+        <v>45791</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>10.2</v>
+        <v>0.6</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13877,7 +13877,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 30724-2024</t>
+          <t>A 23509-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13887,14 +13887,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45496</v>
+        <v>45792</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13950,7 +13950,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 23374-2025</t>
+          <t>A 5743-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13964,10 +13964,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45791</v>
+        <v>45694</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14023,7 +14023,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 23509-2025</t>
+          <t>A 24053-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14033,14 +14033,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45792</v>
+        <v>45796</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.3</v>
+        <v>11.1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14096,7 +14096,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 5743-2025</t>
+          <t>A 7819-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14110,10 +14110,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45694</v>
+        <v>45706</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.8</v>
+        <v>5.6</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14169,7 +14169,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 24053-2025</t>
+          <t>A 5740-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14179,14 +14179,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45796</v>
+        <v>45694</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>11.1</v>
+        <v>1.4</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14242,7 +14242,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 7819-2025</t>
+          <t>A 6384-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14256,10 +14256,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45706</v>
+        <v>45699</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>5.6</v>
+        <v>2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14315,7 +14315,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 5740-2025</t>
+          <t>A 36984-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14329,10 +14329,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45694</v>
+        <v>45539</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14388,7 +14388,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 6384-2025</t>
+          <t>A 27222-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14402,10 +14402,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45699</v>
+        <v>45812</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14461,7 +14461,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 36984-2024</t>
+          <t>A 28515-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14475,10 +14475,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45539</v>
+        <v>45819</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 27222-2025</t>
+          <t>A 35420-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14548,10 +14548,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45812</v>
+        <v>45855</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14607,7 +14607,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 28515-2025</t>
+          <t>A 35717-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14621,10 +14621,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45819</v>
+        <v>45860</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14677,27 +14677,27 @@
       </c>
       <c r="V178" s="2" t="inlineStr"/>
     </row>
-    <row r="179" ht="15" customHeight="1">
+    <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 35420-2025</t>
+          <t>S 460-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45855</v>
+        <v>44964</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14749,225 +14749,6 @@
         <v>0</v>
       </c>
       <c r="V179" s="2" t="inlineStr"/>
-    </row>
-    <row r="180" ht="15" customHeight="1">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>A 35717-2025</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D180" s="1" t="n">
-        <v>45860</v>
-      </c>
-      <c r="E180" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I180" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J180" t="n">
-        <v>0</v>
-      </c>
-      <c r="K180" t="n">
-        <v>0</v>
-      </c>
-      <c r="L180" t="n">
-        <v>0</v>
-      </c>
-      <c r="M180" t="n">
-        <v>0</v>
-      </c>
-      <c r="N180" t="n">
-        <v>0</v>
-      </c>
-      <c r="O180" t="n">
-        <v>0</v>
-      </c>
-      <c r="P180" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
-      <c r="R180" t="n">
-        <v>0</v>
-      </c>
-      <c r="S180" t="n">
-        <v>0</v>
-      </c>
-      <c r="T180" t="n">
-        <v>0</v>
-      </c>
-      <c r="U180" t="n">
-        <v>0</v>
-      </c>
-      <c r="V180" s="2" t="inlineStr"/>
-    </row>
-    <row r="181" ht="15" customHeight="1">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>A 12784-2025</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D181" s="1" t="n">
-        <v>45733</v>
-      </c>
-      <c r="E181" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I181" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J181" t="n">
-        <v>0</v>
-      </c>
-      <c r="K181" t="n">
-        <v>0</v>
-      </c>
-      <c r="L181" t="n">
-        <v>0</v>
-      </c>
-      <c r="M181" t="n">
-        <v>0</v>
-      </c>
-      <c r="N181" t="n">
-        <v>0</v>
-      </c>
-      <c r="O181" t="n">
-        <v>0</v>
-      </c>
-      <c r="P181" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
-      <c r="R181" t="n">
-        <v>0</v>
-      </c>
-      <c r="S181" t="n">
-        <v>0</v>
-      </c>
-      <c r="T181" t="n">
-        <v>0</v>
-      </c>
-      <c r="U181" t="n">
-        <v>0</v>
-      </c>
-      <c r="V181" s="2" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>S 460-2023</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D182" s="1" t="n">
-        <v>44964</v>
-      </c>
-      <c r="E182" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I182" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J182" t="n">
-        <v>0</v>
-      </c>
-      <c r="K182" t="n">
-        <v>0</v>
-      </c>
-      <c r="L182" t="n">
-        <v>0</v>
-      </c>
-      <c r="M182" t="n">
-        <v>0</v>
-      </c>
-      <c r="N182" t="n">
-        <v>0</v>
-      </c>
-      <c r="O182" t="n">
-        <v>0</v>
-      </c>
-      <c r="P182" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
-      <c r="R182" t="n">
-        <v>0</v>
-      </c>
-      <c r="S182" t="n">
-        <v>0</v>
-      </c>
-      <c r="T182" t="n">
-        <v>0</v>
-      </c>
-      <c r="U182" t="n">
-        <v>0</v>
-      </c>
-      <c r="V182" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LILLA EDET.xlsx
+++ b/Översikt LILLA EDET.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE179"/>
+  <dimension ref="A1:AE178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>46169</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45295</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45295</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45827</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45272</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>45139</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46044</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25298-2024</t>
+          <t>A 43771-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45462</v>
+        <v>45187</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1432,51 +1432,159 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>5.9</v>
+        <v>1.7</v>
       </c>
       <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2</v>
       </c>
-      <c r="K9" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
       </c>
       <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Slåtterfibbla
+Vätteros
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 43771-2023 artfynd.xlsx", "A 43771-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 43771-2023 karta.png", "A 43771-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 43771-2023 georefererad karta.tif", "A 43771-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 43771-2023 FSC-klagomål.docx", "A 43771-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 43771-2023 FSC-klagomål mail.docx", "A 43771-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 43771-2023 tillsynsbegäran.docx", "A 43771-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 43771-2023 tillsynsbegäran mail.docx", "A 43771-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 25298-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45462</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="n">
         <v>5</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>5</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Västlig hakmossa
@@ -1484,111 +1592,111 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 25298-2024 artfynd.xlsx", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 25298-2024 karta.png", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 25298-2024 georefererad karta.tif", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 25298-2024 FSC-klagomål.docx", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 25298-2024 FSC-klagomål mail.docx", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 25298-2024 tillsynsbegäran.docx", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 25298-2024 tillsynsbegäran mail.docx", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 25298-2024 prioriterade fågelarter.docx", "A 25298-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 28512-2025</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>45819</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>10.9</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>2</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K11" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>4</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>19</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>19</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Västlig hakmossa
@@ -1596,116 +1704,228 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 28512-2025 artfynd.xlsx", "A 28512-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 28512-2025 karta.png", "A 28512-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 28512-2025 georefererad karta.tif", "A 28512-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 28512-2025 FSC-klagomål.docx", "A 28512-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 28512-2025 FSC-klagomål mail.docx", "A 28512-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 28512-2025 tillsynsbegäran.docx", "A 28512-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 28512-2025 tillsynsbegäran mail.docx", "A 28512-2025")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 28512-2025 prioriterade fågelarter.docx", "A 28512-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 24290-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46169</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Blanksvart trämyra
+Grönpyrola
+Västlig hakmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 24290-2026 artfynd.xlsx", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 24290-2026 karta.png", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 24290-2026 georefererad karta.tif", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 24290-2026 FSC-klagomål.docx", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 24290-2026 FSC-klagomål mail.docx", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 24290-2026 tillsynsbegäran.docx", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 24290-2026 tillsynsbegäran mail.docx", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 24290-2026 prioriterade fågelarter.docx", "A 24290-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 23563-2023</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>45072</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="E13" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>Kyrkan</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="I13" t="n">
         <v>1</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J13" t="n">
         <v>4</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>4</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T13" t="n">
         <v>7</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U13" t="n">
         <v>7</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Nordfladdermus
 Dvärgpipistrell
@@ -1713,252 +1933,32 @@
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23563-2023 artfynd.xlsx", "A 23563-2023")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23563-2023 karta.png", "A 23563-2023")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23563-2023 georefererad karta.tif", "A 23563-2023")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23563-2023 FSC-klagomål.docx", "A 23563-2023")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23563-2023 FSC-klagomål mail.docx", "A 23563-2023")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23563-2023 tillsynsbegäran.docx", "A 23563-2023")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23563-2023 tillsynsbegäran mail.docx", "A 23563-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 24290-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46169</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>5</v>
-      </c>
-      <c r="U12" t="n">
-        <v>5</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Blanksvart trämyra
-Grönpyrola
-Västlig hakmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 24290-2026 artfynd.xlsx", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 24290-2026 karta.png", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 24290-2026 georefererad karta.tif", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 24290-2026 FSC-klagomål.docx", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 24290-2026 FSC-klagomål mail.docx", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 24290-2026 tillsynsbegäran.docx", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 24290-2026 tillsynsbegäran mail.docx", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 24290-2026 prioriterade fågelarter.docx", "A 24290-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 43771-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45187</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>4</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Slåtterfibbla
-Vätteros
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 43771-2023 artfynd.xlsx", "A 43771-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 43771-2023 karta.png", "A 43771-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 43771-2023 georefererad karta.tif", "A 43771-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 43771-2023 FSC-klagomål.docx", "A 43771-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 43771-2023 FSC-klagomål mail.docx", "A 43771-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 43771-2023 tillsynsbegäran.docx", "A 43771-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 43771-2023 tillsynsbegäran mail.docx", "A 43771-2023")</f>
         <v/>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         <v>45089</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 28021-2023</t>
+          <t>A 17376-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45098</v>
+        <v>46119</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2102,20 +2102,20 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2138,275 +2138,275 @@
         <v>3</v>
       </c>
       <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Slåttergubbe
+Almsnabbvinge
+Granspira</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 17376-2026 artfynd.xlsx", "A 17376-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 17376-2026 karta.png", "A 17376-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 17376-2026 georefererad karta.tif", "A 17376-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 17376-2026 FSC-klagomål.docx", "A 17376-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 17376-2026 FSC-klagomål mail.docx", "A 17376-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 17376-2026 tillsynsbegäran.docx", "A 17376-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 17376-2026 tillsynsbegäran mail.docx", "A 17376-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 28021-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45098</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>3</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Stor revmossa
 Nattskärra
 Törnskata</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 28021-2023 artfynd.xlsx", "A 28021-2023")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 28021-2023 karta.png", "A 28021-2023")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 28021-2023 georefererad karta.tif", "A 28021-2023")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 28021-2023 FSC-klagomål.docx", "A 28021-2023")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 28021-2023 FSC-klagomål mail.docx", "A 28021-2023")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 28021-2023 tillsynsbegäran.docx", "A 28021-2023")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 28021-2023 tillsynsbegäran mail.docx", "A 28021-2023")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 28021-2023 prioriterade fågelarter.docx", "A 28021-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 23559-2023</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>45072</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="E17" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>Kyrkan</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="I17" t="n">
         <v>1.7</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>1</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>1</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R17" t="n">
         <v>1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S17" t="n">
         <v>3</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>8</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>8</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Flodpärlmussla
 Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23559-2023 artfynd.xlsx", "A 23559-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23559-2023 karta.png", "A 23559-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23559-2023 georefererad karta.tif", "A 23559-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23559-2023 FSC-klagomål.docx", "A 23559-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23559-2023 FSC-klagomål mail.docx", "A 23559-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23559-2023 tillsynsbegäran.docx", "A 23559-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23559-2023 tillsynsbegäran mail.docx", "A 23559-2023")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 23559-2023 prioriterade fågelarter.docx", "A 23559-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 17376-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46119</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Slåttergubbe
-Almsnabbvinge
-Granspira</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 17376-2026 artfynd.xlsx", "A 17376-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 17376-2026 karta.png", "A 17376-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 17376-2026 georefererad karta.tif", "A 17376-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 17376-2026 FSC-klagomål.docx", "A 17376-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 17376-2026 FSC-klagomål mail.docx", "A 17376-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 17376-2026 tillsynsbegäran.docx", "A 17376-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 17376-2026 tillsynsbegäran mail.docx", "A 17376-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 23497-2023</t>
+          <t>A 5866-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45072</v>
+        <v>46052</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,17 +2437,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2474,505 +2474,505 @@
         <v>2</v>
       </c>
       <c r="T18" t="n">
+        <v>9</v>
+      </c>
+      <c r="U18" t="n">
+        <v>9</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 5866-2026 artfynd.xlsx", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 5866-2026 karta.png", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 5866-2026 georefererad karta.tif", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 5866-2026 FSC-klagomål.docx", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 5866-2026 FSC-klagomål mail.docx", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 5866-2026 tillsynsbegäran.docx", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 5866-2026 tillsynsbegäran mail.docx", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 5866-2026 prioriterade fågelarter.docx", "A 5866-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 32690-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Skirmossa
+Dunmossa</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 32690-2026 artfynd.xlsx", "A 32690-2026")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 32690-2026 karta.png", "A 32690-2026")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 32690-2026 georefererad karta.tif", "A 32690-2026")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 32690-2026 FSC-klagomål.docx", "A 32690-2026")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 32690-2026 FSC-klagomål mail.docx", "A 32690-2026")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 32690-2026 tillsynsbegäran.docx", "A 32690-2026")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 32690-2026 tillsynsbegäran mail.docx", "A 32690-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 23494-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45072</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23494-2023 artfynd.xlsx", "A 23494-2023")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23494-2023 karta.png", "A 23494-2023")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23494-2023 georefererad karta.tif", "A 23494-2023")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23494-2023 FSC-klagomål.docx", "A 23494-2023")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23494-2023 FSC-klagomål mail.docx", "A 23494-2023")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23494-2023 tillsynsbegäran.docx", "A 23494-2023")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23494-2023 tillsynsbegäran mail.docx", "A 23494-2023")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 23494-2023 prioriterade fågelarter.docx", "A 23494-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 23497-2023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45072</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
         <v>3</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U21" t="n">
         <v>3</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Stor revmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23497-2023 artfynd.xlsx", "A 23497-2023")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23497-2023 karta.png", "A 23497-2023")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23497-2023 georefererad karta.tif", "A 23497-2023")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23497-2023 FSC-klagomål.docx", "A 23497-2023")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23497-2023 FSC-klagomål mail.docx", "A 23497-2023")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23497-2023 tillsynsbegäran.docx", "A 23497-2023")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23497-2023 tillsynsbegäran mail.docx", "A 23497-2023")</f>
         <v/>
       </c>
-      <c r="AE18">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 23497-2023 prioriterade fågelarter.docx", "A 23497-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>A 13699-2024</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
         <v>45390</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+      <c r="E22" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
         <v>6.6</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J22" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K22" t="n">
         <v>1</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T22" t="n">
         <v>7</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Västlig hakmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 13699-2024 artfynd.xlsx", "A 13699-2024")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 13699-2024 karta.png", "A 13699-2024")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 13699-2024 georefererad karta.tif", "A 13699-2024")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 13699-2024 FSC-klagomål.docx", "A 13699-2024")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 13699-2024 FSC-klagomål mail.docx", "A 13699-2024")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 13699-2024 tillsynsbegäran.docx", "A 13699-2024")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 13699-2024 tillsynsbegäran mail.docx", "A 13699-2024")</f>
         <v/>
       </c>
-      <c r="AE19">
+      <c r="AE22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 13699-2024 prioriterade fågelarter.docx", "A 13699-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 5866-2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>46052</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>9</v>
-      </c>
-      <c r="U20" t="n">
-        <v>9</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 5866-2026 artfynd.xlsx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 5866-2026 karta.png", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 5866-2026 georefererad karta.tif", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 5866-2026 FSC-klagomål.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 5866-2026 FSC-klagomål mail.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 5866-2026 tillsynsbegäran.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 5866-2026 tillsynsbegäran mail.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 5866-2026 prioriterade fågelarter.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 32690-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46240</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Skirmossa
-Dunmossa</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 32690-2026 artfynd.xlsx", "A 32690-2026")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 32690-2026 karta.png", "A 32690-2026")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 32690-2026 georefererad karta.tif", "A 32690-2026")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 32690-2026 FSC-klagomål.docx", "A 32690-2026")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 32690-2026 FSC-klagomål mail.docx", "A 32690-2026")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 32690-2026 tillsynsbegäran.docx", "A 32690-2026")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 32690-2026 tillsynsbegäran mail.docx", "A 32690-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 23494-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45072</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>4</v>
-      </c>
-      <c r="U22" t="n">
-        <v>4</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23494-2023 artfynd.xlsx", "A 23494-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23494-2023 karta.png", "A 23494-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23494-2023 georefererad karta.tif", "A 23494-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23494-2023 FSC-klagomål.docx", "A 23494-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23494-2023 FSC-klagomål mail.docx", "A 23494-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23494-2023 tillsynsbegäran.docx", "A 23494-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23494-2023 tillsynsbegäran mail.docx", "A 23494-2023")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 23494-2023 prioriterade fågelarter.docx", "A 23494-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 49384-2023</t>
+          <t>A 30273-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2982,14 +2982,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45205</v>
+        <v>44759</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3001,22 +3001,17 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>1.2</v>
+        <v>12.5</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -3031,7 +3026,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3040,49 +3035,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 49384-2023 artfynd.xlsx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 30273-2022 artfynd.xlsx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 49384-2023 karta.png", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 30273-2022 karta.png", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 49384-2023 georefererad karta.tif", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 30273-2022 georefererad karta.tif", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 49384-2023 FSC-klagomål.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 30273-2022 FSC-klagomål.docx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 49384-2023 FSC-klagomål mail.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 30273-2022 FSC-klagomål mail.docx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 49384-2023 tillsynsbegäran.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 30273-2022 tillsynsbegäran.docx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 49384-2023 tillsynsbegäran mail.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 30273-2022 tillsynsbegäran mail.docx", "A 30273-2022")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 30273-2022</t>
+          <t>A 49384-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3092,14 +3087,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44759</v>
+        <v>45205</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3111,18 +3106,23 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>12.5</v>
+        <v>1.2</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
@@ -3136,7 +3136,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3145,49 +3145,49 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 30273-2022 artfynd.xlsx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 49384-2023 artfynd.xlsx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 30273-2022 karta.png", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 49384-2023 karta.png", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 30273-2022 georefererad karta.tif", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 49384-2023 georefererad karta.tif", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 30273-2022 FSC-klagomål.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 49384-2023 FSC-klagomål.docx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 30273-2022 FSC-klagomål mail.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 49384-2023 FSC-klagomål mail.docx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 30273-2022 tillsynsbegäran.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 49384-2023 tillsynsbegäran.docx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 30273-2022 tillsynsbegäran mail.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 49384-2023 tillsynsbegäran mail.docx", "A 49384-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 38522-2024</t>
+          <t>A 41756-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3201,10 +3201,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45546</v>
+        <v>45902</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3216,13 +3216,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>5.3</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3258,50 +3253,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 38522-2024 artfynd.xlsx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 41756-2025 artfynd.xlsx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 38522-2024 karta.png", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 41756-2025 karta.png", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 38522-2024 georefererad karta.tif", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 41756-2025 georefererad karta.tif", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 38522-2024 FSC-klagomål.docx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 41756-2025 FSC-klagomål.docx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 38522-2024 FSC-klagomål mail.docx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 41756-2025 FSC-klagomål mail.docx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 38522-2024 tillsynsbegäran.docx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 41756-2025 tillsynsbegäran.docx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 38522-2024 tillsynsbegäran mail.docx", "A 38522-2024")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 38522-2024 prioriterade fågelarter.docx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 41756-2025 tillsynsbegäran mail.docx", "A 41756-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41756-2025</t>
+          <t>A 7062-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3311,14 +3302,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45902</v>
+        <v>45343</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3331,7 +3322,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>9.1</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3371,35 +3362,35 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 41756-2025 artfynd.xlsx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 7062-2024 artfynd.xlsx", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 41756-2025 karta.png", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 7062-2024 karta.png", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 41756-2025 georefererad karta.tif", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 7062-2024 georefererad karta.tif", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 41756-2025 FSC-klagomål.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 7062-2024 FSC-klagomål.docx", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 41756-2025 FSC-klagomål mail.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 7062-2024 FSC-klagomål mail.docx", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 41756-2025 tillsynsbegäran.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 7062-2024 tillsynsbegäran.docx", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 41756-2025 tillsynsbegäran mail.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 7062-2024 tillsynsbegäran mail.docx", "A 7062-2024")</f>
         <v/>
       </c>
     </row>
@@ -3423,7 +3414,7 @@
         <v>45371</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3528,7 +3519,7 @@
         <v>45924</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3616,7 +3607,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 7062-2024</t>
+          <t>A 32692-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3626,14 +3617,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45343</v>
+        <v>46240</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3645,11 +3636,16 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>9.1</v>
+        <v>1.2</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -3686,42 +3682,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 7062-2024 artfynd.xlsx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 32692-2026 artfynd.xlsx", "A 32692-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 7062-2024 karta.png", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 32692-2026 karta.png", "A 32692-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 7062-2024 georefererad karta.tif", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 32692-2026 georefererad karta.tif", "A 32692-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 7062-2024 FSC-klagomål.docx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 32692-2026 FSC-klagomål.docx", "A 32692-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 7062-2024 FSC-klagomål mail.docx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 32692-2026 FSC-klagomål mail.docx", "A 32692-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 7062-2024 tillsynsbegäran.docx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 32692-2026 tillsynsbegäran.docx", "A 32692-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 7062-2024 tillsynsbegäran mail.docx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 32692-2026 tillsynsbegäran mail.docx", "A 32692-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 32692-2026</t>
+          <t>A 38522-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3735,10 +3731,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46240</v>
+        <v>45546</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3756,10 +3752,10 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.2</v>
+        <v>5.3</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -3792,39 +3788,43 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 32692-2026 artfynd.xlsx", "A 32692-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 38522-2024 artfynd.xlsx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 32692-2026 karta.png", "A 32692-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 38522-2024 karta.png", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 32692-2026 georefererad karta.tif", "A 32692-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 38522-2024 georefererad karta.tif", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 32692-2026 FSC-klagomål.docx", "A 32692-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 38522-2024 FSC-klagomål.docx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 32692-2026 FSC-klagomål mail.docx", "A 32692-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 38522-2024 FSC-klagomål mail.docx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 32692-2026 tillsynsbegäran.docx", "A 32692-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 38522-2024 tillsynsbegäran.docx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 32692-2026 tillsynsbegäran mail.docx", "A 32692-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 38522-2024 tillsynsbegäran mail.docx", "A 38522-2024")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 38522-2024 prioriterade fågelarter.docx", "A 38522-2024")</f>
         <v/>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
         <v>44812</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44581</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>44875</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 18346-2022</t>
+          <t>A 12363-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4064,10 +4064,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44685</v>
+        <v>44637</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4123,7 +4123,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 30285-2022</t>
+          <t>A 18346-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44760</v>
+        <v>44685</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4196,7 +4196,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 12363-2022</t>
+          <t>A 30285-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44637</v>
+        <v>44760</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4286,7 +4286,7 @@
         <v>44720</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>44627</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>44476</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>44467</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>44803</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>44812</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>44826</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 51569-2021</t>
+          <t>A 5328-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4794,10 +4794,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44462</v>
+        <v>45692</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4853,7 +4853,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 38059-2022</t>
+          <t>A 21617-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4867,10 +4867,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44811</v>
+        <v>45441</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4926,7 +4926,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 296-2022</t>
+          <t>A 10726-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44565</v>
+        <v>44627</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4999,7 +4999,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 30284-2022</t>
+          <t>A 38059-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44760</v>
+        <v>44811</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 30287-2022</t>
+          <t>A 296-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5086,10 +5086,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44760</v>
+        <v>44565</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 10726-2022</t>
+          <t>A 30284-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5159,10 +5159,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44627</v>
+        <v>44760</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5218,7 +5218,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 12234-2024</t>
+          <t>A 30287-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5232,10 +5232,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45378</v>
+        <v>44760</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5291,7 +5291,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 4881-2024</t>
+          <t>A 12234-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5305,10 +5305,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45329</v>
+        <v>45378</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5364,7 +5364,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 26443-2023</t>
+          <t>A 30724-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5374,14 +5374,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45092</v>
+        <v>45496</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5437,7 +5437,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 43770-2023</t>
+          <t>A 22561-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45187</v>
+        <v>45789</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5510,7 +5510,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 58750-2021</t>
+          <t>A 23509-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5524,10 +5524,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44489</v>
+        <v>45792</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5583,7 +5583,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 54681-2021</t>
+          <t>A 23374-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44473</v>
+        <v>45791</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5656,7 +5656,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 406-2024</t>
+          <t>A 12790-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45296</v>
+        <v>45733</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5729,7 +5729,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 47511-2024</t>
+          <t>A 12784-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5743,10 +5743,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45587</v>
+        <v>45733</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5802,7 +5802,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 61435-2024</t>
+          <t>A 12243-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45646</v>
+        <v>45729</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.7</v>
+        <v>10.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 5612-2025</t>
+          <t>A 13887-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5889,10 +5889,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45693</v>
+        <v>45391</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>11.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5948,7 +5948,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 37063-2024</t>
+          <t>A 24053-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5958,14 +5958,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45539</v>
+        <v>45796</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>8.800000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6021,7 +6021,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 587-2025</t>
+          <t>A 61284-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6035,10 +6035,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45664</v>
+        <v>44915</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6094,7 +6094,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 12628-2023</t>
+          <t>A 52431-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6108,10 +6108,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45000</v>
+        <v>45225</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6167,7 +6167,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 65619-2021</t>
+          <t>A 2867-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6181,10 +6181,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44516</v>
+        <v>45677</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.9</v>
+        <v>10.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6240,7 +6240,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 41411-2022</t>
+          <t>A 35423-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6254,10 +6254,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44826</v>
+        <v>45855</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 12647-2023</t>
+          <t>A 5743-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6327,10 +6327,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45000</v>
+        <v>45694</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6386,7 +6386,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 8117-2023</t>
+          <t>A 7819-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6400,10 +6400,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44974</v>
+        <v>45706</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>11</v>
+        <v>5.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 12784-2025</t>
+          <t>A 11104-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6473,10 +6473,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45733</v>
+        <v>45371</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6532,7 +6532,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 2867-2025</t>
+          <t>A 26886-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45677</v>
+        <v>45093</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>10.7</v>
+        <v>3.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6605,7 +6605,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 19079-2025</t>
+          <t>A 26443-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45766</v>
+        <v>45092</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6678,7 +6678,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 61952-2024</t>
+          <t>A 17114-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6692,10 +6692,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45653</v>
+        <v>45034</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.2</v>
+        <v>1.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6751,7 +6751,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 28022-2023</t>
+          <t>A 58750-2021</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6765,10 +6765,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45098</v>
+        <v>44489</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5.7</v>
+        <v>1.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6824,7 +6824,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 55972-2022</t>
+          <t>A 7947-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6838,10 +6838,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44889</v>
+        <v>45350</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6897,7 +6897,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 35423-2025</t>
+          <t>A 41758-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6911,10 +6911,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45855</v>
+        <v>45902</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6970,7 +6970,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 41759-2025</t>
+          <t>A 41760-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6987,7 +6987,7 @@
         <v>45902</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 41758-2025</t>
+          <t>A 41759-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7060,7 +7060,7 @@
         <v>45902</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7116,7 +7116,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 41760-2025</t>
+          <t>A 33993-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7130,10 +7130,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45902</v>
+        <v>45134</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7189,7 +7189,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 35422-2025</t>
+          <t>A 33996-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7203,10 +7203,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45855</v>
+        <v>45134</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7262,7 +7262,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 42857-2025</t>
+          <t>A 35422-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7276,10 +7276,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45908</v>
+        <v>45855</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7335,7 +7335,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 61475-2025</t>
+          <t>A 42857-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7349,10 +7349,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46001</v>
+        <v>45908</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.6</v>
+        <v>1.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7408,7 +7408,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 43684-2025</t>
+          <t>A 65619-2021</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7422,10 +7422,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45912</v>
+        <v>44516</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7481,7 +7481,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 44916-2025</t>
+          <t>A 13581-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7495,10 +7495,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45918</v>
+        <v>45006</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7510,8 +7510,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7554,7 +7559,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 44918-2025</t>
+          <t>A 51488-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7568,10 +7573,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45918</v>
+        <v>44869</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7584,7 +7589,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>5.7</v>
+        <v>2.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7627,7 +7632,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 44914-2025</t>
+          <t>A 43684-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7641,10 +7646,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45918</v>
+        <v>45912</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7657,7 +7662,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7700,7 +7705,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 44915-2025</t>
+          <t>A 28910-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7714,10 +7719,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45918</v>
+        <v>45480</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7730,7 +7735,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7773,7 +7778,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 50349-2024</t>
+          <t>A 11604-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7787,10 +7792,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45600</v>
+        <v>45373</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7803,7 +7808,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7846,7 +7851,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 7912-2024</t>
+          <t>A 44914-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7860,10 +7865,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45350</v>
+        <v>45918</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7876,7 +7881,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7919,7 +7924,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 57381-2022</t>
+          <t>A 44915-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7933,10 +7938,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44896</v>
+        <v>45918</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7949,7 +7954,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7992,7 +7997,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 48730-2025</t>
+          <t>A 44918-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8006,10 +8011,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45936</v>
+        <v>45918</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8022,7 +8027,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8065,7 +8070,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 48727-2025</t>
+          <t>A 54681-2021</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8079,10 +8084,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45936</v>
+        <v>44473</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8095,7 +8100,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>6.1</v>
+        <v>4.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8138,7 +8143,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 48904-2024</t>
+          <t>A 15567-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8152,10 +8157,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45594</v>
+        <v>44662</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8168,7 +8173,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8211,7 +8216,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 13581-2023</t>
+          <t>A 44916-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8225,10 +8230,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45006</v>
+        <v>45918</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8240,13 +8245,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8289,7 +8289,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 61695-2025</t>
+          <t>A 1382-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46002</v>
+        <v>45303</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8362,7 +8362,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 8071-2024</t>
+          <t>A 587-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8376,10 +8376,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45351</v>
+        <v>45664</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8435,7 +8435,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 49188-2025</t>
+          <t>A 5740-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8449,10 +8449,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45938</v>
+        <v>45694</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8508,7 +8508,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 13801-2025</t>
+          <t>A 6384-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8522,10 +8522,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45737</v>
+        <v>45699</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8581,7 +8581,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 13975-2023</t>
+          <t>A 47511-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8595,10 +8595,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45008</v>
+        <v>45587</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8654,7 +8654,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 16473-2022</t>
+          <t>A 36984-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8668,10 +8668,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44671</v>
+        <v>45539</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 6323-2023</t>
+          <t>A 43770-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8741,10 +8741,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44960</v>
+        <v>45187</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8756,13 +8756,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8805,7 +8800,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 40092-2024</t>
+          <t>A 4881-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8819,10 +8814,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45554</v>
+        <v>45329</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8835,7 +8830,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8878,7 +8873,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 57754-2023</t>
+          <t>A 57381-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8892,10 +8887,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45246</v>
+        <v>44896</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8908,7 +8903,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8951,7 +8946,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 26886-2023</t>
+          <t>A 48727-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8965,10 +8960,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45093</v>
+        <v>45936</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8981,7 +8976,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.6</v>
+        <v>6.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9024,7 +9019,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 23541-2026</t>
+          <t>A 48730-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9034,14 +9029,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46163</v>
+        <v>45936</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9054,7 +9049,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9097,7 +9092,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 55324-2025</t>
+          <t>A 27222-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9111,10 +9106,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45971</v>
+        <v>45812</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9126,13 +9121,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9175,7 +9165,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 302-2024</t>
+          <t>A 7912-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9189,10 +9179,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45295</v>
+        <v>45350</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9204,13 +9194,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9253,7 +9238,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 29068-2024</t>
+          <t>A 13801-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9267,10 +9252,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45481</v>
+        <v>45737</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9283,7 +9268,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9326,7 +9311,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 4225-2024</t>
+          <t>A 49188-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9340,10 +9325,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45324</v>
+        <v>45938</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9356,7 +9341,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9399,7 +9384,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 4227-2024</t>
+          <t>A 6323-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9413,10 +9398,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45324</v>
+        <v>44960</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9428,8 +9413,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9472,7 +9462,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 14891-2025</t>
+          <t>A 54804-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9486,10 +9476,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45743</v>
+        <v>44883</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9502,7 +9492,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.7</v>
+        <v>22.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9545,7 +9535,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 38093-2022</t>
+          <t>A 9046-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9559,10 +9549,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44811</v>
+        <v>44615</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9575,7 +9565,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9618,7 +9608,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 24700-2026</t>
+          <t>A 8117-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9632,10 +9622,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46171</v>
+        <v>44974</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9647,13 +9637,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>1.7</v>
+        <v>11</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9696,7 +9681,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 5420-2025</t>
+          <t>A 12628-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9710,10 +9695,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45692</v>
+        <v>45000</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9726,7 +9711,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9769,7 +9754,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 51488-2022</t>
+          <t>A 28515-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9783,10 +9768,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44869</v>
+        <v>45819</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9799,7 +9784,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9842,7 +9827,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 6489-2025</t>
+          <t>A 61435-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9856,10 +9841,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45699</v>
+        <v>45646</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9872,7 +9857,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9915,7 +9900,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 9046-2022</t>
+          <t>A 50349-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9929,10 +9914,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44615</v>
+        <v>45600</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9945,7 +9930,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9988,7 +9973,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 28903-2024</t>
+          <t>A 55324-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10002,10 +9987,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45480</v>
+        <v>45971</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10017,8 +10002,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10061,7 +10051,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 61284-2022</t>
+          <t>A 14929-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10075,10 +10065,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44915</v>
+        <v>45398</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10091,7 +10081,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>5.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10134,7 +10124,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 12760-2023</t>
+          <t>A 21630-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10148,10 +10138,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45001</v>
+        <v>45442</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10164,7 +10154,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10207,7 +10197,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 62730-2023</t>
+          <t>A 28903-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10221,10 +10211,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45268</v>
+        <v>45480</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10237,7 +10227,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10280,7 +10270,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 25729-2026</t>
+          <t>A 43767-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10294,10 +10284,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46178</v>
+        <v>45187</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10310,7 +10300,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10353,7 +10343,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 11604-2024</t>
+          <t>A 12647-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10367,10 +10357,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45373</v>
+        <v>45000</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10383,7 +10373,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10426,7 +10416,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 27643-2026</t>
+          <t>A 33991-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10440,10 +10430,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46190</v>
+        <v>45134</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10456,7 +10446,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10499,7 +10489,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 5324-2025</t>
+          <t>A 41411-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10513,10 +10503,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45692</v>
+        <v>44826</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10529,7 +10519,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10572,7 +10562,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 56584-2025</t>
+          <t>A 4225-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10586,10 +10576,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45974</v>
+        <v>45324</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10602,7 +10592,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10645,7 +10635,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 54804-2022</t>
+          <t>A 4227-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10659,10 +10649,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44883</v>
+        <v>45324</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10675,7 +10665,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>22.6</v>
+        <v>1.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10718,7 +10708,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 52431-2023</t>
+          <t>A 37508-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10732,10 +10722,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45225</v>
+        <v>45158</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10748,7 +10738,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.6</v>
+        <v>6.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10791,7 +10781,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 33993-2023</t>
+          <t>A 37509-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10805,10 +10795,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45134</v>
+        <v>45158</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10821,7 +10811,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10864,7 +10854,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 33996-2023</t>
+          <t>A 32822-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10878,10 +10868,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45134</v>
+        <v>46242</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10894,7 +10884,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10937,7 +10927,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 15351-2024</t>
+          <t>A 56584-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10951,10 +10941,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45400</v>
+        <v>45974</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10966,13 +10956,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11015,7 +11000,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 14427-2026</t>
+          <t>A 15351-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11029,10 +11014,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46100</v>
+        <v>45400</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11044,8 +11029,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11088,7 +11078,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 7947-2024</t>
+          <t>A 13382-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11102,10 +11092,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45350</v>
+        <v>45005</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11118,7 +11108,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11161,7 +11151,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 17116-2023</t>
+          <t>A 38093-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11175,10 +11165,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45034</v>
+        <v>44811</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11191,7 +11181,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11234,7 +11224,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 15567-2022</t>
+          <t>A 16473-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11248,10 +11238,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44662</v>
+        <v>44671</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11264,7 +11254,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11307,7 +11297,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 21630-2024</t>
+          <t>A 14427-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11321,10 +11311,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45442</v>
+        <v>46100</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11337,7 +11327,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11380,7 +11370,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 17377-2026</t>
+          <t>A 40092-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11394,10 +11384,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46119</v>
+        <v>45554</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11410,7 +11400,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11453,7 +11443,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 18841-2026</t>
+          <t>A 35420-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11467,10 +11457,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46129</v>
+        <v>45855</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11483,7 +11473,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11526,7 +11516,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 13382-2023</t>
+          <t>A 57754-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11540,10 +11530,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45005</v>
+        <v>45246</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11556,7 +11546,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11599,7 +11589,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 550-2024</t>
+          <t>A 35717-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11613,10 +11603,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45299</v>
+        <v>45860</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11629,7 +11619,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11672,7 +11662,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 33842-2026</t>
+          <t>A 17377-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11686,10 +11676,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46251</v>
+        <v>46119</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11702,7 +11692,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>7.2</v>
+        <v>1.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11745,7 +11735,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 2438-2026</t>
+          <t>A 44445-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11759,10 +11749,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46036</v>
+        <v>45189</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11775,7 +11765,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11818,7 +11808,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 30605-2026</t>
+          <t>A 18841-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11832,10 +11822,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46210</v>
+        <v>46129</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11848,7 +11838,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>10.5</v>
+        <v>1.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11891,7 +11881,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 13887-2024</t>
+          <t>A 17116-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11905,10 +11895,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45391</v>
+        <v>45034</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11921,7 +11911,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>11.3</v>
+        <v>1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11964,7 +11954,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 14929-2024</t>
+          <t>A 12760-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11978,10 +11968,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45398</v>
+        <v>45001</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11994,7 +11984,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12037,7 +12027,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 35883-2026</t>
+          <t>A 5612-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12051,10 +12041,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46266</v>
+        <v>45693</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12067,7 +12057,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>6.6</v>
+        <v>1.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12110,7 +12100,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 11104-2024</t>
+          <t>A 302-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12124,10 +12114,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45371</v>
+        <v>45295</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12139,8 +12129,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12183,7 +12178,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 28910-2024</t>
+          <t>A 29068-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12197,10 +12192,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45480</v>
+        <v>45481</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12213,7 +12208,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12256,7 +12251,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 36722-2026</t>
+          <t>A 5324-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12270,10 +12265,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46272</v>
+        <v>45692</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12285,13 +12280,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>2.2</v>
+        <v>5.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12334,7 +12324,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 1382-2024</t>
+          <t>A 19079-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12348,10 +12338,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45303</v>
+        <v>45766</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12364,7 +12354,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12407,7 +12397,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 37037-2026</t>
+          <t>A 13631-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12421,10 +12411,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46273</v>
+        <v>45390</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12437,7 +12427,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3.9</v>
+        <v>16.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12480,7 +12470,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 36773-2026</t>
+          <t>A 37063-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12494,10 +12484,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46272</v>
+        <v>45539</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12509,13 +12499,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>2.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12558,7 +12543,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 17114-2023</t>
+          <t>A 15159-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12572,10 +12557,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45034</v>
+        <v>45016</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12587,8 +12572,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12631,7 +12621,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 43767-2023</t>
+          <t>A 28022-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12645,10 +12635,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45187</v>
+        <v>45098</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12661,7 +12651,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.3</v>
+        <v>5.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12704,7 +12694,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 13631-2024</t>
+          <t>A 550-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12718,10 +12708,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45390</v>
+        <v>45299</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12734,7 +12724,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>16.4</v>
+        <v>2.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12777,7 +12767,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 37508-2023</t>
+          <t>A 13975-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12791,10 +12781,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45158</v>
+        <v>45008</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12807,7 +12797,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>6.9</v>
+        <v>2.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12850,7 +12840,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 37509-2023</t>
+          <t>A 48904-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12864,10 +12854,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45158</v>
+        <v>45594</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12880,7 +12870,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12923,7 +12913,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 15159-2023</t>
+          <t>A 8071-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12937,10 +12927,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45016</v>
+        <v>45351</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12952,13 +12942,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13001,7 +12986,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 32822-2026</t>
+          <t>A 61952-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13015,10 +13000,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46242</v>
+        <v>45653</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13031,7 +13016,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13074,7 +13059,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 49879-2023</t>
+          <t>A 61475-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13088,10 +13073,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45213</v>
+        <v>46001</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13104,7 +13089,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13147,7 +13132,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 44445-2023</t>
+          <t>A 6489-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13161,10 +13146,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45189</v>
+        <v>45699</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13177,7 +13162,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13220,7 +13205,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 33991-2023</t>
+          <t>A 406-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13234,10 +13219,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45134</v>
+        <v>45296</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13250,7 +13235,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13293,7 +13278,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 5328-2025</t>
+          <t>A 55972-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13307,10 +13292,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45692</v>
+        <v>44889</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13323,7 +13308,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13366,7 +13351,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 3867-2025</t>
+          <t>A 62730-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13380,10 +13365,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45684</v>
+        <v>45268</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13396,7 +13381,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13439,7 +13424,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 21617-2024</t>
+          <t>A 49879-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13453,10 +13438,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45441</v>
+        <v>45213</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13469,7 +13454,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>9.699999999999999</v>
+        <v>5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13512,7 +13497,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 22561-2025</t>
+          <t>A 5420-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13526,10 +13511,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45789</v>
+        <v>45692</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13542,7 +13527,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13585,7 +13570,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 12790-2025</t>
+          <t>A 61695-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13599,10 +13584,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45733</v>
+        <v>46002</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13615,7 +13600,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13658,7 +13643,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 12243-2025</t>
+          <t>A 3867-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13672,10 +13657,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45729</v>
+        <v>45684</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13688,7 +13673,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>10.2</v>
+        <v>1.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13731,7 +13716,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 30724-2024</t>
+          <t>A 23541-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13745,10 +13730,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45496</v>
+        <v>46163</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13761,7 +13746,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13804,7 +13789,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 23374-2025</t>
+          <t>A 14891-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13818,10 +13803,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45791</v>
+        <v>45743</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13834,7 +13819,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13877,7 +13862,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 23509-2025</t>
+          <t>A 24700-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13891,10 +13876,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45792</v>
+        <v>46171</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13906,8 +13891,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13950,7 +13940,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 5743-2025</t>
+          <t>A 25729-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13964,10 +13954,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45694</v>
+        <v>46178</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13980,7 +13970,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14023,7 +14013,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 24053-2025</t>
+          <t>A 27643-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14033,14 +14023,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45796</v>
+        <v>46190</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14053,7 +14043,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>11.1</v>
+        <v>2.2</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14096,7 +14086,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 7819-2025</t>
+          <t>A 33842-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14110,10 +14100,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45706</v>
+        <v>46251</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14126,7 +14116,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14169,7 +14159,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 5740-2025</t>
+          <t>A 30605-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14183,10 +14173,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45694</v>
+        <v>46210</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14199,7 +14189,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.4</v>
+        <v>10.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14242,7 +14232,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 6384-2025</t>
+          <t>A 2438-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14256,10 +14246,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45699</v>
+        <v>46036</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14272,7 +14262,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14315,7 +14305,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 36984-2024</t>
+          <t>A 35883-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14329,10 +14319,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45539</v>
+        <v>46266</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14345,7 +14335,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.7</v>
+        <v>6.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14388,7 +14378,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 27222-2025</t>
+          <t>A 36773-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14402,10 +14392,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45812</v>
+        <v>46272</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14417,8 +14407,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14461,7 +14456,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 28515-2025</t>
+          <t>A 36722-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14475,10 +14470,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45819</v>
+        <v>46272</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14490,8 +14485,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14534,7 +14534,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 35420-2025</t>
+          <t>A 37037-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14548,10 +14548,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45855</v>
+        <v>46273</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14604,27 +14604,27 @@
       </c>
       <c r="V177" s="2" t="inlineStr"/>
     </row>
-    <row r="178" ht="15" customHeight="1">
+    <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 35717-2025</t>
+          <t>S 460-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45860</v>
+        <v>44964</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14676,79 +14676,6 @@
         <v>0</v>
       </c>
       <c r="V178" s="2" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>S 460-2023</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D179" s="1" t="n">
-        <v>44964</v>
-      </c>
-      <c r="E179" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I179" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J179" t="n">
-        <v>0</v>
-      </c>
-      <c r="K179" t="n">
-        <v>0</v>
-      </c>
-      <c r="L179" t="n">
-        <v>0</v>
-      </c>
-      <c r="M179" t="n">
-        <v>0</v>
-      </c>
-      <c r="N179" t="n">
-        <v>0</v>
-      </c>
-      <c r="O179" t="n">
-        <v>0</v>
-      </c>
-      <c r="P179" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
-      <c r="R179" t="n">
-        <v>0</v>
-      </c>
-      <c r="S179" t="n">
-        <v>0</v>
-      </c>
-      <c r="T179" t="n">
-        <v>0</v>
-      </c>
-      <c r="U179" t="n">
-        <v>0</v>
-      </c>
-      <c r="V179" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LILLA EDET.xlsx
+++ b/Översikt LILLA EDET.xlsx
@@ -601,7 +601,7 @@
         <v>46169</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45295</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45295</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45827</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45272</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>45139</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46044</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 43771-2023</t>
+          <t>A 25298-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45187</v>
+        <v>45462</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1432,23 +1432,28 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>1.7</v>
+        <v>5.9</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1457,21 +1462,470 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
       </c>
       <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>5</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Västlig hakmossa
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 25298-2024 artfynd.xlsx", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 25298-2024 karta.png", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 25298-2024 georefererad karta.tif", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 25298-2024 FSC-klagomål.docx", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 25298-2024 FSC-klagomål mail.docx", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 25298-2024 tillsynsbegäran.docx", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 25298-2024 tillsynsbegäran mail.docx", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 25298-2024 prioriterade fågelarter.docx", "A 25298-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 28512-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45819</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>4</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="T10" t="n">
+        <v>19</v>
+      </c>
+      <c r="U10" t="n">
+        <v>19</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Västlig hakmossa
+Spillkråka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 28512-2025 artfynd.xlsx", "A 28512-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 28512-2025 karta.png", "A 28512-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 28512-2025 georefererad karta.tif", "A 28512-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 28512-2025 FSC-klagomål.docx", "A 28512-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 28512-2025 FSC-klagomål mail.docx", "A 28512-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 28512-2025 tillsynsbegäran.docx", "A 28512-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 28512-2025 tillsynsbegäran mail.docx", "A 28512-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 28512-2025 prioriterade fågelarter.docx", "A 28512-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 23563-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45072</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7</v>
+      </c>
+      <c r="U11" t="n">
+        <v>7</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Nordfladdermus
+Dvärgpipistrell
+Vattenfladdermus
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23563-2023 artfynd.xlsx", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23563-2023 karta.png", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23563-2023 georefererad karta.tif", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23563-2023 FSC-klagomål.docx", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23563-2023 FSC-klagomål mail.docx", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23563-2023 tillsynsbegäran.docx", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23563-2023 tillsynsbegäran mail.docx", "A 23563-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 24290-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46169</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Blanksvart trämyra
+Grönpyrola
+Västlig hakmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 24290-2026 artfynd.xlsx", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 24290-2026 karta.png", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 24290-2026 georefererad karta.tif", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 24290-2026 FSC-klagomål.docx", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 24290-2026 FSC-klagomål mail.docx", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 24290-2026 tillsynsbegäran.docx", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 24290-2026 tillsynsbegäran mail.docx", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 24290-2026 prioriterade fågelarter.docx", "A 24290-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 43771-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45187</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Ask
 Slåtterfibbla
@@ -1479,486 +1933,32 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 43771-2023 artfynd.xlsx", "A 43771-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 43771-2023 karta.png", "A 43771-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 43771-2023 georefererad karta.tif", "A 43771-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 43771-2023 FSC-klagomål.docx", "A 43771-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 43771-2023 FSC-klagomål mail.docx", "A 43771-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 43771-2023 tillsynsbegäran.docx", "A 43771-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 43771-2023 tillsynsbegäran mail.docx", "A 43771-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 25298-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45462</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>5</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Västlig hakmossa
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 25298-2024 artfynd.xlsx", "A 25298-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 25298-2024 karta.png", "A 25298-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 25298-2024 georefererad karta.tif", "A 25298-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 25298-2024 FSC-klagomål.docx", "A 25298-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 25298-2024 FSC-klagomål mail.docx", "A 25298-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 25298-2024 tillsynsbegäran.docx", "A 25298-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 25298-2024 tillsynsbegäran mail.docx", "A 25298-2024")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 25298-2024 prioriterade fågelarter.docx", "A 25298-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 28512-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45819</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>19</v>
-      </c>
-      <c r="U11" t="n">
-        <v>19</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa
-Västlig hakmossa
-Spillkråka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 28512-2025 artfynd.xlsx", "A 28512-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 28512-2025 karta.png", "A 28512-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 28512-2025 georefererad karta.tif", "A 28512-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 28512-2025 FSC-klagomål.docx", "A 28512-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 28512-2025 FSC-klagomål mail.docx", "A 28512-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 28512-2025 tillsynsbegäran.docx", "A 28512-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 28512-2025 tillsynsbegäran mail.docx", "A 28512-2025")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 28512-2025 prioriterade fågelarter.docx", "A 28512-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 24290-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46169</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>5</v>
-      </c>
-      <c r="U12" t="n">
-        <v>5</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Blanksvart trämyra
-Grönpyrola
-Västlig hakmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 24290-2026 artfynd.xlsx", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 24290-2026 karta.png", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 24290-2026 georefererad karta.tif", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 24290-2026 FSC-klagomål.docx", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 24290-2026 FSC-klagomål mail.docx", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 24290-2026 tillsynsbegäran.docx", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 24290-2026 tillsynsbegäran mail.docx", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 24290-2026 prioriterade fågelarter.docx", "A 24290-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 23563-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45072</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>4</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>7</v>
-      </c>
-      <c r="U13" t="n">
-        <v>7</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Nordfladdermus
-Dvärgpipistrell
-Vattenfladdermus
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23563-2023 artfynd.xlsx", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23563-2023 karta.png", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23563-2023 georefererad karta.tif", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23563-2023 FSC-klagomål.docx", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23563-2023 FSC-klagomål mail.docx", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23563-2023 tillsynsbegäran.docx", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23563-2023 tillsynsbegäran mail.docx", "A 23563-2023")</f>
         <v/>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         <v>45089</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 17376-2026</t>
+          <t>A 28021-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46119</v>
+        <v>45098</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2102,19 +2102,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2138,275 +2138,275 @@
         <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Stor revmossa
+Nattskärra
+Törnskata</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 28021-2023 artfynd.xlsx", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 28021-2023 karta.png", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 28021-2023 georefererad karta.tif", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 28021-2023 FSC-klagomål.docx", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 28021-2023 FSC-klagomål mail.docx", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 28021-2023 tillsynsbegäran.docx", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 28021-2023 tillsynsbegäran mail.docx", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 28021-2023 prioriterade fågelarter.docx", "A 28021-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 23559-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45072</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>8</v>
+      </c>
+      <c r="U16" t="n">
+        <v>8</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Flodpärlmussla
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23559-2023 artfynd.xlsx", "A 23559-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23559-2023 karta.png", "A 23559-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23559-2023 georefererad karta.tif", "A 23559-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23559-2023 FSC-klagomål.docx", "A 23559-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23559-2023 FSC-klagomål mail.docx", "A 23559-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23559-2023 tillsynsbegäran.docx", "A 23559-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23559-2023 tillsynsbegäran mail.docx", "A 23559-2023")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 23559-2023 prioriterade fågelarter.docx", "A 23559-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 17376-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46119</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Slåttergubbe
 Almsnabbvinge
 Granspira</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 17376-2026 artfynd.xlsx", "A 17376-2026")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 17376-2026 karta.png", "A 17376-2026")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 17376-2026 georefererad karta.tif", "A 17376-2026")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 17376-2026 FSC-klagomål.docx", "A 17376-2026")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 17376-2026 FSC-klagomål mail.docx", "A 17376-2026")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 17376-2026 tillsynsbegäran.docx", "A 17376-2026")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 17376-2026 tillsynsbegäran mail.docx", "A 17376-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 28021-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45098</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Stor revmossa
-Nattskärra
-Törnskata</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 28021-2023 artfynd.xlsx", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 28021-2023 karta.png", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 28021-2023 georefererad karta.tif", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 28021-2023 FSC-klagomål.docx", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 28021-2023 FSC-klagomål mail.docx", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 28021-2023 tillsynsbegäran.docx", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 28021-2023 tillsynsbegäran mail.docx", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 28021-2023 prioriterade fågelarter.docx", "A 28021-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 23559-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45072</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>8</v>
-      </c>
-      <c r="U17" t="n">
-        <v>8</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Flodpärlmussla
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23559-2023 artfynd.xlsx", "A 23559-2023")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23559-2023 karta.png", "A 23559-2023")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23559-2023 georefererad karta.tif", "A 23559-2023")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23559-2023 FSC-klagomål.docx", "A 23559-2023")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23559-2023 FSC-klagomål mail.docx", "A 23559-2023")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23559-2023 tillsynsbegäran.docx", "A 23559-2023")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23559-2023 tillsynsbegäran mail.docx", "A 23559-2023")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 23559-2023 prioriterade fågelarter.docx", "A 23559-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 5866-2026</t>
+          <t>A 23497-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46052</v>
+        <v>45072</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,17 +2437,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2474,505 +2474,505 @@
         <v>2</v>
       </c>
       <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Stor revmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23497-2023 artfynd.xlsx", "A 23497-2023")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23497-2023 karta.png", "A 23497-2023")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23497-2023 georefererad karta.tif", "A 23497-2023")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23497-2023 FSC-klagomål.docx", "A 23497-2023")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23497-2023 FSC-klagomål mail.docx", "A 23497-2023")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23497-2023 tillsynsbegäran.docx", "A 23497-2023")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23497-2023 tillsynsbegäran mail.docx", "A 23497-2023")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 23497-2023 prioriterade fågelarter.docx", "A 23497-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 5866-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
         <v>9</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>9</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 5866-2026 artfynd.xlsx", "A 5866-2026")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 5866-2026 karta.png", "A 5866-2026")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 5866-2026 georefererad karta.tif", "A 5866-2026")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 5866-2026 FSC-klagomål.docx", "A 5866-2026")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 5866-2026 FSC-klagomål mail.docx", "A 5866-2026")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 5866-2026 tillsynsbegäran.docx", "A 5866-2026")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 5866-2026 tillsynsbegäran mail.docx", "A 5866-2026")</f>
         <v/>
       </c>
-      <c r="AE18">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 5866-2026 prioriterade fågelarter.docx", "A 5866-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 13699-2024</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45390</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>7</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 13699-2024 artfynd.xlsx", "A 13699-2024")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 13699-2024 karta.png", "A 13699-2024")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 13699-2024 georefererad karta.tif", "A 13699-2024")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 13699-2024 FSC-klagomål.docx", "A 13699-2024")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 13699-2024 FSC-klagomål mail.docx", "A 13699-2024")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 13699-2024 tillsynsbegäran.docx", "A 13699-2024")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 13699-2024 tillsynsbegäran mail.docx", "A 13699-2024")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 13699-2024 prioriterade fågelarter.docx", "A 13699-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A 32690-2026</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
         <v>46240</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
+      <c r="E21" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>Kyrkan</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="I21" t="n">
         <v>4.6</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M21" t="n">
         <v>1</v>
       </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>2</v>
       </c>
-      <c r="R19" t="n">
+      <c r="R21" t="n">
         <v>1</v>
       </c>
-      <c r="S19" t="n">
+      <c r="S21" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T21" t="n">
         <v>2</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U21" t="n">
         <v>1</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Skirmossa
 Dunmossa</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 32690-2026 artfynd.xlsx", "A 32690-2026")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 32690-2026 karta.png", "A 32690-2026")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 32690-2026 georefererad karta.tif", "A 32690-2026")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 32690-2026 FSC-klagomål.docx", "A 32690-2026")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 32690-2026 FSC-klagomål mail.docx", "A 32690-2026")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 32690-2026 tillsynsbegäran.docx", "A 32690-2026")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 32690-2026 tillsynsbegäran mail.docx", "A 32690-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>A 23494-2023</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
         <v>45072</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
+      <c r="E22" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>Kyrkan</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="I22" t="n">
         <v>1.3</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J22" t="n">
         <v>2</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>2</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T22" t="n">
         <v>4</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U22" t="n">
         <v>4</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23494-2023 artfynd.xlsx", "A 23494-2023")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23494-2023 karta.png", "A 23494-2023")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23494-2023 georefererad karta.tif", "A 23494-2023")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23494-2023 FSC-klagomål.docx", "A 23494-2023")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23494-2023 FSC-klagomål mail.docx", "A 23494-2023")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23494-2023 tillsynsbegäran.docx", "A 23494-2023")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23494-2023 tillsynsbegäran mail.docx", "A 23494-2023")</f>
         <v/>
       </c>
-      <c r="AE20">
+      <c r="AE22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 23494-2023 prioriterade fågelarter.docx", "A 23494-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 23497-2023</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45072</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>3</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Stor revmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23497-2023 artfynd.xlsx", "A 23497-2023")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23497-2023 karta.png", "A 23497-2023")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23497-2023 georefererad karta.tif", "A 23497-2023")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23497-2023 FSC-klagomål.docx", "A 23497-2023")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23497-2023 FSC-klagomål mail.docx", "A 23497-2023")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23497-2023 tillsynsbegäran.docx", "A 23497-2023")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23497-2023 tillsynsbegäran mail.docx", "A 23497-2023")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 23497-2023 prioriterade fågelarter.docx", "A 23497-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 13699-2024</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45390</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>7</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Västlig hakmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 13699-2024 artfynd.xlsx", "A 13699-2024")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 13699-2024 karta.png", "A 13699-2024")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 13699-2024 georefererad karta.tif", "A 13699-2024")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 13699-2024 FSC-klagomål.docx", "A 13699-2024")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 13699-2024 FSC-klagomål mail.docx", "A 13699-2024")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 13699-2024 tillsynsbegäran.docx", "A 13699-2024")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 13699-2024 tillsynsbegäran mail.docx", "A 13699-2024")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 13699-2024 prioriterade fågelarter.docx", "A 13699-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 30273-2022</t>
+          <t>A 49384-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2982,14 +2982,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44759</v>
+        <v>45205</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3001,18 +3001,23 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>12.5</v>
+        <v>1.2</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
@@ -3026,7 +3031,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3035,49 +3040,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 30273-2022 artfynd.xlsx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 49384-2023 artfynd.xlsx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 30273-2022 karta.png", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 49384-2023 karta.png", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 30273-2022 georefererad karta.tif", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 49384-2023 georefererad karta.tif", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 30273-2022 FSC-klagomål.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 49384-2023 FSC-klagomål.docx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 30273-2022 FSC-klagomål mail.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 49384-2023 FSC-klagomål mail.docx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 30273-2022 tillsynsbegäran.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 49384-2023 tillsynsbegäran.docx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 30273-2022 tillsynsbegäran mail.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 49384-2023 tillsynsbegäran mail.docx", "A 49384-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 49384-2023</t>
+          <t>A 30273-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3087,14 +3092,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45205</v>
+        <v>44759</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3106,22 +3111,17 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>1.2</v>
+        <v>12.5</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3136,7 +3136,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3145,42 +3145,42 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 49384-2023 artfynd.xlsx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 30273-2022 artfynd.xlsx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 49384-2023 karta.png", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 30273-2022 karta.png", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 49384-2023 georefererad karta.tif", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 30273-2022 georefererad karta.tif", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 49384-2023 FSC-klagomål.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 30273-2022 FSC-klagomål.docx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 49384-2023 FSC-klagomål mail.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 30273-2022 FSC-klagomål mail.docx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 49384-2023 tillsynsbegäran.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 30273-2022 tillsynsbegäran.docx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 49384-2023 tillsynsbegäran mail.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 30273-2022 tillsynsbegäran mail.docx", "A 30273-2022")</f>
         <v/>
       </c>
     </row>
@@ -3204,7 +3204,7 @@
         <v>45902</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 7062-2024</t>
+          <t>A 38522-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3302,14 +3302,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45343</v>
+        <v>45546</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3321,8 +3321,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>9.1</v>
+        <v>5.3</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3358,39 +3363,43 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 7062-2024 artfynd.xlsx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 38522-2024 artfynd.xlsx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 7062-2024 karta.png", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 38522-2024 karta.png", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 7062-2024 georefererad karta.tif", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 38522-2024 georefererad karta.tif", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 7062-2024 FSC-klagomål.docx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 38522-2024 FSC-klagomål.docx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 7062-2024 FSC-klagomål mail.docx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 38522-2024 FSC-klagomål mail.docx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 7062-2024 tillsynsbegäran.docx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 38522-2024 tillsynsbegäran.docx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 7062-2024 tillsynsbegäran mail.docx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 38522-2024 tillsynsbegäran mail.docx", "A 38522-2024")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 38522-2024 prioriterade fågelarter.docx", "A 38522-2024")</f>
         <v/>
       </c>
     </row>
@@ -3414,7 +3423,7 @@
         <v>45371</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3519,7 +3528,7 @@
         <v>45924</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3607,7 +3616,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 32692-2026</t>
+          <t>A 7062-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3617,14 +3626,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46240</v>
+        <v>45343</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3636,16 +3645,11 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>1.2</v>
+        <v>9.1</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -3682,42 +3686,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 32692-2026 artfynd.xlsx", "A 32692-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 7062-2024 artfynd.xlsx", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 32692-2026 karta.png", "A 32692-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 7062-2024 karta.png", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 32692-2026 georefererad karta.tif", "A 32692-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 7062-2024 georefererad karta.tif", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 32692-2026 FSC-klagomål.docx", "A 32692-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 7062-2024 FSC-klagomål.docx", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 32692-2026 FSC-klagomål mail.docx", "A 32692-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 7062-2024 FSC-klagomål mail.docx", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 32692-2026 tillsynsbegäran.docx", "A 32692-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 7062-2024 tillsynsbegäran.docx", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 32692-2026 tillsynsbegäran mail.docx", "A 32692-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 7062-2024 tillsynsbegäran mail.docx", "A 7062-2024")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 38522-2024</t>
+          <t>A 32692-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3731,10 +3735,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45546</v>
+        <v>46240</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3752,10 +3756,10 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>5.3</v>
+        <v>1.2</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -3788,43 +3792,39 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 38522-2024 artfynd.xlsx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 32692-2026 artfynd.xlsx", "A 32692-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 38522-2024 karta.png", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 32692-2026 karta.png", "A 32692-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 38522-2024 georefererad karta.tif", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 32692-2026 georefererad karta.tif", "A 32692-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 38522-2024 FSC-klagomål.docx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 32692-2026 FSC-klagomål.docx", "A 32692-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 38522-2024 FSC-klagomål mail.docx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 32692-2026 FSC-klagomål mail.docx", "A 32692-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 38522-2024 tillsynsbegäran.docx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 32692-2026 tillsynsbegäran.docx", "A 32692-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 38522-2024 tillsynsbegäran mail.docx", "A 38522-2024")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 38522-2024 prioriterade fågelarter.docx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 32692-2026 tillsynsbegäran mail.docx", "A 32692-2026")</f>
         <v/>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
         <v>44812</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44581</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>44875</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>44637</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 18346-2022</t>
+          <t>A 30285-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44685</v>
+        <v>44760</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4196,7 +4196,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30285-2022</t>
+          <t>A 18346-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44760</v>
+        <v>44685</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4286,7 +4286,7 @@
         <v>44720</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>44627</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>44476</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>44467</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>44803</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>44812</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>44826</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 5328-2025</t>
+          <t>A 38059-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4794,10 +4794,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45692</v>
+        <v>44811</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4853,7 +4853,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 21617-2024</t>
+          <t>A 296-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4867,10 +4867,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45441</v>
+        <v>44565</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>9.699999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4926,7 +4926,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10726-2022</t>
+          <t>A 30284-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44627</v>
+        <v>44760</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4999,7 +4999,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 38059-2022</t>
+          <t>A 30287-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44811</v>
+        <v>44760</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 296-2022</t>
+          <t>A 10726-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5086,10 +5086,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44565</v>
+        <v>44627</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 30284-2022</t>
+          <t>A 58750-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5159,10 +5159,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44760</v>
+        <v>44489</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5218,7 +5218,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 30287-2022</t>
+          <t>A 12234-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5232,10 +5232,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44760</v>
+        <v>45378</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5291,7 +5291,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 12234-2024</t>
+          <t>A 4881-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5305,10 +5305,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45378</v>
+        <v>45329</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5364,7 +5364,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 30724-2024</t>
+          <t>A 26443-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5374,14 +5374,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45496</v>
+        <v>45092</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5437,7 +5437,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 22561-2025</t>
+          <t>A 43770-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45789</v>
+        <v>45187</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5510,7 +5510,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 23509-2025</t>
+          <t>A 406-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5524,10 +5524,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45792</v>
+        <v>45296</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.3</v>
+        <v>4.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5583,7 +5583,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 23374-2025</t>
+          <t>A 54681-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45791</v>
+        <v>44473</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5656,7 +5656,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 12790-2025</t>
+          <t>A 47511-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45733</v>
+        <v>45587</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5729,7 +5729,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 12784-2025</t>
+          <t>A 61435-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5743,10 +5743,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45733</v>
+        <v>45646</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5802,7 +5802,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 12243-2025</t>
+          <t>A 5612-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45729</v>
+        <v>45693</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>10.2</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 13887-2024</t>
+          <t>A 37063-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5889,10 +5889,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45391</v>
+        <v>45539</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>11.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5948,7 +5948,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 24053-2025</t>
+          <t>A 587-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5958,14 +5958,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45796</v>
+        <v>45664</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>11.1</v>
+        <v>0.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6021,7 +6021,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 61284-2022</t>
+          <t>A 12628-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6035,10 +6035,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44915</v>
+        <v>45000</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6094,7 +6094,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 52431-2023</t>
+          <t>A 65619-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6108,10 +6108,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45225</v>
+        <v>44516</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6167,7 +6167,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 2867-2025</t>
+          <t>A 41411-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6181,10 +6181,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45677</v>
+        <v>44826</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>10.7</v>
+        <v>3.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6240,7 +6240,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 35423-2025</t>
+          <t>A 12647-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6254,10 +6254,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45855</v>
+        <v>45000</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6313,7 +6313,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 5743-2025</t>
+          <t>A 8117-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6327,10 +6327,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45694</v>
+        <v>44974</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.8</v>
+        <v>11</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6386,7 +6386,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 7819-2025</t>
+          <t>A 12784-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6400,10 +6400,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45706</v>
+        <v>45733</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5.6</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 11104-2024</t>
+          <t>A 2867-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6473,10 +6473,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45371</v>
+        <v>45677</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.6</v>
+        <v>10.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6532,7 +6532,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 26886-2023</t>
+          <t>A 19079-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45093</v>
+        <v>45766</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6605,7 +6605,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 26443-2023</t>
+          <t>A 41759-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45092</v>
+        <v>45902</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6678,7 +6678,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 17114-2023</t>
+          <t>A 61952-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6692,10 +6692,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45034</v>
+        <v>45653</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6751,7 +6751,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 58750-2021</t>
+          <t>A 41758-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6765,10 +6765,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44489</v>
+        <v>45902</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 7947-2024</t>
+          <t>A 41760-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6838,10 +6838,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45350</v>
+        <v>45902</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6897,7 +6897,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 41758-2025</t>
+          <t>A 35422-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6911,10 +6911,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45902</v>
+        <v>45855</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6970,7 +6970,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 41760-2025</t>
+          <t>A 42857-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6984,10 +6984,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45902</v>
+        <v>45908</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 41759-2025</t>
+          <t>A 35423-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45902</v>
+        <v>45855</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7116,7 +7116,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 33993-2023</t>
+          <t>A 43684-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7130,10 +7130,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45134</v>
+        <v>45912</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7189,7 +7189,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 33996-2023</t>
+          <t>A 50349-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7203,10 +7203,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45134</v>
+        <v>45600</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7262,7 +7262,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35422-2025</t>
+          <t>A 28022-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7276,10 +7276,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45855</v>
+        <v>45098</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>5.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7335,7 +7335,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 42857-2025</t>
+          <t>A 44916-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7349,10 +7349,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45908</v>
+        <v>45918</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 65619-2021</t>
+          <t>A 44918-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7422,10 +7422,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44516</v>
+        <v>45918</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.9</v>
+        <v>5.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7481,7 +7481,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 13581-2023</t>
+          <t>A 44914-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7495,10 +7495,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45006</v>
+        <v>45918</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7510,13 +7510,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7559,7 +7554,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 51488-2022</t>
+          <t>A 44915-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7573,10 +7568,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44869</v>
+        <v>45918</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7589,7 +7584,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7632,7 +7627,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 43684-2025</t>
+          <t>A 55972-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7646,10 +7641,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45912</v>
+        <v>44889</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7662,7 +7657,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7705,7 +7700,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 28910-2024</t>
+          <t>A 7912-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7719,10 +7714,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45480</v>
+        <v>45350</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7735,7 +7730,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7778,7 +7773,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 11604-2024</t>
+          <t>A 57381-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7792,10 +7787,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45373</v>
+        <v>44896</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7808,7 +7803,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7851,7 +7846,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 44914-2025</t>
+          <t>A 13581-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7865,10 +7860,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45918</v>
+        <v>45006</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7880,8 +7875,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7924,7 +7924,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 44915-2025</t>
+          <t>A 8071-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7938,10 +7938,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45918</v>
+        <v>45351</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 44918-2025</t>
+          <t>A 48730-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8011,10 +8011,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45918</v>
+        <v>45936</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8070,7 +8070,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 54681-2021</t>
+          <t>A 48727-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44473</v>
+        <v>45936</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.1</v>
+        <v>6.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8143,7 +8143,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 15567-2022</t>
+          <t>A 49188-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8157,10 +8157,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44662</v>
+        <v>45938</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8216,7 +8216,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 44916-2025</t>
+          <t>A 13801-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8230,10 +8230,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45918</v>
+        <v>45737</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8289,7 +8289,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 1382-2024</t>
+          <t>A 13975-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45303</v>
+        <v>45008</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8362,7 +8362,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 587-2025</t>
+          <t>A 16473-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8376,10 +8376,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45664</v>
+        <v>44671</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8435,7 +8435,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 5740-2025</t>
+          <t>A 6323-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8449,10 +8449,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45694</v>
+        <v>44960</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8464,8 +8464,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8508,7 +8513,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 6384-2025</t>
+          <t>A 61475-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8522,10 +8527,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45699</v>
+        <v>46001</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8538,7 +8543,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8581,7 +8586,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 47511-2024</t>
+          <t>A 40092-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8595,10 +8600,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45587</v>
+        <v>45554</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8611,7 +8616,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8654,7 +8659,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 36984-2024</t>
+          <t>A 57754-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8668,10 +8673,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45539</v>
+        <v>45246</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8684,7 +8689,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8727,7 +8732,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 43770-2023</t>
+          <t>A 26886-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8741,10 +8746,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45187</v>
+        <v>45093</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8757,7 +8762,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8800,7 +8805,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 4881-2024</t>
+          <t>A 48904-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8814,10 +8819,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45329</v>
+        <v>45594</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8830,7 +8835,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8873,7 +8878,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 57381-2022</t>
+          <t>A 55324-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8887,10 +8892,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44896</v>
+        <v>45971</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8902,8 +8907,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8946,7 +8956,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 48727-2025</t>
+          <t>A 302-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8960,10 +8970,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45936</v>
+        <v>45295</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8975,8 +8985,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>6.1</v>
+        <v>2.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9019,7 +9034,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 48730-2025</t>
+          <t>A 29068-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9033,10 +9048,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45936</v>
+        <v>45481</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9049,7 +9064,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9092,7 +9107,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 27222-2025</t>
+          <t>A 4225-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9106,10 +9121,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45812</v>
+        <v>45324</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9165,7 +9180,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 7912-2024</t>
+          <t>A 4227-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9179,10 +9194,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45350</v>
+        <v>45324</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9195,7 +9210,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9238,7 +9253,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 13801-2025</t>
+          <t>A 38093-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9252,10 +9267,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45737</v>
+        <v>44811</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9268,7 +9283,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9311,7 +9326,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 49188-2025</t>
+          <t>A 61695-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9325,10 +9340,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45938</v>
+        <v>46002</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9341,7 +9356,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9384,7 +9399,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 6323-2023</t>
+          <t>A 5420-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9398,10 +9413,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44960</v>
+        <v>45692</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9413,13 +9428,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9462,7 +9472,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 54804-2022</t>
+          <t>A 51488-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9476,10 +9486,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44883</v>
+        <v>44869</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9492,7 +9502,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>22.6</v>
+        <v>2.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9535,7 +9545,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 9046-2022</t>
+          <t>A 6489-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9549,10 +9559,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44615</v>
+        <v>45699</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9565,7 +9575,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9608,7 +9618,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 8117-2023</t>
+          <t>A 9046-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9622,10 +9632,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44974</v>
+        <v>44615</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9638,7 +9648,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9681,7 +9691,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 12628-2023</t>
+          <t>A 28903-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9695,10 +9705,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45000</v>
+        <v>45480</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9711,7 +9721,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9754,7 +9764,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 28515-2025</t>
+          <t>A 61284-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9768,10 +9778,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45819</v>
+        <v>44915</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9784,7 +9794,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9827,7 +9837,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 61435-2024</t>
+          <t>A 12760-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9841,10 +9851,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45646</v>
+        <v>45001</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9857,7 +9867,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9900,7 +9910,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 50349-2024</t>
+          <t>A 62730-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9914,10 +9924,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45600</v>
+        <v>45268</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9930,7 +9940,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9973,7 +9983,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 55324-2025</t>
+          <t>A 23541-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9983,14 +9993,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45971</v>
+        <v>46163</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10002,13 +10012,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10051,7 +10056,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 14929-2024</t>
+          <t>A 11604-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10065,10 +10070,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45398</v>
+        <v>45373</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10081,7 +10086,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>5.1</v>
+        <v>2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10124,7 +10129,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 21630-2024</t>
+          <t>A 5324-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10138,10 +10143,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45442</v>
+        <v>45692</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10154,7 +10159,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10197,7 +10202,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 28903-2024</t>
+          <t>A 54804-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10211,10 +10216,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45480</v>
+        <v>44883</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10227,7 +10232,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>3.4</v>
+        <v>22.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10270,7 +10275,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 43767-2023</t>
+          <t>A 52431-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10284,10 +10289,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45187</v>
+        <v>45225</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10300,7 +10305,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10343,7 +10348,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 12647-2023</t>
+          <t>A 33993-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10357,10 +10362,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45000</v>
+        <v>45134</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10373,7 +10378,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10416,7 +10421,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 33991-2023</t>
+          <t>A 33996-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10433,7 +10438,7 @@
         <v>45134</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10446,7 +10451,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10489,7 +10494,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 41411-2022</t>
+          <t>A 56584-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10503,10 +10508,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44826</v>
+        <v>45974</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10519,7 +10524,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10562,7 +10567,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 4225-2024</t>
+          <t>A 14891-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10576,10 +10581,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45324</v>
+        <v>45743</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10592,7 +10597,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10635,7 +10640,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 4227-2024</t>
+          <t>A 24700-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10649,10 +10654,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45324</v>
+        <v>46171</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10664,8 +10669,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10708,7 +10718,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 37508-2023</t>
+          <t>A 15351-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10722,10 +10732,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45158</v>
+        <v>45400</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10737,8 +10747,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>6.9</v>
+        <v>3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10781,7 +10796,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 37509-2023</t>
+          <t>A 7947-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10795,10 +10810,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45158</v>
+        <v>45350</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10811,7 +10826,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10854,7 +10869,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 32822-2026</t>
+          <t>A 17116-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10868,10 +10883,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46242</v>
+        <v>45034</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10884,7 +10899,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10927,7 +10942,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 56584-2025</t>
+          <t>A 14427-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10941,10 +10956,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45974</v>
+        <v>46100</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10957,7 +10972,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11000,7 +11015,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 15351-2024</t>
+          <t>A 15567-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11014,10 +11029,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45400</v>
+        <v>44662</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11029,13 +11044,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11078,7 +11088,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 13382-2023</t>
+          <t>A 21630-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11092,10 +11102,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45005</v>
+        <v>45442</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11108,7 +11118,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11151,7 +11161,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 38093-2022</t>
+          <t>A 25729-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11165,10 +11175,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44811</v>
+        <v>46178</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11224,7 +11234,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 16473-2022</t>
+          <t>A 27643-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11238,10 +11248,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44671</v>
+        <v>46190</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11254,7 +11264,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11297,7 +11307,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 14427-2026</t>
+          <t>A 17377-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11311,10 +11321,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46100</v>
+        <v>46119</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11327,7 +11337,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11370,7 +11380,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 40092-2024</t>
+          <t>A 13382-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11384,10 +11394,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45554</v>
+        <v>45005</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11400,7 +11410,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11443,7 +11453,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 35420-2025</t>
+          <t>A 550-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11457,10 +11467,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45855</v>
+        <v>45299</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11473,7 +11483,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11516,7 +11526,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 57754-2023</t>
+          <t>A 18841-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11530,10 +11540,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45246</v>
+        <v>46129</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11546,7 +11556,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11589,7 +11599,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 35717-2025</t>
+          <t>A 13887-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11603,10 +11613,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45860</v>
+        <v>45391</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11619,7 +11629,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.6</v>
+        <v>11.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11662,7 +11672,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 17377-2026</t>
+          <t>A 33842-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11676,10 +11686,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46119</v>
+        <v>46251</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11692,7 +11702,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.4</v>
+        <v>7.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11735,7 +11745,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 44445-2023</t>
+          <t>A 14929-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11749,10 +11759,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45189</v>
+        <v>45398</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11765,7 +11775,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11808,7 +11818,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 18841-2026</t>
+          <t>A 2438-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11822,10 +11832,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46129</v>
+        <v>46036</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11838,7 +11848,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11881,7 +11891,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 17116-2023</t>
+          <t>A 30605-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11895,10 +11905,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45034</v>
+        <v>46210</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11911,7 +11921,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
+        <v>10.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11954,7 +11964,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 12760-2023</t>
+          <t>A 11104-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11968,10 +11978,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45001</v>
+        <v>45371</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11984,7 +11994,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12027,7 +12037,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 5612-2025</t>
+          <t>A 28910-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12041,10 +12051,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45693</v>
+        <v>45480</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12057,7 +12067,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12100,7 +12110,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 302-2024</t>
+          <t>A 1382-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12114,10 +12124,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45295</v>
+        <v>45303</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12129,13 +12139,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12178,7 +12183,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 29068-2024</t>
+          <t>A 17114-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12192,10 +12197,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45481</v>
+        <v>45034</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12208,7 +12213,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12251,7 +12256,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 5324-2025</t>
+          <t>A 35883-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12265,10 +12270,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45692</v>
+        <v>46266</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12281,7 +12286,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12324,7 +12329,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 19079-2025</t>
+          <t>A 43767-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12338,10 +12343,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45766</v>
+        <v>45187</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12354,7 +12359,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12414,7 +12419,7 @@
         <v>45390</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12470,7 +12475,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 37063-2024</t>
+          <t>A 36722-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12484,10 +12489,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45539</v>
+        <v>46272</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12499,8 +12504,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>8.800000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12543,7 +12553,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 15159-2023</t>
+          <t>A 37037-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12557,10 +12567,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45016</v>
+        <v>46273</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12572,13 +12582,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12621,7 +12626,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 28022-2023</t>
+          <t>A 36773-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12635,10 +12640,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45098</v>
+        <v>46272</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12650,8 +12655,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12694,7 +12704,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 550-2024</t>
+          <t>A 37508-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12708,10 +12718,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45299</v>
+        <v>45158</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12724,7 +12734,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.3</v>
+        <v>6.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12767,7 +12777,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 13975-2023</t>
+          <t>A 37509-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12781,10 +12791,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45008</v>
+        <v>45158</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12797,7 +12807,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12840,7 +12850,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 48904-2024</t>
+          <t>A 15159-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12854,10 +12864,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45594</v>
+        <v>45016</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12869,8 +12879,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>3.9</v>
+        <v>0.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12913,7 +12928,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 8071-2024</t>
+          <t>A 49879-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12927,10 +12942,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45351</v>
+        <v>45213</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12943,7 +12958,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12986,7 +13001,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 61952-2024</t>
+          <t>A 44445-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13000,10 +13015,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45653</v>
+        <v>45189</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13016,7 +13031,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13059,7 +13074,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 61475-2025</t>
+          <t>A 33991-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13073,10 +13088,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46001</v>
+        <v>45134</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13089,7 +13104,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>4.6</v>
+        <v>0.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13132,7 +13147,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 6489-2025</t>
+          <t>A 5328-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13146,10 +13161,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45699</v>
+        <v>45692</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13162,7 +13177,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13205,7 +13220,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 406-2024</t>
+          <t>A 3867-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13219,10 +13234,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45296</v>
+        <v>45684</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13235,7 +13250,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13278,7 +13293,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 55972-2022</t>
+          <t>A 21617-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13292,10 +13307,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44889</v>
+        <v>45441</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13308,7 +13323,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13351,7 +13366,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 62730-2023</t>
+          <t>A 32822-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13365,10 +13380,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45268</v>
+        <v>46242</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13381,7 +13396,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13424,7 +13439,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 49879-2023</t>
+          <t>A 22561-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13438,10 +13453,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45213</v>
+        <v>45789</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13454,7 +13469,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13497,7 +13512,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 5420-2025</t>
+          <t>A 12790-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13511,10 +13526,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45692</v>
+        <v>45733</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13527,7 +13542,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13570,7 +13585,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 61695-2025</t>
+          <t>A 12243-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13584,10 +13599,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46002</v>
+        <v>45729</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13600,7 +13615,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>3.7</v>
+        <v>10.2</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13643,7 +13658,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 3867-2025</t>
+          <t>A 30724-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13653,14 +13668,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45684</v>
+        <v>45496</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13673,7 +13688,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13716,7 +13731,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 23541-2026</t>
+          <t>A 23374-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13726,14 +13741,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46163</v>
+        <v>45791</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13746,7 +13761,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13789,7 +13804,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 14891-2025</t>
+          <t>A 23509-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13803,10 +13818,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45743</v>
+        <v>45792</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13819,7 +13834,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13862,7 +13877,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 24700-2026</t>
+          <t>A 5743-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13876,10 +13891,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46171</v>
+        <v>45694</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13891,13 +13906,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13940,7 +13950,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 25729-2026</t>
+          <t>A 24053-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13950,14 +13960,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46178</v>
+        <v>45796</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13970,7 +13980,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.4</v>
+        <v>11.1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14013,7 +14023,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 27643-2026</t>
+          <t>A 7819-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14027,10 +14037,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46190</v>
+        <v>45706</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14043,7 +14053,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2.2</v>
+        <v>5.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14086,7 +14096,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 33842-2026</t>
+          <t>A 5740-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14100,10 +14110,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46251</v>
+        <v>45694</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14116,7 +14126,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>7.2</v>
+        <v>1.4</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14159,7 +14169,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 30605-2026</t>
+          <t>A 6384-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14173,10 +14183,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46210</v>
+        <v>45699</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14189,7 +14199,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>10.5</v>
+        <v>2</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14232,7 +14242,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 2438-2026</t>
+          <t>A 36984-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14246,10 +14256,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46036</v>
+        <v>45539</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14262,7 +14272,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14305,7 +14315,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 35883-2026</t>
+          <t>A 27222-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14319,10 +14329,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46266</v>
+        <v>45812</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14335,7 +14345,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>6.6</v>
+        <v>1.3</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14378,7 +14388,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 36773-2026</t>
+          <t>A 28515-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14392,10 +14402,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46272</v>
+        <v>45819</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14407,13 +14417,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14456,7 +14461,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 36722-2026</t>
+          <t>A 35420-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14470,10 +14475,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46272</v>
+        <v>45855</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14485,13 +14490,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14534,7 +14534,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 37037-2026</t>
+          <t>A 35717-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14548,10 +14548,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46273</v>
+        <v>45860</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14624,7 +14624,7 @@
         <v>44964</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>

--- a/Översikt LILLA EDET.xlsx
+++ b/Översikt LILLA EDET.xlsx
@@ -601,7 +601,7 @@
         <v>46169</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45295</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45295</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45827</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 62846-2023</t>
+          <t>A 34396-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45272</v>
+        <v>45139</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.4</v>
+        <v>7</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1127,12 +1127,127 @@
         <v>7</v>
       </c>
       <c r="T6" t="n">
+        <v>24</v>
+      </c>
+      <c r="U6" t="n">
+        <v>24</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Blåmossa
+Kambräken
+Stor revmossa
+Västlig hakmossa
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 34396-2023 artfynd.xlsx", "A 34396-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 34396-2023 karta.png", "A 34396-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 34396-2023 georefererad karta.tif", "A 34396-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 34396-2023 FSC-klagomål.docx", "A 34396-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 34396-2023 FSC-klagomål mail.docx", "A 34396-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 34396-2023 tillsynsbegäran.docx", "A 34396-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 34396-2023 tillsynsbegäran mail.docx", "A 34396-2023")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 34396-2023 prioriterade fågelarter.docx", "A 34396-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 62846-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45272</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>7</v>
+      </c>
+      <c r="T7" t="n">
         <v>17</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Kattfotslav
 Blåmossa
@@ -1143,147 +1258,32 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 62846-2023 artfynd.xlsx", "A 62846-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 62846-2023 karta.png", "A 62846-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 62846-2023 georefererad karta.tif", "A 62846-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 62846-2023 FSC-klagomål.docx", "A 62846-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 62846-2023 FSC-klagomål mail.docx", "A 62846-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 62846-2023 tillsynsbegäran.docx", "A 62846-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 62846-2023 tillsynsbegäran mail.docx", "A 62846-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 34396-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45139</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>5</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>7</v>
-      </c>
-      <c r="T7" t="n">
-        <v>24</v>
-      </c>
-      <c r="U7" t="n">
-        <v>24</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Blåmossa
-Kambräken
-Stor revmossa
-Västlig hakmossa
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 34396-2023 artfynd.xlsx", "A 34396-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 34396-2023 karta.png", "A 34396-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 34396-2023 georefererad karta.tif", "A 34396-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 34396-2023 FSC-klagomål.docx", "A 34396-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 34396-2023 FSC-klagomål mail.docx", "A 34396-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 34396-2023 tillsynsbegäran.docx", "A 34396-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 34396-2023 tillsynsbegäran mail.docx", "A 34396-2023")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 34396-2023 prioriterade fågelarter.docx", "A 34396-2023")</f>
         <v/>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
         <v>46044</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25298-2024</t>
+          <t>A 43771-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45462</v>
+        <v>45187</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1432,51 +1432,496 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>5.9</v>
+        <v>1.7</v>
       </c>
       <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2</v>
       </c>
-      <c r="K9" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
       </c>
       <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Slåtterfibbla
+Vätteros
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 43771-2023 artfynd.xlsx", "A 43771-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 43771-2023 karta.png", "A 43771-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 43771-2023 georefererad karta.tif", "A 43771-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 43771-2023 FSC-klagomål.docx", "A 43771-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 43771-2023 FSC-klagomål mail.docx", "A 43771-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 43771-2023 tillsynsbegäran.docx", "A 43771-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 43771-2023 tillsynsbegäran mail.docx", "A 43771-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 28512-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45819</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>19</v>
+      </c>
+      <c r="U10" t="n">
+        <v>19</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Västlig hakmossa
+Spillkråka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 28512-2025 artfynd.xlsx", "A 28512-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 28512-2025 karta.png", "A 28512-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 28512-2025 georefererad karta.tif", "A 28512-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 28512-2025 FSC-klagomål.docx", "A 28512-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 28512-2025 FSC-klagomål mail.docx", "A 28512-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 28512-2025 tillsynsbegäran.docx", "A 28512-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 28512-2025 tillsynsbegäran mail.docx", "A 28512-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 28512-2025 prioriterade fågelarter.docx", "A 28512-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 24290-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46169</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
         <v>5</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U11" t="n">
         <v>5</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Blanksvart trämyra
+Grönpyrola
+Västlig hakmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 24290-2026 artfynd.xlsx", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 24290-2026 karta.png", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 24290-2026 georefererad karta.tif", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 24290-2026 FSC-klagomål.docx", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 24290-2026 FSC-klagomål mail.docx", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 24290-2026 tillsynsbegäran.docx", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 24290-2026 tillsynsbegäran mail.docx", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 24290-2026 prioriterade fågelarter.docx", "A 24290-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 23563-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45072</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>7</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Nordfladdermus
+Dvärgpipistrell
+Vattenfladdermus
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23563-2023 artfynd.xlsx", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23563-2023 karta.png", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23563-2023 georefererad karta.tif", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23563-2023 FSC-klagomål.docx", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23563-2023 FSC-klagomål mail.docx", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23563-2023 tillsynsbegäran.docx", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23563-2023 tillsynsbegäran mail.docx", "A 23563-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 25298-2024</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45462</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>5</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Västlig hakmossa
@@ -1484,488 +1929,43 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 25298-2024 artfynd.xlsx", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 25298-2024 karta.png", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 25298-2024 georefererad karta.tif", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 25298-2024 FSC-klagomål.docx", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 25298-2024 FSC-klagomål mail.docx", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 25298-2024 tillsynsbegäran.docx", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 25298-2024 tillsynsbegäran mail.docx", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 25298-2024 prioriterade fågelarter.docx", "A 25298-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 28512-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45819</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>19</v>
-      </c>
-      <c r="U10" t="n">
-        <v>19</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa
-Västlig hakmossa
-Spillkråka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 28512-2025 artfynd.xlsx", "A 28512-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 28512-2025 karta.png", "A 28512-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 28512-2025 georefererad karta.tif", "A 28512-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 28512-2025 FSC-klagomål.docx", "A 28512-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 28512-2025 FSC-klagomål mail.docx", "A 28512-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 28512-2025 tillsynsbegäran.docx", "A 28512-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 28512-2025 tillsynsbegäran mail.docx", "A 28512-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 28512-2025 prioriterade fågelarter.docx", "A 28512-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 23563-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45072</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>7</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Nordfladdermus
-Dvärgpipistrell
-Vattenfladdermus
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23563-2023 artfynd.xlsx", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23563-2023 karta.png", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23563-2023 georefererad karta.tif", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23563-2023 FSC-klagomål.docx", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23563-2023 FSC-klagomål mail.docx", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23563-2023 tillsynsbegäran.docx", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23563-2023 tillsynsbegäran mail.docx", "A 23563-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 24290-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46169</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>5</v>
-      </c>
-      <c r="U12" t="n">
-        <v>5</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Blanksvart trämyra
-Grönpyrola
-Västlig hakmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 24290-2026 artfynd.xlsx", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 24290-2026 karta.png", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 24290-2026 georefererad karta.tif", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 24290-2026 FSC-klagomål.docx", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 24290-2026 FSC-klagomål mail.docx", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 24290-2026 tillsynsbegäran.docx", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 24290-2026 tillsynsbegäran mail.docx", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 24290-2026 prioriterade fågelarter.docx", "A 24290-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 43771-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45187</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>4</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Slåtterfibbla
-Vätteros
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 43771-2023 artfynd.xlsx", "A 43771-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 43771-2023 karta.png", "A 43771-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 43771-2023 georefererad karta.tif", "A 43771-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 43771-2023 FSC-klagomål.docx", "A 43771-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 43771-2023 FSC-klagomål mail.docx", "A 43771-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 43771-2023 tillsynsbegäran.docx", "A 43771-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 43771-2023 tillsynsbegäran mail.docx", "A 43771-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 25655-2023</t>
+          <t>A 17376-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45089</v>
+        <v>46119</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.1</v>
+        <v>2.5</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
         <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2019,394 +2019,394 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
       </c>
       <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Slåttergubbe
+Almsnabbvinge
+Granspira</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 17376-2026 artfynd.xlsx", "A 17376-2026")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 17376-2026 karta.png", "A 17376-2026")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 17376-2026 georefererad karta.tif", "A 17376-2026")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 17376-2026 FSC-klagomål.docx", "A 17376-2026")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 17376-2026 FSC-klagomål mail.docx", "A 17376-2026")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 17376-2026 tillsynsbegäran.docx", "A 17376-2026")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 17376-2026 tillsynsbegäran mail.docx", "A 17376-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 28021-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45098</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Stor revmossa
+Nattskärra
+Törnskata</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 28021-2023 artfynd.xlsx", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 28021-2023 karta.png", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 28021-2023 georefererad karta.tif", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 28021-2023 FSC-klagomål.docx", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 28021-2023 FSC-klagomål mail.docx", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 28021-2023 tillsynsbegäran.docx", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 28021-2023 tillsynsbegäran mail.docx", "A 28021-2023")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 28021-2023 prioriterade fågelarter.docx", "A 28021-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 25655-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45089</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
         <v>9</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U16" t="n">
         <v>7</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Bergjohannesört
 Svinrot
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 25655-2023 artfynd.xlsx", "A 25655-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 25655-2023 karta.png", "A 25655-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 25655-2023 georefererad karta.tif", "A 25655-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 25655-2023 FSC-klagomål.docx", "A 25655-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 25655-2023 FSC-klagomål mail.docx", "A 25655-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 25655-2023 tillsynsbegäran.docx", "A 25655-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 25655-2023 tillsynsbegäran mail.docx", "A 25655-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 28021-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45098</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J15" t="n">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 23559-2023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45072</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
         <v>3</v>
       </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Stor revmossa
-Nattskärra
-Törnskata</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 28021-2023 artfynd.xlsx", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 28021-2023 karta.png", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 28021-2023 georefererad karta.tif", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 28021-2023 FSC-klagomål.docx", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 28021-2023 FSC-klagomål mail.docx", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 28021-2023 tillsynsbegäran.docx", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 28021-2023 tillsynsbegäran mail.docx", "A 28021-2023")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 28021-2023 prioriterade fågelarter.docx", "A 28021-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 23559-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45072</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>8</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>8</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Flodpärlmussla
 Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23559-2023 artfynd.xlsx", "A 23559-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23559-2023 karta.png", "A 23559-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23559-2023 georefererad karta.tif", "A 23559-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23559-2023 FSC-klagomål.docx", "A 23559-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23559-2023 FSC-klagomål mail.docx", "A 23559-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23559-2023 tillsynsbegäran.docx", "A 23559-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23559-2023 tillsynsbegäran mail.docx", "A 23559-2023")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 23559-2023 prioriterade fågelarter.docx", "A 23559-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 17376-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46119</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Slåttergubbe
-Almsnabbvinge
-Granspira</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 17376-2026 artfynd.xlsx", "A 17376-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 17376-2026 karta.png", "A 17376-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 17376-2026 georefererad karta.tif", "A 17376-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 17376-2026 FSC-klagomål.docx", "A 17376-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 17376-2026 FSC-klagomål mail.docx", "A 17376-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 17376-2026 tillsynsbegäran.docx", "A 17376-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 17376-2026 tillsynsbegäran mail.docx", "A 17376-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 23497-2023</t>
+          <t>A 5866-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45072</v>
+        <v>46052</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2437,17 +2437,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2474,468 +2474,468 @@
         <v>2</v>
       </c>
       <c r="T18" t="n">
+        <v>9</v>
+      </c>
+      <c r="U18" t="n">
+        <v>9</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 5866-2026 artfynd.xlsx", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 5866-2026 karta.png", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 5866-2026 georefererad karta.tif", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 5866-2026 FSC-klagomål.docx", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 5866-2026 FSC-klagomål mail.docx", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 5866-2026 tillsynsbegäran.docx", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 5866-2026 tillsynsbegäran mail.docx", "A 5866-2026")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 5866-2026 prioriterade fågelarter.docx", "A 5866-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 23497-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45072</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
         <v>3</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>3</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Stor revmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23497-2023 artfynd.xlsx", "A 23497-2023")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23497-2023 karta.png", "A 23497-2023")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23497-2023 georefererad karta.tif", "A 23497-2023")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23497-2023 FSC-klagomål.docx", "A 23497-2023")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23497-2023 FSC-klagomål mail.docx", "A 23497-2023")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23497-2023 tillsynsbegäran.docx", "A 23497-2023")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23497-2023 tillsynsbegäran mail.docx", "A 23497-2023")</f>
         <v/>
       </c>
-      <c r="AE18">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 23497-2023 prioriterade fågelarter.docx", "A 23497-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 5866-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46052</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J19" t="n">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 13699-2024</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45390</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>2</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="T20" t="n">
+        <v>7</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 13699-2024 artfynd.xlsx", "A 13699-2024")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 13699-2024 karta.png", "A 13699-2024")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 13699-2024 georefererad karta.tif", "A 13699-2024")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 13699-2024 FSC-klagomål.docx", "A 13699-2024")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 13699-2024 FSC-klagomål mail.docx", "A 13699-2024")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 13699-2024 tillsynsbegäran.docx", "A 13699-2024")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 13699-2024 tillsynsbegäran mail.docx", "A 13699-2024")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 13699-2024 prioriterade fågelarter.docx", "A 13699-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 32690-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
-        <v>9</v>
-      </c>
-      <c r="U19" t="n">
-        <v>9</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Skirmossa
+Dunmossa</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 32690-2026 artfynd.xlsx", "A 32690-2026")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 32690-2026 karta.png", "A 32690-2026")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 32690-2026 georefererad karta.tif", "A 32690-2026")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 32690-2026 FSC-klagomål.docx", "A 32690-2026")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 32690-2026 FSC-klagomål mail.docx", "A 32690-2026")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 32690-2026 tillsynsbegäran.docx", "A 32690-2026")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 32690-2026 tillsynsbegäran mail.docx", "A 32690-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 23494-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45072</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 5866-2026 artfynd.xlsx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 5866-2026 karta.png", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 5866-2026 georefererad karta.tif", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 5866-2026 FSC-klagomål.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 5866-2026 FSC-klagomål mail.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 5866-2026 tillsynsbegäran.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 5866-2026 tillsynsbegäran mail.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 5866-2026 prioriterade fågelarter.docx", "A 5866-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 13699-2024</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45390</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>7</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Västlig hakmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 13699-2024 artfynd.xlsx", "A 13699-2024")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 13699-2024 karta.png", "A 13699-2024")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 13699-2024 georefererad karta.tif", "A 13699-2024")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 13699-2024 FSC-klagomål.docx", "A 13699-2024")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 13699-2024 FSC-klagomål mail.docx", "A 13699-2024")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 13699-2024 tillsynsbegäran.docx", "A 13699-2024")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 13699-2024 tillsynsbegäran mail.docx", "A 13699-2024")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 13699-2024 prioriterade fågelarter.docx", "A 13699-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 32690-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46240</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Skirmossa
-Dunmossa</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 32690-2026 artfynd.xlsx", "A 32690-2026")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 32690-2026 karta.png", "A 32690-2026")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 32690-2026 georefererad karta.tif", "A 32690-2026")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 32690-2026 FSC-klagomål.docx", "A 32690-2026")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 32690-2026 FSC-klagomål mail.docx", "A 32690-2026")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 32690-2026 tillsynsbegäran.docx", "A 32690-2026")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 32690-2026 tillsynsbegäran mail.docx", "A 32690-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 23494-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45072</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>4</v>
-      </c>
-      <c r="U22" t="n">
-        <v>4</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Revlummer</t>
-        </is>
-      </c>
       <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23494-2023 artfynd.xlsx", "A 23494-2023")</f>
         <v/>
@@ -2972,7 +2972,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 49384-2023</t>
+          <t>A 30273-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2982,14 +2982,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45205</v>
+        <v>44759</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3001,22 +3001,17 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>1.2</v>
+        <v>12.5</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -3031,7 +3026,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3040,49 +3035,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 49384-2023 artfynd.xlsx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 30273-2022 artfynd.xlsx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 49384-2023 karta.png", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 30273-2022 karta.png", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 49384-2023 georefererad karta.tif", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 30273-2022 georefererad karta.tif", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 49384-2023 FSC-klagomål.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 30273-2022 FSC-klagomål.docx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 49384-2023 FSC-klagomål mail.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 30273-2022 FSC-klagomål mail.docx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 49384-2023 tillsynsbegäran.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 30273-2022 tillsynsbegäran.docx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 49384-2023 tillsynsbegäran mail.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 30273-2022 tillsynsbegäran mail.docx", "A 30273-2022")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 30273-2022</t>
+          <t>A 49384-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3092,14 +3087,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44759</v>
+        <v>45205</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3111,18 +3106,23 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>12.5</v>
+        <v>1.2</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
@@ -3136,7 +3136,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3145,42 +3145,42 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 30273-2022 artfynd.xlsx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 49384-2023 artfynd.xlsx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 30273-2022 karta.png", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 49384-2023 karta.png", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 30273-2022 georefererad karta.tif", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 49384-2023 georefererad karta.tif", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 30273-2022 FSC-klagomål.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 49384-2023 FSC-klagomål.docx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 30273-2022 FSC-klagomål mail.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 49384-2023 FSC-klagomål mail.docx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 30273-2022 tillsynsbegäran.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 49384-2023 tillsynsbegäran.docx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 30273-2022 tillsynsbegäran mail.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 49384-2023 tillsynsbegäran mail.docx", "A 49384-2023")</f>
         <v/>
       </c>
     </row>
@@ -3204,7 +3204,7 @@
         <v>45902</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 38522-2024</t>
+          <t>A 45941-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45546</v>
+        <v>45924</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3321,23 +3321,18 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>5.3</v>
+        <v>1.2</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
@@ -3351,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3360,53 +3355,49 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 38522-2024 artfynd.xlsx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 45941-2025 artfynd.xlsx", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 38522-2024 karta.png", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 45941-2025 karta.png", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 38522-2024 georefererad karta.tif", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 45941-2025 georefererad karta.tif", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 38522-2024 FSC-klagomål.docx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 45941-2025 FSC-klagomål.docx", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 38522-2024 FSC-klagomål mail.docx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 45941-2025 FSC-klagomål mail.docx", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 38522-2024 tillsynsbegäran.docx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 45941-2025 tillsynsbegäran.docx", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 38522-2024 tillsynsbegäran mail.docx", "A 38522-2024")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 38522-2024 prioriterade fågelarter.docx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 45941-2025 tillsynsbegäran mail.docx", "A 45941-2025")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 11102-2024</t>
+          <t>A 38522-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3420,10 +3411,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45371</v>
+        <v>45546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3435,11 +3426,16 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3448,7 +3444,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3460,10 +3456,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3472,46 +3468,50 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 11102-2024 artfynd.xlsx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 38522-2024 artfynd.xlsx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 11102-2024 karta.png", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 38522-2024 karta.png", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 11102-2024 georefererad karta.tif", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 38522-2024 georefererad karta.tif", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 11102-2024 FSC-klagomål.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 38522-2024 FSC-klagomål.docx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 11102-2024 FSC-klagomål mail.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 38522-2024 FSC-klagomål mail.docx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 11102-2024 tillsynsbegäran.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 38522-2024 tillsynsbegäran.docx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 11102-2024 tillsynsbegäran mail.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 38522-2024 tillsynsbegäran mail.docx", "A 38522-2024")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 38522-2024 prioriterade fågelarter.docx", "A 38522-2024")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 45941-2025</t>
+          <t>A 7062-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3521,14 +3521,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45924</v>
+        <v>45343</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3541,16 +3541,16 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.2</v>
+        <v>9.1</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3574,49 +3574,49 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 45941-2025 artfynd.xlsx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 7062-2024 artfynd.xlsx", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 45941-2025 karta.png", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 7062-2024 karta.png", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 45941-2025 georefererad karta.tif", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 7062-2024 georefererad karta.tif", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 45941-2025 FSC-klagomål.docx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 7062-2024 FSC-klagomål.docx", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 45941-2025 FSC-klagomål mail.docx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 7062-2024 FSC-klagomål mail.docx", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 45941-2025 tillsynsbegäran.docx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 7062-2024 tillsynsbegäran.docx", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 45941-2025 tillsynsbegäran mail.docx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 7062-2024 tillsynsbegäran mail.docx", "A 7062-2024")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 7062-2024</t>
+          <t>A 11102-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3626,14 +3626,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45343</v>
+        <v>45371</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3646,20 +3646,20 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>9.1</v>
+        <v>2.8</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
@@ -3670,10 +3670,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3686,35 +3686,35 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 7062-2024 artfynd.xlsx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 11102-2024 artfynd.xlsx", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 7062-2024 karta.png", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 11102-2024 karta.png", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 7062-2024 georefererad karta.tif", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 11102-2024 georefererad karta.tif", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 7062-2024 FSC-klagomål.docx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 11102-2024 FSC-klagomål.docx", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 7062-2024 FSC-klagomål mail.docx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 11102-2024 FSC-klagomål mail.docx", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 7062-2024 tillsynsbegäran.docx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 11102-2024 tillsynsbegäran.docx", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 7062-2024 tillsynsbegäran mail.docx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 11102-2024 tillsynsbegäran mail.docx", "A 11102-2024")</f>
         <v/>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
         <v>46240</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44812</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44581</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>44875</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>44637</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 30285-2022</t>
+          <t>A 18346-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44760</v>
+        <v>44685</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4196,7 +4196,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 18346-2022</t>
+          <t>A 30285-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44685</v>
+        <v>44760</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4286,7 +4286,7 @@
         <v>44720</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>44627</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>44476</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>44467</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>44803</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>44812</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>44826</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>44811</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>44565</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         <v>44760</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>44760</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>44627</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 58750-2021</t>
+          <t>A 12234-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5159,10 +5159,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44489</v>
+        <v>45378</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5218,7 +5218,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 12234-2024</t>
+          <t>A 13887-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5232,10 +5232,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45378</v>
+        <v>45391</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>11.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5291,7 +5291,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 4881-2024</t>
+          <t>A 61284-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5305,10 +5305,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45329</v>
+        <v>44915</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5364,7 +5364,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 26443-2023</t>
+          <t>A 52431-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5378,10 +5378,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45092</v>
+        <v>45225</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5437,7 +5437,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 43770-2023</t>
+          <t>A 11104-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45187</v>
+        <v>45371</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5510,7 +5510,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 406-2024</t>
+          <t>A 24053-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5520,14 +5520,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45296</v>
+        <v>45796</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.8</v>
+        <v>11.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5583,7 +5583,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 54681-2021</t>
+          <t>A 12784-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44473</v>
+        <v>45733</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.1</v>
+        <v>1.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5656,7 +5656,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 47511-2024</t>
+          <t>A 33993-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45587</v>
+        <v>45134</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5729,7 +5729,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 61435-2024</t>
+          <t>A 33996-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5743,10 +5743,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45646</v>
+        <v>45134</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5802,7 +5802,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 5612-2025</t>
+          <t>A 65619-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45693</v>
+        <v>44516</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 37063-2024</t>
+          <t>A 5743-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5889,10 +5889,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45539</v>
+        <v>45694</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>8.800000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5948,7 +5948,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 587-2025</t>
+          <t>A 7819-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5962,10 +5962,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45664</v>
+        <v>45706</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.3</v>
+        <v>5.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6021,7 +6021,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 12628-2023</t>
+          <t>A 51488-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6035,10 +6035,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45000</v>
+        <v>44869</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6094,7 +6094,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 65619-2021</t>
+          <t>A 2867-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6108,10 +6108,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44516</v>
+        <v>45677</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.9</v>
+        <v>10.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6167,7 +6167,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 41411-2022</t>
+          <t>A 35423-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6181,10 +6181,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44826</v>
+        <v>45855</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 12647-2023</t>
+          <t>A 28910-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6254,10 +6254,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45000</v>
+        <v>45480</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6313,7 +6313,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 8117-2023</t>
+          <t>A 11604-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6327,10 +6327,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44974</v>
+        <v>45373</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6386,7 +6386,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 12784-2025</t>
+          <t>A 15567-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6400,10 +6400,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45733</v>
+        <v>44662</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 2867-2025</t>
+          <t>A 1382-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6473,10 +6473,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45677</v>
+        <v>45303</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>10.7</v>
+        <v>1.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6532,7 +6532,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 19079-2025</t>
+          <t>A 41758-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45766</v>
+        <v>45902</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6605,7 +6605,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 41759-2025</t>
+          <t>A 41760-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6622,7 +6622,7 @@
         <v>45902</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6678,7 +6678,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 61952-2024</t>
+          <t>A 41759-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6692,10 +6692,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45653</v>
+        <v>45902</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.2</v>
+        <v>1.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6751,7 +6751,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 41758-2025</t>
+          <t>A 587-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6765,10 +6765,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45902</v>
+        <v>45664</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6824,7 +6824,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 41760-2025</t>
+          <t>A 35422-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6838,10 +6838,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45902</v>
+        <v>45855</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6897,7 +6897,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 35422-2025</t>
+          <t>A 42857-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6911,10 +6911,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45855</v>
+        <v>45908</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6970,7 +6970,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 42857-2025</t>
+          <t>A 43684-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6984,10 +6984,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45908</v>
+        <v>45912</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 35423-2025</t>
+          <t>A 44914-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45855</v>
+        <v>45918</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7116,7 +7116,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 43684-2025</t>
+          <t>A 44915-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7130,10 +7130,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45912</v>
+        <v>45918</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7189,7 +7189,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 50349-2024</t>
+          <t>A 44918-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7203,10 +7203,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45600</v>
+        <v>45918</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.7</v>
+        <v>5.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7262,7 +7262,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 28022-2023</t>
+          <t>A 44916-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7276,10 +7276,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45098</v>
+        <v>45918</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>5.7</v>
+        <v>1.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7335,7 +7335,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 44916-2025</t>
+          <t>A 7912-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7349,10 +7349,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45918</v>
+        <v>45350</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7408,7 +7408,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 44918-2025</t>
+          <t>A 56584-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7422,10 +7422,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45918</v>
+        <v>45974</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>5.7</v>
+        <v>1.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7481,7 +7481,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 44914-2025</t>
+          <t>A 6323-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7495,10 +7495,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45918</v>
+        <v>44960</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7510,8 +7510,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7554,7 +7559,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 44915-2025</t>
+          <t>A 54804-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7568,10 +7573,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45918</v>
+        <v>44883</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7584,7 +7589,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.2</v>
+        <v>22.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7627,7 +7632,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 55972-2022</t>
+          <t>A 5740-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7641,10 +7646,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44889</v>
+        <v>45694</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7657,7 +7662,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7700,7 +7705,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 7912-2024</t>
+          <t>A 6384-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7714,10 +7719,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45350</v>
+        <v>45699</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7730,7 +7735,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7773,7 +7778,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 57381-2022</t>
+          <t>A 36984-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7787,10 +7792,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44896</v>
+        <v>45539</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7803,7 +7808,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7846,7 +7851,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 13581-2023</t>
+          <t>A 57381-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7860,10 +7865,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45006</v>
+        <v>44896</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7875,13 +7880,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7924,7 +7924,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 8071-2024</t>
+          <t>A 48727-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7938,10 +7938,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45351</v>
+        <v>45936</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.6</v>
+        <v>6.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 48730-2025</t>
+          <t>A 15351-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8011,10 +8011,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45936</v>
+        <v>45400</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8026,8 +8026,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8070,7 +8075,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 48727-2025</t>
+          <t>A 48730-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8087,7 +8092,7 @@
         <v>45936</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8100,7 +8105,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>6.1</v>
+        <v>4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8143,7 +8148,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 49188-2025</t>
+          <t>A 13801-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8157,10 +8162,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45938</v>
+        <v>45737</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8173,7 +8178,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8216,7 +8221,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 13801-2025</t>
+          <t>A 8117-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8230,10 +8235,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45737</v>
+        <v>44974</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8246,7 +8251,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.1</v>
+        <v>11</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8289,7 +8294,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 13975-2023</t>
+          <t>A 49188-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8303,10 +8308,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45008</v>
+        <v>45938</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8319,7 +8324,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8362,7 +8367,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 16473-2022</t>
+          <t>A 14427-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8376,10 +8381,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44671</v>
+        <v>46100</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8392,7 +8397,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8435,7 +8440,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 6323-2023</t>
+          <t>A 12628-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8449,10 +8454,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44960</v>
+        <v>45000</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8464,13 +8469,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8513,7 +8513,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 61475-2025</t>
+          <t>A 50349-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8527,10 +8527,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46001</v>
+        <v>45600</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8586,7 +8586,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 40092-2024</t>
+          <t>A 17377-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8600,10 +8600,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45554</v>
+        <v>46119</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8659,7 +8659,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 57754-2023</t>
+          <t>A 28903-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8673,10 +8673,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45246</v>
+        <v>45480</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8689,7 +8689,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8732,7 +8732,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 26886-2023</t>
+          <t>A 27222-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8746,10 +8746,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45093</v>
+        <v>45812</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8805,7 +8805,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 48904-2024</t>
+          <t>A 55324-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8819,10 +8819,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45594</v>
+        <v>45971</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8834,8 +8834,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8878,7 +8883,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 55324-2025</t>
+          <t>A 12647-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8892,10 +8897,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45971</v>
+        <v>45000</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8907,13 +8912,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8956,7 +8956,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 302-2024</t>
+          <t>A 18841-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8970,10 +8970,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45295</v>
+        <v>46129</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8985,13 +8985,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9034,7 +9029,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 29068-2024</t>
+          <t>A 5328-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9048,10 +9043,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45481</v>
+        <v>45692</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9064,7 +9059,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9107,7 +9102,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 4225-2024</t>
+          <t>A 19079-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9121,10 +9116,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45324</v>
+        <v>45766</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9137,7 +9132,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9180,7 +9175,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 4227-2024</t>
+          <t>A 28022-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9194,10 +9189,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45324</v>
+        <v>45098</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9210,7 +9205,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.6</v>
+        <v>5.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9253,7 +9248,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 38093-2022</t>
+          <t>A 28515-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9267,10 +9262,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44811</v>
+        <v>45819</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9283,7 +9278,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9326,7 +9321,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 61695-2025</t>
+          <t>A 48904-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9340,10 +9335,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46002</v>
+        <v>45594</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9356,7 +9351,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9399,7 +9394,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 5420-2025</t>
+          <t>A 61952-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9413,10 +9408,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45692</v>
+        <v>45653</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9429,7 +9424,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9472,7 +9467,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 51488-2022</t>
+          <t>A 61475-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9486,10 +9481,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44869</v>
+        <v>46001</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9502,7 +9497,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.5</v>
+        <v>4.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9545,7 +9540,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 6489-2025</t>
+          <t>A 55972-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9559,10 +9554,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45699</v>
+        <v>44889</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9575,7 +9570,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9618,7 +9613,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 9046-2022</t>
+          <t>A 61695-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9632,10 +9627,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44615</v>
+        <v>46002</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9648,7 +9643,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9691,7 +9686,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 28903-2024</t>
+          <t>A 26886-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9705,10 +9700,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45480</v>
+        <v>45093</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9721,7 +9716,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9764,7 +9759,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 61284-2022</t>
+          <t>A 26443-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9778,10 +9773,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44915</v>
+        <v>45092</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9794,7 +9789,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9837,7 +9832,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 12760-2023</t>
+          <t>A 17114-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9851,10 +9846,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45001</v>
+        <v>45034</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9867,7 +9862,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9910,7 +9905,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 62730-2023</t>
+          <t>A 58750-2021</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9924,10 +9919,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45268</v>
+        <v>44489</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9940,7 +9935,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9983,7 +9978,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 23541-2026</t>
+          <t>A 7947-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9993,14 +9988,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46163</v>
+        <v>45350</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10013,7 +10008,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10056,7 +10051,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 11604-2024</t>
+          <t>A 23541-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10066,14 +10061,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45373</v>
+        <v>46163</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10086,7 +10081,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10129,7 +10124,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 5324-2025</t>
+          <t>A 35420-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10143,10 +10138,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45692</v>
+        <v>45855</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10159,7 +10154,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>5.1</v>
+        <v>1.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10202,7 +10197,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 54804-2022</t>
+          <t>A 35717-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10216,10 +10211,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44883</v>
+        <v>45860</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10232,7 +10227,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>22.6</v>
+        <v>0.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10275,7 +10270,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 52431-2023</t>
+          <t>A 14891-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10289,10 +10284,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45225</v>
+        <v>45743</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10305,7 +10300,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10348,7 +10343,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 33993-2023</t>
+          <t>A 24700-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10362,10 +10357,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45134</v>
+        <v>46171</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10377,8 +10372,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10421,7 +10421,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 33996-2023</t>
+          <t>A 13581-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10435,10 +10435,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45134</v>
+        <v>45006</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10450,8 +10450,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10494,7 +10499,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 56584-2025</t>
+          <t>A 54681-2021</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10508,10 +10513,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45974</v>
+        <v>44473</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10524,7 +10529,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10567,7 +10572,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 14891-2025</t>
+          <t>A 25729-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10581,10 +10586,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45743</v>
+        <v>46178</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10597,7 +10602,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10640,7 +10645,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 24700-2026</t>
+          <t>A 47511-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10654,10 +10659,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46171</v>
+        <v>45587</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10669,13 +10674,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10718,7 +10718,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 15351-2024</t>
+          <t>A 43770-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10732,10 +10732,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45400</v>
+        <v>45187</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10747,13 +10747,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10796,7 +10791,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 7947-2024</t>
+          <t>A 4881-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10810,10 +10805,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45350</v>
+        <v>45329</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10826,7 +10821,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10869,7 +10864,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 17116-2023</t>
+          <t>A 27643-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10883,10 +10878,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45034</v>
+        <v>46190</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10899,7 +10894,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10942,7 +10937,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 14427-2026</t>
+          <t>A 9046-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10956,10 +10951,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46100</v>
+        <v>44615</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10972,7 +10967,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11015,7 +11010,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 15567-2022</t>
+          <t>A 61435-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11029,10 +11024,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44662</v>
+        <v>45646</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11045,7 +11040,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11088,7 +11083,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 21630-2024</t>
+          <t>A 33842-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11102,10 +11097,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45442</v>
+        <v>46251</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11118,7 +11113,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11161,7 +11156,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 25729-2026</t>
+          <t>A 30605-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11175,10 +11170,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46178</v>
+        <v>46210</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11191,7 +11186,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.4</v>
+        <v>10.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11234,7 +11229,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 27643-2026</t>
+          <t>A 2438-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11248,10 +11243,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46190</v>
+        <v>46036</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11264,7 +11259,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11307,7 +11302,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 17377-2026</t>
+          <t>A 14929-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11321,10 +11316,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46119</v>
+        <v>45398</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11337,7 +11332,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.4</v>
+        <v>5.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11380,7 +11375,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 13382-2023</t>
+          <t>A 21630-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11394,10 +11389,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45005</v>
+        <v>45442</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11410,7 +11405,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11453,7 +11448,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 550-2024</t>
+          <t>A 43767-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11467,10 +11462,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45299</v>
+        <v>45187</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11526,7 +11521,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 18841-2026</t>
+          <t>A 33991-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11540,10 +11535,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46129</v>
+        <v>45134</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11556,7 +11551,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11599,7 +11594,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 13887-2024</t>
+          <t>A 35883-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11613,10 +11608,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45391</v>
+        <v>46266</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11629,7 +11624,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>11.3</v>
+        <v>6.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11672,7 +11667,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 33842-2026</t>
+          <t>A 41411-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11686,10 +11681,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46251</v>
+        <v>44826</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11702,7 +11697,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>7.2</v>
+        <v>3.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11745,7 +11740,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 14929-2024</t>
+          <t>A 36773-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11759,10 +11754,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45398</v>
+        <v>46272</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11774,8 +11769,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>5.1</v>
+        <v>2.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11818,7 +11818,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 2438-2026</t>
+          <t>A 4225-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11832,10 +11832,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46036</v>
+        <v>45324</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11848,7 +11848,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11891,7 +11891,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 30605-2026</t>
+          <t>A 4227-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11905,10 +11905,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46210</v>
+        <v>45324</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>10.5</v>
+        <v>1.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11964,7 +11964,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 11104-2024</t>
+          <t>A 36722-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11978,10 +11978,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45371</v>
+        <v>46272</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11993,8 +11993,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12037,7 +12042,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 28910-2024</t>
+          <t>A 37037-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12051,10 +12056,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45480</v>
+        <v>46273</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12067,7 +12072,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12110,7 +12115,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 1382-2024</t>
+          <t>A 37508-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12124,10 +12129,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45303</v>
+        <v>45158</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12140,7 +12145,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.4</v>
+        <v>6.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12183,7 +12188,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 17114-2023</t>
+          <t>A 37509-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12197,10 +12202,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45034</v>
+        <v>45158</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12213,7 +12218,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12256,7 +12261,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 35883-2026</t>
+          <t>A 32822-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12270,10 +12275,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46266</v>
+        <v>46242</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12286,7 +12291,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>6.6</v>
+        <v>2.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12329,7 +12334,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 43767-2023</t>
+          <t>A 13382-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12343,10 +12348,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45187</v>
+        <v>45005</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12359,7 +12364,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12402,7 +12407,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 13631-2024</t>
+          <t>A 38093-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12416,10 +12421,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45390</v>
+        <v>44811</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12432,7 +12437,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>16.4</v>
+        <v>1.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12475,7 +12480,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 36722-2026</t>
+          <t>A 16473-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12489,10 +12494,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46272</v>
+        <v>44671</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12504,13 +12509,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12553,7 +12553,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 37037-2026</t>
+          <t>A 40092-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12567,10 +12567,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46273</v>
+        <v>45554</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12626,7 +12626,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 36773-2026</t>
+          <t>A 57754-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12640,10 +12640,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46272</v>
+        <v>45246</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12655,13 +12655,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12704,7 +12699,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 37508-2023</t>
+          <t>A 44445-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12718,10 +12713,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45158</v>
+        <v>45189</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12734,7 +12729,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>6.9</v>
+        <v>3.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12777,7 +12772,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 37509-2023</t>
+          <t>A 17116-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12791,10 +12786,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45158</v>
+        <v>45034</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12807,7 +12802,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12850,7 +12845,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 15159-2023</t>
+          <t>A 12760-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12864,10 +12859,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45016</v>
+        <v>45001</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12879,13 +12874,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12928,7 +12918,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 49879-2023</t>
+          <t>A 5612-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12942,10 +12932,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45213</v>
+        <v>45693</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12958,7 +12948,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13001,7 +12991,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 44445-2023</t>
+          <t>A 302-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13015,10 +13005,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45189</v>
+        <v>45295</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13030,8 +13020,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13074,7 +13069,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 33991-2023</t>
+          <t>A 29068-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13088,10 +13083,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45134</v>
+        <v>45481</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13104,7 +13099,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13147,7 +13142,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 5328-2025</t>
+          <t>A 5324-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13164,7 +13159,7 @@
         <v>45692</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13177,7 +13172,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13220,7 +13215,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 3867-2025</t>
+          <t>A 13631-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13234,10 +13229,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45684</v>
+        <v>45390</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13250,7 +13245,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.5</v>
+        <v>16.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13293,7 +13288,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 21617-2024</t>
+          <t>A 37063-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13307,10 +13302,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45441</v>
+        <v>45539</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13323,7 +13318,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>9.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13366,7 +13361,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 32822-2026</t>
+          <t>A 15159-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13380,10 +13375,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46242</v>
+        <v>45016</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13395,8 +13390,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13439,7 +13439,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 22561-2025</t>
+          <t>A 550-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13453,10 +13453,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45789</v>
+        <v>45299</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13512,7 +13512,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 12790-2025</t>
+          <t>A 13975-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13526,10 +13526,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45733</v>
+        <v>45008</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13585,7 +13585,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 12243-2025</t>
+          <t>A 8071-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13599,10 +13599,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45729</v>
+        <v>45351</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>10.2</v>
+        <v>1.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13658,7 +13658,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 30724-2024</t>
+          <t>A 6489-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13668,14 +13668,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45496</v>
+        <v>45699</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13688,7 +13688,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13731,7 +13731,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 23374-2025</t>
+          <t>A 406-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45791</v>
+        <v>45296</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13804,7 +13804,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 23509-2025</t>
+          <t>A 62730-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13818,10 +13818,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45792</v>
+        <v>45268</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13877,7 +13877,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 5743-2025</t>
+          <t>A 49879-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13891,10 +13891,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45694</v>
+        <v>45213</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13950,7 +13950,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 24053-2025</t>
+          <t>A 5420-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13960,14 +13960,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45796</v>
+        <v>45692</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>11.1</v>
+        <v>0.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14023,7 +14023,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 7819-2025</t>
+          <t>A 3867-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14037,10 +14037,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45706</v>
+        <v>45684</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>5.6</v>
+        <v>1.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14096,7 +14096,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 5740-2025</t>
+          <t>A 21617-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14110,10 +14110,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45694</v>
+        <v>45441</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14169,7 +14169,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 6384-2025</t>
+          <t>A 30724-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14179,14 +14179,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45699</v>
+        <v>45496</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14242,7 +14242,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 36984-2024</t>
+          <t>A 22561-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14256,10 +14256,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45539</v>
+        <v>45789</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14315,7 +14315,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 27222-2025</t>
+          <t>A 23509-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14329,10 +14329,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45812</v>
+        <v>45792</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14388,7 +14388,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 28515-2025</t>
+          <t>A 23374-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14402,10 +14402,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45819</v>
+        <v>45791</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14461,7 +14461,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 35420-2025</t>
+          <t>A 12790-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14475,10 +14475,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45855</v>
+        <v>45733</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14534,7 +14534,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 35717-2025</t>
+          <t>A 12243-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14548,10 +14548,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45860</v>
+        <v>45729</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.6</v>
+        <v>10.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14624,7 +14624,7 @@
         <v>44964</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>

--- a/Översikt LILLA EDET.xlsx
+++ b/Översikt LILLA EDET.xlsx
@@ -601,7 +601,7 @@
         <v>46169</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45295</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45295</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45827</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45139</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>45272</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46044</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>45187</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>45819</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>46169</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>45072</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>45462</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>46119</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>45098</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>45089</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45072</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>46052</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45072</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>45390</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>46240</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>45072</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>44759</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>45205</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>45902</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>45924</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>45546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>45343</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45371</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>46240</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44812</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44581</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>44875</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>44637</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>44685</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>44760</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>44720</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>44627</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>44476</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>44467</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>44803</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>44812</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>44826</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>44811</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>44565</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         <v>44760</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>44760</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>44627</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>45378</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>45391</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>44915</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         <v>45225</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>45371</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>45796</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>45733</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>45134</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>45134</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>44516</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>45694</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>45706</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>44869</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>45677</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>45855</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>45480</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>45373</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>44662</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         <v>45303</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>45902</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>45902</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>45902</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>45664</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>45855</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>45908</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>45912</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>45918</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>45918</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>45918</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>45918</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>45350</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>45974</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>44960</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>44883</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>45694</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>45699</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>45539</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>44896</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>45936</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         <v>45400</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>45936</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>45737</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>44974</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>45938</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>46100</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>45000</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         <v>45600</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>46119</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>45480</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>45812</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>45971</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>45000</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>46129</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>45692</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         <v>45766</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         <v>45098</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>45819</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>45594</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>45653</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9484,7 +9484,7 @@
         <v>46001</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>44889</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>46002</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>45093</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>45092</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>45034</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>44489</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>45350</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>46163</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         <v>45855</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>45860</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>45743</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>46171</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>45006</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>44473</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>46178</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>45587</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>45187</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>45329</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>46190</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
         <v>44615</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>45646</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>46251</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         <v>46210</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>46036</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>45398</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
         <v>45442</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11465,7 +11465,7 @@
         <v>45187</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11538,7 +11538,7 @@
         <v>45134</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>46266</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11684,7 +11684,7 @@
         <v>44826</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11757,7 +11757,7 @@
         <v>46272</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>45324</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11908,7 +11908,7 @@
         <v>45324</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11981,7 +11981,7 @@
         <v>46272</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12059,7 +12059,7 @@
         <v>46273</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>45158</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12205,7 +12205,7 @@
         <v>45158</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>46242</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>45005</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>44811</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>44671</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12570,7 +12570,7 @@
         <v>45554</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>45246</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>45189</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>45034</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>45001</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>45693</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13008,7 +13008,7 @@
         <v>45295</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>45481</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>45692</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>45390</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13305,7 +13305,7 @@
         <v>45539</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13378,7 +13378,7 @@
         <v>45016</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>45299</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>45008</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>45351</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>45699</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>45296</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>45268</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         <v>45213</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13967,7 +13967,7 @@
         <v>45692</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>45684</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>45441</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>45496</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>45789</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>45792</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>45791</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>45733</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>45729</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>44964</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>

--- a/Översikt LILLA EDET.xlsx
+++ b/Översikt LILLA EDET.xlsx
@@ -601,7 +601,7 @@
         <v>46169</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45295</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45295</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45827</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>45139</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>45272</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46044</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>45187</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>45819</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>46169</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>45072</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>45462</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>46119</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>45098</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>45089</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45072</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>46052</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45072</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>45390</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>46240</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>45072</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>44759</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>45205</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>45902</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>45924</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>45546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>45343</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45371</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>46240</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44812</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44581</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>44875</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>44637</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>44685</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>44760</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>44720</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>44627</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>44476</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>44467</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>44803</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>44812</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>44826</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>44811</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>44565</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         <v>44760</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>44760</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>44627</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>45378</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>45391</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>44915</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         <v>45225</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>45371</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>45796</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>45733</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>45134</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>45134</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>44516</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>45694</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>45706</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>44869</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>45677</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>45855</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>45480</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>45373</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         <v>44662</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         <v>45303</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
         <v>45902</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>45902</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>45902</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>45664</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>45855</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>45908</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>45912</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>45918</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>45918</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>45918</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>45918</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>45350</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>45974</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>44960</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>44883</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>45694</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>45699</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>45539</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>44896</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>45936</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         <v>45400</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>45936</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>45737</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>44974</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>45938</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>46100</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>45000</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         <v>45600</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>46119</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>45480</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>45812</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>45971</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>45000</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>46129</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>45692</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         <v>45766</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         <v>45098</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>45819</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>45594</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>45653</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9484,7 +9484,7 @@
         <v>46001</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>44889</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>46002</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>45093</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>45092</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>45034</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>44489</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>45350</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>46163</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         <v>45855</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>45860</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>45743</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>46171</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>45006</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>44473</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>46178</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>45587</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>45187</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>45329</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>46190</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
         <v>44615</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>45646</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>46251</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         <v>46210</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>46036</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>45398</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
         <v>45442</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11465,7 +11465,7 @@
         <v>45187</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11538,7 +11538,7 @@
         <v>45134</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>46266</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11684,7 +11684,7 @@
         <v>44826</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11757,7 +11757,7 @@
         <v>46272</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>45324</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11908,7 +11908,7 @@
         <v>45324</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11981,7 +11981,7 @@
         <v>46272</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12059,7 +12059,7 @@
         <v>46273</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>45158</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12205,7 +12205,7 @@
         <v>45158</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>46242</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>45005</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>44811</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>44671</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12570,7 +12570,7 @@
         <v>45554</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>45246</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>45189</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>45034</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>45001</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>45693</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13008,7 +13008,7 @@
         <v>45295</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>45481</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>45692</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>45390</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13305,7 +13305,7 @@
         <v>45539</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13378,7 +13378,7 @@
         <v>45016</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>45299</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>45008</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>45351</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>45699</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>45296</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>45268</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         <v>45213</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13967,7 +13967,7 @@
         <v>45692</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>45684</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>45441</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>45496</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>45789</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>45792</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>45791</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>45733</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>45729</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>44964</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>

--- a/Översikt LILLA EDET.xlsx
+++ b/Översikt LILLA EDET.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE178"/>
+  <dimension ref="A1:AE177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>46169</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45295</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45295</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45827</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 34396-2023</t>
+          <t>A 62846-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45139</v>
+        <v>45272</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1127,12 +1127,123 @@
         <v>7</v>
       </c>
       <c r="T6" t="n">
+        <v>17</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Kattfotslav
+Blåmossa
+Bronshjon
+Stor revmossa
+Vågbandad barkbock
+Större vattensalamander
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 62846-2023 artfynd.xlsx", "A 62846-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 62846-2023 karta.png", "A 62846-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 62846-2023 georefererad karta.tif", "A 62846-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 62846-2023 FSC-klagomål.docx", "A 62846-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 62846-2023 FSC-klagomål mail.docx", "A 62846-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 62846-2023 tillsynsbegäran.docx", "A 62846-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 62846-2023 tillsynsbegäran mail.docx", "A 62846-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 34396-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45139</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>7</v>
+      </c>
+      <c r="T7" t="n">
         <v>24</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>24</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Blåmossa
@@ -1143,147 +1254,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 34396-2023 artfynd.xlsx", "A 34396-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 34396-2023 karta.png", "A 34396-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 34396-2023 georefererad karta.tif", "A 34396-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 34396-2023 FSC-klagomål.docx", "A 34396-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 34396-2023 FSC-klagomål mail.docx", "A 34396-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 34396-2023 tillsynsbegäran.docx", "A 34396-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 34396-2023 tillsynsbegäran mail.docx", "A 34396-2023")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 34396-2023 prioriterade fågelarter.docx", "A 34396-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 62846-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45272</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>7</v>
-      </c>
-      <c r="T7" t="n">
-        <v>17</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Kattfotslav
-Blåmossa
-Bronshjon
-Stor revmossa
-Vågbandad barkbock
-Större vattensalamander
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 62846-2023 artfynd.xlsx", "A 62846-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 62846-2023 karta.png", "A 62846-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 62846-2023 georefererad karta.tif", "A 62846-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 62846-2023 FSC-klagomål.docx", "A 62846-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 62846-2023 FSC-klagomål mail.docx", "A 62846-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 62846-2023 tillsynsbegäran.docx", "A 62846-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 62846-2023 tillsynsbegäran mail.docx", "A 62846-2023")</f>
         <v/>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
         <v>46044</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 43771-2023</t>
+          <t>A 25298-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45187</v>
+        <v>45462</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1432,23 +1432,28 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>1.7</v>
+        <v>5.9</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1457,21 +1462,133 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
       </c>
       <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>5</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Västlig hakmossa
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 25298-2024 artfynd.xlsx", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 25298-2024 karta.png", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 25298-2024 georefererad karta.tif", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 25298-2024 FSC-klagomål.docx", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 25298-2024 FSC-klagomål mail.docx", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 25298-2024 tillsynsbegäran.docx", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 25298-2024 tillsynsbegäran mail.docx", "A 25298-2024")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 25298-2024 prioriterade fågelarter.docx", "A 25298-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 43771-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45187</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
         <v>4</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Ask
 Slåtterfibbla
@@ -1479,107 +1596,107 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 43771-2023 artfynd.xlsx", "A 43771-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 43771-2023 karta.png", "A 43771-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 43771-2023 georefererad karta.tif", "A 43771-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 43771-2023 FSC-klagomål.docx", "A 43771-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 43771-2023 FSC-klagomål mail.docx", "A 43771-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 43771-2023 tillsynsbegäran.docx", "A 43771-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 43771-2023 tillsynsbegäran mail.docx", "A 43771-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 28512-2025</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>45819</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>10.9</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>2</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K11" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>4</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>19</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>19</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Västlig hakmossa
@@ -1587,111 +1704,224 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 28512-2025 artfynd.xlsx", "A 28512-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 28512-2025 karta.png", "A 28512-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 28512-2025 georefererad karta.tif", "A 28512-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 28512-2025 FSC-klagomål.docx", "A 28512-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 28512-2025 FSC-klagomål mail.docx", "A 28512-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 28512-2025 tillsynsbegäran.docx", "A 28512-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 28512-2025 tillsynsbegäran mail.docx", "A 28512-2025")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 28512-2025 prioriterade fågelarter.docx", "A 28512-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 23563-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45072</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>7</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Nordfladdermus
+Dvärgpipistrell
+Vattenfladdermus
+Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23563-2023 artfynd.xlsx", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23563-2023 karta.png", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23563-2023 georefererad karta.tif", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23563-2023 FSC-klagomål.docx", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23563-2023 FSC-klagomål mail.docx", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23563-2023 tillsynsbegäran.docx", "A 23563-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23563-2023 tillsynsbegäran mail.docx", "A 23563-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 24290-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>46169</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
+      <c r="E13" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>3.6</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K13" t="n">
         <v>3</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>4</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T13" t="n">
         <v>5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U13" t="n">
         <v>5</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Blanksvart trämyra
 Grönpyrola
@@ -1699,273 +1929,43 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 24290-2026 artfynd.xlsx", "A 24290-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 24290-2026 karta.png", "A 24290-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 24290-2026 georefererad karta.tif", "A 24290-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 24290-2026 FSC-klagomål.docx", "A 24290-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 24290-2026 FSC-klagomål mail.docx", "A 24290-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 24290-2026 tillsynsbegäran.docx", "A 24290-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 24290-2026 tillsynsbegäran mail.docx", "A 24290-2026")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 24290-2026 prioriterade fågelarter.docx", "A 24290-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 23563-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45072</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>7</v>
-      </c>
-      <c r="U12" t="n">
-        <v>7</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Nordfladdermus
-Dvärgpipistrell
-Vattenfladdermus
-Grönvit nattviol</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23563-2023 artfynd.xlsx", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23563-2023 karta.png", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23563-2023 georefererad karta.tif", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23563-2023 FSC-klagomål.docx", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23563-2023 FSC-klagomål mail.docx", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23563-2023 tillsynsbegäran.docx", "A 23563-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23563-2023 tillsynsbegäran mail.docx", "A 23563-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 25298-2024</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45462</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>5</v>
-      </c>
-      <c r="U13" t="n">
-        <v>5</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Västlig hakmossa
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 25298-2024 artfynd.xlsx", "A 25298-2024")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 25298-2024 karta.png", "A 25298-2024")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 25298-2024 georefererad karta.tif", "A 25298-2024")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 25298-2024 FSC-klagomål.docx", "A 25298-2024")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 25298-2024 FSC-klagomål mail.docx", "A 25298-2024")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 25298-2024 tillsynsbegäran.docx", "A 25298-2024")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 25298-2024 tillsynsbegäran mail.docx", "A 25298-2024")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 25298-2024 prioriterade fågelarter.docx", "A 25298-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 17376-2026</t>
+          <t>A 25655-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46119</v>
+        <v>45089</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
         <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2019,271 +2019,271 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
       </c>
       <c r="T14" t="n">
+        <v>9</v>
+      </c>
+      <c r="U14" t="n">
+        <v>7</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Bergjohannesört
+Svinrot
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 25655-2023 artfynd.xlsx", "A 25655-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 25655-2023 karta.png", "A 25655-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 25655-2023 georefererad karta.tif", "A 25655-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 25655-2023 FSC-klagomål.docx", "A 25655-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 25655-2023 FSC-klagomål mail.docx", "A 25655-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 25655-2023 tillsynsbegäran.docx", "A 25655-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 25655-2023 tillsynsbegäran mail.docx", "A 25655-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 17376-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46119</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>3</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Slåttergubbe
 Almsnabbvinge
 Granspira</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 17376-2026 artfynd.xlsx", "A 17376-2026")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 17376-2026 karta.png", "A 17376-2026")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 17376-2026 georefererad karta.tif", "A 17376-2026")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 17376-2026 FSC-klagomål.docx", "A 17376-2026")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 17376-2026 FSC-klagomål mail.docx", "A 17376-2026")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 17376-2026 tillsynsbegäran.docx", "A 17376-2026")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 17376-2026 tillsynsbegäran mail.docx", "A 17376-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>A 28021-2023</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
         <v>45098</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E16" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>1.5</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J16" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K16" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>3</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T16" t="n">
         <v>3</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U16" t="n">
         <v>3</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Stor revmossa
 Nattskärra
 Törnskata</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 28021-2023 artfynd.xlsx", "A 28021-2023")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 28021-2023 karta.png", "A 28021-2023")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 28021-2023 georefererad karta.tif", "A 28021-2023")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 28021-2023 FSC-klagomål.docx", "A 28021-2023")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 28021-2023 FSC-klagomål mail.docx", "A 28021-2023")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 28021-2023 tillsynsbegäran.docx", "A 28021-2023")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 28021-2023 tillsynsbegäran mail.docx", "A 28021-2023")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 28021-2023 prioriterade fågelarter.docx", "A 28021-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 25655-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45089</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>9</v>
-      </c>
-      <c r="U16" t="n">
-        <v>7</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Bergjohannesört
-Svinrot
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 25655-2023 artfynd.xlsx", "A 25655-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 25655-2023 karta.png", "A 25655-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 25655-2023 georefererad karta.tif", "A 25655-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 25655-2023 FSC-klagomål.docx", "A 25655-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 25655-2023 FSC-klagomål mail.docx", "A 25655-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 25655-2023 tillsynsbegäran.docx", "A 25655-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 25655-2023 tillsynsbegäran mail.docx", "A 25655-2023")</f>
         <v/>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
         <v>45072</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>46052</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45072</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>45390</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>46240</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>45072</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 30273-2022</t>
+          <t>A 41756-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2986,10 +2986,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44759</v>
+        <v>45902</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>12.5</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3035,49 +3035,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 30273-2022 artfynd.xlsx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 41756-2025 artfynd.xlsx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 30273-2022 karta.png", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 41756-2025 karta.png", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 30273-2022 georefererad karta.tif", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 41756-2025 georefererad karta.tif", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 30273-2022 FSC-klagomål.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 41756-2025 FSC-klagomål.docx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 30273-2022 FSC-klagomål mail.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 41756-2025 FSC-klagomål mail.docx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 30273-2022 tillsynsbegäran.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 41756-2025 tillsynsbegäran.docx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 30273-2022 tillsynsbegäran mail.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 41756-2025 tillsynsbegäran mail.docx", "A 41756-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 49384-2023</t>
+          <t>A 45941-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3087,14 +3087,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45205</v>
+        <v>45924</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3104,11 +3104,6 @@
       <c r="G24" t="inlineStr">
         <is>
           <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -3145,49 +3140,49 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 49384-2023 artfynd.xlsx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 45941-2025 artfynd.xlsx", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 49384-2023 karta.png", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 45941-2025 karta.png", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 49384-2023 georefererad karta.tif", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 45941-2025 georefererad karta.tif", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 49384-2023 FSC-klagomål.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 45941-2025 FSC-klagomål.docx", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 49384-2023 FSC-klagomål mail.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 45941-2025 FSC-klagomål mail.docx", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 49384-2023 tillsynsbegäran.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 45941-2025 tillsynsbegäran.docx", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 49384-2023 tillsynsbegäran mail.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 45941-2025 tillsynsbegäran mail.docx", "A 45941-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 41756-2025</t>
+          <t>A 49384-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3197,14 +3192,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45902</v>
+        <v>45205</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3216,18 +3211,23 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
@@ -3241,7 +3241,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3253,46 +3253,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 41756-2025 artfynd.xlsx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 49384-2023 artfynd.xlsx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 41756-2025 karta.png", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 49384-2023 karta.png", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 41756-2025 georefererad karta.tif", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 49384-2023 georefererad karta.tif", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 41756-2025 FSC-klagomål.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 49384-2023 FSC-klagomål.docx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 41756-2025 FSC-klagomål mail.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 49384-2023 FSC-klagomål mail.docx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 41756-2025 tillsynsbegäran.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 49384-2023 tillsynsbegäran.docx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 41756-2025 tillsynsbegäran mail.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 49384-2023 tillsynsbegäran mail.docx", "A 49384-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 45941-2025</t>
+          <t>A 30273-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45924</v>
+        <v>44759</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3322,16 +3322,16 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.2</v>
+        <v>12.5</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3346,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3362,42 +3362,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 45941-2025 artfynd.xlsx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 30273-2022 artfynd.xlsx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 45941-2025 karta.png", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 30273-2022 karta.png", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 45941-2025 georefererad karta.tif", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 30273-2022 georefererad karta.tif", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 45941-2025 FSC-klagomål.docx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 30273-2022 FSC-klagomål.docx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 45941-2025 FSC-klagomål mail.docx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 30273-2022 FSC-klagomål mail.docx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 45941-2025 tillsynsbegäran.docx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 30273-2022 tillsynsbegäran.docx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 45941-2025 tillsynsbegäran mail.docx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 30273-2022 tillsynsbegäran mail.docx", "A 30273-2022")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 38522-2024</t>
+          <t>A 11102-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3411,10 +3411,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45546</v>
+        <v>45371</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3426,26 +3426,21 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>5.3</v>
+        <v>2.8</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
@@ -3456,10 +3451,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3468,43 +3463,39 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 38522-2024 artfynd.xlsx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 11102-2024 artfynd.xlsx", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 38522-2024 karta.png", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 11102-2024 karta.png", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 38522-2024 georefererad karta.tif", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 11102-2024 georefererad karta.tif", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 38522-2024 FSC-klagomål.docx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 11102-2024 FSC-klagomål.docx", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 38522-2024 FSC-klagomål mail.docx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 11102-2024 FSC-klagomål mail.docx", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 38522-2024 tillsynsbegäran.docx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 11102-2024 tillsynsbegäran.docx", "A 11102-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 38522-2024 tillsynsbegäran mail.docx", "A 38522-2024")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 38522-2024 prioriterade fågelarter.docx", "A 38522-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 11102-2024 tillsynsbegäran mail.docx", "A 11102-2024")</f>
         <v/>
       </c>
     </row>
@@ -3528,7 +3519,7 @@
         <v>45343</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3616,7 +3607,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 11102-2024</t>
+          <t>A 38522-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3630,10 +3621,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45371</v>
+        <v>45546</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3645,11 +3636,16 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -3658,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3670,10 +3666,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3682,39 +3678,43 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 11102-2024 artfynd.xlsx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 38522-2024 artfynd.xlsx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 11102-2024 karta.png", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 38522-2024 karta.png", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 11102-2024 georefererad karta.tif", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 38522-2024 georefererad karta.tif", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 11102-2024 FSC-klagomål.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 38522-2024 FSC-klagomål.docx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 11102-2024 FSC-klagomål mail.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 38522-2024 FSC-klagomål mail.docx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 11102-2024 tillsynsbegäran.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 38522-2024 tillsynsbegäran.docx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 11102-2024 tillsynsbegäran mail.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 38522-2024 tillsynsbegäran mail.docx", "A 38522-2024")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 38522-2024 prioriterade fågelarter.docx", "A 38522-2024")</f>
         <v/>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
         <v>46240</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44812</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>44581</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>44875</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>44637</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>44685</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>44760</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>44720</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>44627</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>44476</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 52953-2021</t>
+          <t>A 36359-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44467</v>
+        <v>44803</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4561,7 +4561,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 36359-2022</t>
+          <t>A 38386-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4575,10 +4575,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44803</v>
+        <v>44812</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 38386-2022</t>
+          <t>A 41420-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4648,10 +4648,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44812</v>
+        <v>44826</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4707,7 +4707,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 41420-2022</t>
+          <t>A 30284-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4721,10 +4721,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44826</v>
+        <v>44760</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4780,7 +4780,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 38059-2022</t>
+          <t>A 30287-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4794,10 +4794,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44811</v>
+        <v>44760</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 296-2022</t>
+          <t>A 38059-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4867,10 +4867,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44565</v>
+        <v>44811</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4926,7 +4926,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 30284-2022</t>
+          <t>A 296-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44760</v>
+        <v>44565</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4999,7 +4999,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 30287-2022</t>
+          <t>A 10726-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44760</v>
+        <v>44627</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5072,7 +5072,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 10726-2022</t>
+          <t>A 58750-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5086,10 +5086,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44627</v>
+        <v>44489</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5162,7 +5162,7 @@
         <v>45378</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 13887-2024</t>
+          <t>A 4881-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5232,10 +5232,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45391</v>
+        <v>45329</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>11.3</v>
+        <v>3.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5291,7 +5291,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 61284-2022</t>
+          <t>A 26443-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5305,10 +5305,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44915</v>
+        <v>45092</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5364,7 +5364,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 52431-2023</t>
+          <t>A 43770-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5378,10 +5378,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45225</v>
+        <v>45187</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5437,7 +5437,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 11104-2024</t>
+          <t>A 22561-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45371</v>
+        <v>45789</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5510,7 +5510,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 24053-2025</t>
+          <t>A 12790-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5520,14 +5520,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45796</v>
+        <v>45733</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>11.1</v>
+        <v>2.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5583,7 +5583,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 12784-2025</t>
+          <t>A 12243-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45733</v>
+        <v>45729</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.2</v>
+        <v>10.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5656,7 +5656,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 33993-2023</t>
+          <t>A 54681-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45134</v>
+        <v>44473</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>4.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5729,7 +5729,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 33996-2023</t>
+          <t>A 30724-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5739,14 +5739,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45134</v>
+        <v>45496</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5802,7 +5802,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 65619-2021</t>
+          <t>A 23374-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44516</v>
+        <v>45791</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 5743-2025</t>
+          <t>A 23509-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5889,10 +5889,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45694</v>
+        <v>45792</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5948,7 +5948,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 7819-2025</t>
+          <t>A 5743-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5962,10 +5962,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45706</v>
+        <v>45694</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5.6</v>
+        <v>0.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6021,7 +6021,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 51488-2022</t>
+          <t>A 24053-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6031,14 +6031,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44869</v>
+        <v>45796</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.5</v>
+        <v>11.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6094,7 +6094,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 2867-2025</t>
+          <t>A 406-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6108,10 +6108,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45677</v>
+        <v>45296</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>10.7</v>
+        <v>4.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6167,7 +6167,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 35423-2025</t>
+          <t>A 2867-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6181,10 +6181,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45855</v>
+        <v>45677</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.4</v>
+        <v>10.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6240,7 +6240,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 28910-2024</t>
+          <t>A 7819-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6254,10 +6254,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45480</v>
+        <v>45706</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.7</v>
+        <v>5.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6313,7 +6313,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 11604-2024</t>
+          <t>A 41759-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6327,10 +6327,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45373</v>
+        <v>45902</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6386,7 +6386,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 15567-2022</t>
+          <t>A 41758-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6400,10 +6400,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44662</v>
+        <v>45902</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 1382-2024</t>
+          <t>A 41760-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6473,10 +6473,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45303</v>
+        <v>45902</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6532,7 +6532,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 41758-2025</t>
+          <t>A 5740-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45902</v>
+        <v>45694</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6605,7 +6605,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 41760-2025</t>
+          <t>A 35422-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45902</v>
+        <v>45855</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6678,7 +6678,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 41759-2025</t>
+          <t>A 42857-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6692,10 +6692,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45902</v>
+        <v>45908</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6751,7 +6751,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 587-2025</t>
+          <t>A 6384-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6765,10 +6765,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45664</v>
+        <v>45699</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6824,7 +6824,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 35422-2025</t>
+          <t>A 36984-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6838,10 +6838,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45855</v>
+        <v>45539</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6897,7 +6897,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 42857-2025</t>
+          <t>A 27222-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6911,10 +6911,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45908</v>
+        <v>45812</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6987,7 +6987,7 @@
         <v>45912</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 44914-2025</t>
+          <t>A 28515-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45918</v>
+        <v>45819</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7116,7 +7116,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 44915-2025</t>
+          <t>A 44916-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7133,7 +7133,7 @@
         <v>45918</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7206,7 +7206,7 @@
         <v>45918</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 44916-2025</t>
+          <t>A 44914-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7279,7 +7279,7 @@
         <v>45918</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7335,7 +7335,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 7912-2024</t>
+          <t>A 44915-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7349,10 +7349,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45350</v>
+        <v>45918</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7408,7 +7408,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 56584-2025</t>
+          <t>A 47511-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7422,10 +7422,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45974</v>
+        <v>45587</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7481,7 +7481,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 6323-2023</t>
+          <t>A 61435-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7495,10 +7495,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44960</v>
+        <v>45646</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7510,13 +7510,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7559,7 +7554,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 54804-2022</t>
+          <t>A 57381-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7573,10 +7568,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44883</v>
+        <v>44896</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7589,7 +7584,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>22.6</v>
+        <v>2.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7632,7 +7627,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 5740-2025</t>
+          <t>A 48730-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7646,10 +7641,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45694</v>
+        <v>45936</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7662,7 +7657,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7705,7 +7700,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 6384-2025</t>
+          <t>A 48727-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7719,10 +7714,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45699</v>
+        <v>45936</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7735,7 +7730,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>6.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7778,7 +7773,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 36984-2024</t>
+          <t>A 49188-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7792,10 +7787,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45539</v>
+        <v>45938</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7851,7 +7846,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 57381-2022</t>
+          <t>A 13801-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7865,10 +7860,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44896</v>
+        <v>45737</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7881,7 +7876,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7924,7 +7919,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 48727-2025</t>
+          <t>A 5612-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7938,10 +7933,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45936</v>
+        <v>45693</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7954,7 +7949,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>6.1</v>
+        <v>1.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7997,7 +7992,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 15351-2024</t>
+          <t>A 37063-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8011,10 +8006,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45400</v>
+        <v>45539</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8026,13 +8021,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8075,7 +8065,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 48730-2025</t>
+          <t>A 587-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8089,10 +8079,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45936</v>
+        <v>45664</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8105,7 +8095,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4</v>
+        <v>0.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8148,7 +8138,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 13801-2025</t>
+          <t>A 12628-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8162,10 +8152,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45737</v>
+        <v>45000</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8178,7 +8168,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8221,7 +8211,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 8117-2023</t>
+          <t>A 35420-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8235,10 +8225,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44974</v>
+        <v>45855</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8251,7 +8241,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>11</v>
+        <v>1.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8294,7 +8284,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 49188-2025</t>
+          <t>A 35717-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8308,10 +8298,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45938</v>
+        <v>45860</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8324,7 +8314,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8367,7 +8357,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 14427-2026</t>
+          <t>A 65619-2021</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8381,10 +8371,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46100</v>
+        <v>44516</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8397,7 +8387,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8440,7 +8430,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 12628-2023</t>
+          <t>A 12784-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8454,10 +8444,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45000</v>
+        <v>45733</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8470,7 +8460,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8513,7 +8503,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 50349-2024</t>
+          <t>A 41411-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8527,10 +8517,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45600</v>
+        <v>44826</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8543,7 +8533,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8586,7 +8576,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 17377-2026</t>
+          <t>A 12647-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8600,10 +8590,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46119</v>
+        <v>45000</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8616,7 +8606,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8659,7 +8649,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 28903-2024</t>
+          <t>A 55324-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8673,10 +8663,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45480</v>
+        <v>45971</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8688,8 +8678,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8732,7 +8727,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 27222-2025</t>
+          <t>A 8117-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8746,10 +8741,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45812</v>
+        <v>44974</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8762,7 +8757,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.3</v>
+        <v>11</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8805,7 +8800,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 55324-2025</t>
+          <t>A 35423-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8819,10 +8814,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45971</v>
+        <v>45855</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8834,13 +8829,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8883,7 +8873,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 12647-2023</t>
+          <t>A 56584-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8897,10 +8887,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45000</v>
+        <v>45974</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8913,7 +8903,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8956,7 +8946,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 18841-2026</t>
+          <t>A 50349-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8970,10 +8960,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46129</v>
+        <v>45600</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8986,7 +8976,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9029,7 +9019,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 5328-2025</t>
+          <t>A 7912-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9043,10 +9033,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45692</v>
+        <v>45350</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9102,7 +9092,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 19079-2025</t>
+          <t>A 13581-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9116,10 +9106,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45766</v>
+        <v>45006</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9131,8 +9121,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9175,7 +9170,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 28022-2023</t>
+          <t>A 8071-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9189,10 +9184,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45098</v>
+        <v>45351</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9205,7 +9200,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5.7</v>
+        <v>1.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9248,7 +9243,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 28515-2025</t>
+          <t>A 15351-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9262,10 +9257,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45819</v>
+        <v>45400</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9277,8 +9272,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9321,7 +9321,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 48904-2024</t>
+          <t>A 13975-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9335,10 +9335,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45594</v>
+        <v>45008</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9394,7 +9394,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 61952-2024</t>
+          <t>A 16473-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9408,10 +9408,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45653</v>
+        <v>44671</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9467,7 +9467,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 61475-2025</t>
+          <t>A 6323-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9481,10 +9481,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46001</v>
+        <v>44960</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9496,8 +9496,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>4.6</v>
+        <v>0.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9540,7 +9545,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 55972-2022</t>
+          <t>A 40092-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9554,10 +9559,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44889</v>
+        <v>45554</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9570,7 +9575,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9613,7 +9618,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 61695-2025</t>
+          <t>A 14427-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9627,10 +9632,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46002</v>
+        <v>46100</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9643,7 +9648,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9686,7 +9691,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 26886-2023</t>
+          <t>A 57754-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9700,10 +9705,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45093</v>
+        <v>45246</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9716,7 +9721,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9759,7 +9764,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 26443-2023</t>
+          <t>A 26886-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9773,10 +9778,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45092</v>
+        <v>45093</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9789,7 +9794,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9832,7 +9837,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 17114-2023</t>
+          <t>A 17377-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9846,10 +9851,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45034</v>
+        <v>46119</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9862,7 +9867,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9905,7 +9910,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 58750-2021</t>
+          <t>A 302-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9919,10 +9924,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44489</v>
+        <v>45295</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9934,8 +9939,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9978,7 +9988,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 7947-2024</t>
+          <t>A 18841-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9992,10 +10002,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45350</v>
+        <v>46129</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10008,7 +10018,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10051,7 +10061,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 23541-2026</t>
+          <t>A 29068-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10061,14 +10071,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46163</v>
+        <v>45481</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10081,7 +10091,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10124,7 +10134,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 35420-2025</t>
+          <t>A 4225-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10138,10 +10148,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45855</v>
+        <v>45324</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10154,7 +10164,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10197,7 +10207,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 35717-2025</t>
+          <t>A 4227-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10211,10 +10221,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45860</v>
+        <v>45324</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10227,7 +10237,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10270,7 +10280,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 14891-2025</t>
+          <t>A 38093-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10284,10 +10294,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45743</v>
+        <v>44811</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10300,7 +10310,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10343,7 +10353,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 24700-2026</t>
+          <t>A 5420-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10357,10 +10367,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46171</v>
+        <v>45692</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10372,13 +10382,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10421,7 +10426,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 13581-2023</t>
+          <t>A 51488-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10435,10 +10440,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45006</v>
+        <v>44869</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10450,13 +10455,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10499,7 +10499,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 54681-2021</t>
+          <t>A 6489-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10513,10 +10513,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44473</v>
+        <v>45699</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10572,7 +10572,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 25729-2026</t>
+          <t>A 19079-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10586,10 +10586,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46178</v>
+        <v>45766</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10645,7 +10645,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 47511-2024</t>
+          <t>A 61952-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10659,10 +10659,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45587</v>
+        <v>45653</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10718,7 +10718,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 43770-2023</t>
+          <t>A 9046-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10732,10 +10732,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45187</v>
+        <v>44615</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10791,7 +10791,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 4881-2024</t>
+          <t>A 28022-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10805,10 +10805,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45329</v>
+        <v>45098</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>3.5</v>
+        <v>5.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10864,7 +10864,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 27643-2026</t>
+          <t>A 55972-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10878,10 +10878,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46190</v>
+        <v>44889</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10937,7 +10937,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 9046-2022</t>
+          <t>A 61475-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10951,10 +10951,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44615</v>
+        <v>46001</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11010,7 +11010,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 61435-2024</t>
+          <t>A 28903-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11024,10 +11024,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45646</v>
+        <v>45480</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11083,7 +11083,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 33842-2026</t>
+          <t>A 61284-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11097,10 +11097,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46251</v>
+        <v>44915</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>7.2</v>
+        <v>1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11156,7 +11156,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 30605-2026</t>
+          <t>A 12760-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11170,10 +11170,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46210</v>
+        <v>45001</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>10.5</v>
+        <v>1.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11229,7 +11229,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 2438-2026</t>
+          <t>A 62730-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11243,10 +11243,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46036</v>
+        <v>45268</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11302,7 +11302,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 14929-2024</t>
+          <t>A 48904-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11316,10 +11316,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45398</v>
+        <v>45594</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11375,7 +11375,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 21630-2024</t>
+          <t>A 11604-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11389,10 +11389,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45442</v>
+        <v>45373</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11448,7 +11448,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 43767-2023</t>
+          <t>A 5324-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11462,10 +11462,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45187</v>
+        <v>45692</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.3</v>
+        <v>5.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11521,7 +11521,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 33991-2023</t>
+          <t>A 61695-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11535,10 +11535,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45134</v>
+        <v>46002</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11594,7 +11594,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 35883-2026</t>
+          <t>A 54804-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11608,10 +11608,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46266</v>
+        <v>44883</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11624,7 +11624,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>6.6</v>
+        <v>22.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11667,7 +11667,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 41411-2022</t>
+          <t>A 52431-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11681,10 +11681,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44826</v>
+        <v>45225</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11740,7 +11740,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 36773-2026</t>
+          <t>A 33993-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11754,10 +11754,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46272</v>
+        <v>45134</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11769,13 +11769,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11818,7 +11813,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 4225-2024</t>
+          <t>A 33996-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11832,10 +11827,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45324</v>
+        <v>45134</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11848,7 +11843,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11891,7 +11886,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 4227-2024</t>
+          <t>A 23541-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11901,14 +11896,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45324</v>
+        <v>46163</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11921,7 +11916,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11964,7 +11959,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 36722-2026</t>
+          <t>A 7947-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11978,10 +11973,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46272</v>
+        <v>45350</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11993,13 +11988,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12042,7 +12032,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 37037-2026</t>
+          <t>A 17116-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12056,10 +12046,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46273</v>
+        <v>45034</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12072,7 +12062,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12115,7 +12105,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 37508-2023</t>
+          <t>A 15567-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12129,10 +12119,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45158</v>
+        <v>44662</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12145,7 +12135,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>6.9</v>
+        <v>1.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12188,7 +12178,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 37509-2023</t>
+          <t>A 21630-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12202,10 +12192,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45158</v>
+        <v>45442</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12218,7 +12208,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.9</v>
+        <v>4.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12261,7 +12251,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 32822-2026</t>
+          <t>A 14891-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12275,10 +12265,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46242</v>
+        <v>45743</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12291,7 +12281,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12334,7 +12324,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 13382-2023</t>
+          <t>A 24700-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12348,10 +12338,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45005</v>
+        <v>46171</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12363,8 +12353,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12407,7 +12402,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 38093-2022</t>
+          <t>A 13382-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12421,10 +12416,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44811</v>
+        <v>45005</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12437,7 +12432,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12480,7 +12475,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 16473-2022</t>
+          <t>A 550-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12494,10 +12489,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44671</v>
+        <v>45299</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12510,7 +12505,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12553,7 +12548,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 40092-2024</t>
+          <t>A 25729-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12567,10 +12562,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45554</v>
+        <v>46178</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12583,7 +12578,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12626,7 +12621,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 57754-2023</t>
+          <t>A 27643-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12640,10 +12635,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45246</v>
+        <v>46190</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12656,7 +12651,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12699,7 +12694,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 44445-2023</t>
+          <t>A 13887-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12713,10 +12708,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45189</v>
+        <v>45391</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12729,7 +12724,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>3.8</v>
+        <v>11.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12772,7 +12767,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 17116-2023</t>
+          <t>A 14929-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12786,10 +12781,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45034</v>
+        <v>45398</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12802,7 +12797,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>5.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12845,7 +12840,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 12760-2023</t>
+          <t>A 11104-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12859,10 +12854,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45001</v>
+        <v>45371</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12875,7 +12870,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12918,7 +12913,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 5612-2025</t>
+          <t>A 2438-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12932,10 +12927,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45693</v>
+        <v>46036</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12948,7 +12943,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12991,7 +12986,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 302-2024</t>
+          <t>A 30605-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13005,10 +13000,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45295</v>
+        <v>46210</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13020,13 +13015,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>2.3</v>
+        <v>10.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13069,7 +13059,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 29068-2024</t>
+          <t>A 28910-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13083,10 +13073,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45481</v>
+        <v>45480</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13099,7 +13089,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13142,7 +13132,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 5324-2025</t>
+          <t>A 1382-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13156,10 +13146,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45692</v>
+        <v>45303</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13172,7 +13162,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>5.1</v>
+        <v>1.4</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13215,7 +13205,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 13631-2024</t>
+          <t>A 17114-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13229,10 +13219,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45390</v>
+        <v>45034</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13245,7 +13235,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>16.4</v>
+        <v>1.2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13288,7 +13278,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 37063-2024</t>
+          <t>A 43767-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13302,10 +13292,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45539</v>
+        <v>45187</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13318,7 +13308,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>8.800000000000001</v>
+        <v>2.3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13361,7 +13351,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 15159-2023</t>
+          <t>A 35883-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13375,10 +13365,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45016</v>
+        <v>46266</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13390,13 +13380,8 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>0.9</v>
+        <v>6.6</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13439,7 +13424,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 550-2024</t>
+          <t>A 13631-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13453,10 +13438,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45299</v>
+        <v>45390</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13469,7 +13454,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.3</v>
+        <v>16.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13512,7 +13497,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 13975-2023</t>
+          <t>A 37508-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13526,10 +13511,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45008</v>
+        <v>45158</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13542,7 +13527,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.2</v>
+        <v>6.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13585,7 +13570,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 8071-2024</t>
+          <t>A 37509-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13599,10 +13584,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45351</v>
+        <v>45158</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13615,7 +13600,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13658,7 +13643,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 6489-2025</t>
+          <t>A 15159-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13672,10 +13657,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45699</v>
+        <v>45016</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13687,8 +13672,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13731,7 +13721,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 406-2024</t>
+          <t>A 36722-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13745,10 +13735,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45296</v>
+        <v>46272</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13760,8 +13750,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13804,7 +13799,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 62730-2023</t>
+          <t>A 37037-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13818,10 +13813,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45268</v>
+        <v>46273</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13834,7 +13829,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13877,7 +13872,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 49879-2023</t>
+          <t>A 36773-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13891,10 +13886,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45213</v>
+        <v>46272</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13906,8 +13901,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13950,7 +13950,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 5420-2025</t>
+          <t>A 49879-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13964,10 +13964,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45692</v>
+        <v>45213</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14023,7 +14023,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 3867-2025</t>
+          <t>A 44445-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14037,10 +14037,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45684</v>
+        <v>45189</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14096,7 +14096,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 21617-2024</t>
+          <t>A 33991-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14110,10 +14110,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45441</v>
+        <v>45134</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>9.699999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14169,7 +14169,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 30724-2024</t>
+          <t>A 5328-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14179,14 +14179,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45496</v>
+        <v>45692</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14242,7 +14242,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 22561-2025</t>
+          <t>A 3867-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14256,10 +14256,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45789</v>
+        <v>45684</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14315,7 +14315,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 23509-2025</t>
+          <t>A 21617-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14329,10 +14329,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45792</v>
+        <v>45441</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14388,7 +14388,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 23374-2025</t>
+          <t>A 32822-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14402,10 +14402,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45791</v>
+        <v>46242</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14461,7 +14461,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 12790-2025</t>
+          <t>A 33842-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14475,10 +14475,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45733</v>
+        <v>46251</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2.9</v>
+        <v>7.2</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14531,27 +14531,27 @@
       </c>
       <c r="V176" s="2" t="inlineStr"/>
     </row>
-    <row r="177" ht="15" customHeight="1">
+    <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 12243-2025</t>
+          <t>S 460-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45729</v>
+        <v>44964</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14603,79 +14603,6 @@
         <v>0</v>
       </c>
       <c r="V177" s="2" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>S 460-2023</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D178" s="1" t="n">
-        <v>44964</v>
-      </c>
-      <c r="E178" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I178" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J178" t="n">
-        <v>0</v>
-      </c>
-      <c r="K178" t="n">
-        <v>0</v>
-      </c>
-      <c r="L178" t="n">
-        <v>0</v>
-      </c>
-      <c r="M178" t="n">
-        <v>0</v>
-      </c>
-      <c r="N178" t="n">
-        <v>0</v>
-      </c>
-      <c r="O178" t="n">
-        <v>0</v>
-      </c>
-      <c r="P178" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
-      <c r="R178" t="n">
-        <v>0</v>
-      </c>
-      <c r="S178" t="n">
-        <v>0</v>
-      </c>
-      <c r="T178" t="n">
-        <v>0</v>
-      </c>
-      <c r="U178" t="n">
-        <v>0</v>
-      </c>
-      <c r="V178" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LILLA EDET.xlsx
+++ b/Översikt LILLA EDET.xlsx
@@ -601,7 +601,7 @@
         <v>46169</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45295</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45295</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45827</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 62846-2023</t>
+          <t>A 34396-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45272</v>
+        <v>45139</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.4</v>
+        <v>7</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1127,12 +1127,127 @@
         <v>7</v>
       </c>
       <c r="T6" t="n">
+        <v>24</v>
+      </c>
+      <c r="U6" t="n">
+        <v>24</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Blåmossa
+Kambräken
+Stor revmossa
+Västlig hakmossa
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 34396-2023 artfynd.xlsx", "A 34396-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 34396-2023 karta.png", "A 34396-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 34396-2023 georefererad karta.tif", "A 34396-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 34396-2023 FSC-klagomål.docx", "A 34396-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 34396-2023 FSC-klagomål mail.docx", "A 34396-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 34396-2023 tillsynsbegäran.docx", "A 34396-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 34396-2023 tillsynsbegäran mail.docx", "A 34396-2023")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 34396-2023 prioriterade fågelarter.docx", "A 34396-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 62846-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45272</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>7</v>
+      </c>
+      <c r="T7" t="n">
         <v>17</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Kattfotslav
 Blåmossa
@@ -1143,147 +1258,32 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 62846-2023 artfynd.xlsx", "A 62846-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 62846-2023 karta.png", "A 62846-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 62846-2023 georefererad karta.tif", "A 62846-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 62846-2023 FSC-klagomål.docx", "A 62846-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 62846-2023 FSC-klagomål mail.docx", "A 62846-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 62846-2023 tillsynsbegäran.docx", "A 62846-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 62846-2023 tillsynsbegäran mail.docx", "A 62846-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 34396-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45139</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>5</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>7</v>
-      </c>
-      <c r="T7" t="n">
-        <v>24</v>
-      </c>
-      <c r="U7" t="n">
-        <v>24</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Blåmossa
-Kambräken
-Stor revmossa
-Västlig hakmossa
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 34396-2023 artfynd.xlsx", "A 34396-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 34396-2023 karta.png", "A 34396-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 34396-2023 georefererad karta.tif", "A 34396-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 34396-2023 FSC-klagomål.docx", "A 34396-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 34396-2023 FSC-klagomål mail.docx", "A 34396-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 34396-2023 tillsynsbegäran.docx", "A 34396-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 34396-2023 tillsynsbegäran mail.docx", "A 34396-2023")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 34396-2023 prioriterade fågelarter.docx", "A 34396-2023")</f>
         <v/>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
         <v>46044</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25298-2024</t>
+          <t>A 43771-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45462</v>
+        <v>45187</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1432,51 +1432,159 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>5.9</v>
+        <v>1.7</v>
       </c>
       <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2</v>
       </c>
-      <c r="K9" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
       </c>
       <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Slåtterfibbla
+Vätteros
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 43771-2023 artfynd.xlsx", "A 43771-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 43771-2023 karta.png", "A 43771-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 43771-2023 georefererad karta.tif", "A 43771-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 43771-2023 FSC-klagomål.docx", "A 43771-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 43771-2023 FSC-klagomål mail.docx", "A 43771-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 43771-2023 tillsynsbegäran.docx", "A 43771-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 43771-2023 tillsynsbegäran mail.docx", "A 43771-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 25298-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45462</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="n">
         <v>5</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>5</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Västlig hakmossa
@@ -1484,144 +1592,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 25298-2024 artfynd.xlsx", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 25298-2024 karta.png", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 25298-2024 georefererad karta.tif", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 25298-2024 FSC-klagomål.docx", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 25298-2024 FSC-klagomål mail.docx", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 25298-2024 tillsynsbegäran.docx", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 25298-2024 tillsynsbegäran mail.docx", "A 25298-2024")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 25298-2024 prioriterade fågelarter.docx", "A 25298-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 43771-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45187</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Slåtterfibbla
-Vätteros
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 43771-2023 artfynd.xlsx", "A 43771-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 43771-2023 karta.png", "A 43771-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 43771-2023 georefererad karta.tif", "A 43771-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 43771-2023 FSC-klagomål.docx", "A 43771-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 43771-2023 FSC-klagomål mail.docx", "A 43771-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 43771-2023 tillsynsbegäran.docx", "A 43771-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 43771-2023 tillsynsbegäran mail.docx", "A 43771-2023")</f>
         <v/>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
         <v>45819</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 23563-2023</t>
+          <t>A 24290-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45072</v>
+        <v>46169</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1769,22 +1769,17 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="J12" t="n">
-        <v>4</v>
-      </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1799,7 +1794,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1808,12 +1803,129 @@
         <v>4</v>
       </c>
       <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Blanksvart trämyra
+Grönpyrola
+Västlig hakmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 24290-2026 artfynd.xlsx", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 24290-2026 karta.png", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 24290-2026 georefererad karta.tif", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 24290-2026 FSC-klagomål.docx", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 24290-2026 FSC-klagomål mail.docx", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 24290-2026 tillsynsbegäran.docx", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 24290-2026 tillsynsbegäran mail.docx", "A 24290-2026")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 24290-2026 prioriterade fågelarter.docx", "A 24290-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 23563-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45072</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" t="n">
         <v>7</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U13" t="n">
         <v>7</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Nordfladdermus
 Dvärgpipistrell
@@ -1821,151 +1933,39 @@
 Grönvit nattviol</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 23563-2023 artfynd.xlsx", "A 23563-2023")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 23563-2023 karta.png", "A 23563-2023")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 23563-2023 georefererad karta.tif", "A 23563-2023")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 23563-2023 FSC-klagomål.docx", "A 23563-2023")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 23563-2023 FSC-klagomål mail.docx", "A 23563-2023")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 23563-2023 tillsynsbegäran.docx", "A 23563-2023")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 23563-2023 tillsynsbegäran mail.docx", "A 23563-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 24290-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46169</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>5</v>
-      </c>
-      <c r="U13" t="n">
-        <v>5</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Blanksvart trämyra
-Grönpyrola
-Västlig hakmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 24290-2026 artfynd.xlsx", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 24290-2026 karta.png", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 24290-2026 georefererad karta.tif", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 24290-2026 FSC-klagomål.docx", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 24290-2026 FSC-klagomål mail.docx", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 24290-2026 tillsynsbegäran.docx", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 24290-2026 tillsynsbegäran mail.docx", "A 24290-2026")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 24290-2026 prioriterade fågelarter.docx", "A 24290-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 25655-2023</t>
+          <t>A 17376-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45089</v>
+        <v>46119</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.1</v>
+        <v>2.5</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
         <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2019,160 +2019,160 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
       </c>
       <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Slåttergubbe
+Almsnabbvinge
+Granspira</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 17376-2026 artfynd.xlsx", "A 17376-2026")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 17376-2026 karta.png", "A 17376-2026")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 17376-2026 georefererad karta.tif", "A 17376-2026")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 17376-2026 FSC-klagomål.docx", "A 17376-2026")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 17376-2026 FSC-klagomål mail.docx", "A 17376-2026")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 17376-2026 tillsynsbegäran.docx", "A 17376-2026")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 17376-2026 tillsynsbegäran mail.docx", "A 17376-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 25655-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45089</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
         <v>9</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U15" t="n">
         <v>7</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Bergjohannesört
 Svinrot
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 25655-2023 artfynd.xlsx", "A 25655-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 25655-2023 karta.png", "A 25655-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 25655-2023 georefererad karta.tif", "A 25655-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 25655-2023 FSC-klagomål.docx", "A 25655-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 25655-2023 FSC-klagomål mail.docx", "A 25655-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 25655-2023 tillsynsbegäran.docx", "A 25655-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 25655-2023 tillsynsbegäran mail.docx", "A 25655-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 17376-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46119</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>LILLA EDET</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Slåttergubbe
-Almsnabbvinge
-Granspira</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 17376-2026 artfynd.xlsx", "A 17376-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 17376-2026 karta.png", "A 17376-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 17376-2026 georefererad karta.tif", "A 17376-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 17376-2026 FSC-klagomål.docx", "A 17376-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 17376-2026 FSC-klagomål mail.docx", "A 17376-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 17376-2026 tillsynsbegäran.docx", "A 17376-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 17376-2026 tillsynsbegäran mail.docx", "A 17376-2026")</f>
         <v/>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
         <v>45098</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45072</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>46052</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45072</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>45390</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>46240</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>45072</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 41756-2025</t>
+          <t>A 30273-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2986,10 +2986,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45902</v>
+        <v>44759</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>12.5</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3035,49 +3035,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 41756-2025 artfynd.xlsx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 30273-2022 artfynd.xlsx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 41756-2025 karta.png", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 30273-2022 karta.png", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 41756-2025 georefererad karta.tif", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 30273-2022 georefererad karta.tif", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 41756-2025 FSC-klagomål.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 30273-2022 FSC-klagomål.docx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 41756-2025 FSC-klagomål mail.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 30273-2022 FSC-klagomål mail.docx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 41756-2025 tillsynsbegäran.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 30273-2022 tillsynsbegäran.docx", "A 30273-2022")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 41756-2025 tillsynsbegäran mail.docx", "A 41756-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 30273-2022 tillsynsbegäran mail.docx", "A 30273-2022")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 45941-2025</t>
+          <t>A 49384-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3087,14 +3087,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45924</v>
+        <v>45205</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3104,6 +3104,11 @@
       <c r="G24" t="inlineStr">
         <is>
           <t>LILLA EDET</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -3140,49 +3145,49 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 45941-2025 artfynd.xlsx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 49384-2023 artfynd.xlsx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 45941-2025 karta.png", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 49384-2023 karta.png", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 45941-2025 georefererad karta.tif", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 49384-2023 georefererad karta.tif", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 45941-2025 FSC-klagomål.docx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 49384-2023 FSC-klagomål.docx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 45941-2025 FSC-klagomål mail.docx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 49384-2023 FSC-klagomål mail.docx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 45941-2025 tillsynsbegäran.docx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 49384-2023 tillsynsbegäran.docx", "A 49384-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 45941-2025 tillsynsbegäran mail.docx", "A 45941-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 49384-2023 tillsynsbegäran mail.docx", "A 49384-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 49384-2023</t>
+          <t>A 41756-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3192,14 +3197,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45205</v>
+        <v>45902</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3211,22 +3216,17 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3253,46 +3253,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 49384-2023 artfynd.xlsx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 41756-2025 artfynd.xlsx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 49384-2023 karta.png", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 41756-2025 karta.png", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 49384-2023 georefererad karta.tif", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 41756-2025 georefererad karta.tif", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 49384-2023 FSC-klagomål.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 41756-2025 FSC-klagomål.docx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 49384-2023 FSC-klagomål mail.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 41756-2025 FSC-klagomål mail.docx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 49384-2023 tillsynsbegäran.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 41756-2025 tillsynsbegäran.docx", "A 41756-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 49384-2023 tillsynsbegäran mail.docx", "A 49384-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 41756-2025 tillsynsbegäran mail.docx", "A 41756-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 30273-2022</t>
+          <t>A 45941-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44759</v>
+        <v>45924</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3322,17 +3322,17 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>12.5</v>
+        <v>1.2</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
@@ -3346,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3362,42 +3362,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 30273-2022 artfynd.xlsx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 45941-2025 artfynd.xlsx", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 30273-2022 karta.png", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 45941-2025 karta.png", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 30273-2022 georefererad karta.tif", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 45941-2025 georefererad karta.tif", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 30273-2022 FSC-klagomål.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 45941-2025 FSC-klagomål.docx", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 30273-2022 FSC-klagomål mail.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 45941-2025 FSC-klagomål mail.docx", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 30273-2022 tillsynsbegäran.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 45941-2025 tillsynsbegäran.docx", "A 45941-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 30273-2022 tillsynsbegäran mail.docx", "A 30273-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 45941-2025 tillsynsbegäran mail.docx", "A 45941-2025")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 11102-2024</t>
+          <t>A 7062-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3407,14 +3407,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45371</v>
+        <v>45343</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.8</v>
+        <v>9.1</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3451,10 +3451,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3467,42 +3467,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 11102-2024 artfynd.xlsx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 7062-2024 artfynd.xlsx", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 11102-2024 karta.png", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 7062-2024 karta.png", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 11102-2024 georefererad karta.tif", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 7062-2024 georefererad karta.tif", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 11102-2024 FSC-klagomål.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 7062-2024 FSC-klagomål.docx", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 11102-2024 FSC-klagomål mail.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 7062-2024 FSC-klagomål mail.docx", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 11102-2024 tillsynsbegäran.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 7062-2024 tillsynsbegäran.docx", "A 7062-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 11102-2024 tillsynsbegäran mail.docx", "A 11102-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 7062-2024 tillsynsbegäran mail.docx", "A 7062-2024")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 7062-2024</t>
+          <t>A 38522-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3512,14 +3512,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45343</v>
+        <v>45546</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3531,8 +3531,13 @@
           <t>LILLA EDET</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>9.1</v>
+        <v>5.3</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3568,46 +3573,50 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 7062-2024 artfynd.xlsx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/artfynd/A 38522-2024 artfynd.xlsx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 7062-2024 karta.png", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor/A 38522-2024 karta.png", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 7062-2024 georefererad karta.tif", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/kartor_geotiff/A 38522-2024 georefererad karta.tif", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 7062-2024 FSC-klagomål.docx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomål/A 38522-2024 FSC-klagomål.docx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 7062-2024 FSC-klagomål mail.docx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/klagomålsmail/A 38522-2024 FSC-klagomål mail.docx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 7062-2024 tillsynsbegäran.docx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsyn/A 38522-2024 tillsynsbegäran.docx", "A 38522-2024")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 7062-2024 tillsynsbegäran mail.docx", "A 7062-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/tillsynsmail/A 38522-2024 tillsynsbegäran mail.docx", "A 38522-2024")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1462/fåglar/A 38522-2024 prioriterade fågelarter.docx", "A 38522-2024")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 38522-2024</t>
+          <t>A 11102-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3621,10 +3630,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45546</v>
+        <v>45371</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3636,26 +3645,21 @@
           <t>LILLA EDET</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>5.3</v>
+        <v>2.8</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
@@ -3666,10 +3670,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3678,43 +3682,39 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
- 